--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8447C29-6608-40AA-AA2B-DF6BC83D431D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE9C2AD-919F-48F5-8D99-93D1B01CD8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="803" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
@@ -1318,9 +1318,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1356,8 +1353,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1401,14 +1409,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2216,7 +2216,7 @@
       <c r="D28" s="65"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tFmPhD6MIKTlqHk378nalDlCyNZGsOUPXbRp8DMtggj7Be85PK7/SNxPKvq+rxiORXcNZM0XvyA2/+bwviM7RA==" saltValue="UmBb+dwPGUcfjXsIFLoXJg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2277,25 +2277,25 @@
       <c r="C2" s="166" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="112" t="s">
+      <c r="D2" s="114" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="165"/>
       <c r="B3" s="166"/>
       <c r="C3" s="166"/>
-      <c r="D3" s="112" t="s">
+      <c r="D3" s="114" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
+      <c r="H3" s="114"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="165"/>
@@ -4328,7 +4328,7 @@
       <c r="H205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="nXX3Z+Qx2s5zsgV1qV9cxAKmH/Xvc8/P0tUUgUqoQR3A52ynNkZr/tdeXPJv8BoA5o8EkFJ2bFNENjSRjOQF6Q==" saltValue="l0RcpwiXyrzVEBDM5c35MA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="10">
     <mergeCell ref="D3:H3"/>
     <mergeCell ref="D4:D5"/>
@@ -4437,25 +4437,25 @@
       <c r="F2" s="168"/>
       <c r="G2" s="168"/>
       <c r="H2" s="169"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="108"/>
-      <c r="AA2" s="109"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
+      <c r="W2" s="110"/>
+      <c r="X2" s="110"/>
+      <c r="Y2" s="110"/>
+      <c r="Z2" s="110"/>
+      <c r="AA2" s="111"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="166"/>
@@ -4468,25 +4468,25 @@
       <c r="F3" s="140"/>
       <c r="G3" s="140"/>
       <c r="H3" s="140"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="108"/>
-      <c r="Q3" s="108"/>
-      <c r="R3" s="108"/>
-      <c r="S3" s="108"/>
-      <c r="T3" s="108"/>
-      <c r="U3" s="108"/>
-      <c r="V3" s="108"/>
-      <c r="W3" s="108"/>
-      <c r="X3" s="108"/>
-      <c r="Y3" s="108"/>
-      <c r="Z3" s="108"/>
-      <c r="AA3" s="109"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="110"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="110"/>
+      <c r="R3" s="110"/>
+      <c r="S3" s="110"/>
+      <c r="T3" s="110"/>
+      <c r="U3" s="110"/>
+      <c r="V3" s="110"/>
+      <c r="W3" s="110"/>
+      <c r="X3" s="110"/>
+      <c r="Y3" s="110"/>
+      <c r="Z3" s="110"/>
+      <c r="AA3" s="111"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="166"/>
@@ -4501,17 +4501,17 @@
       <c r="F4" s="140"/>
       <c r="G4" s="140"/>
       <c r="H4" s="140"/>
-      <c r="I4" s="112" t="s">
+      <c r="I4" s="114" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112"/>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112" t="s">
+      <c r="J4" s="114"/>
+      <c r="K4" s="114"/>
+      <c r="L4" s="114"/>
+      <c r="M4" s="114" t="s">
         <v>88</v>
       </c>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114"/>
       <c r="P4" s="128" t="s">
         <v>95</v>
       </c>
@@ -4519,19 +4519,19 @@
         <v>155</v>
       </c>
       <c r="R4" s="159"/>
-      <c r="S4" s="112" t="s">
+      <c r="S4" s="114" t="s">
         <v>102</v>
       </c>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112" t="s">
+      <c r="T4" s="114"/>
+      <c r="U4" s="114" t="s">
         <v>108</v>
       </c>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112"/>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="166"/>
@@ -10407,7 +10407,7 @@
       <c r="AA205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TxbwinAmwlTdwQg04LLIVhrrUWgFGLnfoPZBjFCdSRA7AnH1RCq6risHXJfMb55ptOqV62K16890H7PQ+LK53w==" saltValue="Ugvp5EF9qMGWzeccqZ5fmg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="16">
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="P4:P5"/>
@@ -10526,21 +10526,21 @@
       <c r="K3" s="179" t="s">
         <v>197</v>
       </c>
-      <c r="L3" s="112" t="s">
+      <c r="L3" s="114" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="103"/>
       <c r="B4" s="160"/>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="114" t="s">
         <v>142</v>
       </c>
       <c r="D4" s="125" t="s">
         <v>127</v>
       </c>
       <c r="E4" s="125"/>
-      <c r="F4" s="112" t="s">
+      <c r="F4" s="114" t="s">
         <v>142</v>
       </c>
       <c r="G4" s="125" t="s">
@@ -10550,19 +10550,19 @@
       <c r="I4" s="133"/>
       <c r="J4" s="135"/>
       <c r="K4" s="179"/>
-      <c r="L4" s="112"/>
+      <c r="L4" s="114"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="103"/>
       <c r="B5" s="127"/>
-      <c r="C5" s="112"/>
+      <c r="C5" s="114"/>
       <c r="D5" s="14" t="s">
         <v>0</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="112"/>
+      <c r="F5" s="114"/>
       <c r="G5" s="14" t="s">
         <v>0</v>
       </c>
@@ -10576,7 +10576,7 @@
         <v>182</v>
       </c>
       <c r="K5" s="179"/>
-      <c r="L5" s="112"/>
+      <c r="L5" s="114"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -13379,7 +13379,7 @@
       <c r="L205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oMPtPwqdhSMRxg8oMyolwuD+PZ276NazXLu36OisObUAdSrzy1/K41lWbxwoNxn71aDsuoj47Fe4lncG3YJ6AQ==" saltValue="9XULsp/Qo5jFfAzk1UmpNA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="13">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C2:L2"/>
@@ -13424,20 +13424,20 @@
       <c r="C1" s="40"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="91" t="s">
         <v>88</v>
       </c>
       <c r="B2" s="180" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="115" t="s">
+      <c r="C2" s="117" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="92"/>
+      <c r="A3" s="91"/>
       <c r="B3" s="180"/>
-      <c r="C3" s="116"/>
+      <c r="C3" s="118"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -14440,7 +14440,7 @@
       <c r="C203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kwJKSbF7anP+mwd7SJq7SkvnGWcqnlveqqWSl9vfd8dIxQb4DFwqN6plberTYQmYMibS/toko8by/odOnHIxiQ==" saltValue="THbYaRsKch3dS25+pYW7Qw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -14486,26 +14486,26 @@
       <c r="G1" s="35"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="112" t="s">
+      <c r="A2" s="114" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="112"/>
-      <c r="C2" s="112"/>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="112" t="s">
+      <c r="A3" s="114" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="112"/>
-      <c r="C3" s="112"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="112"/>
-      <c r="F3" s="112"/>
-      <c r="G3" s="112"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="114"/>
+      <c r="D3" s="114"/>
+      <c r="E3" s="114"/>
+      <c r="F3" s="114"/>
+      <c r="G3" s="114"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="128" t="s">
@@ -16340,7 +16340,7 @@
       <c r="G205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ng6xy7cIwiQjNc/RNyjytmIWWygWVmc6tYRGrGdDQ0fMlClyNpfquTsZkcax81gbGLYKL/tfc8pgLP2yowGPag==" saltValue="h9iL5QCZ5DlHZAW0yaDGgw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="A2:G2"/>
@@ -17827,7 +17827,7 @@
       <c r="E205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3N5+7VUI+HZmvPiQF35PdGHJabHDVXqb7pdYfDtaubjaMqUr7XHQLnqefsSHFitmJHMeRCtPCCl1cbvkZWMNeg==" saltValue="EaY16JZzXnBSBEkIITwwSg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="1">
     <mergeCell ref="A2:A3"/>
   </mergeCells>
@@ -17895,101 +17895,101 @@
       <c r="X1" s="68"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
+      <c r="A2" s="90" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="91" t="s">
+      <c r="B2" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92" t="s">
+      <c r="C2" s="90"/>
+      <c r="D2" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
-      <c r="L2" s="92"/>
-      <c r="M2" s="92"/>
-      <c r="N2" s="93" t="s">
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="93"/>
-      <c r="S2" s="93"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="93"/>
-      <c r="W2" s="93"/>
-      <c r="X2" s="93"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="92"/>
+      <c r="Q2" s="92"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="92"/>
+      <c r="T2" s="92"/>
+      <c r="U2" s="92"/>
+      <c r="V2" s="92"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="92"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="91"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="94" t="s">
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="93" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="96"/>
-      <c r="I3" s="94" t="s">
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="95"/>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="93"/>
-      <c r="U3" s="93"/>
-      <c r="V3" s="93"/>
-      <c r="W3" s="93"/>
-      <c r="X3" s="93"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="92"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="92"/>
+      <c r="W3" s="92"/>
+      <c r="X3" s="92"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="91"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="97" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="98"/>
-      <c r="F4" s="97" t="s">
+      <c r="E4" s="97"/>
+      <c r="F4" s="96" t="s">
         <v>123</v>
       </c>
-      <c r="G4" s="98"/>
-      <c r="H4" s="99" t="s">
+      <c r="G4" s="97"/>
+      <c r="H4" s="98" t="s">
         <v>142</v>
       </c>
-      <c r="I4" s="97" t="s">
+      <c r="I4" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="J4" s="98"/>
-      <c r="K4" s="97" t="s">
+      <c r="J4" s="97"/>
+      <c r="K4" s="96" t="s">
         <v>123</v>
       </c>
-      <c r="L4" s="98"/>
-      <c r="M4" s="101" t="s">
+      <c r="L4" s="97"/>
+      <c r="M4" s="100" t="s">
         <v>142</v>
       </c>
-      <c r="N4" s="90" t="s">
+      <c r="N4" s="102" t="s">
         <v>215</v>
       </c>
-      <c r="O4" s="90"/>
+      <c r="O4" s="102"/>
       <c r="P4" s="103" t="s">
         <v>14</v>
       </c>
@@ -18005,7 +18005,7 @@
       <c r="X4" s="103"/>
     </row>
     <row r="5" spans="1:25" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="91"/>
+      <c r="A5" s="90"/>
       <c r="B5" s="70" t="s">
         <v>216</v>
       </c>
@@ -18024,7 +18024,7 @@
       <c r="G5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="100"/>
+      <c r="H5" s="99"/>
       <c r="I5" s="30" t="s">
         <v>7</v>
       </c>
@@ -18037,7 +18037,7 @@
       <c r="L5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="102"/>
+      <c r="M5" s="101"/>
       <c r="N5" s="36" t="s">
         <v>10</v>
       </c>
@@ -23247,7 +23247,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ka/HtMUEd01dnBRIYrHwOf0FOyhm16B1TbEsRvJl5LqfAzg/VHEqbLs/HtyTBSLnZj20FdcSRD9aB8sTQI2eIA==" saltValue="qBFN/JLAlhLHqsgwWCmOig==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:C4"/>
@@ -23332,7 +23332,7 @@
       <c r="P1" s="68"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="102" t="s">
         <v>192</v>
       </c>
       <c r="B2" s="73" t="s">
@@ -23354,89 +23354,89 @@
       <c r="P2" s="75"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="B3" s="104" t="s">
+      <c r="A3" s="102"/>
+      <c r="B3" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="106"/>
-      <c r="G3" s="107" t="s">
+      <c r="C3" s="107"/>
+      <c r="D3" s="107"/>
+      <c r="E3" s="107"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="108"/>
-      <c r="I3" s="109"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="111"/>
       <c r="J3" s="76" t="s">
         <v>24</v>
       </c>
       <c r="K3" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="L3" s="104" t="s">
+      <c r="L3" s="106" t="s">
         <v>218</v>
       </c>
-      <c r="M3" s="105"/>
-      <c r="N3" s="105"/>
-      <c r="O3" s="105"/>
-      <c r="P3" s="106"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="107"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="108"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
-      <c r="B4" s="91" t="s">
+      <c r="A4" s="102"/>
+      <c r="B4" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="110" t="s">
+      <c r="C4" s="112" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="93" t="s">
+      <c r="D4" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="99" t="s">
+      <c r="E4" s="98" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="92" t="s">
+      <c r="F4" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="111" t="s">
+      <c r="G4" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="113" t="s">
+      <c r="H4" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="115" t="s">
+      <c r="I4" s="117" t="s">
         <v>219</v>
       </c>
-      <c r="J4" s="111" t="s">
+      <c r="J4" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="117" t="s">
+      <c r="K4" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="90" t="s">
+      <c r="L4" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="90"/>
-      <c r="N4" s="90" t="s">
+      <c r="M4" s="102"/>
+      <c r="N4" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="O4" s="90"/>
-      <c r="P4" s="112" t="s">
+      <c r="O4" s="102"/>
+      <c r="P4" s="114" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="90"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="116"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="118"/>
+      <c r="A5" s="102"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="113"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="113"/>
+      <c r="K5" s="105"/>
       <c r="L5" s="77" t="s">
         <v>4</v>
       </c>
@@ -23449,7 +23449,7 @@
       <c r="O5" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="112"/>
+      <c r="P5" s="114"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -27052,8 +27052,9 @@
       <c r="P205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="L4qzapnu2Pie5M6M+VqNy06BMKJGmzAz/nbL0FRyyFkfEcHy6Tv4O6TxB3V0b+dtvMDWXensSOS0zD05lvNeCg==" saltValue="2bcGRrxFYEnLofE/L5Qkfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:M4"/>
     <mergeCell ref="N4:O4"/>
@@ -27070,7 +27071,6 @@
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5 C4:C5 J4:K4 M5 G4:H4" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
@@ -27126,7 +27126,7 @@
       <c r="K1" s="68"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="102" t="s">
         <v>192</v>
       </c>
       <c r="B2" s="103" t="s">
@@ -27143,7 +27143,7 @@
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
+      <c r="A3" s="102"/>
       <c r="B3" s="103" t="s">
         <v>31</v>
       </c>
@@ -27160,28 +27160,28 @@
       <c r="K3" s="103"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
-      <c r="B4" s="107" t="s">
+      <c r="A4" s="102"/>
+      <c r="B4" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
       <c r="F4" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="107" t="s">
+      <c r="G4" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="108"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="109"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="111"/>
       <c r="K4" s="119" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="90"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="30" t="s">
         <v>7</v>
       </c>
@@ -29810,7 +29810,7 @@
       <c r="K205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gfZrPLniNXIFnLy1vOgXex/iJpDHFoumsQiPwE0Xpbq2Qc/ZLK0EV8W9d74qT2NYyOopeZk29FHZJ/6A9NkzSA==" saltValue="i7WQ491h5dezlRtkiDQ+qg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:K2"/>
@@ -29933,7 +29933,7 @@
       <c r="AS1" s="68"/>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="102" t="s">
         <v>192</v>
       </c>
       <c r="B2" s="130" t="s">
@@ -29988,7 +29988,7 @@
       <c r="AS2" s="125"/>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
+      <c r="A3" s="102"/>
       <c r="B3" s="133"/>
       <c r="C3" s="134"/>
       <c r="D3" s="134"/>
@@ -30008,7 +30008,7 @@
       <c r="R3" s="134"/>
       <c r="S3" s="134"/>
       <c r="T3" s="135"/>
-      <c r="U3" s="97"/>
+      <c r="U3" s="96"/>
       <c r="V3" s="124"/>
       <c r="W3" s="124"/>
       <c r="X3" s="124"/>
@@ -30020,7 +30020,7 @@
       <c r="AD3" s="124"/>
       <c r="AE3" s="124"/>
       <c r="AF3" s="124"/>
-      <c r="AG3" s="98"/>
+      <c r="AG3" s="97"/>
       <c r="AH3" s="125"/>
       <c r="AI3" s="125"/>
       <c r="AJ3" s="125"/>
@@ -30035,7 +30035,7 @@
       <c r="AS3" s="125"/>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
+      <c r="A4" s="102"/>
       <c r="B4" s="126" t="s">
         <v>220</v>
       </c>
@@ -30058,21 +30058,21 @@
       <c r="K4" s="126" t="s">
         <v>223</v>
       </c>
-      <c r="L4" s="112" t="s">
+      <c r="L4" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="112"/>
-      <c r="N4" s="112"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112" t="s">
+      <c r="M4" s="114"/>
+      <c r="N4" s="114"/>
+      <c r="O4" s="114"/>
+      <c r="P4" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112" t="s">
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="T4" s="112"/>
+      <c r="T4" s="114"/>
       <c r="U4" s="103" t="s">
         <v>60</v>
       </c>
@@ -30112,29 +30112,29 @@
       <c r="AG4" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="AH4" s="112" t="s">
+      <c r="AH4" s="114" t="s">
         <v>77</v>
       </c>
-      <c r="AI4" s="112"/>
-      <c r="AJ4" s="112"/>
-      <c r="AK4" s="112" t="s">
+      <c r="AI4" s="114"/>
+      <c r="AJ4" s="114"/>
+      <c r="AK4" s="114" t="s">
         <v>80</v>
       </c>
-      <c r="AL4" s="112"/>
-      <c r="AM4" s="112"/>
-      <c r="AN4" s="112" t="s">
+      <c r="AL4" s="114"/>
+      <c r="AM4" s="114"/>
+      <c r="AN4" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="AO4" s="112"/>
-      <c r="AP4" s="112"/>
-      <c r="AQ4" s="112" t="s">
+      <c r="AO4" s="114"/>
+      <c r="AP4" s="114"/>
+      <c r="AQ4" s="114" t="s">
         <v>79</v>
       </c>
-      <c r="AR4" s="112"/>
-      <c r="AS4" s="112"/>
+      <c r="AR4" s="114"/>
+      <c r="AS4" s="114"/>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A5" s="90"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="127"/>
       <c r="C5" s="127"/>
       <c r="D5" s="129"/>
@@ -39635,22 +39635,8 @@
       <c r="AS205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+SaHzzDEGw4gqvt+nIFZqUT6j8i5al1ZYgkPFJOo8wC7nXT8fzuZeM4Z+aphRTG7O56wdtrC22PEij5IX4RQGQ==" saltValue="UrzhHisYrfsnIOJY9wxxxA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AN4:AP4"/>
-    <mergeCell ref="AQ4:AS4"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AJ4"/>
-    <mergeCell ref="AK4:AM4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="U2:AG3"/>
     <mergeCell ref="AH2:AS3"/>
@@ -39667,6 +39653,20 @@
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="B2:T3"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="AN4:AP4"/>
+    <mergeCell ref="AQ4:AS4"/>
+    <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AH4:AJ4"/>
+    <mergeCell ref="AK4:AM4"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="AA4:AA5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 L5:R5 AH5:AI5 AK5:AL5 AN5:AO5 AQ5:AR5" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -39735,18 +39735,18 @@
         <v>82</v>
       </c>
       <c r="C2" s="141"/>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="106" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="106"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="108"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
+      <c r="A3" s="102"/>
       <c r="B3" s="140" t="s">
         <v>159</v>
       </c>
@@ -39768,7 +39768,7 @@
       <c r="J3" s="125"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
+      <c r="A4" s="102"/>
       <c r="B4" s="140"/>
       <c r="C4" s="140"/>
       <c r="D4" s="143"/>
@@ -39780,7 +39780,7 @@
       <c r="J4" s="125"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="90"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="140"/>
       <c r="C5" s="140"/>
       <c r="D5" s="141"/>
@@ -42204,7 +42204,7 @@
       <c r="J205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jJULh9yioXw3/eaPfcC3Grd4q9vJiuevAvJVyVy22w1Pq+jj4rolwVX3OXZGM3uA5hKLN7cB45omn5kdoKVJZA==" saltValue="eOuqoOCXuLzNjw5mMZr0dw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="10">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="H3:J4"/>
@@ -42312,7 +42312,7 @@
       <c r="T2" s="141"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
+      <c r="A3" s="102"/>
       <c r="B3" s="147"/>
       <c r="C3" s="148" t="s">
         <v>126</v>
@@ -42327,12 +42327,12 @@
       </c>
       <c r="H3" s="125"/>
       <c r="I3" s="125"/>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="92" t="s">
         <v>172</v>
       </c>
-      <c r="K3" s="93"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="93"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
       <c r="N3" s="140" t="s">
         <v>173</v>
       </c>
@@ -42342,7 +42342,7 @@
       <c r="P3" s="131"/>
       <c r="Q3" s="131"/>
       <c r="R3" s="132"/>
-      <c r="S3" s="112" t="s">
+      <c r="S3" s="114" t="s">
         <v>176</v>
       </c>
       <c r="T3" s="144" t="s">
@@ -42350,35 +42350,35 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
+      <c r="A4" s="102"/>
       <c r="B4" s="147"/>
       <c r="C4" s="140" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="93" t="s">
+      <c r="D4" s="92" t="s">
         <v>127</v>
       </c>
-      <c r="E4" s="93"/>
+      <c r="E4" s="92"/>
       <c r="F4" s="140" t="s">
         <v>142</v>
       </c>
       <c r="G4" s="125"/>
       <c r="H4" s="125"/>
       <c r="I4" s="125"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="93"/>
+      <c r="J4" s="92"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="92"/>
+      <c r="M4" s="92"/>
       <c r="N4" s="140"/>
       <c r="O4" s="133"/>
       <c r="P4" s="134"/>
       <c r="Q4" s="134"/>
       <c r="R4" s="135"/>
-      <c r="S4" s="112"/>
+      <c r="S4" s="114"/>
       <c r="T4" s="145"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="90"/>
+      <c r="A5" s="102"/>
       <c r="B5" s="139"/>
       <c r="C5" s="140"/>
       <c r="D5" s="37" t="s">
@@ -42422,7 +42422,7 @@
       <c r="R5" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="S5" s="112"/>
+      <c r="S5" s="114"/>
       <c r="T5" s="146"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -46826,7 +46826,7 @@
       <c r="T205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+dD8Y9JmmkNvxBwrPccesEhEhPtOalD2DiMz+ZFeSaLwPr+0KkoZfO2W+HDvxokDCGwNLlDZT2ygZdd1AFIbNg==" saltValue="9pjZZi5t4TILs/fmQ/refg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="14">
     <mergeCell ref="A1:T1"/>
     <mergeCell ref="O3:R4"/>
@@ -49152,7 +49152,7 @@
       <c r="I204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s07PvIule7+RpMFFgEoiiwF7xOnmX0Rp5DrtTgSH76K8Cd73djoRF84G5TugUnCjnWJs2BpV4HhnOVm3ufahrQ==" saltValue="qdTxf5OyiyB5BEdPdOhIyQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="6">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="F3:F4"/>
@@ -49217,7 +49217,7 @@
       <c r="N1" s="157"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="102" t="s">
         <v>192</v>
       </c>
       <c r="B2" s="103" t="s">
@@ -49241,7 +49241,7 @@
       <c r="N2" s="125"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
+      <c r="A3" s="102"/>
       <c r="B3" s="103"/>
       <c r="C3" s="160"/>
       <c r="D3" s="161" t="s">
@@ -49271,7 +49271,7 @@
       <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
+      <c r="A4" s="102"/>
       <c r="B4" s="103"/>
       <c r="C4" s="127"/>
       <c r="D4" s="162"/>
@@ -52503,7 +52503,7 @@
       <c r="N204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="MuSDoJyttw354xJFTxLWWs9hcYvSS1xVt571LcnNvE8ALx+IzgTNBCz/rp2XrvmgY8FyWcJGhCPqgOWyH+T1ZQ==" saltValue="1dyENYOnxMmfU8YUTE0Kzg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="10">
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="M3:N3"/>

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE9C2AD-919F-48F5-8D99-93D1B01CD8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BC2CF4-914D-462F-A77D-E5A29FFB3845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="803" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
@@ -1359,6 +1359,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1387,10 +1391,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4437,25 +4437,25 @@
       <c r="F2" s="168"/>
       <c r="G2" s="168"/>
       <c r="H2" s="169"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="110"/>
-      <c r="S2" s="110"/>
-      <c r="T2" s="110"/>
-      <c r="U2" s="110"/>
-      <c r="V2" s="110"/>
-      <c r="W2" s="110"/>
-      <c r="X2" s="110"/>
-      <c r="Y2" s="110"/>
-      <c r="Z2" s="110"/>
-      <c r="AA2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
+      <c r="T2" s="111"/>
+      <c r="U2" s="111"/>
+      <c r="V2" s="111"/>
+      <c r="W2" s="111"/>
+      <c r="X2" s="111"/>
+      <c r="Y2" s="111"/>
+      <c r="Z2" s="111"/>
+      <c r="AA2" s="112"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="166"/>
@@ -4468,25 +4468,25 @@
       <c r="F3" s="140"/>
       <c r="G3" s="140"/>
       <c r="H3" s="140"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="110"/>
-      <c r="S3" s="110"/>
-      <c r="T3" s="110"/>
-      <c r="U3" s="110"/>
-      <c r="V3" s="110"/>
-      <c r="W3" s="110"/>
-      <c r="X3" s="110"/>
-      <c r="Y3" s="110"/>
-      <c r="Z3" s="110"/>
-      <c r="AA3" s="111"/>
+      <c r="I3" s="111"/>
+      <c r="J3" s="111"/>
+      <c r="K3" s="111"/>
+      <c r="L3" s="111"/>
+      <c r="M3" s="111"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="111"/>
+      <c r="P3" s="111"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="111"/>
+      <c r="Y3" s="111"/>
+      <c r="Z3" s="111"/>
+      <c r="AA3" s="112"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="166"/>
@@ -23247,7 +23247,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ka/HtMUEd01dnBRIYrHwOf0FOyhm16B1TbEsRvJl5LqfAzg/VHEqbLs/HtyTBSLnZj20FdcSRD9aB8sTQI2eIA==" saltValue="qBFN/JLAlhLHqsgwWCmOig==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Zf5JvYpvuW/HWvs4gTw5e2IGDbL+iU3j+X0AB9eUyNE5n9SXQByVGuTo5o2vccF+Dt06DVfT61vzD7oIvQ7E+A==" saltValue="pHq0gAQ5oUMOWi3p7akqAQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:C4"/>
@@ -23277,8 +23277,8 @@
     <hyperlink ref="V5" r:id="rId4" location="reasonsDaysLost" xr:uid="{97696E2A-D771-4DE7-BD06-1B0737D662F5}"/>
     <hyperlink ref="W5" r:id="rId5" location="reasonsDaysLost" xr:uid="{DDC8B8E4-165B-40F3-9FF0-D7029574446F}"/>
     <hyperlink ref="X5" r:id="rId6" location="reasonsDaysLost" xr:uid="{D28A352C-1A1C-4FB8-A48F-5E310525AEF4}"/>
-    <hyperlink ref="E5" r:id="rId7" xr:uid="{5B1C3021-F6F9-4F61-9E0E-4225D5395400}"/>
-    <hyperlink ref="J5" r:id="rId8" xr:uid="{93A72983-23E8-4E45-8EB9-744217E6A48E}"/>
+    <hyperlink ref="E5" r:id="rId7" location="Ports" xr:uid="{5B1C3021-F6F9-4F61-9E0E-4225D5395400}"/>
+    <hyperlink ref="J5" r:id="rId8" location="Ports" xr:uid="{93A72983-23E8-4E45-8EB9-744217E6A48E}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -23355,38 +23355,38 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="102"/>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="107" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="107"/>
-      <c r="D3" s="107"/>
-      <c r="E3" s="107"/>
-      <c r="F3" s="108"/>
-      <c r="G3" s="109" t="s">
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="109"/>
+      <c r="G3" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="110"/>
-      <c r="I3" s="111"/>
+      <c r="H3" s="111"/>
+      <c r="I3" s="112"/>
       <c r="J3" s="76" t="s">
         <v>24</v>
       </c>
       <c r="K3" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="L3" s="106" t="s">
+      <c r="L3" s="107" t="s">
         <v>218</v>
       </c>
-      <c r="M3" s="107"/>
-      <c r="N3" s="107"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="108"/>
+      <c r="M3" s="108"/>
+      <c r="N3" s="108"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="109"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="102"/>
       <c r="B4" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="112" t="s">
+      <c r="C4" s="113" t="s">
         <v>115</v>
       </c>
       <c r="D4" s="92" t="s">
@@ -23398,7 +23398,7 @@
       <c r="F4" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="113" t="s">
+      <c r="G4" s="104" t="s">
         <v>7</v>
       </c>
       <c r="H4" s="115" t="s">
@@ -23407,10 +23407,10 @@
       <c r="I4" s="117" t="s">
         <v>219</v>
       </c>
-      <c r="J4" s="113" t="s">
+      <c r="J4" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="104" t="s">
+      <c r="K4" s="105" t="s">
         <v>40</v>
       </c>
       <c r="L4" s="102" t="s">
@@ -23428,15 +23428,15 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="102"/>
       <c r="B5" s="90"/>
-      <c r="C5" s="112"/>
+      <c r="C5" s="113"/>
       <c r="D5" s="92"/>
       <c r="E5" s="99"/>
       <c r="F5" s="91"/>
-      <c r="G5" s="113"/>
+      <c r="G5" s="104"/>
       <c r="H5" s="116"/>
       <c r="I5" s="118"/>
-      <c r="J5" s="113"/>
-      <c r="K5" s="105"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="106"/>
       <c r="L5" s="77" t="s">
         <v>4</v>
       </c>
@@ -27054,6 +27054,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="L4qzapnu2Pie5M6M+VqNy06BMKJGmzAz/nbL0FRyyFkfEcHy6Tv4O6TxB3V0b+dtvMDWXensSOS0zD05lvNeCg==" saltValue="2bcGRrxFYEnLofE/L5Qkfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:M4"/>
@@ -27070,7 +27071,6 @@
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5 C4:C5 J4:K4 M5 G4:H4" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
@@ -27161,21 +27161,21 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="102"/>
-      <c r="B4" s="109" t="s">
+      <c r="B4" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
       <c r="F4" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="109" t="s">
+      <c r="G4" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="111"/>
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="112"/>
       <c r="K4" s="119" t="s">
         <v>142</v>
       </c>
@@ -29810,7 +29810,7 @@
       <c r="K205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="gfZrPLniNXIFnLy1vOgXex/iJpDHFoumsQiPwE0Xpbq2Qc/ZLK0EV8W9d74qT2NYyOopeZk29FHZJ/6A9NkzSA==" saltValue="i7WQ491h5dezlRtkiDQ+qg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3Syo+nyaW7JcH8enc98JZc60EF96Ax/2zMhpv4WzQcfv9uaf7QKTSGcoO4vp8K3hIqipQOweUigRPRVx2o2dGA==" saltValue="fqHtwNa+oBukK7bnqQOPaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:K2"/>
@@ -29829,8 +29829,8 @@
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" location="countries" xr:uid="{8D3300FC-6F86-415F-AC6B-9DDE03FD16A0}"/>
     <hyperlink ref="G5" r:id="rId2" location="countries" xr:uid="{CF77365D-9090-4AE6-ABA5-779409F5DE2E}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{9D055D8E-BB15-4868-A672-20C620D20414}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{D6729014-A717-47B0-A571-0625D8189490}"/>
+    <hyperlink ref="C5" r:id="rId3" location="Ports" xr:uid="{9D055D8E-BB15-4868-A672-20C620D20414}"/>
+    <hyperlink ref="H5" r:id="rId4" location="Ports" xr:uid="{D6729014-A717-47B0-A571-0625D8189490}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -39637,6 +39637,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="+SaHzzDEGw4gqvt+nIFZqUT6j8i5al1ZYgkPFJOo8wC7nXT8fzuZeM4Z+aphRTG7O56wdtrC22PEij5IX4RQGQ==" saltValue="UrzhHisYrfsnIOJY9wxxxA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="X4:X5"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="Z4:Z5"/>
+    <mergeCell ref="AA4:AA5"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="AN4:AP4"/>
+    <mergeCell ref="AQ4:AS4"/>
+    <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AH4:AJ4"/>
+    <mergeCell ref="AK4:AM4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="U2:AG3"/>
     <mergeCell ref="AH2:AS3"/>
@@ -39653,20 +39667,6 @@
     <mergeCell ref="V4:V5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="B2:T3"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AN4:AP4"/>
-    <mergeCell ref="AQ4:AS4"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AJ4"/>
-    <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 L5:R5 AH5:AI5 AK5:AL5 AN5:AO5 AQ5:AR5" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -39735,15 +39735,15 @@
         <v>82</v>
       </c>
       <c r="C2" s="141"/>
-      <c r="D2" s="106" t="s">
+      <c r="D2" s="107" t="s">
         <v>83</v>
       </c>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="108"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="109"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="102"/>

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BC2CF4-914D-462F-A77D-E5A29FFB3845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513B1F81-54B1-4D89-AC6C-04ACB48D638F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="803" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="285" yWindow="180" windowWidth="27705" windowHeight="15090" tabRatio="803" firstSheet="8" activeTab="14" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="35" r:id="rId1"/>
@@ -50,15 +50,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="210">
   <si>
     <t>LATITUDE</t>
   </si>
   <si>
     <t>LONGITUDE</t>
-  </si>
-  <si>
-    <t>OBSERVER_IDENTIFICATION</t>
   </si>
   <si>
     <t>IOTC_NUMBER</t>
@@ -67,34 +64,13 @@
     <t>FULL_NAME</t>
   </si>
   <si>
-    <t>OBSERVER_TRIP_DETAILS</t>
-  </si>
-  <si>
     <t>PORT</t>
-  </si>
-  <si>
-    <t>COUNTRY_CODE</t>
-  </si>
-  <si>
-    <t>PORT_CODE</t>
-  </si>
-  <si>
-    <t>NATIONALITY_CODE</t>
   </si>
   <si>
     <t>CONDUCTED</t>
   </si>
   <si>
     <t>OBSERVED</t>
-  </si>
-  <si>
-    <t>OBSERVED_TRIP_SUMMARY</t>
-  </si>
-  <si>
-    <t>REASONS_FOR_DAYS_LOST</t>
-  </si>
-  <si>
-    <t>NUMBER_OF_DAYS</t>
   </si>
   <si>
     <t>SEARCHING</t>
@@ -124,67 +100,13 @@
     <t>REGISTRATION</t>
   </si>
   <si>
-    <t>LICENSED_TARGET_SPECIES</t>
-  </si>
-  <si>
-    <t>FISHING_MASTER</t>
-  </si>
-  <si>
-    <t>SKIPPER_CAPTAIN</t>
-  </si>
-  <si>
     <t>CREW_NUMBER</t>
   </si>
   <si>
     <t>IDENTIFICATION</t>
   </si>
   <si>
-    <t>VESSEL_INFORMATION</t>
-  </si>
-  <si>
-    <t>TRIP_DETAILS</t>
-  </si>
-  <si>
-    <t>VESSEL_DEPARTURE</t>
-  </si>
-  <si>
-    <t>VESSEL_RETURN</t>
-  </si>
-  <si>
     <t>VALUE</t>
-  </si>
-  <si>
-    <t>HULL_MATERIAL_CODE</t>
-  </si>
-  <si>
-    <t>TYPE_CODE</t>
-  </si>
-  <si>
-    <t>SPECIES_1_CODE</t>
-  </si>
-  <si>
-    <t>SPECIES_2_CODE</t>
-  </si>
-  <si>
-    <t>SPECIES_3_CODE</t>
-  </si>
-  <si>
-    <t>SPECIES_4_CODE</t>
-  </si>
-  <si>
-    <t>MAIN_FISHING_GEAR_CODE</t>
-  </si>
-  <si>
-    <t>REASON_1_CODE</t>
-  </si>
-  <si>
-    <t>REASON_2_CODE</t>
-  </si>
-  <si>
-    <t>REASON_3_CODE</t>
-  </si>
-  <si>
-    <t>REASON_4_CODE</t>
   </si>
   <si>
     <t>MAKE</t>
@@ -193,46 +115,7 @@
     <t>POWER_VALUE</t>
   </si>
   <si>
-    <t>MAIN_ENGINE_1</t>
-  </si>
-  <si>
-    <t>MAIN_ENGINE_2</t>
-  </si>
-  <si>
-    <t>METHOD_1_CODE</t>
-  </si>
-  <si>
-    <t>METHOD_2_CODE</t>
-  </si>
-  <si>
-    <t>METHOD_3_CODE</t>
-  </si>
-  <si>
-    <t>METHOD_4_CODE</t>
-  </si>
-  <si>
-    <t>FISH_PRESERVATION_METHODS</t>
-  </si>
-  <si>
-    <t>TYPE_1_CODE</t>
-  </si>
-  <si>
-    <t>TYPE_2_CODE</t>
-  </si>
-  <si>
-    <t>TYPE_3_CODE</t>
-  </si>
-  <si>
     <t>AUTONOMY_RANGE</t>
-  </si>
-  <si>
-    <t>FISH_STORAGE_TYPES</t>
-  </si>
-  <si>
-    <t>VESSEL_ATTRIBUTES</t>
-  </si>
-  <si>
-    <t>GPS</t>
   </si>
   <si>
     <t>VMS</t>
@@ -271,67 +154,10 @@
     <t>AIS</t>
   </si>
   <si>
-    <t>VESSEL_ELECTRONICS</t>
-  </si>
-  <si>
-    <t>OTHER_1</t>
-  </si>
-  <si>
-    <t>CATEGORY_1_CODE</t>
-  </si>
-  <si>
-    <t>STORAGE_DISPOSAL_METHOD_1_CODE</t>
-  </si>
-  <si>
-    <t>WASTE_MANAGEMENT_DETAIL_1</t>
-  </si>
-  <si>
-    <t>WASTE_MANAGEMENT_DETAIL_3</t>
-  </si>
-  <si>
-    <t>WASTE_MANAGEMENT_DETAIL_4</t>
-  </si>
-  <si>
-    <t>WASTE_MANAGEMENT_DETAIL_2</t>
-  </si>
-  <si>
-    <t>WASTE_MANAGEMENT</t>
-  </si>
-  <si>
-    <t>SPECIAL_EQUIPMENT_OR_MACHINERY</t>
-  </si>
-  <si>
-    <t>GENERAL_GEAR_ATTRIBUTES</t>
-  </si>
-  <si>
-    <t>SETTING_OPERATIONS</t>
-  </si>
-  <si>
-    <t>SPECIES_CODE</t>
-  </si>
-  <si>
-    <t>PROCESSING_TYPE_CODE</t>
-  </si>
-  <si>
-    <t>CATCH_DETAILS</t>
-  </si>
-  <si>
     <t>WEIGHT</t>
   </si>
   <si>
-    <t>MEASURING_TOOL_CODE</t>
-  </si>
-  <si>
-    <t>LENGTH_1</t>
-  </si>
-  <si>
-    <t>LENGTH_2</t>
-  </si>
-  <si>
     <t>VALUE_KG</t>
-  </si>
-  <si>
-    <t>ESTIMATION_METHOD_CODE</t>
   </si>
   <si>
     <t>VALUE_CM</t>
@@ -340,28 +166,7 @@
     <t>SEX</t>
   </si>
   <si>
-    <t>DEPREDATION_DETAILS</t>
-  </si>
-  <si>
-    <t>ADDITIONAL_DETAILS</t>
-  </si>
-  <si>
-    <t>DEPREDATION_SOURCE_CODE</t>
-  </si>
-  <si>
-    <t>CONDITION_AT_CAPTURE_CODE</t>
-  </si>
-  <si>
-    <t>CONDITION_AT_RELEASE_CODE</t>
-  </si>
-  <si>
     <t>PRESERVATION_METHOD</t>
-  </si>
-  <si>
-    <t>SAMPLE_COLLECTED</t>
-  </si>
-  <si>
-    <t>ALL_SPECIES</t>
   </si>
   <si>
     <t>RELEASE</t>
@@ -376,15 +181,6 @@
     <t>TAG_NUMBER_2</t>
   </si>
   <si>
-    <t>TAG_DETAILS</t>
-  </si>
-  <si>
-    <t>SPECIMEN_DETAILS</t>
-  </si>
-  <si>
-    <t>GEAR_INTERACTION_CODE</t>
-  </si>
-  <si>
     <t>BROUGHT_ONBOARD</t>
   </si>
   <si>
@@ -392,15 +188,6 @@
   </si>
   <si>
     <t>PHOTO_ID</t>
-  </si>
-  <si>
-    <t>ADDITIONAL_CATCH_DETAILS_SSI</t>
-  </si>
-  <si>
-    <t>FLAG_OR_CHARTERING_CODE</t>
-  </si>
-  <si>
-    <t>SAMPLING_METHOD_CODE</t>
   </si>
   <si>
     <t>IS_STRAIGHT</t>
@@ -418,64 +205,13 @@
     <t>Vessel &gt; Vessel attributes</t>
   </si>
   <si>
-    <t>IN_PORT</t>
-  </si>
-  <si>
-    <t>AT_SEA</t>
-  </si>
-  <si>
     <t>EMBARKATION</t>
   </si>
   <si>
     <t>DISEMBARKATION</t>
   </si>
   <si>
-    <t>START_SETTING</t>
-  </si>
-  <si>
     <t>POSITION</t>
-  </si>
-  <si>
-    <t>CATEGORY_2_CODE</t>
-  </si>
-  <si>
-    <t>STORAGE_DISPOSAL_METHOD_2_CODE</t>
-  </si>
-  <si>
-    <t>OTHER_2</t>
-  </si>
-  <si>
-    <t>CATEGORY_3_CODE</t>
-  </si>
-  <si>
-    <t>STORAGE_DISPOSAL_METHOD_3_CODE</t>
-  </si>
-  <si>
-    <t>OTHER_3</t>
-  </si>
-  <si>
-    <t>CATEGORY_4_CODE</t>
-  </si>
-  <si>
-    <t>STORAGE_DISPOSAL_METHOD_4_CODE</t>
-  </si>
-  <si>
-    <t>OTHER_4</t>
-  </si>
-  <si>
-    <t>NUM_FISH</t>
-  </si>
-  <si>
-    <t>SCHOOL_SIGHTING_CUES</t>
-  </si>
-  <si>
-    <t>CUE_1_CODE</t>
-  </si>
-  <si>
-    <t>CUE_2_CODE</t>
-  </si>
-  <si>
-    <t>CUE_3_CODE</t>
   </si>
   <si>
     <t>DATE_TIME_UTC</t>
@@ -487,12 +223,6 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>ACTIVITY_DETAILS</t>
-  </si>
-  <si>
-    <t>Surface fisheries &gt; Dailiy activities</t>
-  </si>
-  <si>
     <t>Submission date</t>
   </si>
   <si>
@@ -502,16 +232,10 @@
     <t>Flag / chartering state</t>
   </si>
   <si>
-    <t>KW | HP | BHP</t>
-  </si>
-  <si>
     <t>DAYS | NM</t>
   </si>
   <si>
     <t>KG | T</t>
-  </si>
-  <si>
-    <t>OBSERVED_PREDATOR_CODE</t>
   </si>
   <si>
     <t>TYPE</t>
@@ -526,22 +250,10 @@
     <t>STAGE</t>
   </si>
   <si>
-    <t>HANDLING_METHOD_CODE</t>
-  </si>
-  <si>
     <t>LIVE_BAIT_TANK_CAPACITY_M3</t>
   </si>
   <si>
-    <t>POLE_MATERIAL</t>
-  </si>
-  <si>
     <t>NUM_AUTOMATIC_POLES</t>
-  </si>
-  <si>
-    <t>NUM_ANGLERS</t>
-  </si>
-  <si>
-    <t>MATERIAL_CODE</t>
   </si>
   <si>
     <t>HOOK</t>
@@ -553,22 +265,7 @@
     <t>Pole-and-line gear specifications</t>
   </si>
   <si>
-    <t>HOOK_TYPE_CODE_2</t>
-  </si>
-  <si>
-    <t>HOOK_TYPE_CODE_3</t>
-  </si>
-  <si>
-    <t>HOOK_TYPE_CODE_4</t>
-  </si>
-  <si>
-    <t>END_SETTING</t>
-  </si>
-  <si>
     <t>Pole-and-line fishing events &gt; Tuna fishing &gt; Setting operations</t>
-  </si>
-  <si>
-    <t>TARGET_SPECIES</t>
   </si>
   <si>
     <t>MAX_LINES_FISHING_AT_SAME_TIME</t>
@@ -577,16 +274,10 @@
     <t>BAIT</t>
   </si>
   <si>
-    <t>CONDITION_CODE</t>
-  </si>
-  <si>
     <t>NUM_HOOKS_LOST</t>
   </si>
   <si>
     <t>WEIGHT_KG</t>
-  </si>
-  <si>
-    <t>Pole-and-line fishing events &gt; Tuna fishing &gt; Set-level catch details &gt; Specimen details &gt; SSIs</t>
   </si>
   <si>
     <t>Pole-and-line fishing events &gt; Bait fishing &gt; Set-level catch details</t>
@@ -601,13 +292,7 @@
     <t>FT | M</t>
   </si>
   <si>
-    <t>NUM_FISHERS</t>
-  </si>
-  <si>
     <t>Pole-and-line fishing events &gt; Bait fishing &gt; Set-level catch details &gt; Specimen details</t>
-  </si>
-  <si>
-    <t>Pole-and-line fishing events &gt; Bait fishing &gt; Set-level catch details &gt; Specimen details &gt; SSIs</t>
   </si>
   <si>
     <t>FATE</t>
@@ -697,9 +382,6 @@
     <t>ROS-PL</t>
   </si>
   <si>
-    <t>NUMBER_FISHING_EVENTS</t>
-  </si>
-  <si>
     <t>IOTC_ID</t>
   </si>
   <si>
@@ -724,10 +406,280 @@
     <t>FISH_STORAGE_CAPACITY_M3</t>
   </si>
   <si>
-    <t>MEASUREMENT_TOOL_CODE</t>
+    <t xml:space="preserve"> IOTC ROS data reporting form - Pole and line</t>
   </si>
   <si>
-    <t xml:space="preserve"> IOTC ROS data reporting form - Pole and line</t>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>FLAG_OR_CHARTERING</t>
+  </si>
+  <si>
+    <t>REASON_4</t>
+  </si>
+  <si>
+    <t>REASON_3</t>
+  </si>
+  <si>
+    <t>REASON_2</t>
+  </si>
+  <si>
+    <t>REASON_1</t>
+  </si>
+  <si>
+    <t>SPECIES_1</t>
+  </si>
+  <si>
+    <t>MAIN_FISHING_GEAR</t>
+  </si>
+  <si>
+    <t>NATIONALITY</t>
+  </si>
+  <si>
+    <t>HULL_MATERIAL</t>
+  </si>
+  <si>
+    <t>UNIT</t>
+  </si>
+  <si>
+    <t>METHOD_1</t>
+  </si>
+  <si>
+    <t>METHOD_2</t>
+  </si>
+  <si>
+    <t>METHOD_3</t>
+  </si>
+  <si>
+    <t>METHOD_4</t>
+  </si>
+  <si>
+    <t>TYPE_1</t>
+  </si>
+  <si>
+    <t>TYPE_2</t>
+  </si>
+  <si>
+    <t>TYPE_3</t>
+  </si>
+  <si>
+    <t>CATEGORY_1</t>
+  </si>
+  <si>
+    <t>STORAGE_DISPOSAL_METHOD_1</t>
+  </si>
+  <si>
+    <t>GNSS</t>
+  </si>
+  <si>
+    <t>CATEGORY_2</t>
+  </si>
+  <si>
+    <t>STORAGE_DISPOSAL_METHOD_2</t>
+  </si>
+  <si>
+    <t>CATEGORY_3</t>
+  </si>
+  <si>
+    <t>STORAGE_DISPOSAL_METHOD_3</t>
+  </si>
+  <si>
+    <t>CATEGORY_4</t>
+  </si>
+  <si>
+    <t>STORAGE_DISPOSAL_METHOD_4</t>
+  </si>
+  <si>
+    <t>WASTE MANAGEMENT DETAIL 1</t>
+  </si>
+  <si>
+    <t>WASTE MANAGEMENT DETAIL 2</t>
+  </si>
+  <si>
+    <t>WASTE MANAGEMENT DETAIL 3</t>
+  </si>
+  <si>
+    <t>WASTE MANAGEMENT DETAIL 4</t>
+  </si>
+  <si>
+    <t>VESSEL ELECTRONICS</t>
+  </si>
+  <si>
+    <t>VESSEL ATTRIBUTES</t>
+  </si>
+  <si>
+    <t>MAIN ENGINE 1</t>
+  </si>
+  <si>
+    <t>MAIN ENGINE 2</t>
+  </si>
+  <si>
+    <t>FISH PRESERVATION METHODS</t>
+  </si>
+  <si>
+    <t>FISH STORAGE TYPES</t>
+  </si>
+  <si>
+    <t>START SETTING</t>
+  </si>
+  <si>
+    <t>END SETTING</t>
+  </si>
+  <si>
+    <t>SCHOOL SIGHTING CUES</t>
+  </si>
+  <si>
+    <t>TARGET SPECIES</t>
+  </si>
+  <si>
+    <t>CUE_1</t>
+  </si>
+  <si>
+    <t>CUE_2</t>
+  </si>
+  <si>
+    <t>CUE_3</t>
+  </si>
+  <si>
+    <t>SPECIES_2</t>
+  </si>
+  <si>
+    <t>SPECIES_3</t>
+  </si>
+  <si>
+    <t>SPECIES_4</t>
+  </si>
+  <si>
+    <t>CONDITION</t>
+  </si>
+  <si>
+    <t>SPECIES</t>
+  </si>
+  <si>
+    <t>SAMPLING_METHOD</t>
+  </si>
+  <si>
+    <t>NUMBER_OF_FISH</t>
+  </si>
+  <si>
+    <t>ESTIMATION_METHOD</t>
+  </si>
+  <si>
+    <t>DEPREDATION_SOURCE</t>
+  </si>
+  <si>
+    <t>OBSERVED_PREDATOR</t>
+  </si>
+  <si>
+    <t>GEAR_INTERACTION</t>
+  </si>
+  <si>
+    <t>HANDLING_METHOD</t>
+  </si>
+  <si>
+    <t>MEASURING_TOOL</t>
+  </si>
+  <si>
+    <t>PROCESSING_TYPE</t>
+  </si>
+  <si>
+    <t>MEASUREMENT_TOOL</t>
+  </si>
+  <si>
+    <t>SAMPLE COLLECTED</t>
+  </si>
+  <si>
+    <t>TAG DETAILS</t>
+  </si>
+  <si>
+    <t>NUMBER_OF_FISHERS</t>
+  </si>
+  <si>
+    <t>Pole-and-line fishing events &gt; Bait fishing &gt; Set-level catch details &gt; Specimen details &gt;  Additional catch details SSIs</t>
+  </si>
+  <si>
+    <t>Surface fisheries &gt; Daily activities &gt; Activity details</t>
+  </si>
+  <si>
+    <t>REASONS FOR DAYS LOST</t>
+  </si>
+  <si>
+    <t>NUMBER OF DAYS</t>
+  </si>
+  <si>
+    <t>NUMBER OF FISHING EVENTS</t>
+  </si>
+  <si>
+    <t>AT SEA</t>
+  </si>
+  <si>
+    <t>IN PORT</t>
+  </si>
+  <si>
+    <t>OBSERVED TRIP SUMMARY</t>
+  </si>
+  <si>
+    <t>OBSERVER TRIP DETAILS</t>
+  </si>
+  <si>
+    <t>OBSERVER IDENTIFICATION</t>
+  </si>
+  <si>
+    <t>LICENSED TARGET SPECIES</t>
+  </si>
+  <si>
+    <t>FISHING MASTER</t>
+  </si>
+  <si>
+    <t>SKIPPER CAPTAIN</t>
+  </si>
+  <si>
+    <t>VESSEL DEPARTURE</t>
+  </si>
+  <si>
+    <t>VESSEL RETURN</t>
+  </si>
+  <si>
+    <t>WASTE MANAGEMENT</t>
+  </si>
+  <si>
+    <t>MATERIAL</t>
+  </si>
+  <si>
+    <t>HOOK_TYPE_2</t>
+  </si>
+  <si>
+    <t>HOOK_TYPE_3</t>
+  </si>
+  <si>
+    <t>HOOK_TYPE_4</t>
+  </si>
+  <si>
+    <t>POLE MATERIAL</t>
+  </si>
+  <si>
+    <t>SPECIAL EQUIPMENT OR MACHINERY</t>
+  </si>
+  <si>
+    <t>GENERAL GEAR ATTRIBUTES</t>
+  </si>
+  <si>
+    <t>NUMBER_OF_ANGLERS</t>
+  </si>
+  <si>
+    <t>DEPREDATION DETAILS</t>
+  </si>
+  <si>
+    <t>ADDITIONAL DETAILS</t>
+  </si>
+  <si>
+    <t>Pole-and-line fishing events &gt; Tuna fishing &gt; Set-level catch details &gt; Specimen details &gt; Additional catch details SSIs</t>
+  </si>
+  <si>
+    <t>LENGTH 1</t>
+  </si>
+  <si>
+    <t>LENGTH 2</t>
   </si>
 </sst>
 </file>
@@ -738,7 +690,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -763,24 +715,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -815,6 +752,26 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1106,9 +1063,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1120,94 +1077,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1223,7 +1101,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -1244,7 +1122,7 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1261,48 +1139,32 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1317,154 +1179,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1474,113 +1188,11 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1591,21 +1203,261 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1938,285 +1790,285 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="80" t="s">
-        <v>225</v>
+      <c r="B2" s="45" t="s">
+        <v>118</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="82"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="47"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="83"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="85"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="42"/>
-      <c r="C4" s="43" t="s">
-        <v>200</v>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15" t="s">
+        <v>95</v>
       </c>
-      <c r="D4" s="44" t="s">
-        <v>214</v>
+      <c r="D4" s="16" t="s">
+        <v>109</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="43" t="s">
-        <v>201</v>
+      <c r="E4" s="17"/>
+      <c r="F4" s="15" t="s">
+        <v>96</v>
       </c>
-      <c r="G4" s="46" t="s">
-        <v>202</v>
+      <c r="G4" s="18" t="s">
+        <v>97</v>
       </c>
-      <c r="H4" s="47"/>
+      <c r="H4" s="19"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="48"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="50"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="22"/>
     </row>
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B6" s="48"/>
-      <c r="C6" s="51" t="s">
-        <v>203</v>
+      <c r="B6" s="20"/>
+      <c r="C6" s="23" t="s">
+        <v>98</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="50"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="22"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="48"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="50"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="22"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="48"/>
-      <c r="C8" s="86" t="s">
-        <v>204</v>
+      <c r="B8" s="20"/>
+      <c r="C8" s="51" t="s">
+        <v>99</v>
       </c>
-      <c r="D8" s="86"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="86" t="s">
-        <v>205</v>
+      <c r="D8" s="51"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="51" t="s">
+        <v>100</v>
       </c>
-      <c r="G8" s="86"/>
-      <c r="H8" s="50"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="22"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
-      <c r="C9" s="52" t="s">
-        <v>206</v>
+      <c r="B9" s="20"/>
+      <c r="C9" s="24" t="s">
+        <v>101</v>
       </c>
-      <c r="D9" s="53"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="52" t="s">
-        <v>207</v>
+      <c r="D9" s="25"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="24" t="s">
+        <v>102</v>
       </c>
-      <c r="G9" s="53"/>
-      <c r="H9" s="50"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
-      <c r="C10" s="54" t="s">
-        <v>208</v>
+      <c r="B10" s="20"/>
+      <c r="C10" s="26" t="s">
+        <v>103</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49" t="s">
-        <v>208</v>
+      <c r="D10" s="25"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21" t="s">
+        <v>103</v>
       </c>
-      <c r="G10" s="53"/>
-      <c r="H10" s="50"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="50"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="22"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="54" t="s">
-        <v>209</v>
+      <c r="B12" s="20"/>
+      <c r="C12" s="26" t="s">
+        <v>104</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="22"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="54" t="s">
-        <v>147</v>
+      <c r="B13" s="20"/>
+      <c r="C13" s="26" t="s">
+        <v>57</v>
       </c>
-      <c r="D13" s="56"/>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="22"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="48"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="50"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="22"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="48"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="50"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="22"/>
     </row>
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B16" s="48"/>
-      <c r="C16" s="51" t="s">
-        <v>210</v>
+      <c r="B16" s="20"/>
+      <c r="C16" s="23" t="s">
+        <v>105</v>
       </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="22"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="48"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="50"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="22"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="48"/>
-      <c r="C18" s="54" t="s">
-        <v>211</v>
+      <c r="B18" s="20"/>
+      <c r="C18" s="26" t="s">
+        <v>106</v>
       </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="50"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="22"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="48"/>
-      <c r="C19" s="59" t="s">
-        <v>212</v>
+      <c r="B19" s="20"/>
+      <c r="C19" s="31" t="s">
+        <v>107</v>
       </c>
-      <c r="D19" s="58"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="50"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="48"/>
-      <c r="C20" s="79" t="s">
-        <v>149</v>
+      <c r="B20" s="20"/>
+      <c r="C20" s="44" t="s">
+        <v>59</v>
       </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="50"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="48"/>
-      <c r="C21" s="54" t="s">
-        <v>213</v>
+      <c r="B21" s="20"/>
+      <c r="C21" s="26" t="s">
+        <v>108</v>
       </c>
-      <c r="D21" s="58"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="50"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="22"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="48"/>
-      <c r="C22" s="54"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="49"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="22"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="48"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="50"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="22"/>
     </row>
     <row r="24" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B24" s="48"/>
-      <c r="C24" s="51" t="s">
-        <v>148</v>
+      <c r="B24" s="20"/>
+      <c r="C24" s="23" t="s">
+        <v>58</v>
       </c>
-      <c r="D24" s="55"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="50"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="48"/>
-      <c r="C25" s="49"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="49"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="50"/>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="22"/>
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="48"/>
-      <c r="C26" s="87"/>
-      <c r="D26" s="88"/>
-      <c r="E26" s="88"/>
-      <c r="F26" s="88"/>
-      <c r="G26" s="89"/>
-      <c r="H26" s="50"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="54"/>
+      <c r="H26" s="22"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="62"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="63"/>
-      <c r="F27" s="63"/>
-      <c r="G27" s="63"/>
-      <c r="H27" s="64"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="36"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C28" s="1"/>
-      <c r="D28" s="65"/>
+      <c r="D28" s="37"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tFmPhD6MIKTlqHk378nalDlCyNZGsOUPXbRp8DMtggj7Be85PK7/SNxPKvq+rxiORXcNZM0XvyA2/+bwviM7RA==" saltValue="UmBb+dwPGUcfjXsIFLoXJg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2242,90 +2094,86 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H205"/>
+  <dimension ref="A1:H203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="3" customWidth="1"/>
     <col min="4" max="4" width="25" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" style="3" customWidth="1"/>
     <col min="6" max="6" width="25.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
-        <v>178</v>
+      <c r="A1" s="9" t="s">
+        <v>207</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="165" t="s">
-        <v>192</v>
+      <c r="A2" s="136" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="166" t="s">
-        <v>194</v>
+      <c r="B2" s="136" t="s">
+        <v>89</v>
       </c>
-      <c r="C2" s="166" t="s">
-        <v>193</v>
+      <c r="C2" s="136" t="s">
+        <v>88</v>
       </c>
-      <c r="D2" s="114" t="s">
-        <v>109</v>
+      <c r="D2" s="100" t="s">
+        <v>173</v>
       </c>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
+      <c r="E2" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="100" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="71" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="165"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="166"/>
-      <c r="D3" s="114" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
-      <c r="H3" s="114"/>
+      <c r="A3" s="137"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="165"/>
-      <c r="B4" s="166"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="128" t="s">
-        <v>110</v>
-      </c>
-      <c r="E4" s="119" t="s">
-        <v>111</v>
-      </c>
-      <c r="F4" s="128" t="s">
-        <v>158</v>
-      </c>
-      <c r="G4" s="119" t="s">
-        <v>112</v>
-      </c>
-      <c r="H4" s="119" t="s">
-        <v>113</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="165"/>
-      <c r="B5" s="166"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="129"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="120"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -4307,48 +4155,26 @@
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="nXX3Z+Qx2s5zsgV1qV9cxAKmH/Xvc8/P0tUUgUqoQR3A52ynNkZr/tdeXPJv8BoA5o8EkFJ2bFNENjSRjOQF6Q==" saltValue="l0RcpwiXyrzVEBDM5c35MA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="10">
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="8">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 F4:F5" xr:uid="{8F3C96D1-E191-4693-B29A-79D17608E9F5}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 F2:F3" xr:uid="{8F3C96D1-E191-4693-B29A-79D17608E9F5}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D4:D5" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{78235951-ABFA-474C-9817-7631D9D14409}"/>
-    <hyperlink ref="F4:F5" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{8BA4CC5E-2A66-4A5F-8835-F30335A7CEAF}"/>
+    <hyperlink ref="D2:D3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{78235951-ABFA-474C-9817-7631D9D14409}"/>
+    <hyperlink ref="F2:F3" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{8BA4CC5E-2A66-4A5F-8835-F30335A7CEAF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4359,7 +4185,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AA205"/>
+  <dimension ref="A1:AA203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="3" customWidth="1"/>
@@ -4390,221 +4216,217 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="136" t="s">
-        <v>184</v>
+      <c r="A1" s="55" t="s">
+        <v>80</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="137"/>
-      <c r="U1" s="137"/>
-      <c r="V1" s="137"/>
-      <c r="W1" s="137"/>
-      <c r="X1" s="137"/>
-      <c r="Y1" s="137"/>
-      <c r="Z1" s="137"/>
-      <c r="AA1" s="138"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56"/>
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56"/>
+      <c r="AA1" s="57"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="166" t="s">
-        <v>192</v>
+      <c r="A2" s="136" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="166" t="s">
-        <v>194</v>
+      <c r="B2" s="136" t="s">
+        <v>89</v>
       </c>
-      <c r="C2" s="165" t="s">
-        <v>193</v>
+      <c r="C2" s="136" t="s">
+        <v>88</v>
       </c>
-      <c r="D2" s="167" t="s">
-        <v>109</v>
+      <c r="D2" s="89" t="s">
+        <v>168</v>
       </c>
-      <c r="E2" s="168"/>
-      <c r="F2" s="168"/>
-      <c r="G2" s="168"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
-      <c r="W2" s="111"/>
-      <c r="X2" s="111"/>
-      <c r="Y2" s="111"/>
-      <c r="Z2" s="111"/>
-      <c r="AA2" s="112"/>
+      <c r="E2" s="63" t="s">
+        <v>208</v>
+      </c>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="100" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="66" t="s">
+        <v>63</v>
+      </c>
+      <c r="R2" s="68"/>
+      <c r="S2" s="64" t="s">
+        <v>178</v>
+      </c>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64" t="s">
+        <v>179</v>
+      </c>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="64"/>
+      <c r="AA2" s="64"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="166"/>
-      <c r="B3" s="166"/>
-      <c r="C3" s="165"/>
-      <c r="D3" s="140" t="s">
-        <v>103</v>
+      <c r="A3" s="137"/>
+      <c r="B3" s="137"/>
+      <c r="C3" s="137"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="129" t="s">
+        <v>62</v>
       </c>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="140"/>
-      <c r="H3" s="140"/>
-      <c r="I3" s="111"/>
-      <c r="J3" s="111"/>
-      <c r="K3" s="111"/>
-      <c r="L3" s="111"/>
-      <c r="M3" s="111"/>
-      <c r="N3" s="111"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="111"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="111"/>
-      <c r="Y3" s="111"/>
-      <c r="Z3" s="111"/>
-      <c r="AA3" s="112"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="166"/>
-      <c r="B4" s="166"/>
-      <c r="C4" s="166"/>
-      <c r="D4" s="170" t="s">
-        <v>116</v>
+      <c r="F3" s="74" t="s">
+        <v>36</v>
       </c>
-      <c r="E4" s="140" t="s">
+      <c r="G3" s="129" t="s">
+        <v>175</v>
+      </c>
+      <c r="H3" s="74" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" s="76" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="77" t="s">
+        <v>175</v>
+      </c>
+      <c r="L3" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="N3" s="76" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="P3" s="101"/>
+      <c r="Q3" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="R3" s="110" t="s">
+        <v>65</v>
+      </c>
+      <c r="S3" s="107" t="s">
+        <v>62</v>
+      </c>
+      <c r="T3" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="U3" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="V3" s="76" t="s">
+        <v>40</v>
+      </c>
+      <c r="W3" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="X3" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y3" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z3" s="76" t="s">
         <v>90</v>
       </c>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="140"/>
-      <c r="I4" s="114" t="s">
+      <c r="AA3" s="76" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114" t="s">
-        <v>88</v>
-      </c>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="128" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q4" s="158" t="s">
-        <v>155</v>
-      </c>
-      <c r="R4" s="159"/>
-      <c r="S4" s="114" t="s">
-        <v>102</v>
-      </c>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114" t="s">
-        <v>108</v>
-      </c>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114"/>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="166"/>
-      <c r="B5" s="166"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="171"/>
-      <c r="E5" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="P5" s="129"/>
-      <c r="Q5" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="R5" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="S5" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="T5" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="W5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z5" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA5" s="8" t="s">
-        <v>196</v>
-      </c>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -10348,102 +10170,40 @@
       <c r="Z203" s="2"/>
       <c r="AA203" s="2"/>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-      <c r="J204" s="2"/>
-      <c r="K204" s="2"/>
-      <c r="L204" s="2"/>
-      <c r="M204" s="2"/>
-      <c r="N204" s="2"/>
-      <c r="O204" s="2"/>
-      <c r="P204" s="2"/>
-      <c r="Q204" s="2"/>
-      <c r="R204" s="2"/>
-      <c r="S204" s="2"/>
-      <c r="T204" s="2"/>
-      <c r="U204" s="2"/>
-      <c r="V204" s="2"/>
-      <c r="W204" s="2"/>
-      <c r="X204" s="2"/>
-      <c r="Y204" s="2"/>
-      <c r="Z204" s="2"/>
-      <c r="AA204" s="2"/>
-    </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-      <c r="Q205" s="2"/>
-      <c r="R205" s="2"/>
-      <c r="S205" s="2"/>
-      <c r="T205" s="2"/>
-      <c r="U205" s="2"/>
-      <c r="V205" s="2"/>
-      <c r="W205" s="2"/>
-      <c r="X205" s="2"/>
-      <c r="Y205" s="2"/>
-      <c r="Z205" s="2"/>
-      <c r="AA205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="TxbwinAmwlTdwQg04LLIVhrrUWgFGLnfoPZBjFCdSRA7AnH1RCq6risHXJfMb55ptOqV62K16890H7PQ+LK53w==" saltValue="Ugvp5EF9qMGWzeccqZ5fmg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="16">
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="12">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
     <mergeCell ref="A1:AA1"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="I2:AA2"/>
-    <mergeCell ref="I3:AA3"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:AA4"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P2:P3"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:AA2"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:O2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 E5 G5 I5 K5 M5 W5 P4:P5" xr:uid="{5E4B3162-4EBB-4AB5-B30D-164A47D38785}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 D2:D3 E3 G3 I3 K3 P2:P3" xr:uid="{5E4B3162-4EBB-4AB5-B30D-164A47D38785}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
-    <dataValidation type="custom" sqref="O5" xr:uid="{0C4A21EA-2076-49C9-9297-5A1258997CF8}">
+    <dataValidation type="custom" sqref="O3" xr:uid="{0C4A21EA-2076-49C9-9297-5A1258997CF8}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D4:D5" r:id="rId1" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{BFD2684A-F255-4A45-936A-FA04BB028BCC}"/>
-    <hyperlink ref="G5" r:id="rId2" location="lengthMeasurementTools" xr:uid="{C4FA29B3-2C8D-4339-B3D8-F0EA1EB90752}"/>
-    <hyperlink ref="K5" r:id="rId3" location="lengthMeasurementTools" xr:uid="{75603697-09CE-4919-BF4D-3EBC3F8E1252}"/>
-    <hyperlink ref="E5" r:id="rId4" location="lengthMeasurementTypes" xr:uid="{2187AEC4-49E1-4244-AA70-A980ABD68A20}"/>
-    <hyperlink ref="I5" r:id="rId5" location="lengthMeasurementTypes" xr:uid="{52978703-518C-4A83-BC90-C27264C77908}"/>
-    <hyperlink ref="M5" r:id="rId6" location="fishProcessingTypes" xr:uid="{D43A58E3-BC87-4BAB-B629-28CC81AB8470}"/>
-    <hyperlink ref="P4:P5" r:id="rId7" location="sex" display="SEX" xr:uid="{CF9A9C8D-83EB-473F-A588-FB44C1C23798}"/>
-    <hyperlink ref="W5" r:id="rId8" location="tagTypes" xr:uid="{EA3855C5-793B-43E7-B8B6-CF9F2C339024}"/>
-    <hyperlink ref="O5" r:id="rId9" location="weightMeasurementTools" xr:uid="{938A134D-B03F-4820-AF1D-1B56AC5AF35E}"/>
+    <hyperlink ref="D2:D3" r:id="rId1" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{BFD2684A-F255-4A45-936A-FA04BB028BCC}"/>
+    <hyperlink ref="G3" r:id="rId2" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{C4FA29B3-2C8D-4339-B3D8-F0EA1EB90752}"/>
+    <hyperlink ref="K3" r:id="rId3" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{75603697-09CE-4919-BF4D-3EBC3F8E1252}"/>
+    <hyperlink ref="E3" r:id="rId4" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{2187AEC4-49E1-4244-AA70-A980ABD68A20}"/>
+    <hyperlink ref="I3" r:id="rId5" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{52978703-518C-4A83-BC90-C27264C77908}"/>
+    <hyperlink ref="M3" r:id="rId6" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{D43A58E3-BC87-4BAB-B629-28CC81AB8470}"/>
+    <hyperlink ref="P2:P3" r:id="rId7" location="sex" display="SEX" xr:uid="{CF9A9C8D-83EB-473F-A588-FB44C1C23798}"/>
+    <hyperlink ref="W3" r:id="rId8" location="tagTypes" display="TYPE_CODE" xr:uid="{EA3855C5-793B-43E7-B8B6-CF9F2C339024}"/>
+    <hyperlink ref="O3" r:id="rId9" location="weightMeasurementTools" display="MEASUREMENT_TOOL_CODE" xr:uid="{938A134D-B03F-4820-AF1D-1B56AC5AF35E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10454,7 +10214,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -10467,116 +10227,114 @@
     <col min="8" max="8" width="11.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="11.42578125" style="3" customWidth="1"/>
     <col min="11" max="11" width="15.7109375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="172" t="s">
+      <c r="A1" s="60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="62"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="71" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="138"/>
+      <c r="C2" s="66" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" s="67"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="66" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="67"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="109" t="s">
+        <v>78</v>
+      </c>
+      <c r="J2" s="115"/>
+      <c r="K2" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="L2" s="64" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="174"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="127" t="s">
-        <v>192</v>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="139"/>
+      <c r="B3" s="140" t="s">
+        <v>89</v>
       </c>
-      <c r="B2" s="160" t="s">
-        <v>194</v>
+      <c r="C3" s="73" t="s">
+        <v>54</v>
       </c>
-      <c r="C2" s="158" t="s">
-        <v>84</v>
+      <c r="D3" s="64" t="s">
+        <v>53</v>
       </c>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
-      <c r="J2" s="175"/>
-      <c r="K2" s="175"/>
-      <c r="L2" s="159"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="103"/>
-      <c r="B3" s="160"/>
-      <c r="C3" s="176" t="s">
-        <v>126</v>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64" t="s">
+        <v>54</v>
       </c>
-      <c r="D3" s="177"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="176" t="s">
-        <v>170</v>
+      <c r="G3" s="64" t="s">
+        <v>53</v>
       </c>
-      <c r="G3" s="177"/>
-      <c r="H3" s="178"/>
-      <c r="I3" s="130" t="s">
-        <v>181</v>
-      </c>
-      <c r="J3" s="132"/>
-      <c r="K3" s="179" t="s">
-        <v>197</v>
-      </c>
-      <c r="L3" s="114" t="s">
-        <v>183</v>
-      </c>
+      <c r="H3" s="64"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="70"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="64"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="103"/>
-      <c r="B4" s="160"/>
-      <c r="C4" s="114" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="125" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="125"/>
-      <c r="F4" s="114" t="s">
-        <v>142</v>
-      </c>
-      <c r="G4" s="125" t="s">
-        <v>127</v>
-      </c>
-      <c r="H4" s="125"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="135"/>
-      <c r="K4" s="179"/>
-      <c r="L4" s="114"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="103"/>
-      <c r="B5" s="127"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="14" t="s">
+      <c r="A4" s="75"/>
+      <c r="B4" s="141"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="14" t="s">
+      <c r="F4" s="64"/>
+      <c r="G4" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>33</v>
+      <c r="I4" s="76" t="s">
+        <v>18</v>
       </c>
-      <c r="J5" s="39" t="s">
-        <v>182</v>
+      <c r="J4" s="111" t="s">
+        <v>79</v>
       </c>
-      <c r="K5" s="179"/>
-      <c r="L5" s="114"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="64"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -13364,39 +13122,23 @@
       <c r="K204" s="2"/>
       <c r="L204" s="2"/>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oMPtPwqdhSMRxg8oMyolwuD+PZ276NazXLu36OisObUAdSrzy1/K41lWbxwoNxn71aDsuoj47Fe4lncG3YJ6AQ==" saltValue="9XULsp/Qo5jFfAzk1UmpNA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="13">
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="I3:J4"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="L2:L4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:J3"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" sqref="K3:K5" xr:uid="{FD2DD9C9-32FC-400E-A9C3-9EC968384E9C}">
+    <dataValidation type="custom" sqref="K2:K4" xr:uid="{FD2DD9C9-32FC-400E-A9C3-9EC968384E9C}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13412,32 +13154,33 @@
   <dimension ref="A1:C203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="30.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="22.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="38.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
-        <v>179</v>
+      <c r="A1" s="9" t="s">
+        <v>76</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="91" t="s">
-        <v>88</v>
+      <c r="A2" s="64" t="s">
+        <v>34</v>
       </c>
-      <c r="B2" s="180" t="s">
-        <v>152</v>
+      <c r="B2" s="143" t="s">
+        <v>61</v>
       </c>
-      <c r="C2" s="117" t="s">
-        <v>224</v>
+      <c r="C2" s="88" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="91"/>
-      <c r="B3" s="180"/>
-      <c r="C3" s="118"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="91"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -14440,14 +14183,14 @@
       <c r="C203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kwJKSbF7anP+mwd7SJq7SkvnGWcqnlveqqWSl9vfd8dIxQb4DFwqN6plberTYQmYMibS/toko8by/odOnHIxiQ==" saltValue="THbYaRsKch3dS25+pYW7Qw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="3">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2" xr:uid="{7225598A-9FB2-4A8E-83F8-C019E42E3CA2}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3" xr:uid="{7225598A-9FB2-4A8E-83F8-C019E42E3CA2}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14463,81 +14206,77 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21" style="3" customWidth="1"/>
     <col min="3" max="3" width="25.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="25.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="33" t="s">
-        <v>185</v>
+      <c r="A1" s="9" t="s">
+        <v>181</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="35"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="114" t="s">
-        <v>109</v>
+      <c r="A2" s="100" t="s">
+        <v>173</v>
       </c>
-      <c r="B2" s="114"/>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
+      <c r="B2" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="100" t="s">
+        <v>174</v>
+      </c>
+      <c r="D2" s="100" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="100" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="71" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="114" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" s="114"/>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="F3" s="114"/>
-      <c r="G3" s="114"/>
+      <c r="A3" s="101"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="128" t="s">
-        <v>110</v>
-      </c>
-      <c r="B4" s="119" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="128" t="s">
-        <v>158</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="119" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="119" t="s">
-        <v>113</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="129"/>
-      <c r="B5" s="120"/>
-      <c r="C5" s="129"/>
-      <c r="D5" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="120"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -16321,45 +16060,28 @@
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ng6xy7cIwiQjNc/RNyjytmIWWygWVmc6tYRGrGdDQ0fMlClyNpfquTsZkcax81gbGLYKL/tfc8pgLP2yowGPag==" saltValue="h9iL5QCZ5DlHZAW0yaDGgw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="7">
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="custom" sqref="A4:A5 C4:E5" xr:uid="{F8B687B3-5E24-4067-8597-6A4FE90147BF}">
+  <dataValidations count="2">
+    <dataValidation type="custom" sqref="A2:A3 D2 E2" xr:uid="{F8B687B3-5E24-4067-8597-6A4FE90147BF}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
+    <dataValidation sqref="C2:C3" xr:uid="{F3CBB80A-AF6F-48CC-B46F-C4DD8E36B5F7}"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A4:A5" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{75DA312E-C74E-48FA-ABA3-A517F1CB19F4}"/>
-    <hyperlink ref="C4:C5" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{F9FA0319-7EF4-449A-83AA-43CFA022477A}"/>
-    <hyperlink ref="D5" r:id="rId3" location="individualConditions" xr:uid="{7DEB4137-9B47-4781-8E66-D721BE96ACBC}"/>
-    <hyperlink ref="E5" r:id="rId4" location="individualConditions" xr:uid="{A46D66F4-2BE5-4952-BE85-527FBCA5AA45}"/>
+    <hyperlink ref="A2:A3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{75DA312E-C74E-48FA-ABA3-A517F1CB19F4}"/>
+    <hyperlink ref="C2:C3" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{F9FA0319-7EF4-449A-83AA-43CFA022477A}"/>
+    <hyperlink ref="D2" r:id="rId3" location="individualConditions" xr:uid="{7DEB4137-9B47-4781-8E66-D721BE96ACBC}"/>
+    <hyperlink ref="E2" r:id="rId4" location="individualConditions" xr:uid="{A46D66F4-2BE5-4952-BE85-527FBCA5AA45}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16370,7 +16092,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E205"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -16378,53 +16100,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>146</v>
+      <c r="A1" s="6" t="s">
+        <v>182</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="21"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
-        <v>192</v>
+      <c r="A2" s="132" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>145</v>
+      <c r="B2" s="74" t="s">
+        <v>54</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="139"/>
-      <c r="B3" s="23" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="23" t="s">
+      <c r="C2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D2" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>144</v>
+      <c r="E2" s="76" t="s">
+        <v>56</v>
       </c>
     </row>
+    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="41"/>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -17819,18 +17539,8 @@
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3N5+7VUI+HZmvPiQF35PdGHJabHDVXqb7pdYfDtaubjaMqUr7XHQLnqefsSHFitmJHMeRCtPCCl1cbvkZWMNeg==" saltValue="EaY16JZzXnBSBEkIITwwSg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:A3"/>
-  </mergeCells>
+  <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17866,237 +17576,237 @@
     <col min="21" max="24" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="69" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="66" t="s">
-        <v>118</v>
+    <row r="1" spans="1:25" s="41" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>47</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="68"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="40"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="90" t="s">
-        <v>192</v>
+      <c r="A2" s="63" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="90" t="s">
-        <v>2</v>
+      <c r="B2" s="63" t="s">
+        <v>190</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="91" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+      <c r="Q2" s="63"/>
+      <c r="R2" s="63"/>
+      <c r="S2" s="63"/>
+      <c r="T2" s="63"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="63"/>
+      <c r="X2" s="63"/>
+      <c r="Y2" s="4"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="66" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="63"/>
+      <c r="W3" s="63"/>
+      <c r="X3" s="63"/>
+      <c r="Y3" s="4"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="70"/>
+      <c r="F4" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="G4" s="70"/>
+      <c r="H4" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="J4" s="70"/>
+      <c r="K4" s="69" t="s">
+        <v>186</v>
+      </c>
+      <c r="L4" s="70"/>
+      <c r="M4" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="N4" s="63" t="s">
+        <v>185</v>
+      </c>
+      <c r="O4" s="63"/>
+      <c r="P4" s="64" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64" t="s">
+        <v>183</v>
+      </c>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+    </row>
+    <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="63"/>
+      <c r="B5" s="74" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="75"/>
+      <c r="I5" s="77" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="77" t="s">
+        <v>4</v>
+      </c>
+      <c r="K5" s="76" t="s">
+        <v>0</v>
+      </c>
+      <c r="L5" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="75"/>
+      <c r="N5" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="92" t="s">
-        <v>12</v>
+      <c r="O5" s="74" t="s">
+        <v>6</v>
       </c>
-      <c r="O2" s="92"/>
-      <c r="P2" s="92"/>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="92"/>
-      <c r="S2" s="92"/>
-      <c r="T2" s="92"/>
-      <c r="U2" s="92"/>
-      <c r="V2" s="92"/>
-      <c r="W2" s="92"/>
-      <c r="X2" s="92"/>
-      <c r="Y2" s="4"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="90"/>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="93" t="s">
+      <c r="P5" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q5" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="R5" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="S5" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="U5" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="95"/>
-      <c r="I3" s="93" t="s">
-        <v>125</v>
+      <c r="V5" s="77" t="s">
+        <v>123</v>
       </c>
-      <c r="J3" s="94"/>
-      <c r="K3" s="94"/>
-      <c r="L3" s="94"/>
-      <c r="M3" s="94"/>
-      <c r="N3" s="92"/>
-      <c r="O3" s="92"/>
-      <c r="P3" s="92"/>
-      <c r="Q3" s="92"/>
-      <c r="R3" s="92"/>
-      <c r="S3" s="92"/>
-      <c r="T3" s="92"/>
-      <c r="U3" s="92"/>
-      <c r="V3" s="92"/>
-      <c r="W3" s="92"/>
-      <c r="X3" s="92"/>
-      <c r="Y3" s="4"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="90"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="96" t="s">
+      <c r="W5" s="77" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="97"/>
-      <c r="F4" s="96" t="s">
-        <v>123</v>
+      <c r="X5" s="77" t="s">
+        <v>121</v>
       </c>
-      <c r="G4" s="97"/>
-      <c r="H4" s="98" t="s">
-        <v>142</v>
-      </c>
-      <c r="I4" s="96" t="s">
-        <v>122</v>
-      </c>
-      <c r="J4" s="97"/>
-      <c r="K4" s="96" t="s">
-        <v>123</v>
-      </c>
-      <c r="L4" s="97"/>
-      <c r="M4" s="100" t="s">
-        <v>142</v>
-      </c>
-      <c r="N4" s="102" t="s">
-        <v>215</v>
-      </c>
-      <c r="O4" s="102"/>
-      <c r="P4" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="103"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="103" t="s">
-        <v>13</v>
-      </c>
-      <c r="V4" s="103"/>
-      <c r="W4" s="103"/>
-      <c r="X4" s="103"/>
-    </row>
-    <row r="5" spans="1:25" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="90"/>
-      <c r="B5" s="70" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="99"/>
-      <c r="I5" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="M5" s="101"/>
-      <c r="N5" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="O5" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="P5" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="R5" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="S5" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="T5" s="38" t="s">
-        <v>18</v>
-      </c>
-      <c r="U5" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="V5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="W5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" s="5" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="80"/>
+      <c r="C6" s="80"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="80"/>
+      <c r="M6" s="80"/>
+      <c r="N6" s="80"/>
+      <c r="O6" s="80"/>
+      <c r="P6" s="80"/>
+      <c r="Q6" s="80"/>
+      <c r="R6" s="80"/>
+      <c r="S6" s="80"/>
+      <c r="T6" s="80"/>
+      <c r="U6" s="80"/>
+      <c r="V6" s="80"/>
+      <c r="W6" s="80"/>
+      <c r="X6" s="80"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -23247,7 +22957,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Zf5JvYpvuW/HWvs4gTw5e2IGDbL+iU3j+X0AB9eUyNE5n9SXQByVGuTo5o2vccF+Dt06DVfT61vzD7oIvQ7E+A==" saltValue="pHq0gAQ5oUMOWi3p7akqAQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:C4"/>
@@ -23266,19 +22976,19 @@
     <mergeCell ref="U4:X4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 D5:E5 I5:J5 U5:X5" xr:uid="{91965C69-FE02-41D0-B18A-140404A18B82}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A6 U5 J5 I5 X5 W5 V5 D5 E5" xr:uid="{91965C69-FE02-41D0-B18A-140404A18B82}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" location="countries" xr:uid="{4DEB9E5B-16C0-49D0-834F-E9F1B54E470C}"/>
-    <hyperlink ref="I5" r:id="rId2" location="countries" xr:uid="{BD7C0CE3-847D-412E-82E1-FCED900CF562}"/>
-    <hyperlink ref="U5" r:id="rId3" location="reasonsDaysLost" xr:uid="{A903851E-2541-4BD3-B8BA-DD3DEC50339C}"/>
-    <hyperlink ref="V5" r:id="rId4" location="reasonsDaysLost" xr:uid="{97696E2A-D771-4DE7-BD06-1B0737D662F5}"/>
-    <hyperlink ref="W5" r:id="rId5" location="reasonsDaysLost" xr:uid="{DDC8B8E4-165B-40F3-9FF0-D7029574446F}"/>
-    <hyperlink ref="X5" r:id="rId6" location="reasonsDaysLost" xr:uid="{D28A352C-1A1C-4FB8-A48F-5E310525AEF4}"/>
-    <hyperlink ref="E5" r:id="rId7" location="Ports" xr:uid="{5B1C3021-F6F9-4F61-9E0E-4225D5395400}"/>
-    <hyperlink ref="J5" r:id="rId8" location="Ports" xr:uid="{93A72983-23E8-4E45-8EB9-744217E6A48E}"/>
+    <hyperlink ref="D5" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{4DEB9E5B-16C0-49D0-834F-E9F1B54E470C}"/>
+    <hyperlink ref="I5" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{BD7C0CE3-847D-412E-82E1-FCED900CF562}"/>
+    <hyperlink ref="U5" r:id="rId3" location="reasonsDaysLost" display="REASON_1_CODE" xr:uid="{A903851E-2541-4BD3-B8BA-DD3DEC50339C}"/>
+    <hyperlink ref="V5" r:id="rId4" location="reasonsDaysLost" display="REASON_2_CODE" xr:uid="{97696E2A-D771-4DE7-BD06-1B0737D662F5}"/>
+    <hyperlink ref="W5" r:id="rId5" location="reasonsDaysLost" display="REASON_3_CODE" xr:uid="{DDC8B8E4-165B-40F3-9FF0-D7029574446F}"/>
+    <hyperlink ref="X5" r:id="rId6" location="reasonsDaysLost" display="REASON_4_CODE" xr:uid="{D28A352C-1A1C-4FB8-A48F-5E310525AEF4}"/>
+    <hyperlink ref="E5" r:id="rId7" location="Ports" display="PORT_CODE" xr:uid="{5B1C3021-F6F9-4F61-9E0E-4225D5395400}"/>
+    <hyperlink ref="J5" r:id="rId8" location="Ports" display="PORT_CODE" xr:uid="{93A72983-23E8-4E45-8EB9-744217E6A48E}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -23290,7 +23000,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:P205"/>
+  <dimension ref="A1:P204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -23312,144 +23022,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="40"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="96" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="81" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="82"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="144" t="s">
+        <v>191</v>
+      </c>
+      <c r="K2" s="78" t="s">
+        <v>111</v>
+      </c>
+      <c r="L2" s="84" t="s">
+        <v>112</v>
+      </c>
+      <c r="M2" s="85"/>
+      <c r="N2" s="85"/>
+      <c r="O2" s="85"/>
+      <c r="P2" s="86"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="97"/>
+      <c r="B3" s="63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="99" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="68"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="102" t="s">
+      <c r="H3" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="88" t="s">
+        <v>113</v>
+      </c>
+      <c r="J3" s="87" t="s">
+        <v>125</v>
+      </c>
+      <c r="K3" s="89" t="s">
+        <v>126</v>
+      </c>
+      <c r="L3" s="72" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="73" t="s">
-        <v>29</v>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72" t="s">
+        <v>193</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="75"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="102"/>
-      <c r="B3" s="107" t="s">
-        <v>28</v>
+      <c r="O3" s="72"/>
+      <c r="P3" s="90" t="s">
+        <v>16</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="108"/>
-      <c r="E3" s="108"/>
-      <c r="F3" s="109"/>
-      <c r="G3" s="110" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="111"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="L3" s="107" t="s">
-        <v>218</v>
-      </c>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="108"/>
-      <c r="P3" s="109"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="113" t="s">
-        <v>115</v>
-      </c>
-      <c r="D4" s="92" t="s">
+      <c r="A4" s="98"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="92"/>
+      <c r="L4" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="98" t="s">
-        <v>21</v>
+      <c r="M4" s="102" t="s">
+        <v>127</v>
       </c>
-      <c r="F4" s="91" t="s">
-        <v>22</v>
+      <c r="N4" s="94" t="s">
+        <v>3</v>
       </c>
-      <c r="G4" s="104" t="s">
-        <v>7</v>
+      <c r="O4" s="102" t="s">
+        <v>127</v>
       </c>
-      <c r="H4" s="115" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="117" t="s">
-        <v>219</v>
-      </c>
-      <c r="J4" s="104" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="105" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="102" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="102"/>
-      <c r="P4" s="114" t="s">
-        <v>27</v>
-      </c>
+      <c r="P4" s="90"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="90"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="104"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="104"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="O5" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="P5" s="114"/>
+      <c r="A5" s="95"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
+      <c r="L5" s="95"/>
+      <c r="M5" s="95"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="95"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -23544,7 +23252,7 @@
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="C11"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
@@ -23562,7 +23270,7 @@
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
-      <c r="C12"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
@@ -27033,57 +26741,39 @@
       <c r="O204" s="2"/>
       <c r="P204" s="2"/>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="L4qzapnu2Pie5M6M+VqNy06BMKJGmzAz/nbL0FRyyFkfEcHy6Tv4O6TxB3V0b+dtvMDWXensSOS0zD05lvNeCg==" saltValue="2bcGRrxFYEnLofE/L5Qkfg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="L3:P3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="L2:P2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5 C4:C5 J4:K4 M5 G4:H4" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 C3:C4 H3:H4 K3:K4 G3:G4 J3:J4 O5" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C4:C5" r:id="rId1" location="countries" display="FLAG_OR_CHARTERING_CODE" xr:uid="{97FEB1BE-6CF4-478E-AC2A-4A1593F1C1A5}"/>
-    <hyperlink ref="G4" r:id="rId2" location="countries" xr:uid="{8791D884-795E-400D-B48D-CE9638A5A2B5}"/>
-    <hyperlink ref="J4" r:id="rId3" location="targetSpecies" xr:uid="{319F558C-0F36-4D91-9564-E88A253E4F33}"/>
-    <hyperlink ref="M5" r:id="rId4" location="countries" xr:uid="{FF3BA25E-DB4E-45B8-AD06-4472D5EE754B}"/>
-    <hyperlink ref="O5" r:id="rId5" location="countries" xr:uid="{58541663-F960-49A0-B08C-F339EB147F10}"/>
-    <hyperlink ref="H4" r:id="rId6" xr:uid="{244118BC-9211-4E9B-89AD-768C7F081F6D}"/>
+    <hyperlink ref="C3:C4" r:id="rId1" location="countries" display="FLAG_OR_CHARTERING_CODE" xr:uid="{97FEB1BE-6CF4-478E-AC2A-4A1593F1C1A5}"/>
+    <hyperlink ref="G3" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{8791D884-795E-400D-B48D-CE9638A5A2B5}"/>
+    <hyperlink ref="J3" r:id="rId3" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{319F558C-0F36-4D91-9564-E88A253E4F33}"/>
+    <hyperlink ref="M4" r:id="rId4" location="countries" display="NATIONALITY_CODE" xr:uid="{FF3BA25E-DB4E-45B8-AD06-4472D5EE754B}"/>
+    <hyperlink ref="O4" r:id="rId5" location="countries" display="NATIONALITY_CODE" xr:uid="{58541663-F960-49A0-B08C-F339EB147F10}"/>
+    <hyperlink ref="H3" r:id="rId6" display="PORT_CODE" xr:uid="{244118BC-9211-4E9B-89AD-768C7F081F6D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -27094,7 +26784,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:K205"/>
+  <dimension ref="A1:K204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -27111,103 +26801,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
-        <v>120</v>
+      <c r="A1" s="42" t="s">
+        <v>49</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="68"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="102" t="s">
-        <v>192</v>
+      <c r="A2" s="96" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="103" t="s">
-        <v>30</v>
+      <c r="B2" s="73" t="s">
+        <v>194</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73" t="s">
+        <v>195</v>
+      </c>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="102"/>
-      <c r="B3" s="103" t="s">
-        <v>31</v>
+      <c r="A3" s="97"/>
+      <c r="B3" s="66" t="s">
+        <v>4</v>
       </c>
-      <c r="C3" s="103"/>
-      <c r="D3" s="103"/>
-      <c r="E3" s="103"/>
-      <c r="F3" s="103"/>
-      <c r="G3" s="103" t="s">
-        <v>32</v>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="71" t="s">
+        <v>54</v>
       </c>
-      <c r="H3" s="103"/>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
+      <c r="G3" s="66" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="68"/>
+      <c r="K3" s="71" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="110" t="s">
-        <v>6</v>
+      <c r="A4" s="98"/>
+      <c r="B4" s="77" t="s">
+        <v>119</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="111"/>
-      <c r="E4" s="111"/>
-      <c r="F4" s="119" t="s">
-        <v>142</v>
+      <c r="C4" s="77" t="s">
+        <v>4</v>
       </c>
-      <c r="G4" s="110" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="111"/>
-      <c r="I4" s="111"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="119" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="D4" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="30" t="s">
-        <v>7</v>
+      <c r="F4" s="75"/>
+      <c r="G4" s="77" t="s">
+        <v>119</v>
       </c>
-      <c r="H5" s="30" t="s">
-        <v>8</v>
+      <c r="H4" s="77" t="s">
+        <v>4</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I4" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J4" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="K5" s="120"/>
+      <c r="K4" s="75"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -29796,41 +29484,27 @@
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="3Syo+nyaW7JcH8enc98JZc60EF96Ax/2zMhpv4WzQcfv9uaf7QKTSGcoO4vp8K3hIqipQOweUigRPRVx2o2dGA==" saltValue="fqHtwNa+oBukK7bnqQOPaQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="8">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="K4:K5"/>
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="7">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G2:K2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:C5 G5:H5" xr:uid="{3B1279DC-3A2D-4A0D-93AB-26CB3B0AE330}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4 B4 G4 H4" xr:uid="{3B1279DC-3A2D-4A0D-93AB-26CB3B0AE330}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" location="countries" xr:uid="{8D3300FC-6F86-415F-AC6B-9DDE03FD16A0}"/>
-    <hyperlink ref="G5" r:id="rId2" location="countries" xr:uid="{CF77365D-9090-4AE6-ABA5-779409F5DE2E}"/>
-    <hyperlink ref="C5" r:id="rId3" location="Ports" xr:uid="{9D055D8E-BB15-4868-A672-20C620D20414}"/>
-    <hyperlink ref="H5" r:id="rId4" location="Ports" xr:uid="{D6729014-A717-47B0-A571-0625D8189490}"/>
+    <hyperlink ref="B4" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{8D3300FC-6F86-415F-AC6B-9DDE03FD16A0}"/>
+    <hyperlink ref="G4" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{CF77365D-9090-4AE6-ABA5-779409F5DE2E}"/>
+    <hyperlink ref="C4" r:id="rId3" location="Ports" display="PORT_CODE" xr:uid="{9D055D8E-BB15-4868-A672-20C620D20414}"/>
+    <hyperlink ref="H4" r:id="rId4" location="Ports" display="PORT_CODE" xr:uid="{D6729014-A717-47B0-A571-0625D8189490}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29841,7 +29515,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AS205"/>
+  <dimension ref="A1:AO204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -29871,370 +29545,338 @@
     <col min="33" max="33" width="9.140625" style="3"/>
     <col min="34" max="34" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="36.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="36.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="36.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="36.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="36.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="36.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="8.85546875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="71" t="s">
-        <v>121</v>
+    <row r="1" spans="1:41" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="42" t="s">
+        <v>50</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
-      <c r="P1" s="67"/>
-      <c r="Q1" s="67"/>
-      <c r="R1" s="67"/>
-      <c r="S1" s="67"/>
-      <c r="T1" s="67"/>
-      <c r="U1" s="67"/>
-      <c r="V1" s="67"/>
-      <c r="W1" s="67"/>
-      <c r="X1" s="67"/>
-      <c r="Y1" s="67"/>
-      <c r="Z1" s="67"/>
-      <c r="AA1" s="67"/>
-      <c r="AB1" s="67"/>
-      <c r="AC1" s="67"/>
-      <c r="AD1" s="67"/>
-      <c r="AE1" s="67"/>
-      <c r="AF1" s="67"/>
-      <c r="AG1" s="67"/>
-      <c r="AH1" s="67"/>
-      <c r="AI1" s="67"/>
-      <c r="AJ1" s="67"/>
-      <c r="AK1" s="67"/>
-      <c r="AL1" s="67"/>
-      <c r="AM1" s="67"/>
-      <c r="AN1" s="67"/>
-      <c r="AO1" s="67"/>
-      <c r="AP1" s="67"/>
-      <c r="AQ1" s="67"/>
-      <c r="AR1" s="67"/>
-      <c r="AS1" s="68"/>
-    </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A2" s="102" t="s">
-        <v>192</v>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="39"/>
+      <c r="V1" s="39"/>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="39"/>
+      <c r="Z1" s="39"/>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="39"/>
+      <c r="AF1" s="39"/>
+      <c r="AG1" s="39"/>
+      <c r="AH1" s="39"/>
+      <c r="AI1" s="39"/>
+      <c r="AJ1" s="39"/>
+      <c r="AK1" s="39"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="39"/>
+      <c r="AN1" s="39"/>
+      <c r="AO1" s="39"/>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A2" s="96" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="130" t="s">
-        <v>59</v>
+      <c r="B2" s="66" t="s">
+        <v>151</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="131"/>
-      <c r="O2" s="131"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="132"/>
-      <c r="U2" s="121" t="s">
-        <v>73</v>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="67"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
+      <c r="P2" s="67"/>
+      <c r="Q2" s="67"/>
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="68"/>
+      <c r="U2" s="66" t="s">
+        <v>150</v>
       </c>
-      <c r="V2" s="122"/>
-      <c r="W2" s="122"/>
-      <c r="X2" s="122"/>
-      <c r="Y2" s="122"/>
-      <c r="Z2" s="122"/>
-      <c r="AA2" s="122"/>
-      <c r="AB2" s="122"/>
-      <c r="AC2" s="122"/>
-      <c r="AD2" s="122"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="122"/>
-      <c r="AG2" s="123"/>
-      <c r="AH2" s="125" t="s">
-        <v>81</v>
+      <c r="V2" s="67"/>
+      <c r="W2" s="67"/>
+      <c r="X2" s="67"/>
+      <c r="Y2" s="67"/>
+      <c r="Z2" s="67"/>
+      <c r="AA2" s="67"/>
+      <c r="AB2" s="67"/>
+      <c r="AC2" s="67"/>
+      <c r="AD2" s="67"/>
+      <c r="AE2" s="67"/>
+      <c r="AF2" s="67"/>
+      <c r="AG2" s="68"/>
+      <c r="AH2" s="66" t="s">
+        <v>196</v>
       </c>
-      <c r="AI2" s="125"/>
-      <c r="AJ2" s="125"/>
-      <c r="AK2" s="125"/>
-      <c r="AL2" s="125"/>
-      <c r="AM2" s="125"/>
-      <c r="AN2" s="125"/>
-      <c r="AO2" s="125"/>
-      <c r="AP2" s="125"/>
-      <c r="AQ2" s="125"/>
-      <c r="AR2" s="125"/>
-      <c r="AS2" s="125"/>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A3" s="102"/>
-      <c r="B3" s="133"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="134"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="134"/>
-      <c r="M3" s="134"/>
-      <c r="N3" s="134"/>
-      <c r="O3" s="134"/>
-      <c r="P3" s="134"/>
-      <c r="Q3" s="134"/>
-      <c r="R3" s="134"/>
-      <c r="S3" s="134"/>
-      <c r="T3" s="135"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="124"/>
-      <c r="W3" s="124"/>
-      <c r="X3" s="124"/>
-      <c r="Y3" s="124"/>
-      <c r="Z3" s="124"/>
-      <c r="AA3" s="124"/>
-      <c r="AB3" s="124"/>
-      <c r="AC3" s="124"/>
-      <c r="AD3" s="124"/>
-      <c r="AE3" s="124"/>
-      <c r="AF3" s="124"/>
-      <c r="AG3" s="97"/>
-      <c r="AH3" s="125"/>
-      <c r="AI3" s="125"/>
-      <c r="AJ3" s="125"/>
-      <c r="AK3" s="125"/>
-      <c r="AL3" s="125"/>
-      <c r="AM3" s="125"/>
-      <c r="AN3" s="125"/>
-      <c r="AO3" s="125"/>
-      <c r="AP3" s="125"/>
-      <c r="AQ3" s="125"/>
-      <c r="AR3" s="125"/>
-      <c r="AS3" s="125"/>
-    </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="126" t="s">
-        <v>220</v>
+      <c r="AI2" s="67"/>
+      <c r="AJ2" s="67"/>
+      <c r="AK2" s="67"/>
+      <c r="AL2" s="67"/>
+      <c r="AM2" s="67"/>
+      <c r="AN2" s="67"/>
+      <c r="AO2" s="67"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3" s="97"/>
+      <c r="B3" s="71" t="s">
+        <v>114</v>
       </c>
-      <c r="C4" s="126" t="s">
-        <v>221</v>
+      <c r="C3" s="71" t="s">
+        <v>115</v>
       </c>
-      <c r="D4" s="128" t="s">
-        <v>34</v>
+      <c r="D3" s="100" t="s">
+        <v>128</v>
       </c>
-      <c r="E4" s="103" t="s">
-        <v>47</v>
+      <c r="E3" s="64" t="s">
+        <v>152</v>
       </c>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103" t="s">
-        <v>48</v>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64" t="s">
+        <v>153</v>
       </c>
-      <c r="I4" s="103"/>
-      <c r="J4" s="103"/>
-      <c r="K4" s="126" t="s">
-        <v>223</v>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="71" t="s">
+        <v>117</v>
       </c>
-      <c r="L4" s="114" t="s">
-        <v>53</v>
+      <c r="L3" s="66" t="s">
+        <v>154</v>
       </c>
-      <c r="M4" s="114"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114" t="s">
-        <v>58</v>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="66" t="s">
+        <v>155</v>
       </c>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114" t="s">
-        <v>57</v>
+      <c r="Q3" s="67"/>
+      <c r="R3" s="68"/>
+      <c r="S3" s="66" t="s">
+        <v>21</v>
       </c>
-      <c r="T4" s="114"/>
-      <c r="U4" s="103" t="s">
+      <c r="T3" s="68"/>
+      <c r="U3" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="V3" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="W3" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" s="64" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="64" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="64" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="64" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="64" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="64" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH3" s="81" t="s">
+        <v>146</v>
+      </c>
+      <c r="AI3" s="83"/>
+      <c r="AJ3" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="AK3" s="83"/>
+      <c r="AL3" s="81" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM3" s="83"/>
+      <c r="AN3" s="81" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO3" s="83"/>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A4" s="98"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="106" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="107" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" s="106" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="106" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="107" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" s="75"/>
+      <c r="L4" s="77" t="s">
+        <v>130</v>
+      </c>
+      <c r="M4" s="77" t="s">
+        <v>131</v>
+      </c>
+      <c r="N4" s="77" t="s">
+        <v>132</v>
+      </c>
+      <c r="O4" s="77" t="s">
+        <v>133</v>
+      </c>
+      <c r="P4" s="77" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q4" s="77" t="s">
+        <v>135</v>
+      </c>
+      <c r="R4" s="77" t="s">
+        <v>136</v>
+      </c>
+      <c r="S4" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="V4" s="103" t="s">
-        <v>61</v>
+      <c r="U4" s="64"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="64"/>
+      <c r="AB4" s="64"/>
+      <c r="AC4" s="64"/>
+      <c r="AD4" s="64"/>
+      <c r="AE4" s="64"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="108" t="s">
+        <v>137</v>
       </c>
-      <c r="W4" s="103" t="s">
-        <v>72</v>
+      <c r="AI4" s="79" t="s">
+        <v>138</v>
       </c>
-      <c r="X4" s="103" t="s">
-        <v>62</v>
+      <c r="AJ4" s="79" t="s">
+        <v>140</v>
       </c>
-      <c r="Y4" s="103" t="s">
-        <v>63</v>
+      <c r="AK4" s="79" t="s">
+        <v>141</v>
       </c>
-      <c r="Z4" s="103" t="s">
-        <v>64</v>
+      <c r="AL4" s="79" t="s">
+        <v>142</v>
       </c>
-      <c r="AA4" s="103" t="s">
-        <v>65</v>
+      <c r="AM4" s="79" t="s">
+        <v>143</v>
       </c>
-      <c r="AB4" s="103" t="s">
-        <v>66</v>
+      <c r="AN4" s="79" t="s">
+        <v>144</v>
       </c>
-      <c r="AC4" s="103" t="s">
-        <v>67</v>
+      <c r="AO4" s="79" t="s">
+        <v>145</v>
       </c>
-      <c r="AD4" s="103" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE4" s="103" t="s">
-        <v>69</v>
-      </c>
-      <c r="AF4" s="103" t="s">
-        <v>70</v>
-      </c>
-      <c r="AG4" s="103" t="s">
-        <v>71</v>
-      </c>
-      <c r="AH4" s="114" t="s">
-        <v>77</v>
-      </c>
-      <c r="AI4" s="114"/>
-      <c r="AJ4" s="114"/>
-      <c r="AK4" s="114" t="s">
-        <v>80</v>
-      </c>
-      <c r="AL4" s="114"/>
-      <c r="AM4" s="114"/>
-      <c r="AN4" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO4" s="114"/>
-      <c r="AP4" s="114"/>
-      <c r="AQ4" s="114" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR4" s="114"/>
-      <c r="AS4" s="114"/>
-    </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="127"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="129"/>
-      <c r="E5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="K5" s="127"/>
-      <c r="L5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="R5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="S5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="T5" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
-      <c r="Z5" s="103"/>
-      <c r="AA5" s="103"/>
-      <c r="AB5" s="103"/>
-      <c r="AC5" s="103"/>
-      <c r="AD5" s="103"/>
-      <c r="AE5" s="103"/>
-      <c r="AF5" s="103"/>
-      <c r="AG5" s="103"/>
-      <c r="AH5" s="78" t="s">
-        <v>75</v>
-      </c>
-      <c r="AI5" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="AJ5" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK5" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="AL5" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="AM5" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN5" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO5" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="AP5" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="AQ5" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="AR5" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="AS5" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+      <c r="AH5" s="2"/>
+      <c r="AI5" s="2"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AL5" s="2"/>
+      <c r="AM5" s="2"/>
+      <c r="AN5" s="2"/>
+      <c r="AO5" s="2"/>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -30276,12 +29918,8 @@
       <c r="AM6" s="2"/>
       <c r="AN6" s="2"/>
       <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-    </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -30323,12 +29961,8 @@
       <c r="AM7" s="2"/>
       <c r="AN7" s="2"/>
       <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2"/>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-    </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -30370,12 +30004,8 @@
       <c r="AM8" s="2"/>
       <c r="AN8" s="2"/>
       <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2"/>
-      <c r="AR8" s="2"/>
-      <c r="AS8" s="2"/>
-    </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -30417,12 +30047,8 @@
       <c r="AM9" s="2"/>
       <c r="AN9" s="2"/>
       <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2"/>
-      <c r="AR9" s="2"/>
-      <c r="AS9" s="2"/>
-    </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -30464,12 +30090,8 @@
       <c r="AM10" s="2"/>
       <c r="AN10" s="2"/>
       <c r="AO10" s="2"/>
-      <c r="AP10" s="2"/>
-      <c r="AQ10" s="2"/>
-      <c r="AR10" s="2"/>
-      <c r="AS10" s="2"/>
-    </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -30511,12 +30133,8 @@
       <c r="AM11" s="2"/>
       <c r="AN11" s="2"/>
       <c r="AO11" s="2"/>
-      <c r="AP11" s="2"/>
-      <c r="AQ11" s="2"/>
-      <c r="AR11" s="2"/>
-      <c r="AS11" s="2"/>
-    </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -30558,12 +30176,8 @@
       <c r="AM12" s="2"/>
       <c r="AN12" s="2"/>
       <c r="AO12" s="2"/>
-      <c r="AP12" s="2"/>
-      <c r="AQ12" s="2"/>
-      <c r="AR12" s="2"/>
-      <c r="AS12" s="2"/>
-    </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -30605,12 +30219,8 @@
       <c r="AM13" s="2"/>
       <c r="AN13" s="2"/>
       <c r="AO13" s="2"/>
-      <c r="AP13" s="2"/>
-      <c r="AQ13" s="2"/>
-      <c r="AR13" s="2"/>
-      <c r="AS13" s="2"/>
-    </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -30652,12 +30262,8 @@
       <c r="AM14" s="2"/>
       <c r="AN14" s="2"/>
       <c r="AO14" s="2"/>
-      <c r="AP14" s="2"/>
-      <c r="AQ14" s="2"/>
-      <c r="AR14" s="2"/>
-      <c r="AS14" s="2"/>
-    </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -30699,12 +30305,8 @@
       <c r="AM15" s="2"/>
       <c r="AN15" s="2"/>
       <c r="AO15" s="2"/>
-      <c r="AP15" s="2"/>
-      <c r="AQ15" s="2"/>
-      <c r="AR15" s="2"/>
-      <c r="AS15" s="2"/>
-    </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -30746,12 +30348,8 @@
       <c r="AM16" s="2"/>
       <c r="AN16" s="2"/>
       <c r="AO16" s="2"/>
-      <c r="AP16" s="2"/>
-      <c r="AQ16" s="2"/>
-      <c r="AR16" s="2"/>
-      <c r="AS16" s="2"/>
-    </row>
-    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -30793,12 +30391,8 @@
       <c r="AM17" s="2"/>
       <c r="AN17" s="2"/>
       <c r="AO17" s="2"/>
-      <c r="AP17" s="2"/>
-      <c r="AQ17" s="2"/>
-      <c r="AR17" s="2"/>
-      <c r="AS17" s="2"/>
-    </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -30840,12 +30434,8 @@
       <c r="AM18" s="2"/>
       <c r="AN18" s="2"/>
       <c r="AO18" s="2"/>
-      <c r="AP18" s="2"/>
-      <c r="AQ18" s="2"/>
-      <c r="AR18" s="2"/>
-      <c r="AS18" s="2"/>
-    </row>
-    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -30887,12 +30477,8 @@
       <c r="AM19" s="2"/>
       <c r="AN19" s="2"/>
       <c r="AO19" s="2"/>
-      <c r="AP19" s="2"/>
-      <c r="AQ19" s="2"/>
-      <c r="AR19" s="2"/>
-      <c r="AS19" s="2"/>
-    </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -30934,12 +30520,8 @@
       <c r="AM20" s="2"/>
       <c r="AN20" s="2"/>
       <c r="AO20" s="2"/>
-      <c r="AP20" s="2"/>
-      <c r="AQ20" s="2"/>
-      <c r="AR20" s="2"/>
-      <c r="AS20" s="2"/>
-    </row>
-    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -30981,12 +30563,8 @@
       <c r="AM21" s="2"/>
       <c r="AN21" s="2"/>
       <c r="AO21" s="2"/>
-      <c r="AP21" s="2"/>
-      <c r="AQ21" s="2"/>
-      <c r="AR21" s="2"/>
-      <c r="AS21" s="2"/>
-    </row>
-    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -31028,12 +30606,8 @@
       <c r="AM22" s="2"/>
       <c r="AN22" s="2"/>
       <c r="AO22" s="2"/>
-      <c r="AP22" s="2"/>
-      <c r="AQ22" s="2"/>
-      <c r="AR22" s="2"/>
-      <c r="AS22" s="2"/>
-    </row>
-    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -31075,12 +30649,8 @@
       <c r="AM23" s="2"/>
       <c r="AN23" s="2"/>
       <c r="AO23" s="2"/>
-      <c r="AP23" s="2"/>
-      <c r="AQ23" s="2"/>
-      <c r="AR23" s="2"/>
-      <c r="AS23" s="2"/>
-    </row>
-    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -31122,12 +30692,8 @@
       <c r="AM24" s="2"/>
       <c r="AN24" s="2"/>
       <c r="AO24" s="2"/>
-      <c r="AP24" s="2"/>
-      <c r="AQ24" s="2"/>
-      <c r="AR24" s="2"/>
-      <c r="AS24" s="2"/>
-    </row>
-    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -31169,12 +30735,8 @@
       <c r="AM25" s="2"/>
       <c r="AN25" s="2"/>
       <c r="AO25" s="2"/>
-      <c r="AP25" s="2"/>
-      <c r="AQ25" s="2"/>
-      <c r="AR25" s="2"/>
-      <c r="AS25" s="2"/>
-    </row>
-    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -31216,12 +30778,8 @@
       <c r="AM26" s="2"/>
       <c r="AN26" s="2"/>
       <c r="AO26" s="2"/>
-      <c r="AP26" s="2"/>
-      <c r="AQ26" s="2"/>
-      <c r="AR26" s="2"/>
-      <c r="AS26" s="2"/>
-    </row>
-    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -31263,12 +30821,8 @@
       <c r="AM27" s="2"/>
       <c r="AN27" s="2"/>
       <c r="AO27" s="2"/>
-      <c r="AP27" s="2"/>
-      <c r="AQ27" s="2"/>
-      <c r="AR27" s="2"/>
-      <c r="AS27" s="2"/>
-    </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -31310,12 +30864,8 @@
       <c r="AM28" s="2"/>
       <c r="AN28" s="2"/>
       <c r="AO28" s="2"/>
-      <c r="AP28" s="2"/>
-      <c r="AQ28" s="2"/>
-      <c r="AR28" s="2"/>
-      <c r="AS28" s="2"/>
-    </row>
-    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -31357,12 +30907,8 @@
       <c r="AM29" s="2"/>
       <c r="AN29" s="2"/>
       <c r="AO29" s="2"/>
-      <c r="AP29" s="2"/>
-      <c r="AQ29" s="2"/>
-      <c r="AR29" s="2"/>
-      <c r="AS29" s="2"/>
-    </row>
-    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -31404,12 +30950,8 @@
       <c r="AM30" s="2"/>
       <c r="AN30" s="2"/>
       <c r="AO30" s="2"/>
-      <c r="AP30" s="2"/>
-      <c r="AQ30" s="2"/>
-      <c r="AR30" s="2"/>
-      <c r="AS30" s="2"/>
-    </row>
-    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -31451,12 +30993,8 @@
       <c r="AM31" s="2"/>
       <c r="AN31" s="2"/>
       <c r="AO31" s="2"/>
-      <c r="AP31" s="2"/>
-      <c r="AQ31" s="2"/>
-      <c r="AR31" s="2"/>
-      <c r="AS31" s="2"/>
-    </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -31498,12 +31036,8 @@
       <c r="AM32" s="2"/>
       <c r="AN32" s="2"/>
       <c r="AO32" s="2"/>
-      <c r="AP32" s="2"/>
-      <c r="AQ32" s="2"/>
-      <c r="AR32" s="2"/>
-      <c r="AS32" s="2"/>
-    </row>
-    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -31545,12 +31079,8 @@
       <c r="AM33" s="2"/>
       <c r="AN33" s="2"/>
       <c r="AO33" s="2"/>
-      <c r="AP33" s="2"/>
-      <c r="AQ33" s="2"/>
-      <c r="AR33" s="2"/>
-      <c r="AS33" s="2"/>
-    </row>
-    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -31592,12 +31122,8 @@
       <c r="AM34" s="2"/>
       <c r="AN34" s="2"/>
       <c r="AO34" s="2"/>
-      <c r="AP34" s="2"/>
-      <c r="AQ34" s="2"/>
-      <c r="AR34" s="2"/>
-      <c r="AS34" s="2"/>
-    </row>
-    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -31639,12 +31165,8 @@
       <c r="AM35" s="2"/>
       <c r="AN35" s="2"/>
       <c r="AO35" s="2"/>
-      <c r="AP35" s="2"/>
-      <c r="AQ35" s="2"/>
-      <c r="AR35" s="2"/>
-      <c r="AS35" s="2"/>
-    </row>
-    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -31686,12 +31208,8 @@
       <c r="AM36" s="2"/>
       <c r="AN36" s="2"/>
       <c r="AO36" s="2"/>
-      <c r="AP36" s="2"/>
-      <c r="AQ36" s="2"/>
-      <c r="AR36" s="2"/>
-      <c r="AS36" s="2"/>
-    </row>
-    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -31733,12 +31251,8 @@
       <c r="AM37" s="2"/>
       <c r="AN37" s="2"/>
       <c r="AO37" s="2"/>
-      <c r="AP37" s="2"/>
-      <c r="AQ37" s="2"/>
-      <c r="AR37" s="2"/>
-      <c r="AS37" s="2"/>
-    </row>
-    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -31780,12 +31294,8 @@
       <c r="AM38" s="2"/>
       <c r="AN38" s="2"/>
       <c r="AO38" s="2"/>
-      <c r="AP38" s="2"/>
-      <c r="AQ38" s="2"/>
-      <c r="AR38" s="2"/>
-      <c r="AS38" s="2"/>
-    </row>
-    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -31827,12 +31337,8 @@
       <c r="AM39" s="2"/>
       <c r="AN39" s="2"/>
       <c r="AO39" s="2"/>
-      <c r="AP39" s="2"/>
-      <c r="AQ39" s="2"/>
-      <c r="AR39" s="2"/>
-      <c r="AS39" s="2"/>
-    </row>
-    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -31874,12 +31380,8 @@
       <c r="AM40" s="2"/>
       <c r="AN40" s="2"/>
       <c r="AO40" s="2"/>
-      <c r="AP40" s="2"/>
-      <c r="AQ40" s="2"/>
-      <c r="AR40" s="2"/>
-      <c r="AS40" s="2"/>
-    </row>
-    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -31921,12 +31423,8 @@
       <c r="AM41" s="2"/>
       <c r="AN41" s="2"/>
       <c r="AO41" s="2"/>
-      <c r="AP41" s="2"/>
-      <c r="AQ41" s="2"/>
-      <c r="AR41" s="2"/>
-      <c r="AS41" s="2"/>
-    </row>
-    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -31968,12 +31466,8 @@
       <c r="AM42" s="2"/>
       <c r="AN42" s="2"/>
       <c r="AO42" s="2"/>
-      <c r="AP42" s="2"/>
-      <c r="AQ42" s="2"/>
-      <c r="AR42" s="2"/>
-      <c r="AS42" s="2"/>
-    </row>
-    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -32015,12 +31509,8 @@
       <c r="AM43" s="2"/>
       <c r="AN43" s="2"/>
       <c r="AO43" s="2"/>
-      <c r="AP43" s="2"/>
-      <c r="AQ43" s="2"/>
-      <c r="AR43" s="2"/>
-      <c r="AS43" s="2"/>
-    </row>
-    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -32062,12 +31552,8 @@
       <c r="AM44" s="2"/>
       <c r="AN44" s="2"/>
       <c r="AO44" s="2"/>
-      <c r="AP44" s="2"/>
-      <c r="AQ44" s="2"/>
-      <c r="AR44" s="2"/>
-      <c r="AS44" s="2"/>
-    </row>
-    <row r="45" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -32109,12 +31595,8 @@
       <c r="AM45" s="2"/>
       <c r="AN45" s="2"/>
       <c r="AO45" s="2"/>
-      <c r="AP45" s="2"/>
-      <c r="AQ45" s="2"/>
-      <c r="AR45" s="2"/>
-      <c r="AS45" s="2"/>
-    </row>
-    <row r="46" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -32156,12 +31638,8 @@
       <c r="AM46" s="2"/>
       <c r="AN46" s="2"/>
       <c r="AO46" s="2"/>
-      <c r="AP46" s="2"/>
-      <c r="AQ46" s="2"/>
-      <c r="AR46" s="2"/>
-      <c r="AS46" s="2"/>
-    </row>
-    <row r="47" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -32203,12 +31681,8 @@
       <c r="AM47" s="2"/>
       <c r="AN47" s="2"/>
       <c r="AO47" s="2"/>
-      <c r="AP47" s="2"/>
-      <c r="AQ47" s="2"/>
-      <c r="AR47" s="2"/>
-      <c r="AS47" s="2"/>
-    </row>
-    <row r="48" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -32250,12 +31724,8 @@
       <c r="AM48" s="2"/>
       <c r="AN48" s="2"/>
       <c r="AO48" s="2"/>
-      <c r="AP48" s="2"/>
-      <c r="AQ48" s="2"/>
-      <c r="AR48" s="2"/>
-      <c r="AS48" s="2"/>
-    </row>
-    <row r="49" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -32297,12 +31767,8 @@
       <c r="AM49" s="2"/>
       <c r="AN49" s="2"/>
       <c r="AO49" s="2"/>
-      <c r="AP49" s="2"/>
-      <c r="AQ49" s="2"/>
-      <c r="AR49" s="2"/>
-      <c r="AS49" s="2"/>
-    </row>
-    <row r="50" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -32344,12 +31810,8 @@
       <c r="AM50" s="2"/>
       <c r="AN50" s="2"/>
       <c r="AO50" s="2"/>
-      <c r="AP50" s="2"/>
-      <c r="AQ50" s="2"/>
-      <c r="AR50" s="2"/>
-      <c r="AS50" s="2"/>
-    </row>
-    <row r="51" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -32391,12 +31853,8 @@
       <c r="AM51" s="2"/>
       <c r="AN51" s="2"/>
       <c r="AO51" s="2"/>
-      <c r="AP51" s="2"/>
-      <c r="AQ51" s="2"/>
-      <c r="AR51" s="2"/>
-      <c r="AS51" s="2"/>
-    </row>
-    <row r="52" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -32438,12 +31896,8 @@
       <c r="AM52" s="2"/>
       <c r="AN52" s="2"/>
       <c r="AO52" s="2"/>
-      <c r="AP52" s="2"/>
-      <c r="AQ52" s="2"/>
-      <c r="AR52" s="2"/>
-      <c r="AS52" s="2"/>
-    </row>
-    <row r="53" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -32485,12 +31939,8 @@
       <c r="AM53" s="2"/>
       <c r="AN53" s="2"/>
       <c r="AO53" s="2"/>
-      <c r="AP53" s="2"/>
-      <c r="AQ53" s="2"/>
-      <c r="AR53" s="2"/>
-      <c r="AS53" s="2"/>
-    </row>
-    <row r="54" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -32532,12 +31982,8 @@
       <c r="AM54" s="2"/>
       <c r="AN54" s="2"/>
       <c r="AO54" s="2"/>
-      <c r="AP54" s="2"/>
-      <c r="AQ54" s="2"/>
-      <c r="AR54" s="2"/>
-      <c r="AS54" s="2"/>
-    </row>
-    <row r="55" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -32579,12 +32025,8 @@
       <c r="AM55" s="2"/>
       <c r="AN55" s="2"/>
       <c r="AO55" s="2"/>
-      <c r="AP55" s="2"/>
-      <c r="AQ55" s="2"/>
-      <c r="AR55" s="2"/>
-      <c r="AS55" s="2"/>
-    </row>
-    <row r="56" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -32626,12 +32068,8 @@
       <c r="AM56" s="2"/>
       <c r="AN56" s="2"/>
       <c r="AO56" s="2"/>
-      <c r="AP56" s="2"/>
-      <c r="AQ56" s="2"/>
-      <c r="AR56" s="2"/>
-      <c r="AS56" s="2"/>
-    </row>
-    <row r="57" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -32673,12 +32111,8 @@
       <c r="AM57" s="2"/>
       <c r="AN57" s="2"/>
       <c r="AO57" s="2"/>
-      <c r="AP57" s="2"/>
-      <c r="AQ57" s="2"/>
-      <c r="AR57" s="2"/>
-      <c r="AS57" s="2"/>
-    </row>
-    <row r="58" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -32720,12 +32154,8 @@
       <c r="AM58" s="2"/>
       <c r="AN58" s="2"/>
       <c r="AO58" s="2"/>
-      <c r="AP58" s="2"/>
-      <c r="AQ58" s="2"/>
-      <c r="AR58" s="2"/>
-      <c r="AS58" s="2"/>
-    </row>
-    <row r="59" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -32767,12 +32197,8 @@
       <c r="AM59" s="2"/>
       <c r="AN59" s="2"/>
       <c r="AO59" s="2"/>
-      <c r="AP59" s="2"/>
-      <c r="AQ59" s="2"/>
-      <c r="AR59" s="2"/>
-      <c r="AS59" s="2"/>
-    </row>
-    <row r="60" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -32814,12 +32240,8 @@
       <c r="AM60" s="2"/>
       <c r="AN60" s="2"/>
       <c r="AO60" s="2"/>
-      <c r="AP60" s="2"/>
-      <c r="AQ60" s="2"/>
-      <c r="AR60" s="2"/>
-      <c r="AS60" s="2"/>
-    </row>
-    <row r="61" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -32861,12 +32283,8 @@
       <c r="AM61" s="2"/>
       <c r="AN61" s="2"/>
       <c r="AO61" s="2"/>
-      <c r="AP61" s="2"/>
-      <c r="AQ61" s="2"/>
-      <c r="AR61" s="2"/>
-      <c r="AS61" s="2"/>
-    </row>
-    <row r="62" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -32908,12 +32326,8 @@
       <c r="AM62" s="2"/>
       <c r="AN62" s="2"/>
       <c r="AO62" s="2"/>
-      <c r="AP62" s="2"/>
-      <c r="AQ62" s="2"/>
-      <c r="AR62" s="2"/>
-      <c r="AS62" s="2"/>
-    </row>
-    <row r="63" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -32955,12 +32369,8 @@
       <c r="AM63" s="2"/>
       <c r="AN63" s="2"/>
       <c r="AO63" s="2"/>
-      <c r="AP63" s="2"/>
-      <c r="AQ63" s="2"/>
-      <c r="AR63" s="2"/>
-      <c r="AS63" s="2"/>
-    </row>
-    <row r="64" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -33002,12 +32412,8 @@
       <c r="AM64" s="2"/>
       <c r="AN64" s="2"/>
       <c r="AO64" s="2"/>
-      <c r="AP64" s="2"/>
-      <c r="AQ64" s="2"/>
-      <c r="AR64" s="2"/>
-      <c r="AS64" s="2"/>
-    </row>
-    <row r="65" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -33049,12 +32455,8 @@
       <c r="AM65" s="2"/>
       <c r="AN65" s="2"/>
       <c r="AO65" s="2"/>
-      <c r="AP65" s="2"/>
-      <c r="AQ65" s="2"/>
-      <c r="AR65" s="2"/>
-      <c r="AS65" s="2"/>
-    </row>
-    <row r="66" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -33096,12 +32498,8 @@
       <c r="AM66" s="2"/>
       <c r="AN66" s="2"/>
       <c r="AO66" s="2"/>
-      <c r="AP66" s="2"/>
-      <c r="AQ66" s="2"/>
-      <c r="AR66" s="2"/>
-      <c r="AS66" s="2"/>
-    </row>
-    <row r="67" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -33143,12 +32541,8 @@
       <c r="AM67" s="2"/>
       <c r="AN67" s="2"/>
       <c r="AO67" s="2"/>
-      <c r="AP67" s="2"/>
-      <c r="AQ67" s="2"/>
-      <c r="AR67" s="2"/>
-      <c r="AS67" s="2"/>
-    </row>
-    <row r="68" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -33190,12 +32584,8 @@
       <c r="AM68" s="2"/>
       <c r="AN68" s="2"/>
       <c r="AO68" s="2"/>
-      <c r="AP68" s="2"/>
-      <c r="AQ68" s="2"/>
-      <c r="AR68" s="2"/>
-      <c r="AS68" s="2"/>
-    </row>
-    <row r="69" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -33237,12 +32627,8 @@
       <c r="AM69" s="2"/>
       <c r="AN69" s="2"/>
       <c r="AO69" s="2"/>
-      <c r="AP69" s="2"/>
-      <c r="AQ69" s="2"/>
-      <c r="AR69" s="2"/>
-      <c r="AS69" s="2"/>
-    </row>
-    <row r="70" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -33284,12 +32670,8 @@
       <c r="AM70" s="2"/>
       <c r="AN70" s="2"/>
       <c r="AO70" s="2"/>
-      <c r="AP70" s="2"/>
-      <c r="AQ70" s="2"/>
-      <c r="AR70" s="2"/>
-      <c r="AS70" s="2"/>
-    </row>
-    <row r="71" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -33331,12 +32713,8 @@
       <c r="AM71" s="2"/>
       <c r="AN71" s="2"/>
       <c r="AO71" s="2"/>
-      <c r="AP71" s="2"/>
-      <c r="AQ71" s="2"/>
-      <c r="AR71" s="2"/>
-      <c r="AS71" s="2"/>
-    </row>
-    <row r="72" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -33378,12 +32756,8 @@
       <c r="AM72" s="2"/>
       <c r="AN72" s="2"/>
       <c r="AO72" s="2"/>
-      <c r="AP72" s="2"/>
-      <c r="AQ72" s="2"/>
-      <c r="AR72" s="2"/>
-      <c r="AS72" s="2"/>
-    </row>
-    <row r="73" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -33425,12 +32799,8 @@
       <c r="AM73" s="2"/>
       <c r="AN73" s="2"/>
       <c r="AO73" s="2"/>
-      <c r="AP73" s="2"/>
-      <c r="AQ73" s="2"/>
-      <c r="AR73" s="2"/>
-      <c r="AS73" s="2"/>
-    </row>
-    <row r="74" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -33472,12 +32842,8 @@
       <c r="AM74" s="2"/>
       <c r="AN74" s="2"/>
       <c r="AO74" s="2"/>
-      <c r="AP74" s="2"/>
-      <c r="AQ74" s="2"/>
-      <c r="AR74" s="2"/>
-      <c r="AS74" s="2"/>
-    </row>
-    <row r="75" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -33519,12 +32885,8 @@
       <c r="AM75" s="2"/>
       <c r="AN75" s="2"/>
       <c r="AO75" s="2"/>
-      <c r="AP75" s="2"/>
-      <c r="AQ75" s="2"/>
-      <c r="AR75" s="2"/>
-      <c r="AS75" s="2"/>
-    </row>
-    <row r="76" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -33566,12 +32928,8 @@
       <c r="AM76" s="2"/>
       <c r="AN76" s="2"/>
       <c r="AO76" s="2"/>
-      <c r="AP76" s="2"/>
-      <c r="AQ76" s="2"/>
-      <c r="AR76" s="2"/>
-      <c r="AS76" s="2"/>
-    </row>
-    <row r="77" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -33613,12 +32971,8 @@
       <c r="AM77" s="2"/>
       <c r="AN77" s="2"/>
       <c r="AO77" s="2"/>
-      <c r="AP77" s="2"/>
-      <c r="AQ77" s="2"/>
-      <c r="AR77" s="2"/>
-      <c r="AS77" s="2"/>
-    </row>
-    <row r="78" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -33660,12 +33014,8 @@
       <c r="AM78" s="2"/>
       <c r="AN78" s="2"/>
       <c r="AO78" s="2"/>
-      <c r="AP78" s="2"/>
-      <c r="AQ78" s="2"/>
-      <c r="AR78" s="2"/>
-      <c r="AS78" s="2"/>
-    </row>
-    <row r="79" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -33707,12 +33057,8 @@
       <c r="AM79" s="2"/>
       <c r="AN79" s="2"/>
       <c r="AO79" s="2"/>
-      <c r="AP79" s="2"/>
-      <c r="AQ79" s="2"/>
-      <c r="AR79" s="2"/>
-      <c r="AS79" s="2"/>
-    </row>
-    <row r="80" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -33754,12 +33100,8 @@
       <c r="AM80" s="2"/>
       <c r="AN80" s="2"/>
       <c r="AO80" s="2"/>
-      <c r="AP80" s="2"/>
-      <c r="AQ80" s="2"/>
-      <c r="AR80" s="2"/>
-      <c r="AS80" s="2"/>
-    </row>
-    <row r="81" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -33801,12 +33143,8 @@
       <c r="AM81" s="2"/>
       <c r="AN81" s="2"/>
       <c r="AO81" s="2"/>
-      <c r="AP81" s="2"/>
-      <c r="AQ81" s="2"/>
-      <c r="AR81" s="2"/>
-      <c r="AS81" s="2"/>
-    </row>
-    <row r="82" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -33848,12 +33186,8 @@
       <c r="AM82" s="2"/>
       <c r="AN82" s="2"/>
       <c r="AO82" s="2"/>
-      <c r="AP82" s="2"/>
-      <c r="AQ82" s="2"/>
-      <c r="AR82" s="2"/>
-      <c r="AS82" s="2"/>
-    </row>
-    <row r="83" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -33895,12 +33229,8 @@
       <c r="AM83" s="2"/>
       <c r="AN83" s="2"/>
       <c r="AO83" s="2"/>
-      <c r="AP83" s="2"/>
-      <c r="AQ83" s="2"/>
-      <c r="AR83" s="2"/>
-      <c r="AS83" s="2"/>
-    </row>
-    <row r="84" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -33942,12 +33272,8 @@
       <c r="AM84" s="2"/>
       <c r="AN84" s="2"/>
       <c r="AO84" s="2"/>
-      <c r="AP84" s="2"/>
-      <c r="AQ84" s="2"/>
-      <c r="AR84" s="2"/>
-      <c r="AS84" s="2"/>
-    </row>
-    <row r="85" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -33989,12 +33315,8 @@
       <c r="AM85" s="2"/>
       <c r="AN85" s="2"/>
       <c r="AO85" s="2"/>
-      <c r="AP85" s="2"/>
-      <c r="AQ85" s="2"/>
-      <c r="AR85" s="2"/>
-      <c r="AS85" s="2"/>
-    </row>
-    <row r="86" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -34036,12 +33358,8 @@
       <c r="AM86" s="2"/>
       <c r="AN86" s="2"/>
       <c r="AO86" s="2"/>
-      <c r="AP86" s="2"/>
-      <c r="AQ86" s="2"/>
-      <c r="AR86" s="2"/>
-      <c r="AS86" s="2"/>
-    </row>
-    <row r="87" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -34083,12 +33401,8 @@
       <c r="AM87" s="2"/>
       <c r="AN87" s="2"/>
       <c r="AO87" s="2"/>
-      <c r="AP87" s="2"/>
-      <c r="AQ87" s="2"/>
-      <c r="AR87" s="2"/>
-      <c r="AS87" s="2"/>
-    </row>
-    <row r="88" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -34130,12 +33444,8 @@
       <c r="AM88" s="2"/>
       <c r="AN88" s="2"/>
       <c r="AO88" s="2"/>
-      <c r="AP88" s="2"/>
-      <c r="AQ88" s="2"/>
-      <c r="AR88" s="2"/>
-      <c r="AS88" s="2"/>
-    </row>
-    <row r="89" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -34177,12 +33487,8 @@
       <c r="AM89" s="2"/>
       <c r="AN89" s="2"/>
       <c r="AO89" s="2"/>
-      <c r="AP89" s="2"/>
-      <c r="AQ89" s="2"/>
-      <c r="AR89" s="2"/>
-      <c r="AS89" s="2"/>
-    </row>
-    <row r="90" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -34224,12 +33530,8 @@
       <c r="AM90" s="2"/>
       <c r="AN90" s="2"/>
       <c r="AO90" s="2"/>
-      <c r="AP90" s="2"/>
-      <c r="AQ90" s="2"/>
-      <c r="AR90" s="2"/>
-      <c r="AS90" s="2"/>
-    </row>
-    <row r="91" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -34271,12 +33573,8 @@
       <c r="AM91" s="2"/>
       <c r="AN91" s="2"/>
       <c r="AO91" s="2"/>
-      <c r="AP91" s="2"/>
-      <c r="AQ91" s="2"/>
-      <c r="AR91" s="2"/>
-      <c r="AS91" s="2"/>
-    </row>
-    <row r="92" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -34318,12 +33616,8 @@
       <c r="AM92" s="2"/>
       <c r="AN92" s="2"/>
       <c r="AO92" s="2"/>
-      <c r="AP92" s="2"/>
-      <c r="AQ92" s="2"/>
-      <c r="AR92" s="2"/>
-      <c r="AS92" s="2"/>
-    </row>
-    <row r="93" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -34365,12 +33659,8 @@
       <c r="AM93" s="2"/>
       <c r="AN93" s="2"/>
       <c r="AO93" s="2"/>
-      <c r="AP93" s="2"/>
-      <c r="AQ93" s="2"/>
-      <c r="AR93" s="2"/>
-      <c r="AS93" s="2"/>
-    </row>
-    <row r="94" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -34412,12 +33702,8 @@
       <c r="AM94" s="2"/>
       <c r="AN94" s="2"/>
       <c r="AO94" s="2"/>
-      <c r="AP94" s="2"/>
-      <c r="AQ94" s="2"/>
-      <c r="AR94" s="2"/>
-      <c r="AS94" s="2"/>
-    </row>
-    <row r="95" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -34459,12 +33745,8 @@
       <c r="AM95" s="2"/>
       <c r="AN95" s="2"/>
       <c r="AO95" s="2"/>
-      <c r="AP95" s="2"/>
-      <c r="AQ95" s="2"/>
-      <c r="AR95" s="2"/>
-      <c r="AS95" s="2"/>
-    </row>
-    <row r="96" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -34506,12 +33788,8 @@
       <c r="AM96" s="2"/>
       <c r="AN96" s="2"/>
       <c r="AO96" s="2"/>
-      <c r="AP96" s="2"/>
-      <c r="AQ96" s="2"/>
-      <c r="AR96" s="2"/>
-      <c r="AS96" s="2"/>
-    </row>
-    <row r="97" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -34553,12 +33831,8 @@
       <c r="AM97" s="2"/>
       <c r="AN97" s="2"/>
       <c r="AO97" s="2"/>
-      <c r="AP97" s="2"/>
-      <c r="AQ97" s="2"/>
-      <c r="AR97" s="2"/>
-      <c r="AS97" s="2"/>
-    </row>
-    <row r="98" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -34600,12 +33874,8 @@
       <c r="AM98" s="2"/>
       <c r="AN98" s="2"/>
       <c r="AO98" s="2"/>
-      <c r="AP98" s="2"/>
-      <c r="AQ98" s="2"/>
-      <c r="AR98" s="2"/>
-      <c r="AS98" s="2"/>
-    </row>
-    <row r="99" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -34647,12 +33917,8 @@
       <c r="AM99" s="2"/>
       <c r="AN99" s="2"/>
       <c r="AO99" s="2"/>
-      <c r="AP99" s="2"/>
-      <c r="AQ99" s="2"/>
-      <c r="AR99" s="2"/>
-      <c r="AS99" s="2"/>
-    </row>
-    <row r="100" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -34694,12 +33960,8 @@
       <c r="AM100" s="2"/>
       <c r="AN100" s="2"/>
       <c r="AO100" s="2"/>
-      <c r="AP100" s="2"/>
-      <c r="AQ100" s="2"/>
-      <c r="AR100" s="2"/>
-      <c r="AS100" s="2"/>
-    </row>
-    <row r="101" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -34741,12 +34003,8 @@
       <c r="AM101" s="2"/>
       <c r="AN101" s="2"/>
       <c r="AO101" s="2"/>
-      <c r="AP101" s="2"/>
-      <c r="AQ101" s="2"/>
-      <c r="AR101" s="2"/>
-      <c r="AS101" s="2"/>
-    </row>
-    <row r="102" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -34788,12 +34046,8 @@
       <c r="AM102" s="2"/>
       <c r="AN102" s="2"/>
       <c r="AO102" s="2"/>
-      <c r="AP102" s="2"/>
-      <c r="AQ102" s="2"/>
-      <c r="AR102" s="2"/>
-      <c r="AS102" s="2"/>
-    </row>
-    <row r="103" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -34835,12 +34089,8 @@
       <c r="AM103" s="2"/>
       <c r="AN103" s="2"/>
       <c r="AO103" s="2"/>
-      <c r="AP103" s="2"/>
-      <c r="AQ103" s="2"/>
-      <c r="AR103" s="2"/>
-      <c r="AS103" s="2"/>
-    </row>
-    <row r="104" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -34882,12 +34132,8 @@
       <c r="AM104" s="2"/>
       <c r="AN104" s="2"/>
       <c r="AO104" s="2"/>
-      <c r="AP104" s="2"/>
-      <c r="AQ104" s="2"/>
-      <c r="AR104" s="2"/>
-      <c r="AS104" s="2"/>
-    </row>
-    <row r="105" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -34929,12 +34175,8 @@
       <c r="AM105" s="2"/>
       <c r="AN105" s="2"/>
       <c r="AO105" s="2"/>
-      <c r="AP105" s="2"/>
-      <c r="AQ105" s="2"/>
-      <c r="AR105" s="2"/>
-      <c r="AS105" s="2"/>
-    </row>
-    <row r="106" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -34976,12 +34218,8 @@
       <c r="AM106" s="2"/>
       <c r="AN106" s="2"/>
       <c r="AO106" s="2"/>
-      <c r="AP106" s="2"/>
-      <c r="AQ106" s="2"/>
-      <c r="AR106" s="2"/>
-      <c r="AS106" s="2"/>
-    </row>
-    <row r="107" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -35023,12 +34261,8 @@
       <c r="AM107" s="2"/>
       <c r="AN107" s="2"/>
       <c r="AO107" s="2"/>
-      <c r="AP107" s="2"/>
-      <c r="AQ107" s="2"/>
-      <c r="AR107" s="2"/>
-      <c r="AS107" s="2"/>
-    </row>
-    <row r="108" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -35070,12 +34304,8 @@
       <c r="AM108" s="2"/>
       <c r="AN108" s="2"/>
       <c r="AO108" s="2"/>
-      <c r="AP108" s="2"/>
-      <c r="AQ108" s="2"/>
-      <c r="AR108" s="2"/>
-      <c r="AS108" s="2"/>
-    </row>
-    <row r="109" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -35117,12 +34347,8 @@
       <c r="AM109" s="2"/>
       <c r="AN109" s="2"/>
       <c r="AO109" s="2"/>
-      <c r="AP109" s="2"/>
-      <c r="AQ109" s="2"/>
-      <c r="AR109" s="2"/>
-      <c r="AS109" s="2"/>
-    </row>
-    <row r="110" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -35164,12 +34390,8 @@
       <c r="AM110" s="2"/>
       <c r="AN110" s="2"/>
       <c r="AO110" s="2"/>
-      <c r="AP110" s="2"/>
-      <c r="AQ110" s="2"/>
-      <c r="AR110" s="2"/>
-      <c r="AS110" s="2"/>
-    </row>
-    <row r="111" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -35211,12 +34433,8 @@
       <c r="AM111" s="2"/>
       <c r="AN111" s="2"/>
       <c r="AO111" s="2"/>
-      <c r="AP111" s="2"/>
-      <c r="AQ111" s="2"/>
-      <c r="AR111" s="2"/>
-      <c r="AS111" s="2"/>
-    </row>
-    <row r="112" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -35258,12 +34476,8 @@
       <c r="AM112" s="2"/>
       <c r="AN112" s="2"/>
       <c r="AO112" s="2"/>
-      <c r="AP112" s="2"/>
-      <c r="AQ112" s="2"/>
-      <c r="AR112" s="2"/>
-      <c r="AS112" s="2"/>
-    </row>
-    <row r="113" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -35305,12 +34519,8 @@
       <c r="AM113" s="2"/>
       <c r="AN113" s="2"/>
       <c r="AO113" s="2"/>
-      <c r="AP113" s="2"/>
-      <c r="AQ113" s="2"/>
-      <c r="AR113" s="2"/>
-      <c r="AS113" s="2"/>
-    </row>
-    <row r="114" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -35352,12 +34562,8 @@
       <c r="AM114" s="2"/>
       <c r="AN114" s="2"/>
       <c r="AO114" s="2"/>
-      <c r="AP114" s="2"/>
-      <c r="AQ114" s="2"/>
-      <c r="AR114" s="2"/>
-      <c r="AS114" s="2"/>
-    </row>
-    <row r="115" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -35399,12 +34605,8 @@
       <c r="AM115" s="2"/>
       <c r="AN115" s="2"/>
       <c r="AO115" s="2"/>
-      <c r="AP115" s="2"/>
-      <c r="AQ115" s="2"/>
-      <c r="AR115" s="2"/>
-      <c r="AS115" s="2"/>
-    </row>
-    <row r="116" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -35446,12 +34648,8 @@
       <c r="AM116" s="2"/>
       <c r="AN116" s="2"/>
       <c r="AO116" s="2"/>
-      <c r="AP116" s="2"/>
-      <c r="AQ116" s="2"/>
-      <c r="AR116" s="2"/>
-      <c r="AS116" s="2"/>
-    </row>
-    <row r="117" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -35493,12 +34691,8 @@
       <c r="AM117" s="2"/>
       <c r="AN117" s="2"/>
       <c r="AO117" s="2"/>
-      <c r="AP117" s="2"/>
-      <c r="AQ117" s="2"/>
-      <c r="AR117" s="2"/>
-      <c r="AS117" s="2"/>
-    </row>
-    <row r="118" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -35540,12 +34734,8 @@
       <c r="AM118" s="2"/>
       <c r="AN118" s="2"/>
       <c r="AO118" s="2"/>
-      <c r="AP118" s="2"/>
-      <c r="AQ118" s="2"/>
-      <c r="AR118" s="2"/>
-      <c r="AS118" s="2"/>
-    </row>
-    <row r="119" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -35587,12 +34777,8 @@
       <c r="AM119" s="2"/>
       <c r="AN119" s="2"/>
       <c r="AO119" s="2"/>
-      <c r="AP119" s="2"/>
-      <c r="AQ119" s="2"/>
-      <c r="AR119" s="2"/>
-      <c r="AS119" s="2"/>
-    </row>
-    <row r="120" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -35634,12 +34820,8 @@
       <c r="AM120" s="2"/>
       <c r="AN120" s="2"/>
       <c r="AO120" s="2"/>
-      <c r="AP120" s="2"/>
-      <c r="AQ120" s="2"/>
-      <c r="AR120" s="2"/>
-      <c r="AS120" s="2"/>
-    </row>
-    <row r="121" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -35681,12 +34863,8 @@
       <c r="AM121" s="2"/>
       <c r="AN121" s="2"/>
       <c r="AO121" s="2"/>
-      <c r="AP121" s="2"/>
-      <c r="AQ121" s="2"/>
-      <c r="AR121" s="2"/>
-      <c r="AS121" s="2"/>
-    </row>
-    <row r="122" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -35728,12 +34906,8 @@
       <c r="AM122" s="2"/>
       <c r="AN122" s="2"/>
       <c r="AO122" s="2"/>
-      <c r="AP122" s="2"/>
-      <c r="AQ122" s="2"/>
-      <c r="AR122" s="2"/>
-      <c r="AS122" s="2"/>
-    </row>
-    <row r="123" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -35775,12 +34949,8 @@
       <c r="AM123" s="2"/>
       <c r="AN123" s="2"/>
       <c r="AO123" s="2"/>
-      <c r="AP123" s="2"/>
-      <c r="AQ123" s="2"/>
-      <c r="AR123" s="2"/>
-      <c r="AS123" s="2"/>
-    </row>
-    <row r="124" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -35822,12 +34992,8 @@
       <c r="AM124" s="2"/>
       <c r="AN124" s="2"/>
       <c r="AO124" s="2"/>
-      <c r="AP124" s="2"/>
-      <c r="AQ124" s="2"/>
-      <c r="AR124" s="2"/>
-      <c r="AS124" s="2"/>
-    </row>
-    <row r="125" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -35869,12 +35035,8 @@
       <c r="AM125" s="2"/>
       <c r="AN125" s="2"/>
       <c r="AO125" s="2"/>
-      <c r="AP125" s="2"/>
-      <c r="AQ125" s="2"/>
-      <c r="AR125" s="2"/>
-      <c r="AS125" s="2"/>
-    </row>
-    <row r="126" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -35916,12 +35078,8 @@
       <c r="AM126" s="2"/>
       <c r="AN126" s="2"/>
       <c r="AO126" s="2"/>
-      <c r="AP126" s="2"/>
-      <c r="AQ126" s="2"/>
-      <c r="AR126" s="2"/>
-      <c r="AS126" s="2"/>
-    </row>
-    <row r="127" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -35963,12 +35121,8 @@
       <c r="AM127" s="2"/>
       <c r="AN127" s="2"/>
       <c r="AO127" s="2"/>
-      <c r="AP127" s="2"/>
-      <c r="AQ127" s="2"/>
-      <c r="AR127" s="2"/>
-      <c r="AS127" s="2"/>
-    </row>
-    <row r="128" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -36010,12 +35164,8 @@
       <c r="AM128" s="2"/>
       <c r="AN128" s="2"/>
       <c r="AO128" s="2"/>
-      <c r="AP128" s="2"/>
-      <c r="AQ128" s="2"/>
-      <c r="AR128" s="2"/>
-      <c r="AS128" s="2"/>
-    </row>
-    <row r="129" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -36057,12 +35207,8 @@
       <c r="AM129" s="2"/>
       <c r="AN129" s="2"/>
       <c r="AO129" s="2"/>
-      <c r="AP129" s="2"/>
-      <c r="AQ129" s="2"/>
-      <c r="AR129" s="2"/>
-      <c r="AS129" s="2"/>
-    </row>
-    <row r="130" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -36104,12 +35250,8 @@
       <c r="AM130" s="2"/>
       <c r="AN130" s="2"/>
       <c r="AO130" s="2"/>
-      <c r="AP130" s="2"/>
-      <c r="AQ130" s="2"/>
-      <c r="AR130" s="2"/>
-      <c r="AS130" s="2"/>
-    </row>
-    <row r="131" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -36151,12 +35293,8 @@
       <c r="AM131" s="2"/>
       <c r="AN131" s="2"/>
       <c r="AO131" s="2"/>
-      <c r="AP131" s="2"/>
-      <c r="AQ131" s="2"/>
-      <c r="AR131" s="2"/>
-      <c r="AS131" s="2"/>
-    </row>
-    <row r="132" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -36198,12 +35336,8 @@
       <c r="AM132" s="2"/>
       <c r="AN132" s="2"/>
       <c r="AO132" s="2"/>
-      <c r="AP132" s="2"/>
-      <c r="AQ132" s="2"/>
-      <c r="AR132" s="2"/>
-      <c r="AS132" s="2"/>
-    </row>
-    <row r="133" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -36245,12 +35379,8 @@
       <c r="AM133" s="2"/>
       <c r="AN133" s="2"/>
       <c r="AO133" s="2"/>
-      <c r="AP133" s="2"/>
-      <c r="AQ133" s="2"/>
-      <c r="AR133" s="2"/>
-      <c r="AS133" s="2"/>
-    </row>
-    <row r="134" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -36292,12 +35422,8 @@
       <c r="AM134" s="2"/>
       <c r="AN134" s="2"/>
       <c r="AO134" s="2"/>
-      <c r="AP134" s="2"/>
-      <c r="AQ134" s="2"/>
-      <c r="AR134" s="2"/>
-      <c r="AS134" s="2"/>
-    </row>
-    <row r="135" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -36339,12 +35465,8 @@
       <c r="AM135" s="2"/>
       <c r="AN135" s="2"/>
       <c r="AO135" s="2"/>
-      <c r="AP135" s="2"/>
-      <c r="AQ135" s="2"/>
-      <c r="AR135" s="2"/>
-      <c r="AS135" s="2"/>
-    </row>
-    <row r="136" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -36386,12 +35508,8 @@
       <c r="AM136" s="2"/>
       <c r="AN136" s="2"/>
       <c r="AO136" s="2"/>
-      <c r="AP136" s="2"/>
-      <c r="AQ136" s="2"/>
-      <c r="AR136" s="2"/>
-      <c r="AS136" s="2"/>
-    </row>
-    <row r="137" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -36433,12 +35551,8 @@
       <c r="AM137" s="2"/>
       <c r="AN137" s="2"/>
       <c r="AO137" s="2"/>
-      <c r="AP137" s="2"/>
-      <c r="AQ137" s="2"/>
-      <c r="AR137" s="2"/>
-      <c r="AS137" s="2"/>
-    </row>
-    <row r="138" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -36480,12 +35594,8 @@
       <c r="AM138" s="2"/>
       <c r="AN138" s="2"/>
       <c r="AO138" s="2"/>
-      <c r="AP138" s="2"/>
-      <c r="AQ138" s="2"/>
-      <c r="AR138" s="2"/>
-      <c r="AS138" s="2"/>
-    </row>
-    <row r="139" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -36527,12 +35637,8 @@
       <c r="AM139" s="2"/>
       <c r="AN139" s="2"/>
       <c r="AO139" s="2"/>
-      <c r="AP139" s="2"/>
-      <c r="AQ139" s="2"/>
-      <c r="AR139" s="2"/>
-      <c r="AS139" s="2"/>
-    </row>
-    <row r="140" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -36574,12 +35680,8 @@
       <c r="AM140" s="2"/>
       <c r="AN140" s="2"/>
       <c r="AO140" s="2"/>
-      <c r="AP140" s="2"/>
-      <c r="AQ140" s="2"/>
-      <c r="AR140" s="2"/>
-      <c r="AS140" s="2"/>
-    </row>
-    <row r="141" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -36621,12 +35723,8 @@
       <c r="AM141" s="2"/>
       <c r="AN141" s="2"/>
       <c r="AO141" s="2"/>
-      <c r="AP141" s="2"/>
-      <c r="AQ141" s="2"/>
-      <c r="AR141" s="2"/>
-      <c r="AS141" s="2"/>
-    </row>
-    <row r="142" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -36668,12 +35766,8 @@
       <c r="AM142" s="2"/>
       <c r="AN142" s="2"/>
       <c r="AO142" s="2"/>
-      <c r="AP142" s="2"/>
-      <c r="AQ142" s="2"/>
-      <c r="AR142" s="2"/>
-      <c r="AS142" s="2"/>
-    </row>
-    <row r="143" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -36715,12 +35809,8 @@
       <c r="AM143" s="2"/>
       <c r="AN143" s="2"/>
       <c r="AO143" s="2"/>
-      <c r="AP143" s="2"/>
-      <c r="AQ143" s="2"/>
-      <c r="AR143" s="2"/>
-      <c r="AS143" s="2"/>
-    </row>
-    <row r="144" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -36762,12 +35852,8 @@
       <c r="AM144" s="2"/>
       <c r="AN144" s="2"/>
       <c r="AO144" s="2"/>
-      <c r="AP144" s="2"/>
-      <c r="AQ144" s="2"/>
-      <c r="AR144" s="2"/>
-      <c r="AS144" s="2"/>
-    </row>
-    <row r="145" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -36809,12 +35895,8 @@
       <c r="AM145" s="2"/>
       <c r="AN145" s="2"/>
       <c r="AO145" s="2"/>
-      <c r="AP145" s="2"/>
-      <c r="AQ145" s="2"/>
-      <c r="AR145" s="2"/>
-      <c r="AS145" s="2"/>
-    </row>
-    <row r="146" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -36856,12 +35938,8 @@
       <c r="AM146" s="2"/>
       <c r="AN146" s="2"/>
       <c r="AO146" s="2"/>
-      <c r="AP146" s="2"/>
-      <c r="AQ146" s="2"/>
-      <c r="AR146" s="2"/>
-      <c r="AS146" s="2"/>
-    </row>
-    <row r="147" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -36903,12 +35981,8 @@
       <c r="AM147" s="2"/>
       <c r="AN147" s="2"/>
       <c r="AO147" s="2"/>
-      <c r="AP147" s="2"/>
-      <c r="AQ147" s="2"/>
-      <c r="AR147" s="2"/>
-      <c r="AS147" s="2"/>
-    </row>
-    <row r="148" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -36950,12 +36024,8 @@
       <c r="AM148" s="2"/>
       <c r="AN148" s="2"/>
       <c r="AO148" s="2"/>
-      <c r="AP148" s="2"/>
-      <c r="AQ148" s="2"/>
-      <c r="AR148" s="2"/>
-      <c r="AS148" s="2"/>
-    </row>
-    <row r="149" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -36997,12 +36067,8 @@
       <c r="AM149" s="2"/>
       <c r="AN149" s="2"/>
       <c r="AO149" s="2"/>
-      <c r="AP149" s="2"/>
-      <c r="AQ149" s="2"/>
-      <c r="AR149" s="2"/>
-      <c r="AS149" s="2"/>
-    </row>
-    <row r="150" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -37044,12 +36110,8 @@
       <c r="AM150" s="2"/>
       <c r="AN150" s="2"/>
       <c r="AO150" s="2"/>
-      <c r="AP150" s="2"/>
-      <c r="AQ150" s="2"/>
-      <c r="AR150" s="2"/>
-      <c r="AS150" s="2"/>
-    </row>
-    <row r="151" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -37091,12 +36153,8 @@
       <c r="AM151" s="2"/>
       <c r="AN151" s="2"/>
       <c r="AO151" s="2"/>
-      <c r="AP151" s="2"/>
-      <c r="AQ151" s="2"/>
-      <c r="AR151" s="2"/>
-      <c r="AS151" s="2"/>
-    </row>
-    <row r="152" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -37138,12 +36196,8 @@
       <c r="AM152" s="2"/>
       <c r="AN152" s="2"/>
       <c r="AO152" s="2"/>
-      <c r="AP152" s="2"/>
-      <c r="AQ152" s="2"/>
-      <c r="AR152" s="2"/>
-      <c r="AS152" s="2"/>
-    </row>
-    <row r="153" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -37185,12 +36239,8 @@
       <c r="AM153" s="2"/>
       <c r="AN153" s="2"/>
       <c r="AO153" s="2"/>
-      <c r="AP153" s="2"/>
-      <c r="AQ153" s="2"/>
-      <c r="AR153" s="2"/>
-      <c r="AS153" s="2"/>
-    </row>
-    <row r="154" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -37232,12 +36282,8 @@
       <c r="AM154" s="2"/>
       <c r="AN154" s="2"/>
       <c r="AO154" s="2"/>
-      <c r="AP154" s="2"/>
-      <c r="AQ154" s="2"/>
-      <c r="AR154" s="2"/>
-      <c r="AS154" s="2"/>
-    </row>
-    <row r="155" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -37279,12 +36325,8 @@
       <c r="AM155" s="2"/>
       <c r="AN155" s="2"/>
       <c r="AO155" s="2"/>
-      <c r="AP155" s="2"/>
-      <c r="AQ155" s="2"/>
-      <c r="AR155" s="2"/>
-      <c r="AS155" s="2"/>
-    </row>
-    <row r="156" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -37326,12 +36368,8 @@
       <c r="AM156" s="2"/>
       <c r="AN156" s="2"/>
       <c r="AO156" s="2"/>
-      <c r="AP156" s="2"/>
-      <c r="AQ156" s="2"/>
-      <c r="AR156" s="2"/>
-      <c r="AS156" s="2"/>
-    </row>
-    <row r="157" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -37373,12 +36411,8 @@
       <c r="AM157" s="2"/>
       <c r="AN157" s="2"/>
       <c r="AO157" s="2"/>
-      <c r="AP157" s="2"/>
-      <c r="AQ157" s="2"/>
-      <c r="AR157" s="2"/>
-      <c r="AS157" s="2"/>
-    </row>
-    <row r="158" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -37420,12 +36454,8 @@
       <c r="AM158" s="2"/>
       <c r="AN158" s="2"/>
       <c r="AO158" s="2"/>
-      <c r="AP158" s="2"/>
-      <c r="AQ158" s="2"/>
-      <c r="AR158" s="2"/>
-      <c r="AS158" s="2"/>
-    </row>
-    <row r="159" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -37467,12 +36497,8 @@
       <c r="AM159" s="2"/>
       <c r="AN159" s="2"/>
       <c r="AO159" s="2"/>
-      <c r="AP159" s="2"/>
-      <c r="AQ159" s="2"/>
-      <c r="AR159" s="2"/>
-      <c r="AS159" s="2"/>
-    </row>
-    <row r="160" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -37514,12 +36540,8 @@
       <c r="AM160" s="2"/>
       <c r="AN160" s="2"/>
       <c r="AO160" s="2"/>
-      <c r="AP160" s="2"/>
-      <c r="AQ160" s="2"/>
-      <c r="AR160" s="2"/>
-      <c r="AS160" s="2"/>
-    </row>
-    <row r="161" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -37561,12 +36583,8 @@
       <c r="AM161" s="2"/>
       <c r="AN161" s="2"/>
       <c r="AO161" s="2"/>
-      <c r="AP161" s="2"/>
-      <c r="AQ161" s="2"/>
-      <c r="AR161" s="2"/>
-      <c r="AS161" s="2"/>
-    </row>
-    <row r="162" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -37608,12 +36626,8 @@
       <c r="AM162" s="2"/>
       <c r="AN162" s="2"/>
       <c r="AO162" s="2"/>
-      <c r="AP162" s="2"/>
-      <c r="AQ162" s="2"/>
-      <c r="AR162" s="2"/>
-      <c r="AS162" s="2"/>
-    </row>
-    <row r="163" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -37655,12 +36669,8 @@
       <c r="AM163" s="2"/>
       <c r="AN163" s="2"/>
       <c r="AO163" s="2"/>
-      <c r="AP163" s="2"/>
-      <c r="AQ163" s="2"/>
-      <c r="AR163" s="2"/>
-      <c r="AS163" s="2"/>
-    </row>
-    <row r="164" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -37702,12 +36712,8 @@
       <c r="AM164" s="2"/>
       <c r="AN164" s="2"/>
       <c r="AO164" s="2"/>
-      <c r="AP164" s="2"/>
-      <c r="AQ164" s="2"/>
-      <c r="AR164" s="2"/>
-      <c r="AS164" s="2"/>
-    </row>
-    <row r="165" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -37749,12 +36755,8 @@
       <c r="AM165" s="2"/>
       <c r="AN165" s="2"/>
       <c r="AO165" s="2"/>
-      <c r="AP165" s="2"/>
-      <c r="AQ165" s="2"/>
-      <c r="AR165" s="2"/>
-      <c r="AS165" s="2"/>
-    </row>
-    <row r="166" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -37796,12 +36798,8 @@
       <c r="AM166" s="2"/>
       <c r="AN166" s="2"/>
       <c r="AO166" s="2"/>
-      <c r="AP166" s="2"/>
-      <c r="AQ166" s="2"/>
-      <c r="AR166" s="2"/>
-      <c r="AS166" s="2"/>
-    </row>
-    <row r="167" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -37843,12 +36841,8 @@
       <c r="AM167" s="2"/>
       <c r="AN167" s="2"/>
       <c r="AO167" s="2"/>
-      <c r="AP167" s="2"/>
-      <c r="AQ167" s="2"/>
-      <c r="AR167" s="2"/>
-      <c r="AS167" s="2"/>
-    </row>
-    <row r="168" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -37890,12 +36884,8 @@
       <c r="AM168" s="2"/>
       <c r="AN168" s="2"/>
       <c r="AO168" s="2"/>
-      <c r="AP168" s="2"/>
-      <c r="AQ168" s="2"/>
-      <c r="AR168" s="2"/>
-      <c r="AS168" s="2"/>
-    </row>
-    <row r="169" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -37937,12 +36927,8 @@
       <c r="AM169" s="2"/>
       <c r="AN169" s="2"/>
       <c r="AO169" s="2"/>
-      <c r="AP169" s="2"/>
-      <c r="AQ169" s="2"/>
-      <c r="AR169" s="2"/>
-      <c r="AS169" s="2"/>
-    </row>
-    <row r="170" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -37984,12 +36970,8 @@
       <c r="AM170" s="2"/>
       <c r="AN170" s="2"/>
       <c r="AO170" s="2"/>
-      <c r="AP170" s="2"/>
-      <c r="AQ170" s="2"/>
-      <c r="AR170" s="2"/>
-      <c r="AS170" s="2"/>
-    </row>
-    <row r="171" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -38031,12 +37013,8 @@
       <c r="AM171" s="2"/>
       <c r="AN171" s="2"/>
       <c r="AO171" s="2"/>
-      <c r="AP171" s="2"/>
-      <c r="AQ171" s="2"/>
-      <c r="AR171" s="2"/>
-      <c r="AS171" s="2"/>
-    </row>
-    <row r="172" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -38078,12 +37056,8 @@
       <c r="AM172" s="2"/>
       <c r="AN172" s="2"/>
       <c r="AO172" s="2"/>
-      <c r="AP172" s="2"/>
-      <c r="AQ172" s="2"/>
-      <c r="AR172" s="2"/>
-      <c r="AS172" s="2"/>
-    </row>
-    <row r="173" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -38125,12 +37099,8 @@
       <c r="AM173" s="2"/>
       <c r="AN173" s="2"/>
       <c r="AO173" s="2"/>
-      <c r="AP173" s="2"/>
-      <c r="AQ173" s="2"/>
-      <c r="AR173" s="2"/>
-      <c r="AS173" s="2"/>
-    </row>
-    <row r="174" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -38172,12 +37142,8 @@
       <c r="AM174" s="2"/>
       <c r="AN174" s="2"/>
       <c r="AO174" s="2"/>
-      <c r="AP174" s="2"/>
-      <c r="AQ174" s="2"/>
-      <c r="AR174" s="2"/>
-      <c r="AS174" s="2"/>
-    </row>
-    <row r="175" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -38219,12 +37185,8 @@
       <c r="AM175" s="2"/>
       <c r="AN175" s="2"/>
       <c r="AO175" s="2"/>
-      <c r="AP175" s="2"/>
-      <c r="AQ175" s="2"/>
-      <c r="AR175" s="2"/>
-      <c r="AS175" s="2"/>
-    </row>
-    <row r="176" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -38266,12 +37228,8 @@
       <c r="AM176" s="2"/>
       <c r="AN176" s="2"/>
       <c r="AO176" s="2"/>
-      <c r="AP176" s="2"/>
-      <c r="AQ176" s="2"/>
-      <c r="AR176" s="2"/>
-      <c r="AS176" s="2"/>
-    </row>
-    <row r="177" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -38313,12 +37271,8 @@
       <c r="AM177" s="2"/>
       <c r="AN177" s="2"/>
       <c r="AO177" s="2"/>
-      <c r="AP177" s="2"/>
-      <c r="AQ177" s="2"/>
-      <c r="AR177" s="2"/>
-      <c r="AS177" s="2"/>
-    </row>
-    <row r="178" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -38360,12 +37314,8 @@
       <c r="AM178" s="2"/>
       <c r="AN178" s="2"/>
       <c r="AO178" s="2"/>
-      <c r="AP178" s="2"/>
-      <c r="AQ178" s="2"/>
-      <c r="AR178" s="2"/>
-      <c r="AS178" s="2"/>
-    </row>
-    <row r="179" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -38407,12 +37357,8 @@
       <c r="AM179" s="2"/>
       <c r="AN179" s="2"/>
       <c r="AO179" s="2"/>
-      <c r="AP179" s="2"/>
-      <c r="AQ179" s="2"/>
-      <c r="AR179" s="2"/>
-      <c r="AS179" s="2"/>
-    </row>
-    <row r="180" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -38454,12 +37400,8 @@
       <c r="AM180" s="2"/>
       <c r="AN180" s="2"/>
       <c r="AO180" s="2"/>
-      <c r="AP180" s="2"/>
-      <c r="AQ180" s="2"/>
-      <c r="AR180" s="2"/>
-      <c r="AS180" s="2"/>
-    </row>
-    <row r="181" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -38501,12 +37443,8 @@
       <c r="AM181" s="2"/>
       <c r="AN181" s="2"/>
       <c r="AO181" s="2"/>
-      <c r="AP181" s="2"/>
-      <c r="AQ181" s="2"/>
-      <c r="AR181" s="2"/>
-      <c r="AS181" s="2"/>
-    </row>
-    <row r="182" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -38548,12 +37486,8 @@
       <c r="AM182" s="2"/>
       <c r="AN182" s="2"/>
       <c r="AO182" s="2"/>
-      <c r="AP182" s="2"/>
-      <c r="AQ182" s="2"/>
-      <c r="AR182" s="2"/>
-      <c r="AS182" s="2"/>
-    </row>
-    <row r="183" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -38595,12 +37529,8 @@
       <c r="AM183" s="2"/>
       <c r="AN183" s="2"/>
       <c r="AO183" s="2"/>
-      <c r="AP183" s="2"/>
-      <c r="AQ183" s="2"/>
-      <c r="AR183" s="2"/>
-      <c r="AS183" s="2"/>
-    </row>
-    <row r="184" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -38642,12 +37572,8 @@
       <c r="AM184" s="2"/>
       <c r="AN184" s="2"/>
       <c r="AO184" s="2"/>
-      <c r="AP184" s="2"/>
-      <c r="AQ184" s="2"/>
-      <c r="AR184" s="2"/>
-      <c r="AS184" s="2"/>
-    </row>
-    <row r="185" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -38689,12 +37615,8 @@
       <c r="AM185" s="2"/>
       <c r="AN185" s="2"/>
       <c r="AO185" s="2"/>
-      <c r="AP185" s="2"/>
-      <c r="AQ185" s="2"/>
-      <c r="AR185" s="2"/>
-      <c r="AS185" s="2"/>
-    </row>
-    <row r="186" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -38736,12 +37658,8 @@
       <c r="AM186" s="2"/>
       <c r="AN186" s="2"/>
       <c r="AO186" s="2"/>
-      <c r="AP186" s="2"/>
-      <c r="AQ186" s="2"/>
-      <c r="AR186" s="2"/>
-      <c r="AS186" s="2"/>
-    </row>
-    <row r="187" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -38783,12 +37701,8 @@
       <c r="AM187" s="2"/>
       <c r="AN187" s="2"/>
       <c r="AO187" s="2"/>
-      <c r="AP187" s="2"/>
-      <c r="AQ187" s="2"/>
-      <c r="AR187" s="2"/>
-      <c r="AS187" s="2"/>
-    </row>
-    <row r="188" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -38830,12 +37744,8 @@
       <c r="AM188" s="2"/>
       <c r="AN188" s="2"/>
       <c r="AO188" s="2"/>
-      <c r="AP188" s="2"/>
-      <c r="AQ188" s="2"/>
-      <c r="AR188" s="2"/>
-      <c r="AS188" s="2"/>
-    </row>
-    <row r="189" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -38877,12 +37787,8 @@
       <c r="AM189" s="2"/>
       <c r="AN189" s="2"/>
       <c r="AO189" s="2"/>
-      <c r="AP189" s="2"/>
-      <c r="AQ189" s="2"/>
-      <c r="AR189" s="2"/>
-      <c r="AS189" s="2"/>
-    </row>
-    <row r="190" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -38924,12 +37830,8 @@
       <c r="AM190" s="2"/>
       <c r="AN190" s="2"/>
       <c r="AO190" s="2"/>
-      <c r="AP190" s="2"/>
-      <c r="AQ190" s="2"/>
-      <c r="AR190" s="2"/>
-      <c r="AS190" s="2"/>
-    </row>
-    <row r="191" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -38971,12 +37873,8 @@
       <c r="AM191" s="2"/>
       <c r="AN191" s="2"/>
       <c r="AO191" s="2"/>
-      <c r="AP191" s="2"/>
-      <c r="AQ191" s="2"/>
-      <c r="AR191" s="2"/>
-      <c r="AS191" s="2"/>
-    </row>
-    <row r="192" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -39018,12 +37916,8 @@
       <c r="AM192" s="2"/>
       <c r="AN192" s="2"/>
       <c r="AO192" s="2"/>
-      <c r="AP192" s="2"/>
-      <c r="AQ192" s="2"/>
-      <c r="AR192" s="2"/>
-      <c r="AS192" s="2"/>
-    </row>
-    <row r="193" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -39065,12 +37959,8 @@
       <c r="AM193" s="2"/>
       <c r="AN193" s="2"/>
       <c r="AO193" s="2"/>
-      <c r="AP193" s="2"/>
-      <c r="AQ193" s="2"/>
-      <c r="AR193" s="2"/>
-      <c r="AS193" s="2"/>
-    </row>
-    <row r="194" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -39112,12 +38002,8 @@
       <c r="AM194" s="2"/>
       <c r="AN194" s="2"/>
       <c r="AO194" s="2"/>
-      <c r="AP194" s="2"/>
-      <c r="AQ194" s="2"/>
-      <c r="AR194" s="2"/>
-      <c r="AS194" s="2"/>
-    </row>
-    <row r="195" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -39159,12 +38045,8 @@
       <c r="AM195" s="2"/>
       <c r="AN195" s="2"/>
       <c r="AO195" s="2"/>
-      <c r="AP195" s="2"/>
-      <c r="AQ195" s="2"/>
-      <c r="AR195" s="2"/>
-      <c r="AS195" s="2"/>
-    </row>
-    <row r="196" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -39206,12 +38088,8 @@
       <c r="AM196" s="2"/>
       <c r="AN196" s="2"/>
       <c r="AO196" s="2"/>
-      <c r="AP196" s="2"/>
-      <c r="AQ196" s="2"/>
-      <c r="AR196" s="2"/>
-      <c r="AS196" s="2"/>
-    </row>
-    <row r="197" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -39253,12 +38131,8 @@
       <c r="AM197" s="2"/>
       <c r="AN197" s="2"/>
       <c r="AO197" s="2"/>
-      <c r="AP197" s="2"/>
-      <c r="AQ197" s="2"/>
-      <c r="AR197" s="2"/>
-      <c r="AS197" s="2"/>
-    </row>
-    <row r="198" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -39300,12 +38174,8 @@
       <c r="AM198" s="2"/>
       <c r="AN198" s="2"/>
       <c r="AO198" s="2"/>
-      <c r="AP198" s="2"/>
-      <c r="AQ198" s="2"/>
-      <c r="AR198" s="2"/>
-      <c r="AS198" s="2"/>
-    </row>
-    <row r="199" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -39347,12 +38217,8 @@
       <c r="AM199" s="2"/>
       <c r="AN199" s="2"/>
       <c r="AO199" s="2"/>
-      <c r="AP199" s="2"/>
-      <c r="AQ199" s="2"/>
-      <c r="AR199" s="2"/>
-      <c r="AS199" s="2"/>
-    </row>
-    <row r="200" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -39394,12 +38260,8 @@
       <c r="AM200" s="2"/>
       <c r="AN200" s="2"/>
       <c r="AO200" s="2"/>
-      <c r="AP200" s="2"/>
-      <c r="AQ200" s="2"/>
-      <c r="AR200" s="2"/>
-      <c r="AS200" s="2"/>
-    </row>
-    <row r="201" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -39441,12 +38303,8 @@
       <c r="AM201" s="2"/>
       <c r="AN201" s="2"/>
       <c r="AO201" s="2"/>
-      <c r="AP201" s="2"/>
-      <c r="AQ201" s="2"/>
-      <c r="AR201" s="2"/>
-      <c r="AS201" s="2"/>
-    </row>
-    <row r="202" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -39488,12 +38346,8 @@
       <c r="AM202" s="2"/>
       <c r="AN202" s="2"/>
       <c r="AO202" s="2"/>
-      <c r="AP202" s="2"/>
-      <c r="AQ202" s="2"/>
-      <c r="AR202" s="2"/>
-      <c r="AS202" s="2"/>
-    </row>
-    <row r="203" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -39535,12 +38389,8 @@
       <c r="AM203" s="2"/>
       <c r="AN203" s="2"/>
       <c r="AO203" s="2"/>
-      <c r="AP203" s="2"/>
-      <c r="AQ203" s="2"/>
-      <c r="AR203" s="2"/>
-      <c r="AS203" s="2"/>
-    </row>
-    <row r="204" spans="1:45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -39582,114 +38432,63 @@
       <c r="AM204" s="2"/>
       <c r="AN204" s="2"/>
       <c r="AO204" s="2"/>
-      <c r="AP204" s="2"/>
-      <c r="AQ204" s="2"/>
-      <c r="AR204" s="2"/>
-      <c r="AS204" s="2"/>
-    </row>
-    <row r="205" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-      <c r="Q205" s="2"/>
-      <c r="R205" s="2"/>
-      <c r="S205" s="2"/>
-      <c r="T205" s="2"/>
-      <c r="U205" s="2"/>
-      <c r="V205" s="2"/>
-      <c r="W205" s="2"/>
-      <c r="X205" s="2"/>
-      <c r="Y205" s="2"/>
-      <c r="Z205" s="2"/>
-      <c r="AA205" s="2"/>
-      <c r="AB205" s="2"/>
-      <c r="AC205" s="2"/>
-      <c r="AD205" s="2"/>
-      <c r="AE205" s="2"/>
-      <c r="AF205" s="2"/>
-      <c r="AG205" s="2"/>
-      <c r="AH205" s="2"/>
-      <c r="AI205" s="2"/>
-      <c r="AJ205" s="2"/>
-      <c r="AK205" s="2"/>
-      <c r="AL205" s="2"/>
-      <c r="AM205" s="2"/>
-      <c r="AN205" s="2"/>
-      <c r="AO205" s="2"/>
-      <c r="AP205" s="2"/>
-      <c r="AQ205" s="2"/>
-      <c r="AR205" s="2"/>
-      <c r="AS205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+SaHzzDEGw4gqvt+nIFZqUT6j8i5al1ZYgkPFJOo8wC7nXT8fzuZeM4Z+aphRTG7O56wdtrC22PEij5IX4RQGQ==" saltValue="UrzhHisYrfsnIOJY9wxxxA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="Z4:Z5"/>
-    <mergeCell ref="AA4:AA5"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AN4:AP4"/>
-    <mergeCell ref="AQ4:AS4"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="AF4:AF5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AJ4"/>
-    <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="U2:AG3"/>
-    <mergeCell ref="AH2:AS3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="P4:R4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:U5"/>
-    <mergeCell ref="V4:V5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="B2:T3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="AL3:AM3"/>
+    <mergeCell ref="AJ3:AK3"/>
+    <mergeCell ref="AH3:AI3"/>
+    <mergeCell ref="AH2:AO2"/>
+    <mergeCell ref="U2:AG2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D5 L5:R5 AH5:AI5 AK5:AL5 AN5:AO5 AQ5:AR5" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 L4:R4 AH4:AO4" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D4:D5" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL_CODE" xr:uid="{E1A37C4A-EA65-421A-899B-D3D4EECE0280}"/>
-    <hyperlink ref="L5" r:id="rId2" location="fishPreservationMethods" xr:uid="{054C4D31-B8CE-4C6D-AFCE-E28DEF08D4EE}"/>
-    <hyperlink ref="M5" r:id="rId3" location="fishPreservationMethods" xr:uid="{0D8AEC7A-DF8E-409D-9723-73F05D91141B}"/>
-    <hyperlink ref="N5" r:id="rId4" location="fishPreservationMethods" xr:uid="{5107F5A0-8F93-4A56-A3EF-43FEB84988D7}"/>
-    <hyperlink ref="O5" r:id="rId5" location="fishPreservationMethods" xr:uid="{85356E49-E951-4859-AA55-8E3BEE0EC593}"/>
-    <hyperlink ref="P5" r:id="rId6" location="fishStorageTypes" xr:uid="{69D37979-121E-4978-8B74-0B1FAE758759}"/>
-    <hyperlink ref="Q5" r:id="rId7" location="fishStorageTypes" xr:uid="{A038B6CC-0702-40BB-9E2B-C0526409B22A}"/>
-    <hyperlink ref="R5" r:id="rId8" location="fishStorageTypes" xr:uid="{BC38D7AE-BD26-44F6-A433-3882DFC52CA6}"/>
-    <hyperlink ref="AH5" r:id="rId9" location="wasteManagementCategories" xr:uid="{ACF760F5-C6FA-4F1D-94E8-29D5B930517D}"/>
-    <hyperlink ref="AK5" r:id="rId10" location="wasteManagementCategories" xr:uid="{41E91FE9-A9A0-4C27-AFD6-7E9008BCFEB7}"/>
-    <hyperlink ref="AN5" r:id="rId11" location="wasteManagementCategories" xr:uid="{6B997577-4ECE-44DB-90B5-C3848048D262}"/>
-    <hyperlink ref="AQ5" r:id="rId12" location="wasteManagementCategories" xr:uid="{22421F83-76AB-4229-BA11-8ED0472CDC4C}"/>
-    <hyperlink ref="AI5" r:id="rId13" location="wasteDisposalMethods" xr:uid="{EB1D1F88-2839-4FC7-A159-0A8E80A8297E}"/>
-    <hyperlink ref="AL5" r:id="rId14" location="wasteDisposalMethods" xr:uid="{E40B146B-D992-4927-851D-DDEE2F3C2DCF}"/>
-    <hyperlink ref="AO5" r:id="rId15" location="wasteDisposalMethods" xr:uid="{087F515A-5BB3-49BA-B7BF-CC1331631BA2}"/>
-    <hyperlink ref="AR5" r:id="rId16" location="wasteDisposalMethods" xr:uid="{83C6AD1B-740F-42B7-BD5E-B2BED7456058}"/>
+    <hyperlink ref="D3:D4" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL_CODE" xr:uid="{E1A37C4A-EA65-421A-899B-D3D4EECE0280}"/>
+    <hyperlink ref="L4" r:id="rId2" location="fishPreservationMethods" display="METHOD_1_CODE" xr:uid="{054C4D31-B8CE-4C6D-AFCE-E28DEF08D4EE}"/>
+    <hyperlink ref="M4" r:id="rId3" location="fishPreservationMethods" display="METHOD_2_CODE" xr:uid="{0D8AEC7A-DF8E-409D-9723-73F05D91141B}"/>
+    <hyperlink ref="N4" r:id="rId4" location="fishPreservationMethods" display="METHOD_3_CODE" xr:uid="{5107F5A0-8F93-4A56-A3EF-43FEB84988D7}"/>
+    <hyperlink ref="O4" r:id="rId5" location="fishPreservationMethods" display="METHOD_4_CODE" xr:uid="{85356E49-E951-4859-AA55-8E3BEE0EC593}"/>
+    <hyperlink ref="P4" r:id="rId6" location="fishStorageTypes" display="TYPE_1_CODE" xr:uid="{69D37979-121E-4978-8B74-0B1FAE758759}"/>
+    <hyperlink ref="Q4" r:id="rId7" location="fishStorageTypes" display="TYPE_2_CODE" xr:uid="{A038B6CC-0702-40BB-9E2B-C0526409B22A}"/>
+    <hyperlink ref="R4" r:id="rId8" location="fishStorageTypes" display="TYPE_3_CODE" xr:uid="{BC38D7AE-BD26-44F6-A433-3882DFC52CA6}"/>
+    <hyperlink ref="AH4" r:id="rId9" location="wasteManagementCategories" display="CATEGORY_1_CODE" xr:uid="{ACF760F5-C6FA-4F1D-94E8-29D5B930517D}"/>
+    <hyperlink ref="AJ4" r:id="rId10" location="wasteManagementCategories" display="CATEGORY_2_CODE" xr:uid="{41E91FE9-A9A0-4C27-AFD6-7E9008BCFEB7}"/>
+    <hyperlink ref="AL4" r:id="rId11" location="wasteManagementCategories" display="CATEGORY_3_CODE" xr:uid="{6B997577-4ECE-44DB-90B5-C3848048D262}"/>
+    <hyperlink ref="AN4" r:id="rId12" location="wasteManagementCategories" display="CATEGORY_4_CODE" xr:uid="{22421F83-76AB-4229-BA11-8ED0472CDC4C}"/>
+    <hyperlink ref="AI4" r:id="rId13" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_1_CODE" xr:uid="{EB1D1F88-2839-4FC7-A159-0A8E80A8297E}"/>
+    <hyperlink ref="AK4" r:id="rId14" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_2_CODE" xr:uid="{E40B146B-D992-4927-851D-DDEE2F3C2DCF}"/>
+    <hyperlink ref="AM4" r:id="rId15" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_3_CODE" xr:uid="{087F515A-5BB3-49BA-B7BF-CC1331631BA2}"/>
+    <hyperlink ref="AO4" r:id="rId16" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_4_CODE" xr:uid="{83C6AD1B-740F-42B7-BD5E-B2BED7456058}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -39706,7 +38505,7 @@
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.140625" style="3" bestFit="1" customWidth="1"/>
@@ -39714,93 +38513,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="136" t="s">
-        <v>166</v>
+      <c r="A1" s="55" t="s">
+        <v>70</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="138"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="139" t="s">
-        <v>192</v>
+      <c r="A2" s="98" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="141" t="s">
-        <v>82</v>
+      <c r="B2" s="98" t="s">
+        <v>202</v>
       </c>
-      <c r="C2" s="141"/>
-      <c r="D2" s="107" t="s">
-        <v>83</v>
+      <c r="C2" s="98"/>
+      <c r="D2" s="84" t="s">
+        <v>203</v>
       </c>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="109"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="86"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="102"/>
-      <c r="B3" s="140" t="s">
-        <v>159</v>
+      <c r="A3" s="63"/>
+      <c r="B3" s="63" t="s">
+        <v>66</v>
       </c>
-      <c r="C3" s="140" t="s">
-        <v>161</v>
+      <c r="C3" s="63" t="s">
+        <v>67</v>
       </c>
-      <c r="D3" s="142" t="s">
-        <v>162</v>
+      <c r="D3" s="96" t="s">
+        <v>204</v>
       </c>
-      <c r="E3" s="130" t="s">
-        <v>160</v>
+      <c r="E3" s="109" t="s">
+        <v>201</v>
       </c>
-      <c r="F3" s="132"/>
-      <c r="G3" s="130" t="s">
-        <v>164</v>
+      <c r="F3" s="115"/>
+      <c r="G3" s="109" t="s">
+        <v>68</v>
       </c>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="125"/>
+      <c r="H3" s="114"/>
+      <c r="I3" s="114"/>
+      <c r="J3" s="115"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
-      <c r="D4" s="143"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="135"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="125"/>
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="70"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="140"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="141"/>
-      <c r="E5" s="17" t="s">
-        <v>163</v>
+      <c r="A5" s="63"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="77" t="s">
+        <v>197</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>143</v>
+      <c r="F5" s="107" t="s">
+        <v>55</v>
       </c>
-      <c r="G5" s="17" t="s">
-        <v>35</v>
+      <c r="G5" s="77" t="s">
+        <v>62</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>167</v>
+      <c r="H5" s="77" t="s">
+        <v>198</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>168</v>
+      <c r="I5" s="77" t="s">
+        <v>199</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>169</v>
+      <c r="J5" s="77" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -42204,28 +41003,27 @@
       <c r="J205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="jJULh9yioXw3/eaPfcC3Grd4q9vJiuevAvJVyVy22w1Pq+jj4rolwVX3OXZGM3uA5hKLN7cB45omn5kdoKVJZA==" saltValue="eOuqoOCXuLzNjw5mMZr0dw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="10">
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H3:J4"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B3:B5"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:F4"/>
-    <mergeCell ref="G3:G4"/>
     <mergeCell ref="D2:J2"/>
+    <mergeCell ref="G3:J4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5 G5 H5 I5 J5" xr:uid="{BAE7863D-70B7-46D7-97D5-3B27022E213A}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5 E5 G5 H5 J5" xr:uid="{BAE7863D-70B7-46D7-97D5-3B27022E213A}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1" location="poleMaterialTypes" display="CODE" xr:uid="{164E8273-2EE0-4310-A9EE-530EF285676C}"/>
-    <hyperlink ref="G5" r:id="rId2" location="hookTypes" xr:uid="{3834A26B-6A14-4847-B713-6581D44FE292}"/>
-    <hyperlink ref="H5" r:id="rId3" location="hookTypes" xr:uid="{B8873087-DE19-4D27-AEDC-DB2BCFAFF559}"/>
+    <hyperlink ref="G5" r:id="rId2" location="hookTypes" display="TYPE_CODE" xr:uid="{3834A26B-6A14-4847-B713-6581D44FE292}"/>
+    <hyperlink ref="H5" r:id="rId3" location="hookTypes" display="HOOK_TYPE_CODE_2" xr:uid="{B8873087-DE19-4D27-AEDC-DB2BCFAFF559}"/>
     <hyperlink ref="I5" r:id="rId4" location="hookTypes" display="HOOK_TYPE_CODE_1" xr:uid="{823A6AA6-96BC-4736-9374-9995C0163D9D}"/>
     <hyperlink ref="J5" r:id="rId5" location="hookTypes" display="HOOK_TYPE_CODE_1" xr:uid="{8D5A2BEC-2465-4936-BA34-58061A6C149E}"/>
   </hyperlinks>
@@ -42239,7 +41037,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:T205"/>
+  <dimension ref="A1:T204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -42260,170 +41058,168 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="136" t="s">
-        <v>171</v>
+      <c r="A1" s="55" t="s">
+        <v>71</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
-      <c r="H1" s="137"/>
-      <c r="I1" s="137"/>
-      <c r="J1" s="137"/>
-      <c r="K1" s="137"/>
-      <c r="L1" s="137"/>
-      <c r="M1" s="137"/>
-      <c r="N1" s="137"/>
-      <c r="O1" s="137"/>
-      <c r="P1" s="137"/>
-      <c r="Q1" s="137"/>
-      <c r="R1" s="137"/>
-      <c r="S1" s="137"/>
-      <c r="T1" s="138"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="57"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="139" t="s">
-        <v>192</v>
+      <c r="A2" s="96" t="s">
+        <v>87</v>
       </c>
-      <c r="B2" s="147" t="s">
-        <v>222</v>
+      <c r="B2" s="96" t="s">
+        <v>116</v>
       </c>
-      <c r="C2" s="141" t="s">
-        <v>84</v>
+      <c r="C2" s="123" t="s">
+        <v>156</v>
       </c>
-      <c r="D2" s="141"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="141"/>
-      <c r="G2" s="141"/>
-      <c r="H2" s="141"/>
-      <c r="I2" s="141"/>
-      <c r="J2" s="141"/>
-      <c r="K2" s="141"/>
-      <c r="L2" s="141"/>
-      <c r="M2" s="141"/>
-      <c r="N2" s="141"/>
-      <c r="O2" s="141"/>
-      <c r="P2" s="141"/>
-      <c r="Q2" s="141"/>
-      <c r="R2" s="141"/>
-      <c r="S2" s="141"/>
-      <c r="T2" s="141"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="74" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="109" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="114"/>
+      <c r="I2" s="115"/>
+      <c r="J2" s="117" t="s">
+        <v>159</v>
+      </c>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="O2" s="109" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="T2" s="126" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="102"/>
-      <c r="B3" s="147"/>
-      <c r="C3" s="148" t="s">
-        <v>126</v>
+      <c r="A3" s="97"/>
+      <c r="B3" s="97"/>
+      <c r="C3" s="65" t="s">
+        <v>54</v>
       </c>
-      <c r="D3" s="149"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="37" t="s">
-        <v>170</v>
+      <c r="D3" s="123" t="s">
+        <v>53</v>
       </c>
-      <c r="G3" s="125" t="s">
-        <v>138</v>
+      <c r="E3" s="124"/>
+      <c r="F3" s="65" t="s">
+        <v>54</v>
       </c>
-      <c r="H3" s="125"/>
-      <c r="I3" s="125"/>
-      <c r="J3" s="92" t="s">
-        <v>172</v>
-      </c>
-      <c r="K3" s="92"/>
-      <c r="L3" s="92"/>
-      <c r="M3" s="92"/>
-      <c r="N3" s="140" t="s">
-        <v>173</v>
-      </c>
-      <c r="O3" s="130" t="s">
-        <v>174</v>
-      </c>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="131"/>
-      <c r="R3" s="132"/>
-      <c r="S3" s="114" t="s">
-        <v>176</v>
-      </c>
-      <c r="T3" s="144" t="s">
-        <v>191</v>
-      </c>
+      <c r="G3" s="69"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="70"/>
+      <c r="J3" s="120"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="69"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="116"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="113"/>
+      <c r="T3" s="127"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="147"/>
-      <c r="C4" s="140" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="92"/>
-      <c r="F4" s="140" t="s">
-        <v>142</v>
-      </c>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="125"/>
-      <c r="J4" s="92"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="92"/>
-      <c r="M4" s="92"/>
-      <c r="N4" s="140"/>
-      <c r="O4" s="133"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="134"/>
-      <c r="R4" s="135"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="145"/>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="102"/>
-      <c r="B5" s="139"/>
-      <c r="C5" s="140"/>
-      <c r="D5" s="37" t="s">
+      <c r="A4" s="98"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="112" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E4" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="140"/>
-      <c r="G5" s="30" t="s">
-        <v>139</v>
+      <c r="F4" s="65"/>
+      <c r="G4" s="77" t="s">
+        <v>160</v>
       </c>
-      <c r="H5" s="30" t="s">
-        <v>140</v>
+      <c r="H4" s="77" t="s">
+        <v>161</v>
       </c>
-      <c r="I5" s="30" t="s">
-        <v>141</v>
+      <c r="I4" s="77" t="s">
+        <v>162</v>
       </c>
-      <c r="J5" s="22" t="s">
-        <v>36</v>
+      <c r="J4" s="129" t="s">
+        <v>125</v>
       </c>
-      <c r="K5" s="22" t="s">
-        <v>37</v>
+      <c r="K4" s="129" t="s">
+        <v>163</v>
       </c>
-      <c r="L5" s="22" t="s">
-        <v>38</v>
+      <c r="L4" s="129" t="s">
+        <v>164</v>
       </c>
-      <c r="M5" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="140"/>
-      <c r="O5" s="12" t="s">
+      <c r="M4" s="129" t="s">
         <v>165</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>175</v>
+      <c r="N4" s="63"/>
+      <c r="O4" s="110" t="s">
+        <v>69</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>85</v>
+      <c r="P4" s="77" t="s">
+        <v>166</v>
       </c>
-      <c r="R5" s="31" t="s">
-        <v>177</v>
+      <c r="Q4" s="77" t="s">
+        <v>167</v>
       </c>
-      <c r="S5" s="114"/>
-      <c r="T5" s="146"/>
+      <c r="R4" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="S4" s="113"/>
+      <c r="T4" s="128"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -46803,61 +45599,39 @@
       <c r="S204" s="2"/>
       <c r="T204" s="2"/>
     </row>
-    <row r="205" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
-      <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
-      <c r="J205" s="2"/>
-      <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
-      <c r="M205" s="2"/>
-      <c r="N205" s="2"/>
-      <c r="O205" s="2"/>
-      <c r="P205" s="2"/>
-      <c r="Q205" s="2"/>
-      <c r="R205" s="2"/>
-      <c r="S205" s="2"/>
-      <c r="T205" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+dD8Y9JmmkNvxBwrPccesEhEhPtOalD2DiMz+ZFeSaLwPr+0KkoZfO2W+HDvxokDCGwNLlDZT2ygZdd1AFIbNg==" saltValue="9pjZZi5t4TILs/fmQ/refg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="14">
+  <sheetProtection selectLockedCells="1"/>
+  <dataConsolidate/>
+  <mergeCells count="13">
     <mergeCell ref="A1:T1"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="T3:T5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="J3:M4"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="S3:S5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="C2:T2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:I4"/>
+    <mergeCell ref="O2:R3"/>
+    <mergeCell ref="T2:T4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="J2:M3"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="S2:S4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="G2:I3"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" sqref="G5:M5 T3:T5 Q5 P5" xr:uid="{AF5AE5B6-046A-4AF7-91CF-4FE32EB3CEA6}">
+    <dataValidation type="custom" sqref="T2:T4 P4:Q4 G4:M4" xr:uid="{AF5AE5B6-046A-4AF7-91CF-4FE32EB3CEA6}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G5" r:id="rId1" location="schoolSightingCues" xr:uid="{CE73602B-A48A-428F-8ADB-F071C5823612}"/>
-    <hyperlink ref="H5" r:id="rId2" location="schoolSightingCues" xr:uid="{4B6EE5CF-8B0C-41F8-909C-73EE76A6FF0D}"/>
-    <hyperlink ref="I5" r:id="rId3" location="schoolSightingCues" xr:uid="{9E10D906-8CC4-49D3-B665-5402B5D32BBA}"/>
-    <hyperlink ref="J5" r:id="rId4" location="targetSpecies" xr:uid="{756E96B2-B8F7-4292-B674-2EC4450D0122}"/>
-    <hyperlink ref="L5" r:id="rId5" location="targetSpecies" xr:uid="{16FC335F-AC3D-4796-8D24-BB00CB0C71AB}"/>
-    <hyperlink ref="M5" r:id="rId6" location="targetSpecies" xr:uid="{1E6B4030-C260-4262-A239-50D6E6D41AB5}"/>
-    <hyperlink ref="Q5" r:id="rId7" location="baits" xr:uid="{34EEBE01-6313-42D1-B62B-343CE67EF2F0}"/>
-    <hyperlink ref="P5" r:id="rId8" location="baitConditions" xr:uid="{27255776-50F3-4F60-81B0-82CA41F5BC7D}"/>
-    <hyperlink ref="K5" r:id="rId9" location="targetSpecies" xr:uid="{D81BCA37-60B1-4469-A9B9-202C651AFA82}"/>
+    <hyperlink ref="G4" r:id="rId1" location="schoolSightingCues" display="CUE_1_CODE" xr:uid="{CE73602B-A48A-428F-8ADB-F071C5823612}"/>
+    <hyperlink ref="H4" r:id="rId2" location="schoolSightingCues" display="CUE_2_CODE" xr:uid="{4B6EE5CF-8B0C-41F8-909C-73EE76A6FF0D}"/>
+    <hyperlink ref="I4" r:id="rId3" location="schoolSightingCues" display="CUE_3_CODE" xr:uid="{9E10D906-8CC4-49D3-B665-5402B5D32BBA}"/>
+    <hyperlink ref="J4" r:id="rId4" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{756E96B2-B8F7-4292-B674-2EC4450D0122}"/>
+    <hyperlink ref="L4" r:id="rId5" location="targetSpecies" display="SPECIES_3_CODE" xr:uid="{16FC335F-AC3D-4796-8D24-BB00CB0C71AB}"/>
+    <hyperlink ref="M4" r:id="rId6" location="targetSpecies" display="SPECIES_4_CODE" xr:uid="{1E6B4030-C260-4262-A239-50D6E6D41AB5}"/>
+    <hyperlink ref="Q4" r:id="rId7" location="baits" display="SPECIES_CODE" xr:uid="{34EEBE01-6313-42D1-B62B-343CE67EF2F0}"/>
+    <hyperlink ref="P4" r:id="rId8" location="baitConditions" display="CONDITION_CODE" xr:uid="{27255776-50F3-4F60-81B0-82CA41F5BC7D}"/>
+    <hyperlink ref="K4" r:id="rId9" location="targetSpecies" display="SPECIES_2_CODE" xr:uid="{D81BCA37-60B1-4469-A9B9-202C651AFA82}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -46868,88 +45642,86 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.85546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" style="3" customWidth="1"/>
     <col min="8" max="8" width="11.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
-        <v>189</v>
+      <c r="A1" s="6" t="s">
+        <v>84</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="151" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2" s="148" t="s">
+      <c r="A2" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="150"/>
+      <c r="B2" s="89" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" s="130" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="131"/>
+      <c r="E2" s="89" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" s="96" t="s">
+        <v>169</v>
+      </c>
+      <c r="G2" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="125"/>
+      <c r="I2" s="124"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="147"/>
-      <c r="B3" s="152" t="s">
-        <v>85</v>
+      <c r="A3" s="98"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="129" t="s">
+        <v>62</v>
       </c>
-      <c r="C3" s="154" t="s">
-        <v>186</v>
+      <c r="D3" s="129" t="s">
+        <v>82</v>
       </c>
-      <c r="D3" s="155"/>
-      <c r="E3" s="152" t="s">
-        <v>116</v>
+      <c r="E3" s="92"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="74" t="s">
+        <v>18</v>
       </c>
-      <c r="F3" s="151" t="s">
-        <v>137</v>
+      <c r="H3" s="133" t="s">
+        <v>61</v>
       </c>
-      <c r="G3" s="27" t="s">
-        <v>88</v>
+      <c r="I3" s="129" t="s">
+        <v>170</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="29"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="139"/>
-      <c r="B4" s="153"/>
-      <c r="C4" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="E4" s="153"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="I4" s="22" t="s">
-        <v>93</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -49140,40 +47912,27 @@
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="s07PvIule7+RpMFFgEoiiwF7xOnmX0Rp5DrtTgSH76K8Cd73djoRF84G5TugUnCjnWJs2BpV4HhnOVm3ufahrQ==" saltValue="qdTxf5OyiyB5BEdPdOhIyQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="6">
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4 E3 B3 C4" xr:uid="{F74A31D4-EFBF-4D20-9A28-001D1EE627E7}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 C3 I3 E2" xr:uid="{F74A31D4-EFBF-4D20-9A28-001D1EE627E7}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" location="species" xr:uid="{3C35F152-403E-4D6F-9670-8BA33A2F5094}"/>
-    <hyperlink ref="I4" r:id="rId2" location="weightEstimationMethods" xr:uid="{5DE6CF93-F591-44BB-BEE2-52BDB3386A99}"/>
-    <hyperlink ref="E3" r:id="rId3" location="samplingMethodsForCatchEstimation" xr:uid="{6F194610-022D-4514-B848-7A037E00CF0D}"/>
-    <hyperlink ref="C4" r:id="rId4" location="typesOfFate" xr:uid="{CA3F2F8B-11EA-4E7C-B697-0331CC3614C1}"/>
-    <hyperlink ref="D4" r:id="rId5" location="fates" xr:uid="{4135CEFA-EB46-489F-8386-C479D974217A}"/>
-    <hyperlink ref="B3:B4" r:id="rId6" location="species" display="SPECIES_CODE" xr:uid="{DF16A0F4-1289-41E8-9E6B-5026A8574036}"/>
-    <hyperlink ref="E3:E4" r:id="rId7" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD_CODE" xr:uid="{5ACADFE8-8B59-44DD-9438-A0676C6E3F37}"/>
+    <hyperlink ref="D3" r:id="rId1" location="fates" xr:uid="{4135CEFA-EB46-489F-8386-C479D974217A}"/>
+    <hyperlink ref="C3" r:id="rId2" location="typesOfFate" xr:uid="{CA3F2F8B-11EA-4E7C-B697-0331CC3614C1}"/>
+    <hyperlink ref="E2" r:id="rId3" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD_CODE" xr:uid="{6F194610-022D-4514-B848-7A037E00CF0D}"/>
+    <hyperlink ref="I3" r:id="rId4" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{5DE6CF93-F591-44BB-BEE2-52BDB3386A99}"/>
+    <hyperlink ref="B2" r:id="rId5" location="species" display="SPECIES_CODE" xr:uid="{3C35F152-403E-4D6F-9670-8BA33A2F5094}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49184,7 +47943,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:N204"/>
+  <dimension ref="A1:N203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -49199,108 +47958,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="156" t="s">
-        <v>188</v>
+      <c r="A1" s="58" t="s">
+        <v>83</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="157"/>
-      <c r="H1" s="157"/>
-      <c r="I1" s="157"/>
-      <c r="J1" s="157"/>
-      <c r="K1" s="157"/>
-      <c r="L1" s="157"/>
-      <c r="M1" s="157"/>
-      <c r="N1" s="157"/>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59"/>
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="102" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2" s="103" t="s">
-        <v>190</v>
-      </c>
-      <c r="C2" s="126" t="s">
-        <v>193</v>
-      </c>
-      <c r="D2" s="125" t="s">
+      <c r="A2" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
-      <c r="M2" s="125"/>
-      <c r="N2" s="125"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="102"/>
-      <c r="B3" s="103"/>
-      <c r="C3" s="160"/>
-      <c r="D3" s="161" t="s">
+      <c r="B2" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="163" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="164"/>
-      <c r="G3" s="161" t="s">
-        <v>116</v>
-      </c>
-      <c r="H3" s="32" t="s">
+      <c r="C2" s="71" t="s">
         <v>88</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="161" t="s">
+      <c r="D2" s="100" t="s">
+        <v>167</v>
+      </c>
+      <c r="E2" s="134" t="s">
+        <v>81</v>
+      </c>
+      <c r="F2" s="135"/>
+      <c r="G2" s="100" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2" s="66" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="68"/>
+      <c r="J2" s="100" t="s">
+        <v>170</v>
+      </c>
+      <c r="K2" s="66" t="s">
+        <v>205</v>
+      </c>
+      <c r="L2" s="68"/>
+      <c r="M2" s="81" t="s">
+        <v>206</v>
+      </c>
+      <c r="N2" s="83"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="98"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="77" t="s">
+        <v>82</v>
+      </c>
+      <c r="G3" s="101"/>
+      <c r="H3" s="104" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="105" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="101"/>
+      <c r="K3" s="77" t="s">
+        <v>171</v>
+      </c>
+      <c r="L3" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="M3" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="8" t="s">
-        <v>96</v>
+      <c r="N3" s="77" t="s">
+        <v>94</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="158" t="s">
-        <v>97</v>
-      </c>
-      <c r="N3" s="159"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="102"/>
-      <c r="B4" s="103"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="162"/>
-      <c r="E4" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="G4" s="162"/>
-      <c r="H4" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="J4" s="162"/>
-      <c r="K4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>100</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -52486,52 +51243,37 @@
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-      <c r="J204" s="2"/>
-      <c r="K204" s="2"/>
-      <c r="L204" s="2"/>
-      <c r="M204" s="2"/>
-      <c r="N204" s="2"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MuSDoJyttw354xJFTxLWWs9hcYvSS1xVt571LcnNvE8ALx+IzgTNBCz/rp2XrvmgY8FyWcJGhCPqgOWyH+T1ZQ==" saltValue="1dyENYOnxMmfU8YUTE0Kzg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="10">
+  <sheetProtection selectLockedCells="1"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:N2"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3 E4 G3 D3 K4:N4" xr:uid="{2F2D812A-9500-497F-8725-7E6E70DDE170}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 E3 K3" xr:uid="{2F2D812A-9500-497F-8725-7E6E70DDE170}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J3" r:id="rId1" location="weightEstimationMethods" xr:uid="{1DD75691-93AA-4F11-A684-8796C3C9E569}"/>
-    <hyperlink ref="E4" r:id="rId2" location="typesOfFate" xr:uid="{1403244A-A05E-4DE5-858C-EF04B6AE8958}"/>
-    <hyperlink ref="F4" r:id="rId3" location="fates" xr:uid="{8E385EFE-3151-4CFA-95C6-5D0BFE8C147F}"/>
-    <hyperlink ref="K4" r:id="rId4" location="depredationSources" xr:uid="{B3917325-AB0B-4A1B-ABCC-C0C1A7A1CA59}"/>
-    <hyperlink ref="L4" r:id="rId5" location="predators" xr:uid="{5D63AB31-B94B-4525-AAD3-23EC2F149EFD}"/>
-    <hyperlink ref="N4" r:id="rId6" location="individualConditions" xr:uid="{8232D868-9231-459C-8BCE-1D79652178CC}"/>
-    <hyperlink ref="M4" r:id="rId7" location="individualConditions" xr:uid="{EDAE3586-1489-4D94-AD4C-56C36514399C}"/>
-    <hyperlink ref="D3:D4" r:id="rId8" location="allSpecies" display="SPECIES_CODE" xr:uid="{155765ED-8ADD-47FC-B5D0-94D7C4A8AC7C}"/>
-    <hyperlink ref="G3:G4" r:id="rId9" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{93E01569-6745-464C-91D0-713DC5AB5999}"/>
-    <hyperlink ref="J3:J4" r:id="rId10" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{7F016882-2E73-4F4C-B8D1-312E547767D6}"/>
+    <hyperlink ref="J2" r:id="rId1" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{1DD75691-93AA-4F11-A684-8796C3C9E569}"/>
+    <hyperlink ref="E3" r:id="rId2" location="typesOfFate" xr:uid="{1403244A-A05E-4DE5-858C-EF04B6AE8958}"/>
+    <hyperlink ref="F3" r:id="rId3" location="fates" xr:uid="{8E385EFE-3151-4CFA-95C6-5D0BFE8C147F}"/>
+    <hyperlink ref="K3" r:id="rId4" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{B3917325-AB0B-4A1B-ABCC-C0C1A7A1CA59}"/>
+    <hyperlink ref="L3" r:id="rId5" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{5D63AB31-B94B-4525-AAD3-23EC2F149EFD}"/>
+    <hyperlink ref="N3" r:id="rId6" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{8232D868-9231-459C-8BCE-1D79652178CC}"/>
+    <hyperlink ref="M3" r:id="rId7" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{EDAE3586-1489-4D94-AD4C-56C36514399C}"/>
+    <hyperlink ref="D2:D3" r:id="rId8" location="allSpecies" display="SPECIES_CODE" xr:uid="{155765ED-8ADD-47FC-B5D0-94D7C4A8AC7C}"/>
+    <hyperlink ref="G2:G3" r:id="rId9" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{93E01569-6745-464C-91D0-713DC5AB5999}"/>
+    <hyperlink ref="J2:J3" r:id="rId10" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{7F016882-2E73-4F4C-B8D1-312E547767D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513B1F81-54B1-4D89-AC6C-04ACB48D638F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D1E2AE-ECDC-4F42-9742-748CDDC5AE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="180" windowWidth="27705" windowHeight="15090" tabRatio="803" firstSheet="8" activeTab="14" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="29025" yWindow="360" windowWidth="27705" windowHeight="15090" tabRatio="803" firstSheet="5" activeTab="10" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="35" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="206">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -232,9 +232,6 @@
     <t>Flag / chartering state</t>
   </si>
   <si>
-    <t>DAYS | NM</t>
-  </si>
-  <si>
     <t>KG | T</t>
   </si>
   <si>
@@ -253,9 +250,6 @@
     <t>LIVE_BAIT_TANK_CAPACITY_M3</t>
   </si>
   <si>
-    <t>NUM_AUTOMATIC_POLES</t>
-  </si>
-  <si>
     <t>HOOK</t>
   </si>
   <si>
@@ -272,12 +266,6 @@
   </si>
   <si>
     <t>BAIT</t>
-  </si>
-  <si>
-    <t>NUM_HOOKS_LOST</t>
-  </si>
-  <si>
-    <t>WEIGHT_KG</t>
   </si>
   <si>
     <t>Pole-and-line fishing events &gt; Bait fishing &gt; Set-level catch details</t>
@@ -385,19 +373,7 @@
     <t>IOTC_ID</t>
   </si>
   <si>
-    <t>GEAR</t>
-  </si>
-  <si>
     <t>PERSONNEL</t>
-  </si>
-  <si>
-    <t>REG_NUMBER</t>
-  </si>
-  <si>
-    <t>TONNAGE (GT)</t>
-  </si>
-  <si>
-    <t>LENGTH (M)</t>
   </si>
   <si>
     <t>EVENT_ID</t>
@@ -625,9 +601,6 @@
     <t>OBSERVER IDENTIFICATION</t>
   </si>
   <si>
-    <t>LICENSED TARGET SPECIES</t>
-  </si>
-  <si>
     <t>FISHING MASTER</t>
   </si>
   <si>
@@ -644,15 +617,6 @@
   </si>
   <si>
     <t>MATERIAL</t>
-  </si>
-  <si>
-    <t>HOOK_TYPE_2</t>
-  </si>
-  <si>
-    <t>HOOK_TYPE_3</t>
-  </si>
-  <si>
-    <t>HOOK_TYPE_4</t>
   </si>
   <si>
     <t>POLE MATERIAL</t>
@@ -680,6 +644,30 @@
   </si>
   <si>
     <t>LENGTH 2</t>
+  </si>
+  <si>
+    <t>REGISTRATION_NUMBER</t>
+  </si>
+  <si>
+    <t>LICESNED_TARGET_SPECIES</t>
+  </si>
+  <si>
+    <t>GROSS_TONNAGE</t>
+  </si>
+  <si>
+    <t>LOA_M</t>
+  </si>
+  <si>
+    <t>POWER_UNIT</t>
+  </si>
+  <si>
+    <t>NUMBER_OF_AUTOMATIC_POLES</t>
+  </si>
+  <si>
+    <t>TYPE_4</t>
+  </si>
+  <si>
+    <t>NUMBER_OF_HOOKS_LOST</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1053,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1146,6 +1134,63 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1179,6 +1224,104 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1188,217 +1331,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1413,9 +1355,32 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1423,11 +1388,11 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1441,23 +1406,56 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1790,39 +1788,39 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="45" t="s">
-        <v>118</v>
+      <c r="B2" s="64" t="s">
+        <v>110</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="47"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="66"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="48"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="50"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="69"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="14"/>
       <c r="C4" s="15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H4" s="19"/>
     </row>
@@ -1838,7 +1836,7 @@
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="20"/>
       <c r="C6" s="23" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
@@ -1857,26 +1855,26 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="20"/>
-      <c r="C8" s="51" t="s">
-        <v>99</v>
+      <c r="C8" s="70" t="s">
+        <v>95</v>
       </c>
-      <c r="D8" s="51"/>
+      <c r="D8" s="70"/>
       <c r="E8" s="21"/>
-      <c r="F8" s="51" t="s">
-        <v>100</v>
+      <c r="F8" s="70" t="s">
+        <v>96</v>
       </c>
-      <c r="G8" s="51"/>
+      <c r="G8" s="70"/>
       <c r="H8" s="22"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20"/>
       <c r="C9" s="24" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="21"/>
       <c r="F9" s="24" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="22"/>
@@ -1884,12 +1882,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="20"/>
       <c r="C10" s="26" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="21"/>
       <c r="F10" s="21" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="22"/>
@@ -1906,7 +1904,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="20"/>
       <c r="C12" s="26" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="21"/>
@@ -1946,7 +1944,7 @@
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="20"/>
       <c r="C16" s="23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="21"/>
@@ -1966,7 +1964,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="20"/>
       <c r="C18" s="26" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D18" s="30"/>
       <c r="E18" s="21"/>
@@ -1977,7 +1975,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="20"/>
       <c r="C19" s="31" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D19" s="30"/>
       <c r="E19" s="21"/>
@@ -1999,7 +1997,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="20"/>
       <c r="C21" s="26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D21" s="30"/>
       <c r="E21" s="21"/>
@@ -2047,11 +2045,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="20"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="53"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="54"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="73"/>
       <c r="H26" s="22"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2068,7 +2066,7 @@
       <c r="D28" s="37"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="QXspNp+1PSaoV+3Ex0NtX0ciQUE5017lUR6TNqS4/BWWl8yEi5vIO2XdkGQisIEyujfnCKqy/tmCLCQiiwT+2g==" saltValue="Y9jBrA7Hhv8OsMSdHMh9/g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2109,7 +2107,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -2120,40 +2118,40 @@
       <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="136" t="s">
-        <v>87</v>
+      <c r="A2" s="129" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="136" t="s">
-        <v>89</v>
+      <c r="B2" s="129" t="s">
+        <v>85</v>
       </c>
-      <c r="C2" s="136" t="s">
-        <v>88</v>
+      <c r="C2" s="129" t="s">
+        <v>84</v>
       </c>
-      <c r="D2" s="100" t="s">
-        <v>173</v>
+      <c r="D2" s="93" t="s">
+        <v>165</v>
       </c>
-      <c r="E2" s="71" t="s">
+      <c r="E2" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="100" t="s">
-        <v>174</v>
+      <c r="F2" s="93" t="s">
+        <v>166</v>
       </c>
-      <c r="G2" s="71" t="s">
+      <c r="G2" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="71" t="s">
+      <c r="H2" s="81" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="137"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="A3" s="130"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -4156,16 +4154,16 @@
       <c r="H203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="TY9NRYWySbgKMmZKaT3SF4fhxErdThmV7RW3Y32hqjdOHrUBh9UqYvEM7rxXS9ZwI3XsUrWjuuMNeBcf85bDVg==" saltValue="QGUAZ62U7c78yIwIE4fbww==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 F2:F3" xr:uid="{8F3C96D1-E191-4693-B29A-79D17608E9F5}">
@@ -4173,8 +4171,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2:D3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION_CODE" xr:uid="{78235951-ABFA-474C-9817-7631D9D14409}"/>
-    <hyperlink ref="F2:F3" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD_CODE" xr:uid="{8BA4CC5E-2A66-4A5F-8835-F30335A7CEAF}"/>
+    <hyperlink ref="D2:D3" r:id="rId1" location="gearInteractions" display="GEAR_INTERACTION" xr:uid="{78235951-ABFA-474C-9817-7631D9D14409}"/>
+    <hyperlink ref="F2:F3" r:id="rId2" location="handlingMethods" display="HANDLING_METHOD" xr:uid="{8BA4CC5E-2A66-4A5F-8835-F30335A7CEAF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4216,158 +4214,158 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="55" t="s">
-        <v>80</v>
+      <c r="A1" s="104" t="s">
+        <v>76</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56"/>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56"/>
-      <c r="AA1" s="57"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="106"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="136" t="s">
-        <v>87</v>
+      <c r="A2" s="129" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="136" t="s">
-        <v>89</v>
+      <c r="B2" s="129" t="s">
+        <v>85</v>
       </c>
-      <c r="C2" s="136" t="s">
-        <v>88</v>
+      <c r="C2" s="129" t="s">
+        <v>84</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="E2" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="75" t="s">
+        <v>197</v>
+      </c>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q2" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="78"/>
+      <c r="S2" s="75" t="s">
+        <v>170</v>
+      </c>
+      <c r="T2" s="75"/>
+      <c r="U2" s="75" t="s">
+        <v>171</v>
+      </c>
+      <c r="V2" s="75"/>
+      <c r="W2" s="75"/>
+      <c r="X2" s="75"/>
+      <c r="Y2" s="75"/>
+      <c r="Z2" s="75"/>
+      <c r="AA2" s="75"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="130"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="L3" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" s="49" t="s">
         <v>168</v>
       </c>
-      <c r="E2" s="63" t="s">
-        <v>208</v>
+      <c r="N3" s="46" t="s">
+        <v>35</v>
       </c>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="64" t="s">
-        <v>209</v>
+      <c r="O3" s="49" t="s">
+        <v>169</v>
       </c>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" s="64"/>
-      <c r="O2" s="64"/>
-      <c r="P2" s="100" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q2" s="66" t="s">
+      <c r="P3" s="94"/>
+      <c r="Q3" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="64" t="s">
-        <v>178</v>
-      </c>
-      <c r="T2" s="64"/>
-      <c r="U2" s="64" t="s">
-        <v>179</v>
-      </c>
-      <c r="V2" s="64"/>
-      <c r="W2" s="64"/>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64"/>
-      <c r="AA2" s="64"/>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="137"/>
-      <c r="B3" s="137"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="92"/>
-      <c r="E3" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="129" t="s">
-        <v>175</v>
-      </c>
-      <c r="H3" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="77" t="s">
-        <v>62</v>
-      </c>
-      <c r="J3" s="76" t="s">
-        <v>36</v>
-      </c>
-      <c r="K3" s="77" t="s">
-        <v>175</v>
-      </c>
-      <c r="L3" s="76" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="77" t="s">
-        <v>176</v>
-      </c>
-      <c r="N3" s="76" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="77" t="s">
-        <v>177</v>
-      </c>
-      <c r="P3" s="101"/>
-      <c r="Q3" s="110" t="s">
+      <c r="R3" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="R3" s="110" t="s">
-        <v>65</v>
+      <c r="S3" s="58" t="s">
+        <v>61</v>
       </c>
-      <c r="S3" s="107" t="s">
-        <v>62</v>
-      </c>
-      <c r="T3" s="76" t="s">
+      <c r="T3" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="U3" s="76" t="s">
+      <c r="U3" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="V3" s="76" t="s">
+      <c r="V3" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="W3" s="77" t="s">
-        <v>62</v>
+      <c r="W3" s="49" t="s">
+        <v>61</v>
       </c>
-      <c r="X3" s="76" t="s">
+      <c r="X3" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="76" t="s">
+      <c r="Y3" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="76" t="s">
-        <v>90</v>
+      <c r="Z3" s="46" t="s">
+        <v>86</v>
       </c>
-      <c r="AA3" s="76" t="s">
-        <v>91</v>
+      <c r="AA3" s="46" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -10195,10 +10193,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D2:D3" r:id="rId1" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{BFD2684A-F255-4A45-936A-FA04BB028BCC}"/>
-    <hyperlink ref="G3" r:id="rId2" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{C4FA29B3-2C8D-4339-B3D8-F0EA1EB90752}"/>
+    <hyperlink ref="D2:D3" r:id="rId1" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD" xr:uid="{BFD2684A-F255-4A45-936A-FA04BB028BCC}"/>
+    <hyperlink ref="G3" r:id="rId2" location="lengthMeasurementTools" xr:uid="{C4FA29B3-2C8D-4339-B3D8-F0EA1EB90752}"/>
     <hyperlink ref="K3" r:id="rId3" location="lengthMeasurementTools" display="MEASURING_TOOL_CODE" xr:uid="{75603697-09CE-4919-BF4D-3EBC3F8E1252}"/>
-    <hyperlink ref="E3" r:id="rId4" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{2187AEC4-49E1-4244-AA70-A980ABD68A20}"/>
+    <hyperlink ref="E3" r:id="rId4" location="lengthMeasurementTypes" xr:uid="{2187AEC4-49E1-4244-AA70-A980ABD68A20}"/>
     <hyperlink ref="I3" r:id="rId5" location="lengthMeasurementTypes" display="TYPE_CODE" xr:uid="{52978703-518C-4A83-BC90-C27264C77908}"/>
     <hyperlink ref="M3" r:id="rId6" location="fishProcessingTypes" display="PROCESSING_TYPE_CODE" xr:uid="{D43A58E3-BC87-4BAB-B629-28CC81AB8470}"/>
     <hyperlink ref="P2:P3" r:id="rId7" location="sex" display="SEX" xr:uid="{CF9A9C8D-83EB-473F-A588-FB44C1C23798}"/>
@@ -10231,96 +10229,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="60" t="s">
-        <v>77</v>
+      <c r="A1" s="131" t="s">
+        <v>73</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="62"/>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="133"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
-        <v>87</v>
+      <c r="A2" s="81" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="66" t="s">
-        <v>156</v>
+      <c r="B2" s="61"/>
+      <c r="C2" s="76" t="s">
+        <v>148</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="66" t="s">
-        <v>157</v>
+      <c r="D2" s="77"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="76" t="s">
+        <v>149</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="109" t="s">
-        <v>78</v>
+      <c r="G2" s="77"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="107" t="s">
+        <v>74</v>
       </c>
-      <c r="J2" s="115"/>
-      <c r="K2" s="142" t="s">
-        <v>92</v>
+      <c r="J2" s="108"/>
+      <c r="K2" s="134" t="s">
+        <v>88</v>
       </c>
-      <c r="L2" s="64" t="s">
-        <v>180</v>
+      <c r="L2" s="75" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="139"/>
-      <c r="B3" s="140" t="s">
-        <v>89</v>
+      <c r="A3" s="135"/>
+      <c r="B3" s="62" t="s">
+        <v>85</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64" t="s">
+      <c r="E3" s="75"/>
+      <c r="F3" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="64"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="64"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="79"/>
+      <c r="J3" s="80"/>
+      <c r="K3" s="134"/>
+      <c r="L3" s="75"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="75"/>
-      <c r="B4" s="141"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="76" t="s">
+      <c r="A4" s="82"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="E4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="76" t="s">
+      <c r="F4" s="75"/>
+      <c r="G4" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="76" t="s">
+      <c r="H4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="76" t="s">
+      <c r="I4" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="111" t="s">
-        <v>79</v>
+      <c r="J4" s="60" t="s">
+        <v>75</v>
       </c>
-      <c r="K4" s="142"/>
-      <c r="L4" s="64"/>
+      <c r="K4" s="134"/>
+      <c r="L4" s="75"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -13161,26 +13159,26 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="143" t="s">
-        <v>61</v>
+      <c r="B2" s="136" t="s">
+        <v>60</v>
       </c>
-      <c r="C2" s="88" t="s">
-        <v>177</v>
+      <c r="C2" s="98" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="64"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="91"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="136"/>
+      <c r="C3" s="99"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -14219,7 +14217,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -14229,36 +14227,36 @@
       <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="100" t="s">
-        <v>173</v>
+      <c r="A2" s="93" t="s">
+        <v>165</v>
       </c>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="100" t="s">
-        <v>174</v>
+      <c r="C2" s="93" t="s">
+        <v>166</v>
       </c>
-      <c r="D2" s="100" t="s">
-        <v>93</v>
+      <c r="D2" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="E2" s="100" t="s">
-        <v>94</v>
+      <c r="E2" s="93" t="s">
+        <v>90</v>
       </c>
-      <c r="F2" s="71" t="s">
+      <c r="F2" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="71" t="s">
+      <c r="G2" s="81" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="101"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -16101,7 +16099,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -16109,19 +16107,19 @@
       <c r="E1" s="8"/>
     </row>
     <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="132" t="s">
-        <v>87</v>
+      <c r="A2" s="54" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="76" t="s">
+      <c r="E2" s="46" t="s">
         <v>56</v>
       </c>
     </row>
@@ -17605,208 +17603,208 @@
       <c r="X1" s="40"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
-        <v>87</v>
+      <c r="A2" s="74" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="63" t="s">
-        <v>190</v>
+      <c r="B2" s="74" t="s">
+        <v>182</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="64" t="s">
-        <v>189</v>
+      <c r="C2" s="74"/>
+      <c r="D2" s="75" t="s">
+        <v>181</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="63" t="s">
-        <v>188</v>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="74" t="s">
+        <v>180</v>
       </c>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="63"/>
-      <c r="W2" s="63"/>
-      <c r="X2" s="63"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="74"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="66" t="s">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="66" t="s">
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="78"/>
+      <c r="I3" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="63"/>
-      <c r="W3" s="63"/>
-      <c r="X3" s="63"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="74"/>
+      <c r="P3" s="74"/>
+      <c r="Q3" s="74"/>
+      <c r="R3" s="74"/>
+      <c r="S3" s="74"/>
+      <c r="T3" s="74"/>
+      <c r="U3" s="74"/>
+      <c r="V3" s="74"/>
+      <c r="W3" s="74"/>
+      <c r="X3" s="74"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="69" t="s">
-        <v>187</v>
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="79" t="s">
+        <v>179</v>
       </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="69" t="s">
-        <v>186</v>
+      <c r="E4" s="80"/>
+      <c r="F4" s="79" t="s">
+        <v>178</v>
       </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="71" t="s">
+      <c r="G4" s="80"/>
+      <c r="H4" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="69" t="s">
-        <v>187</v>
+      <c r="I4" s="79" t="s">
+        <v>179</v>
       </c>
-      <c r="J4" s="70"/>
-      <c r="K4" s="69" t="s">
-        <v>186</v>
+      <c r="J4" s="80"/>
+      <c r="K4" s="79" t="s">
+        <v>178</v>
       </c>
-      <c r="L4" s="70"/>
-      <c r="M4" s="71" t="s">
+      <c r="L4" s="80"/>
+      <c r="M4" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="63" t="s">
-        <v>185</v>
+      <c r="N4" s="74" t="s">
+        <v>177</v>
       </c>
-      <c r="O4" s="63"/>
-      <c r="P4" s="64" t="s">
-        <v>184</v>
+      <c r="O4" s="74"/>
+      <c r="P4" s="75" t="s">
+        <v>176</v>
       </c>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64" t="s">
-        <v>183</v>
+      <c r="Q4" s="75"/>
+      <c r="R4" s="75"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="75"/>
+      <c r="U4" s="75" t="s">
+        <v>175</v>
       </c>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="64"/>
+      <c r="V4" s="75"/>
+      <c r="W4" s="75"/>
+      <c r="X4" s="75"/>
     </row>
     <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="63"/>
-      <c r="B5" s="74" t="s">
-        <v>110</v>
+      <c r="A5" s="74"/>
+      <c r="B5" s="45" t="s">
+        <v>106</v>
       </c>
-      <c r="C5" s="76" t="s">
+      <c r="C5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="77" t="s">
-        <v>119</v>
+      <c r="D5" s="49" t="s">
+        <v>111</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="76" t="s">
+      <c r="F5" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="G5" s="76" t="s">
+      <c r="G5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="75"/>
-      <c r="I5" s="77" t="s">
-        <v>119</v>
+      <c r="H5" s="82"/>
+      <c r="I5" s="49" t="s">
+        <v>111</v>
       </c>
-      <c r="J5" s="77" t="s">
+      <c r="J5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="76" t="s">
+      <c r="K5" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="L5" s="76" t="s">
+      <c r="L5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="75"/>
-      <c r="N5" s="74" t="s">
+      <c r="M5" s="82"/>
+      <c r="N5" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="O5" s="74" t="s">
+      <c r="O5" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="76" t="s">
+      <c r="P5" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="Q5" s="76" t="s">
+      <c r="Q5" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="76" t="s">
+      <c r="R5" s="46" t="s">
         <v>8</v>
       </c>
-      <c r="S5" s="76" t="s">
+      <c r="S5" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="76" t="s">
+      <c r="T5" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="U5" s="77" t="s">
-        <v>124</v>
+      <c r="U5" s="49" t="s">
+        <v>116</v>
       </c>
-      <c r="V5" s="77" t="s">
-        <v>123</v>
+      <c r="V5" s="49" t="s">
+        <v>115</v>
       </c>
-      <c r="W5" s="77" t="s">
-        <v>122</v>
+      <c r="W5" s="49" t="s">
+        <v>114</v>
       </c>
-      <c r="X5" s="77" t="s">
-        <v>121</v>
+      <c r="X5" s="49" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="80"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="80"/>
-      <c r="R6" s="80"/>
-      <c r="S6" s="80"/>
-      <c r="T6" s="80"/>
-      <c r="U6" s="80"/>
-      <c r="V6" s="80"/>
-      <c r="W6" s="80"/>
-      <c r="X6" s="80"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="51"/>
+      <c r="U6" s="51"/>
+      <c r="V6" s="51"/>
+      <c r="W6" s="51"/>
+      <c r="X6" s="51"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
@@ -22957,7 +22955,7 @@
       <c r="X204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5MoBerxGW38XtvVoP3/SJE+geSy1RU407xatdnoIimKwmWmo6IfQuoUpGYdZXtSmnIdbdzPw7mbYTx9CnEnn7Q==" saltValue="yqDZ9043T5esDRqrRenUPw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="B2:C4"/>
@@ -22981,14 +22979,14 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D5" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{4DEB9E5B-16C0-49D0-834F-E9F1B54E470C}"/>
-    <hyperlink ref="I5" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{BD7C0CE3-847D-412E-82E1-FCED900CF562}"/>
-    <hyperlink ref="U5" r:id="rId3" location="reasonsDaysLost" display="REASON_1_CODE" xr:uid="{A903851E-2541-4BD3-B8BA-DD3DEC50339C}"/>
+    <hyperlink ref="D5" r:id="rId1" location="countries" xr:uid="{4DEB9E5B-16C0-49D0-834F-E9F1B54E470C}"/>
+    <hyperlink ref="I5" r:id="rId2" location="countries" xr:uid="{BD7C0CE3-847D-412E-82E1-FCED900CF562}"/>
+    <hyperlink ref="U5" r:id="rId3" location="reasonsDaysLost" xr:uid="{A903851E-2541-4BD3-B8BA-DD3DEC50339C}"/>
     <hyperlink ref="V5" r:id="rId4" location="reasonsDaysLost" display="REASON_2_CODE" xr:uid="{97696E2A-D771-4DE7-BD06-1B0737D662F5}"/>
     <hyperlink ref="W5" r:id="rId5" location="reasonsDaysLost" display="REASON_3_CODE" xr:uid="{DDC8B8E4-165B-40F3-9FF0-D7029574446F}"/>
     <hyperlink ref="X5" r:id="rId6" location="reasonsDaysLost" display="REASON_4_CODE" xr:uid="{D28A352C-1A1C-4FB8-A48F-5E310525AEF4}"/>
-    <hyperlink ref="E5" r:id="rId7" location="Ports" display="PORT_CODE" xr:uid="{5B1C3021-F6F9-4F61-9E0E-4225D5395400}"/>
-    <hyperlink ref="J5" r:id="rId8" location="Ports" display="PORT_CODE" xr:uid="{93A72983-23E8-4E45-8EB9-744217E6A48E}"/>
+    <hyperlink ref="E5" r:id="rId7" location="Ports" xr:uid="{5B1C3021-F6F9-4F61-9E0E-4225D5395400}"/>
+    <hyperlink ref="J5" r:id="rId8" location="Ports" xr:uid="{93A72983-23E8-4E45-8EB9-744217E6A48E}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -23011,7 +23009,7 @@
     <col min="6" max="6" width="9.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="15.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="27" style="3" customWidth="1"/>
     <col min="10" max="10" width="25.7109375" style="3" customWidth="1"/>
     <col min="11" max="11" width="26.28515625" style="3" customWidth="1"/>
     <col min="12" max="12" width="11.7109375" style="3" bestFit="1" customWidth="1"/>
@@ -23042,122 +23040,118 @@
       <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
-        <v>87</v>
+      <c r="A2" s="95" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="86"/>
-      <c r="G2" s="81" t="s">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="82"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="144" t="s">
-        <v>191</v>
+      <c r="H2" s="87"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="93" t="s">
+        <v>199</v>
       </c>
-      <c r="K2" s="78" t="s">
+      <c r="K2" s="100" t="s">
+        <v>118</v>
+      </c>
+      <c r="L2" s="83" t="s">
+        <v>107</v>
+      </c>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="85"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="96"/>
+      <c r="B3" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="89" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="90" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="91" t="s">
         <v>111</v>
       </c>
-      <c r="L2" s="84" t="s">
-        <v>112</v>
+      <c r="H3" s="93" t="s">
+        <v>4</v>
       </c>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="86"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="63" t="s">
-        <v>12</v>
+      <c r="I3" s="137" t="s">
+        <v>198</v>
       </c>
-      <c r="C3" s="99" t="s">
-        <v>120</v>
+      <c r="J3" s="139"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="102" t="s">
+        <v>183</v>
       </c>
-      <c r="D3" s="65" t="s">
-        <v>2</v>
+      <c r="M3" s="102"/>
+      <c r="N3" s="102" t="s">
+        <v>184</v>
       </c>
-      <c r="E3" s="71" t="s">
-        <v>13</v>
+      <c r="O3" s="102"/>
+      <c r="P3" s="92" t="s">
+        <v>16</v>
       </c>
-      <c r="F3" s="64" t="s">
-        <v>14</v>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="97"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="52" t="s">
+        <v>3</v>
       </c>
-      <c r="G3" s="87" t="s">
+      <c r="M4" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="H3" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="88" t="s">
-        <v>113</v>
-      </c>
-      <c r="J3" s="87" t="s">
-        <v>125</v>
-      </c>
-      <c r="K3" s="89" t="s">
-        <v>126</v>
-      </c>
-      <c r="L3" s="72" t="s">
-        <v>192</v>
-      </c>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72" t="s">
-        <v>193</v>
-      </c>
-      <c r="O3" s="72"/>
-      <c r="P3" s="90" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="98"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="93" t="s">
+      <c r="N4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="102" t="s">
-        <v>127</v>
+      <c r="O4" s="56" t="s">
+        <v>119</v>
       </c>
-      <c r="N4" s="94" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="102" t="s">
-        <v>127</v>
-      </c>
-      <c r="P4" s="90"/>
+      <c r="P4" s="92"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="95"/>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
-      <c r="L5" s="95"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="95"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="95"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -26742,8 +26736,13 @@
       <c r="P204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="loCcDutONBiXlJqS7jFwjpcmO121MZrDewcncGPPRVgUv73enkrcRPZs4v6OMfPiFQDnf3etYloi77X9bD5i6w==" saltValue="cVv4QLimhWO21UvJ9LYbUQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:K4"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:I2"/>
     <mergeCell ref="L2:P2"/>
@@ -26755,25 +26754,20 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:M3"/>
     <mergeCell ref="N3:O3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 C3:C4 H3:H4 K3:K4 G3:G4 J3:J4 O5" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 C3:C4 G3:H4 O5 J2:K2" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="C3:C4" r:id="rId1" location="countries" display="FLAG_OR_CHARTERING_CODE" xr:uid="{97FEB1BE-6CF4-478E-AC2A-4A1593F1C1A5}"/>
     <hyperlink ref="G3" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{8791D884-795E-400D-B48D-CE9638A5A2B5}"/>
-    <hyperlink ref="J3" r:id="rId3" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{319F558C-0F36-4D91-9564-E88A253E4F33}"/>
-    <hyperlink ref="M4" r:id="rId4" location="countries" display="NATIONALITY_CODE" xr:uid="{FF3BA25E-DB4E-45B8-AD06-4472D5EE754B}"/>
-    <hyperlink ref="O4" r:id="rId5" location="countries" display="NATIONALITY_CODE" xr:uid="{58541663-F960-49A0-B08C-F339EB147F10}"/>
-    <hyperlink ref="H3" r:id="rId6" display="PORT_CODE" xr:uid="{244118BC-9211-4E9B-89AD-768C7F081F6D}"/>
+    <hyperlink ref="M4" r:id="rId3" location="countries" xr:uid="{FF3BA25E-DB4E-45B8-AD06-4472D5EE754B}"/>
+    <hyperlink ref="O4" r:id="rId4" location="countries" xr:uid="{58541663-F960-49A0-B08C-F339EB147F10}"/>
+    <hyperlink ref="H3" r:id="rId5" display="PORT_CODE" xr:uid="{244118BC-9211-4E9B-89AD-768C7F081F6D}"/>
+    <hyperlink ref="J2" r:id="rId6" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{319F558C-0F36-4D91-9564-E88A253E4F33}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26816,73 +26810,73 @@
       <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
-        <v>87</v>
+      <c r="A2" s="95" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="73" t="s">
-        <v>194</v>
+      <c r="B2" s="103" t="s">
+        <v>185</v>
       </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73" t="s">
-        <v>195</v>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103" t="s">
+        <v>186</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="66" t="s">
+      <c r="A3" s="96"/>
+      <c r="B3" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="78"/>
+      <c r="K3" s="81" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="97"/>
+      <c r="B4" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="71" t="s">
-        <v>54</v>
+      <c r="D4" s="46" t="s">
+        <v>0</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="E4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="82"/>
+      <c r="G4" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="H4" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="71" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="98"/>
-      <c r="B4" s="77" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="76" t="s">
+      <c r="I4" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="76" t="s">
+      <c r="J4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="75"/>
-      <c r="G4" s="77" t="s">
-        <v>119</v>
-      </c>
-      <c r="H4" s="77" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="76" t="s">
-        <v>0</v>
-      </c>
-      <c r="J4" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="75"/>
+      <c r="K4" s="82"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -29485,15 +29479,15 @@
       <c r="K204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ibhZce0kqxtasRSQFP5/VH6xWywr0bLnrHwWmWqc5mZ7Cu5Ye7zs8XZ8D5Zwx4e9eCg99celDk+ZjRu5XnzB9A==" saltValue="Cu8YzZ8HERgiuvzY19Cs1w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="7">
+    <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:K2"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:J3"/>
     <mergeCell ref="K3:K4"/>
-    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4 B4 G4 H4" xr:uid="{3B1279DC-3A2D-4A0D-93AB-26CB3B0AE330}">
@@ -29501,10 +29495,10 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" location="countries" display="COUNTRY_CODE" xr:uid="{8D3300FC-6F86-415F-AC6B-9DDE03FD16A0}"/>
-    <hyperlink ref="G4" r:id="rId2" location="countries" display="COUNTRY_CODE" xr:uid="{CF77365D-9090-4AE6-ABA5-779409F5DE2E}"/>
-    <hyperlink ref="C4" r:id="rId3" location="Ports" display="PORT_CODE" xr:uid="{9D055D8E-BB15-4868-A672-20C620D20414}"/>
-    <hyperlink ref="H4" r:id="rId4" location="Ports" display="PORT_CODE" xr:uid="{D6729014-A717-47B0-A571-0625D8189490}"/>
+    <hyperlink ref="B4" r:id="rId1" location="countries" xr:uid="{8D3300FC-6F86-415F-AC6B-9DDE03FD16A0}"/>
+    <hyperlink ref="G4" r:id="rId2" location="countries" xr:uid="{CF77365D-9090-4AE6-ABA5-779409F5DE2E}"/>
+    <hyperlink ref="C4" r:id="rId3" location="Ports" xr:uid="{9D055D8E-BB15-4868-A672-20C620D20414}"/>
+    <hyperlink ref="H4" r:id="rId4" location="Ports" xr:uid="{D6729014-A717-47B0-A571-0625D8189490}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29519,16 +29513,16 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" style="3" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="21.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="3"/>
-    <col min="6" max="6" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="19" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="3"/>
-    <col min="9" max="9" width="14.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="3" customWidth="1"/>
     <col min="10" max="10" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.5703125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="37.140625" style="3" customWidth="1"/>
     <col min="12" max="15" width="16.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="13.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.140625" style="3"/>
@@ -29599,238 +29593,238 @@
       <c r="AO1" s="39"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
-        <v>87</v>
+      <c r="A2" s="95" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="66" t="s">
-        <v>151</v>
+      <c r="B2" s="76" t="s">
+        <v>143</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="68"/>
-      <c r="U2" s="66" t="s">
-        <v>150</v>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
+      <c r="P2" s="77"/>
+      <c r="Q2" s="77"/>
+      <c r="R2" s="77"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="76" t="s">
+        <v>142</v>
       </c>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="67"/>
-      <c r="Y2" s="67"/>
-      <c r="Z2" s="67"/>
-      <c r="AA2" s="67"/>
-      <c r="AB2" s="67"/>
-      <c r="AC2" s="67"/>
-      <c r="AD2" s="67"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="67"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="66" t="s">
-        <v>196</v>
+      <c r="V2" s="77"/>
+      <c r="W2" s="77"/>
+      <c r="X2" s="77"/>
+      <c r="Y2" s="77"/>
+      <c r="Z2" s="77"/>
+      <c r="AA2" s="77"/>
+      <c r="AB2" s="77"/>
+      <c r="AC2" s="77"/>
+      <c r="AD2" s="77"/>
+      <c r="AE2" s="77"/>
+      <c r="AF2" s="77"/>
+      <c r="AG2" s="78"/>
+      <c r="AH2" s="76" t="s">
+        <v>187</v>
       </c>
-      <c r="AI2" s="67"/>
-      <c r="AJ2" s="67"/>
-      <c r="AK2" s="67"/>
-      <c r="AL2" s="67"/>
-      <c r="AM2" s="67"/>
-      <c r="AN2" s="67"/>
-      <c r="AO2" s="67"/>
+      <c r="AI2" s="77"/>
+      <c r="AJ2" s="77"/>
+      <c r="AK2" s="77"/>
+      <c r="AL2" s="77"/>
+      <c r="AM2" s="77"/>
+      <c r="AN2" s="77"/>
+      <c r="AO2" s="77"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="71" t="s">
-        <v>114</v>
+      <c r="A3" s="96"/>
+      <c r="B3" s="81" t="s">
+        <v>200</v>
       </c>
-      <c r="C3" s="71" t="s">
-        <v>115</v>
+      <c r="C3" s="81" t="s">
+        <v>201</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="93" t="s">
+        <v>120</v>
+      </c>
+      <c r="E3" s="75" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75" t="s">
+        <v>145</v>
+      </c>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="L3" s="76" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="76" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="76" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="78"/>
+      <c r="U3" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="V3" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="W3" s="75" t="s">
+        <v>33</v>
+      </c>
+      <c r="X3" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y3" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z3" s="75" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA3" s="75" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB3" s="75" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD3" s="75" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE3" s="75" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF3" s="75" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG3" s="75" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH3" s="86" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI3" s="88"/>
+      <c r="AJ3" s="86" t="s">
+        <v>139</v>
+      </c>
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="86" t="s">
+        <v>140</v>
+      </c>
+      <c r="AM3" s="88"/>
+      <c r="AN3" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="AO3" s="88"/>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A4" s="97"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="H4" s="57" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="K4" s="82"/>
+      <c r="L4" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="M4" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="N4" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="O4" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="P4" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q4" s="49" t="s">
+        <v>127</v>
+      </c>
+      <c r="R4" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="64" t="s">
-        <v>152</v>
+      <c r="S4" s="46" t="s">
+        <v>18</v>
       </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64" t="s">
-        <v>153</v>
+      <c r="T4" s="60" t="s">
+        <v>121</v>
       </c>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
-      <c r="K3" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="L3" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="68"/>
-      <c r="S3" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="T3" s="68"/>
-      <c r="U3" s="64" t="s">
-        <v>139</v>
-      </c>
-      <c r="V3" s="64" t="s">
-        <v>22</v>
-      </c>
-      <c r="W3" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="X3" s="64" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y3" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z3" s="64" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA3" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB3" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC3" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD3" s="64" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE3" s="64" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF3" s="64" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG3" s="64" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH3" s="81" t="s">
-        <v>146</v>
-      </c>
-      <c r="AI3" s="83"/>
-      <c r="AJ3" s="81" t="s">
-        <v>147</v>
-      </c>
-      <c r="AK3" s="83"/>
-      <c r="AL3" s="81" t="s">
-        <v>148</v>
-      </c>
-      <c r="AM3" s="83"/>
-      <c r="AN3" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="AO3" s="83"/>
-    </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="98"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="106" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="106" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="107" t="s">
+      <c r="U4" s="75"/>
+      <c r="V4" s="75"/>
+      <c r="W4" s="75"/>
+      <c r="X4" s="75"/>
+      <c r="Y4" s="75"/>
+      <c r="Z4" s="75"/>
+      <c r="AA4" s="75"/>
+      <c r="AB4" s="75"/>
+      <c r="AC4" s="75"/>
+      <c r="AD4" s="75"/>
+      <c r="AE4" s="75"/>
+      <c r="AF4" s="75"/>
+      <c r="AG4" s="75"/>
+      <c r="AH4" s="59" t="s">
         <v>129</v>
       </c>
-      <c r="H4" s="106" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="106" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="107" t="s">
-        <v>129</v>
-      </c>
-      <c r="K4" s="75"/>
-      <c r="L4" s="77" t="s">
+      <c r="AI4" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="M4" s="77" t="s">
-        <v>131</v>
-      </c>
-      <c r="N4" s="77" t="s">
+      <c r="AJ4" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="O4" s="77" t="s">
+      <c r="AK4" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="P4" s="77" t="s">
+      <c r="AL4" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="Q4" s="77" t="s">
+      <c r="AM4" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="R4" s="77" t="s">
+      <c r="AN4" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="S4" s="76" t="s">
-        <v>18</v>
-      </c>
-      <c r="T4" s="111" t="s">
-        <v>60</v>
-      </c>
-      <c r="U4" s="64"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="64"/>
-      <c r="Y4" s="64"/>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="64"/>
-      <c r="AB4" s="64"/>
-      <c r="AC4" s="64"/>
-      <c r="AD4" s="64"/>
-      <c r="AE4" s="64"/>
-      <c r="AF4" s="64"/>
-      <c r="AG4" s="64"/>
-      <c r="AH4" s="108" t="s">
+      <c r="AO4" s="50" t="s">
         <v>137</v>
-      </c>
-      <c r="AI4" s="79" t="s">
-        <v>138</v>
-      </c>
-      <c r="AJ4" s="79" t="s">
-        <v>140</v>
-      </c>
-      <c r="AK4" s="79" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL4" s="79" t="s">
-        <v>142</v>
-      </c>
-      <c r="AM4" s="79" t="s">
-        <v>143</v>
-      </c>
-      <c r="AN4" s="79" t="s">
-        <v>144</v>
-      </c>
-      <c r="AO4" s="79" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
@@ -38434,8 +38428,22 @@
       <c r="AO204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="8bHlaJi3U8HDWWQ8OCWi25V/b80PL4HwFKcOKS/16PdUN4au/xhycep9yQjaF4zHWMHGim6f0LJ0nfZeKGdm3g==" saltValue="UJ23crOsxF9zWozuSSobSw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="AB3:AB4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="AN3:AO3"/>
@@ -38452,20 +38460,6 @@
     <mergeCell ref="AC3:AC4"/>
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 L4:R4 AH4:AO4" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -38473,19 +38467,19 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D3:D4" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL_CODE" xr:uid="{E1A37C4A-EA65-421A-899B-D3D4EECE0280}"/>
-    <hyperlink ref="L4" r:id="rId2" location="fishPreservationMethods" display="METHOD_1_CODE" xr:uid="{054C4D31-B8CE-4C6D-AFCE-E28DEF08D4EE}"/>
+    <hyperlink ref="D3:D4" r:id="rId1" location="hullMaterialTypes" display="HULL_MATERIAL" xr:uid="{E1A37C4A-EA65-421A-899B-D3D4EECE0280}"/>
+    <hyperlink ref="L4" r:id="rId2" location="fishPreservationMethods" xr:uid="{054C4D31-B8CE-4C6D-AFCE-E28DEF08D4EE}"/>
     <hyperlink ref="M4" r:id="rId3" location="fishPreservationMethods" display="METHOD_2_CODE" xr:uid="{0D8AEC7A-DF8E-409D-9723-73F05D91141B}"/>
     <hyperlink ref="N4" r:id="rId4" location="fishPreservationMethods" display="METHOD_3_CODE" xr:uid="{5107F5A0-8F93-4A56-A3EF-43FEB84988D7}"/>
     <hyperlink ref="O4" r:id="rId5" location="fishPreservationMethods" display="METHOD_4_CODE" xr:uid="{85356E49-E951-4859-AA55-8E3BEE0EC593}"/>
-    <hyperlink ref="P4" r:id="rId6" location="fishStorageTypes" display="TYPE_1_CODE" xr:uid="{69D37979-121E-4978-8B74-0B1FAE758759}"/>
+    <hyperlink ref="P4" r:id="rId6" location="fishStorageTypes" xr:uid="{69D37979-121E-4978-8B74-0B1FAE758759}"/>
     <hyperlink ref="Q4" r:id="rId7" location="fishStorageTypes" display="TYPE_2_CODE" xr:uid="{A038B6CC-0702-40BB-9E2B-C0526409B22A}"/>
     <hyperlink ref="R4" r:id="rId8" location="fishStorageTypes" display="TYPE_3_CODE" xr:uid="{BC38D7AE-BD26-44F6-A433-3882DFC52CA6}"/>
-    <hyperlink ref="AH4" r:id="rId9" location="wasteManagementCategories" display="CATEGORY_1_CODE" xr:uid="{ACF760F5-C6FA-4F1D-94E8-29D5B930517D}"/>
+    <hyperlink ref="AH4" r:id="rId9" location="wasteManagementCategories" xr:uid="{ACF760F5-C6FA-4F1D-94E8-29D5B930517D}"/>
     <hyperlink ref="AJ4" r:id="rId10" location="wasteManagementCategories" display="CATEGORY_2_CODE" xr:uid="{41E91FE9-A9A0-4C27-AFD6-7E9008BCFEB7}"/>
     <hyperlink ref="AL4" r:id="rId11" location="wasteManagementCategories" display="CATEGORY_3_CODE" xr:uid="{6B997577-4ECE-44DB-90B5-C3848048D262}"/>
     <hyperlink ref="AN4" r:id="rId12" location="wasteManagementCategories" display="CATEGORY_4_CODE" xr:uid="{22421F83-76AB-4229-BA11-8ED0472CDC4C}"/>
-    <hyperlink ref="AI4" r:id="rId13" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_1_CODE" xr:uid="{EB1D1F88-2839-4FC7-A159-0A8E80A8297E}"/>
+    <hyperlink ref="AI4" r:id="rId13" location="wasteDisposalMethods" xr:uid="{EB1D1F88-2839-4FC7-A159-0A8E80A8297E}"/>
     <hyperlink ref="AK4" r:id="rId14" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_2_CODE" xr:uid="{E40B146B-D992-4927-851D-DDEE2F3C2DCF}"/>
     <hyperlink ref="AM4" r:id="rId15" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_3_CODE" xr:uid="{087F515A-5BB3-49BA-B7BF-CC1331631BA2}"/>
     <hyperlink ref="AO4" r:id="rId16" location="wasteDisposalMethods" display="STORAGE_DISPOSAL_METHOD_4_CODE" xr:uid="{83C6AD1B-740F-42B7-BD5E-B2BED7456058}"/>
@@ -38504,102 +38498,104 @@
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" style="3" customWidth="1"/>
     <col min="4" max="4" width="25.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="19.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="55" t="s">
-        <v>70</v>
+      <c r="A1" s="104" t="s">
+        <v>68</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="106"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="98" t="s">
-        <v>87</v>
+      <c r="A2" s="97" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="98" t="s">
-        <v>202</v>
+      <c r="B2" s="97" t="s">
+        <v>190</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="84" t="s">
+      <c r="C2" s="97"/>
+      <c r="D2" s="83" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="85"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="74"/>
+      <c r="B3" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="74" t="s">
         <v>203</v>
       </c>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="86"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63" t="s">
+      <c r="D3" s="95" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="107" t="s">
+        <v>189</v>
+      </c>
+      <c r="F3" s="108"/>
+      <c r="G3" s="107" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="63" t="s">
-        <v>67</v>
+      <c r="H3" s="109"/>
+      <c r="I3" s="109"/>
+      <c r="J3" s="108"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="80"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="74"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="49" t="s">
+        <v>188</v>
       </c>
-      <c r="D3" s="96" t="s">
-        <v>204</v>
-      </c>
-      <c r="E3" s="109" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="115"/>
-      <c r="G3" s="109" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="115"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="70"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="63"/>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="77" t="s">
-        <v>197</v>
-      </c>
-      <c r="F5" s="107" t="s">
+      <c r="F5" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="77" t="s">
-        <v>62</v>
+      <c r="G5" s="49" t="s">
+        <v>61</v>
       </c>
-      <c r="H5" s="77" t="s">
-        <v>198</v>
+      <c r="H5" s="49" t="s">
+        <v>127</v>
       </c>
-      <c r="I5" s="77" t="s">
-        <v>199</v>
+      <c r="I5" s="49" t="s">
+        <v>128</v>
       </c>
-      <c r="J5" s="77" t="s">
-        <v>200</v>
+      <c r="J5" s="49" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -41003,7 +40999,7 @@
       <c r="J205" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="p9JMyqoEs+nSH17SGf8m/3bpHpp+IUmtAIAKW1qFHX/O1kkgvO2Fl0zeQcq0Oztmj02Q/0hg3YX7r8NpT+QZ6Q==" saltValue="aOfPgFgKExNW96qD2Jrj4A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="9">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:A5"/>
@@ -41016,7 +41012,7 @@
     <mergeCell ref="G3:J4"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5 E5 G5 H5 J5" xr:uid="{BAE7863D-70B7-46D7-97D5-3B27022E213A}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5 E5 G5 I5 J5" xr:uid="{BAE7863D-70B7-46D7-97D5-3B27022E213A}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -41053,151 +41049,151 @@
     <col min="16" max="16" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.85546875" style="3" customWidth="1"/>
-    <col min="19" max="19" width="18.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="27.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="28.140625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="19.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="105"/>
+      <c r="K1" s="105"/>
+      <c r="L1" s="105"/>
+      <c r="M1" s="105"/>
+      <c r="N1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="105"/>
+      <c r="R1" s="105"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="106"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="95" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="95" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="120" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="122"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="107" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="109"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="114" t="s">
+        <v>151</v>
+      </c>
+      <c r="K2" s="115"/>
+      <c r="L2" s="115"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" s="107" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="57"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
-        <v>87</v>
+      <c r="P2" s="109"/>
+      <c r="Q2" s="109"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="75" t="s">
+        <v>205</v>
       </c>
-      <c r="B2" s="96" t="s">
-        <v>116</v>
+      <c r="T2" s="111" t="s">
+        <v>82</v>
       </c>
-      <c r="C2" s="123" t="s">
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="96"/>
+      <c r="B3" s="96"/>
+      <c r="C3" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="120" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="121"/>
+      <c r="F3" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="79"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="80"/>
+      <c r="J3" s="117"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="118"/>
+      <c r="M3" s="119"/>
+      <c r="N3" s="74"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="110"/>
+      <c r="R3" s="80"/>
+      <c r="S3" s="75"/>
+      <c r="T3" s="112"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="97"/>
+      <c r="B4" s="97"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="90"/>
+      <c r="G4" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>153</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="J4" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="K4" s="55" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="125"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="74" t="s">
+      <c r="M4" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="G2" s="109" t="s">
+      <c r="N4" s="74"/>
+      <c r="O4" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" s="49" t="s">
         <v>158</v>
       </c>
-      <c r="H2" s="114"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="117" t="s">
+      <c r="Q4" s="49" t="s">
         <v>159</v>
       </c>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="63" t="s">
-        <v>72</v>
+      <c r="R4" s="46" t="s">
+        <v>34</v>
       </c>
-      <c r="O2" s="109" t="s">
-        <v>73</v>
-      </c>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="115"/>
-      <c r="S2" s="113" t="s">
-        <v>74</v>
-      </c>
-      <c r="T2" s="126" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="97"/>
-      <c r="C3" s="65" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="123" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="124"/>
-      <c r="F3" s="65" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="69"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="69"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="70"/>
-      <c r="S3" s="113"/>
-      <c r="T3" s="127"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="98"/>
-      <c r="B4" s="98"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="112" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="112" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="65"/>
-      <c r="G4" s="77" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="I4" s="77" t="s">
-        <v>162</v>
-      </c>
-      <c r="J4" s="129" t="s">
-        <v>125</v>
-      </c>
-      <c r="K4" s="129" t="s">
-        <v>163</v>
-      </c>
-      <c r="L4" s="129" t="s">
-        <v>164</v>
-      </c>
-      <c r="M4" s="129" t="s">
-        <v>165</v>
-      </c>
-      <c r="N4" s="63"/>
-      <c r="O4" s="110" t="s">
-        <v>69</v>
-      </c>
-      <c r="P4" s="77" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q4" s="77" t="s">
-        <v>167</v>
-      </c>
-      <c r="R4" s="76" t="s">
-        <v>75</v>
-      </c>
-      <c r="S4" s="113"/>
-      <c r="T4" s="128"/>
+      <c r="S4" s="75"/>
+      <c r="T4" s="113"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -45600,7 +45596,7 @@
       <c r="T204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="59DGogsV1RIKAsMxTlq5T26K6NDXnxqzkS8+VQsGrWIjMPK7tqzxpFiVdAGn0zWKql2KSHkl4UDb7crz7oJmKQ==" saltValue="khbxyODjgE2y1ALdbWgdzw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="13">
     <mergeCell ref="A1:T1"/>
@@ -45649,15 +45645,14 @@
     <col min="2" max="2" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="19.85546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="3" customWidth="1"/>
     <col min="9" max="9" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -45669,47 +45664,47 @@
       <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
-        <v>87</v>
+      <c r="A2" s="95" t="s">
+        <v>83</v>
       </c>
-      <c r="B2" s="89" t="s">
-        <v>167</v>
+      <c r="B2" s="100" t="s">
+        <v>159</v>
       </c>
-      <c r="C2" s="130" t="s">
-        <v>81</v>
+      <c r="C2" s="123" t="s">
+        <v>77</v>
       </c>
-      <c r="D2" s="131"/>
-      <c r="E2" s="89" t="s">
+      <c r="D2" s="124"/>
+      <c r="E2" s="100" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="95" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="114" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="115"/>
+      <c r="I2" s="116"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="97"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="101"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="141" t="s">
         <v>168</v>
       </c>
-      <c r="F2" s="96" t="s">
-        <v>169</v>
+      <c r="H3" s="45" t="s">
+        <v>35</v>
       </c>
-      <c r="G2" s="123" t="s">
-        <v>34</v>
-      </c>
-      <c r="H2" s="125"/>
-      <c r="I2" s="124"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="98"/>
-      <c r="B3" s="92"/>
-      <c r="C3" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="129" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="92"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="133" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="129" t="s">
-        <v>170</v>
+      <c r="I3" s="55" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -47913,14 +47908,14 @@
       <c r="I203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4iEyyC/58IfPB5rnrxl4j/D6DjVzJpAXcOPn7yQDvDS853JgaHxd3xhp2iU3XH1f4NuqAlg2F29ilzERssFxiA==" saltValue="pqQWU9qpemMxXYDLv1Ww4w==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="6">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="B2:B3"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2 C3 I3 E2" xr:uid="{F74A31D4-EFBF-4D20-9A28-001D1EE627E7}">
@@ -47931,8 +47926,11 @@
     <hyperlink ref="D3" r:id="rId1" location="fates" xr:uid="{4135CEFA-EB46-489F-8386-C479D974217A}"/>
     <hyperlink ref="C3" r:id="rId2" location="typesOfFate" xr:uid="{CA3F2F8B-11EA-4E7C-B697-0331CC3614C1}"/>
     <hyperlink ref="E2" r:id="rId3" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD_CODE" xr:uid="{6F194610-022D-4514-B848-7A037E00CF0D}"/>
-    <hyperlink ref="I3" r:id="rId4" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{5DE6CF93-F591-44BB-BEE2-52BDB3386A99}"/>
+    <hyperlink ref="I3" r:id="rId4" location="weightEstimationMethods" xr:uid="{5DE6CF93-F591-44BB-BEE2-52BDB3386A99}"/>
     <hyperlink ref="B2" r:id="rId5" location="species" display="SPECIES_CODE" xr:uid="{3C35F152-403E-4D6F-9670-8BA33A2F5094}"/>
+    <hyperlink ref="B2:B3" r:id="rId6" location="species" display="SPECIES" xr:uid="{6A3C51E5-B0BB-40BE-981E-62271E229859}"/>
+    <hyperlink ref="E2:E3" r:id="rId7" location="samplingMethodsForCatchEstimation" display="SAMPLING_METHOD" xr:uid="{6F994B35-009C-47D0-B534-75C739C73F18}"/>
+    <hyperlink ref="G3" r:id="rId8" location="weightMeasurements" xr:uid="{10BAC135-27C1-41D2-8F2D-3B3B11D1FD7D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -47943,7 +47941,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:N203"/>
+  <dimension ref="A1:O203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.28515625" style="3" bestFit="1" customWidth="1"/>
@@ -47951,99 +47949,105 @@
     <col min="4" max="4" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="10.5703125" style="3" customWidth="1"/>
     <col min="7" max="7" width="25.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="30.7109375" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="15" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="58" t="s">
+    <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="125" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="126"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="96" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" s="100" t="s">
-        <v>167</v>
-      </c>
-      <c r="E2" s="134" t="s">
+      <c r="B2" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="100" t="s">
+      <c r="C2" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="93" t="s">
+        <v>159</v>
+      </c>
+      <c r="E2" s="127" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="128"/>
+      <c r="G2" s="93" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="143" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="78"/>
+      <c r="K2" s="93" t="s">
+        <v>162</v>
+      </c>
+      <c r="L2" s="76" t="s">
+        <v>193</v>
+      </c>
+      <c r="M2" s="78"/>
+      <c r="N2" s="86" t="s">
+        <v>194</v>
+      </c>
+      <c r="O2" s="88"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="97"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="94"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="145" t="s">
         <v>168</v>
       </c>
-      <c r="H2" s="66" t="s">
-        <v>34</v>
+      <c r="J3" s="144" t="s">
+        <v>35</v>
       </c>
-      <c r="I2" s="68"/>
-      <c r="J2" s="100" t="s">
-        <v>170</v>
+      <c r="K3" s="94"/>
+      <c r="L3" s="49" t="s">
+        <v>163</v>
       </c>
-      <c r="K2" s="66" t="s">
-        <v>205</v>
+      <c r="M3" s="49" t="s">
+        <v>164</v>
       </c>
-      <c r="L2" s="68"/>
-      <c r="M2" s="81" t="s">
-        <v>206</v>
+      <c r="N3" s="49" t="s">
+        <v>89</v>
       </c>
-      <c r="N2" s="83"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="98"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="77" t="s">
-        <v>62</v>
+      <c r="O3" s="49" t="s">
+        <v>90</v>
       </c>
-      <c r="F3" s="77" t="s">
-        <v>82</v>
-      </c>
-      <c r="G3" s="101"/>
-      <c r="H3" s="104" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="105" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="101"/>
-      <c r="K3" s="77" t="s">
-        <v>171</v>
-      </c>
-      <c r="L3" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="M3" s="77" t="s">
-        <v>93</v>
-      </c>
-      <c r="N3" s="77" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -48058,8 +48062,9 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -48074,8 +48079,9 @@
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -48090,8 +48096,9 @@
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -48106,8 +48113,9 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -48122,8 +48130,9 @@
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -48138,8 +48147,9 @@
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -48154,8 +48164,9 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -48170,8 +48181,9 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -48186,8 +48198,9 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -48202,8 +48215,9 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -48218,8 +48232,9 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -48234,8 +48249,9 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -48250,8 +48266,9 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -48266,8 +48283,9 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -48282,8 +48300,9 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -48298,8 +48317,9 @@
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -48314,8 +48334,9 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -48330,8 +48351,9 @@
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -48346,8 +48368,9 @@
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -48362,8 +48385,9 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -48378,8 +48402,9 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -48394,8 +48419,9 @@
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -48410,8 +48436,9 @@
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -48426,8 +48453,9 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -48442,8 +48470,9 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -48458,8 +48487,9 @@
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -48474,8 +48504,9 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -48490,8 +48521,9 @@
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -48506,8 +48538,9 @@
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -48522,8 +48555,9 @@
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -48538,8 +48572,9 @@
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -48554,8 +48589,9 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -48570,8 +48606,9 @@
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -48586,8 +48623,9 @@
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O37" s="2"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -48602,8 +48640,9 @@
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -48618,8 +48657,9 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -48634,8 +48674,9 @@
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O40" s="2"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -48650,8 +48691,9 @@
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -48666,8 +48708,9 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -48682,8 +48725,9 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -48698,8 +48742,9 @@
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44" s="2"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -48714,8 +48759,9 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -48730,8 +48776,9 @@
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="2"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -48746,8 +48793,9 @@
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O47" s="2"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -48762,8 +48810,9 @@
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O48" s="2"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -48778,8 +48827,9 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -48794,8 +48844,9 @@
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O50" s="2"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -48810,8 +48861,9 @@
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O51" s="2"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -48826,8 +48878,9 @@
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O52" s="2"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -48842,8 +48895,9 @@
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -48858,8 +48912,9 @@
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -48874,8 +48929,9 @@
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
       <c r="N55" s="2"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -48890,8 +48946,9 @@
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -48906,8 +48963,9 @@
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -48922,8 +48980,9 @@
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -48938,8 +48997,9 @@
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -48954,8 +49014,9 @@
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -48970,8 +49031,9 @@
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O61" s="2"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -48986,8 +49048,9 @@
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -49002,8 +49065,9 @@
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -49018,8 +49082,9 @@
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -49034,8 +49099,9 @@
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -49050,8 +49116,9 @@
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O66" s="2"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -49066,8 +49133,9 @@
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O67" s="2"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -49082,8 +49150,9 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O68" s="2"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -49098,8 +49167,9 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O69" s="2"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -49114,8 +49184,9 @@
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O70" s="2"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -49130,8 +49201,9 @@
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O71" s="2"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -49146,8 +49218,9 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O72" s="2"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -49162,8 +49235,9 @@
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O73" s="2"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -49178,8 +49252,9 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O74" s="2"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -49194,8 +49269,9 @@
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O75" s="2"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -49210,8 +49286,9 @@
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O76" s="2"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -49226,8 +49303,9 @@
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O77" s="2"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -49242,8 +49320,9 @@
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O78" s="2"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -49258,8 +49337,9 @@
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O79" s="2"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -49274,8 +49354,9 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -49290,8 +49371,9 @@
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O81" s="2"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -49306,8 +49388,9 @@
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O82" s="2"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -49322,8 +49405,9 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O83" s="2"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -49338,8 +49422,9 @@
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O84" s="2"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -49354,8 +49439,9 @@
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O85" s="2"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -49370,8 +49456,9 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O86" s="2"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -49386,8 +49473,9 @@
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O87" s="2"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -49402,8 +49490,9 @@
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O88" s="2"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -49418,8 +49507,9 @@
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O89" s="2"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -49434,8 +49524,9 @@
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O90" s="2"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -49450,8 +49541,9 @@
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O91" s="2"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -49466,8 +49558,9 @@
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O92" s="2"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -49482,8 +49575,9 @@
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O93" s="2"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -49498,8 +49592,9 @@
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O94" s="2"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -49514,8 +49609,9 @@
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O95" s="2"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -49530,8 +49626,9 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O96" s="2"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -49546,8 +49643,9 @@
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O97" s="2"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -49562,8 +49660,9 @@
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O98" s="2"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -49578,8 +49677,9 @@
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O99" s="2"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -49594,8 +49694,9 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O100" s="2"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -49610,8 +49711,9 @@
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O101" s="2"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -49626,8 +49728,9 @@
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O102" s="2"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -49642,8 +49745,9 @@
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O103" s="2"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -49658,8 +49762,9 @@
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O104" s="2"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -49674,8 +49779,9 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O105" s="2"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -49690,8 +49796,9 @@
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O106" s="2"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -49706,8 +49813,9 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O107" s="2"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -49722,8 +49830,9 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O108" s="2"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -49738,8 +49847,9 @@
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O109" s="2"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -49754,8 +49864,9 @@
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O110" s="2"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -49770,8 +49881,9 @@
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O111" s="2"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -49786,8 +49898,9 @@
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O112" s="2"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -49802,8 +49915,9 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O113" s="2"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -49818,8 +49932,9 @@
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O114" s="2"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -49834,8 +49949,9 @@
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O115" s="2"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -49850,8 +49966,9 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O116" s="2"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -49866,8 +49983,9 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O117" s="2"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -49882,8 +50000,9 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O118" s="2"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -49898,8 +50017,9 @@
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O119" s="2"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -49914,8 +50034,9 @@
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="2"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O120" s="2"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -49930,8 +50051,9 @@
       <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O121" s="2"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -49946,8 +50068,9 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O122" s="2"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -49962,8 +50085,9 @@
       <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O123" s="2"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -49978,8 +50102,9 @@
       <c r="L124" s="2"/>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O124" s="2"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -49994,8 +50119,9 @@
       <c r="L125" s="2"/>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O125" s="2"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -50010,8 +50136,9 @@
       <c r="L126" s="2"/>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O126" s="2"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -50026,8 +50153,9 @@
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O127" s="2"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -50042,8 +50170,9 @@
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O128" s="2"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -50058,8 +50187,9 @@
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O129" s="2"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -50074,8 +50204,9 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O130" s="2"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -50090,8 +50221,9 @@
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O131" s="2"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -50106,8 +50238,9 @@
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
       <c r="N132" s="2"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O132" s="2"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -50122,8 +50255,9 @@
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O133" s="2"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -50138,8 +50272,9 @@
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O134" s="2"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -50154,8 +50289,9 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O135" s="2"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -50170,8 +50306,9 @@
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
       <c r="N136" s="2"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O136" s="2"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -50186,8 +50323,9 @@
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
       <c r="N137" s="2"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O137" s="2"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -50202,8 +50340,9 @@
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O138" s="2"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -50218,8 +50357,9 @@
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
       <c r="N139" s="2"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O139" s="2"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -50234,8 +50374,9 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O140" s="2"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -50250,8 +50391,9 @@
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O141" s="2"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -50266,8 +50408,9 @@
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O142" s="2"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -50282,8 +50425,9 @@
       <c r="L143" s="2"/>
       <c r="M143" s="2"/>
       <c r="N143" s="2"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O143" s="2"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -50298,8 +50442,9 @@
       <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O144" s="2"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -50314,8 +50459,9 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O145" s="2"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -50330,8 +50476,9 @@
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O146" s="2"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -50346,8 +50493,9 @@
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O147" s="2"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -50362,8 +50510,9 @@
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O148" s="2"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -50378,8 +50527,9 @@
       <c r="L149" s="2"/>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O149" s="2"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -50394,8 +50544,9 @@
       <c r="L150" s="2"/>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O150" s="2"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -50410,8 +50561,9 @@
       <c r="L151" s="2"/>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O151" s="2"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -50426,8 +50578,9 @@
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O152" s="2"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -50442,8 +50595,9 @@
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O153" s="2"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -50458,8 +50612,9 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O154" s="2"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -50474,8 +50629,9 @@
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O155" s="2"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -50490,8 +50646,9 @@
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O156" s="2"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -50506,8 +50663,9 @@
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O157" s="2"/>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -50522,8 +50680,9 @@
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O158" s="2"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -50538,8 +50697,9 @@
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O159" s="2"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -50554,8 +50714,9 @@
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O160" s="2"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -50570,8 +50731,9 @@
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O161" s="2"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -50586,8 +50748,9 @@
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O162" s="2"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -50602,8 +50765,9 @@
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O163" s="2"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -50618,8 +50782,9 @@
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
       <c r="N164" s="2"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O164" s="2"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -50634,8 +50799,9 @@
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O165" s="2"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -50650,8 +50816,9 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O166" s="2"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -50666,8 +50833,9 @@
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O167" s="2"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -50682,8 +50850,9 @@
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O168" s="2"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -50698,8 +50867,9 @@
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O169" s="2"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -50714,8 +50884,9 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O170" s="2"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -50730,8 +50901,9 @@
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O171" s="2"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -50746,8 +50918,9 @@
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O172" s="2"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -50762,8 +50935,9 @@
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O173" s="2"/>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -50778,8 +50952,9 @@
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
       <c r="N174" s="2"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O174" s="2"/>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -50794,8 +50969,9 @@
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O175" s="2"/>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -50810,8 +50986,9 @@
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O176" s="2"/>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -50826,8 +51003,9 @@
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O177" s="2"/>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -50842,8 +51020,9 @@
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O178" s="2"/>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -50858,8 +51037,9 @@
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O179" s="2"/>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -50874,8 +51054,9 @@
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O180" s="2"/>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -50890,8 +51071,9 @@
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O181" s="2"/>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -50906,8 +51088,9 @@
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
       <c r="N182" s="2"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O182" s="2"/>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -50922,8 +51105,9 @@
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O183" s="2"/>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -50938,8 +51122,9 @@
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O184" s="2"/>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -50954,8 +51139,9 @@
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
       <c r="N185" s="2"/>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O185" s="2"/>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -50970,8 +51156,9 @@
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O186" s="2"/>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -50986,8 +51173,9 @@
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
       <c r="N187" s="2"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O187" s="2"/>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -51002,8 +51190,9 @@
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O188" s="2"/>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -51018,8 +51207,9 @@
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O189" s="2"/>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -51034,8 +51224,9 @@
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O190" s="2"/>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -51050,8 +51241,9 @@
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O191" s="2"/>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -51066,8 +51258,9 @@
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
       <c r="N192" s="2"/>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O192" s="2"/>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -51082,8 +51275,9 @@
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O193" s="2"/>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -51098,8 +51292,9 @@
       <c r="L194" s="2"/>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O194" s="2"/>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -51114,8 +51309,9 @@
       <c r="L195" s="2"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O195" s="2"/>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -51130,8 +51326,9 @@
       <c r="L196" s="2"/>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O196" s="2"/>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -51146,8 +51343,9 @@
       <c r="L197" s="2"/>
       <c r="M197" s="2"/>
       <c r="N197" s="2"/>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O197" s="2"/>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -51162,8 +51360,9 @@
       <c r="L198" s="2"/>
       <c r="M198" s="2"/>
       <c r="N198" s="2"/>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O198" s="2"/>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -51178,8 +51377,9 @@
       <c r="L199" s="2"/>
       <c r="M199" s="2"/>
       <c r="N199" s="2"/>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O199" s="2"/>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -51194,8 +51394,9 @@
       <c r="L200" s="2"/>
       <c r="M200" s="2"/>
       <c r="N200" s="2"/>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O200" s="2"/>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -51210,8 +51411,9 @@
       <c r="L201" s="2"/>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O201" s="2"/>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -51226,8 +51428,9 @@
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
       <c r="N202" s="2"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O202" s="2"/>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -51242,38 +51445,41 @@
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
       <c r="N203" s="2"/>
+      <c r="O203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="11">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="M2:N2"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="3HHDMzybrDd9M6HxhkkhmZVdqwjkSrlHqWeFnOpXutff2Alj/O+GfyoLxVtqbb6OWda+wg+AuWyJaN84u2FoVQ==" saltValue="HSFvgX4uKdkyvNaDrqByFA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="12">
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="N2:O2"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="L2:M2"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="H2:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 E3 K3" xr:uid="{2F2D812A-9500-497F-8725-7E6E70DDE170}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 E3 L3" xr:uid="{2F2D812A-9500-497F-8725-7E6E70DDE170}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{1DD75691-93AA-4F11-A684-8796C3C9E569}"/>
+    <hyperlink ref="K2" r:id="rId1" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{1DD75691-93AA-4F11-A684-8796C3C9E569}"/>
     <hyperlink ref="E3" r:id="rId2" location="typesOfFate" xr:uid="{1403244A-A05E-4DE5-858C-EF04B6AE8958}"/>
     <hyperlink ref="F3" r:id="rId3" location="fates" xr:uid="{8E385EFE-3151-4CFA-95C6-5D0BFE8C147F}"/>
-    <hyperlink ref="K3" r:id="rId4" location="depredationSources" display="DEPREDATION_SOURCE_CODE" xr:uid="{B3917325-AB0B-4A1B-ABCC-C0C1A7A1CA59}"/>
-    <hyperlink ref="L3" r:id="rId5" location="predators" display="OBSERVED_PREDATOR_CODE" xr:uid="{5D63AB31-B94B-4525-AAD3-23EC2F149EFD}"/>
-    <hyperlink ref="N3" r:id="rId6" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{8232D868-9231-459C-8BCE-1D79652178CC}"/>
-    <hyperlink ref="M3" r:id="rId7" location="individualConditions" display="CONDITION_AT_CAPTURE_CODE" xr:uid="{EDAE3586-1489-4D94-AD4C-56C36514399C}"/>
+    <hyperlink ref="L3" r:id="rId4" location="depredationSources" xr:uid="{B3917325-AB0B-4A1B-ABCC-C0C1A7A1CA59}"/>
+    <hyperlink ref="M3" r:id="rId5" location="predators" xr:uid="{5D63AB31-B94B-4525-AAD3-23EC2F149EFD}"/>
+    <hyperlink ref="O3" r:id="rId6" location="individualConditions" display="CONDITION_AT_RELEASE_CODE" xr:uid="{8232D868-9231-459C-8BCE-1D79652178CC}"/>
+    <hyperlink ref="N3" r:id="rId7" location="individualConditions" xr:uid="{EDAE3586-1489-4D94-AD4C-56C36514399C}"/>
     <hyperlink ref="D2:D3" r:id="rId8" location="allSpecies" display="SPECIES_CODE" xr:uid="{155765ED-8ADD-47FC-B5D0-94D7C4A8AC7C}"/>
     <hyperlink ref="G2:G3" r:id="rId9" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD_CODE" xr:uid="{93E01569-6745-464C-91D0-713DC5AB5999}"/>
-    <hyperlink ref="J2:J3" r:id="rId10" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{7F016882-2E73-4F4C-B8D1-312E547767D6}"/>
+    <hyperlink ref="K2:K3" r:id="rId10" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{7F016882-2E73-4F4C-B8D1-312E547767D6}"/>
+    <hyperlink ref="I3" r:id="rId11" location="weightMeasurements" xr:uid="{D4D6390B-CA0E-48C5-B20D-5932695BAFA7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D1E2AE-ECDC-4F42-9742-748CDDC5AE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73335974-F38C-4FBA-B999-5F546D3C86B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29025" yWindow="360" windowWidth="27705" windowHeight="15090" tabRatio="803" firstSheet="5" activeTab="10" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="29085" yWindow="495" windowWidth="27705" windowHeight="15090" tabRatio="803" firstSheet="8" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="35" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="206">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -232,9 +232,6 @@
     <t>Flag / chartering state</t>
   </si>
   <si>
-    <t>KG | T</t>
-  </si>
-  <si>
     <t>TYPE</t>
   </si>
   <si>
@@ -275,9 +272,6 @@
   </si>
   <si>
     <t>DEPTH</t>
-  </si>
-  <si>
-    <t>FT | M</t>
   </si>
   <si>
     <t>Pole-and-line fishing events &gt; Bait fishing &gt; Set-level catch details &gt; Specimen details</t>
@@ -669,6 +663,12 @@
   <si>
     <t>NUMBER_OF_HOOKS_LOST</t>
   </si>
+  <si>
+    <t>UNITS</t>
+  </si>
+  <si>
+    <t>ACTIVITY_TYPE</t>
+  </si>
 </sst>
 </file>
 
@@ -809,7 +809,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -1048,12 +1048,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1191,6 +1200,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1251,6 +1273,50 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1282,42 +1348,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1400,6 +1430,14 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1421,41 +1459,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1788,39 +1800,39 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="64" t="s">
-        <v>110</v>
+      <c r="B2" s="68" t="s">
+        <v>108</v>
       </c>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="66"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="69"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="73"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="14"/>
       <c r="C4" s="15" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E4" s="17"/>
       <c r="F4" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H4" s="19"/>
     </row>
@@ -1836,7 +1848,7 @@
     <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B6" s="20"/>
       <c r="C6" s="23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D6" s="21"/>
       <c r="E6" s="21"/>
@@ -1855,26 +1867,26 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="20"/>
-      <c r="C8" s="70" t="s">
-        <v>95</v>
+      <c r="C8" s="74" t="s">
+        <v>93</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="74"/>
       <c r="E8" s="21"/>
-      <c r="F8" s="70" t="s">
-        <v>96</v>
+      <c r="F8" s="74" t="s">
+        <v>94</v>
       </c>
-      <c r="G8" s="70"/>
+      <c r="G8" s="74"/>
       <c r="H8" s="22"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20"/>
       <c r="C9" s="24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="21"/>
       <c r="F9" s="24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G9" s="25"/>
       <c r="H9" s="22"/>
@@ -1882,12 +1894,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="20"/>
       <c r="C10" s="26" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D10" s="25"/>
       <c r="E10" s="21"/>
       <c r="F10" s="21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G10" s="25"/>
       <c r="H10" s="22"/>
@@ -1904,7 +1916,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="20"/>
       <c r="C12" s="26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="21"/>
@@ -1944,7 +1956,7 @@
     <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B16" s="20"/>
       <c r="C16" s="23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="21"/>
@@ -1964,7 +1976,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="20"/>
       <c r="C18" s="26" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D18" s="30"/>
       <c r="E18" s="21"/>
@@ -1975,7 +1987,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="20"/>
       <c r="C19" s="31" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D19" s="30"/>
       <c r="E19" s="21"/>
@@ -1997,7 +2009,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="20"/>
       <c r="C21" s="26" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D21" s="30"/>
       <c r="E21" s="21"/>
@@ -2045,11 +2057,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="20"/>
-      <c r="C26" s="71"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="73"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="77"/>
       <c r="H26" s="22"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2107,7 +2119,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -2118,40 +2130,40 @@
       <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="137" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="137" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="129" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" s="129" t="s">
-        <v>84</v>
+      <c r="C2" s="137" t="s">
+        <v>82</v>
       </c>
       <c r="D2" s="93" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="85" t="s">
         <v>43</v>
       </c>
       <c r="F2" s="93" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="85" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="130"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
+      <c r="A3" s="138"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -4214,134 +4226,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="104" t="s">
-        <v>76</v>
+      <c r="A1" s="110" t="s">
+        <v>74</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="105"/>
-      <c r="U1" s="105"/>
-      <c r="V1" s="105"/>
-      <c r="W1" s="105"/>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
-      <c r="Z1" s="105"/>
-      <c r="AA1" s="106"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="111"/>
+      <c r="U1" s="111"/>
+      <c r="V1" s="111"/>
+      <c r="W1" s="111"/>
+      <c r="X1" s="111"/>
+      <c r="Y1" s="111"/>
+      <c r="Z1" s="111"/>
+      <c r="AA1" s="112"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="137" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="137" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="129" t="s">
-        <v>85</v>
+      <c r="C2" s="137" t="s">
+        <v>82</v>
       </c>
-      <c r="C2" s="129" t="s">
-        <v>84</v>
+      <c r="D2" s="96" t="s">
+        <v>158</v>
       </c>
-      <c r="D2" s="100" t="s">
-        <v>160</v>
+      <c r="E2" s="78" t="s">
+        <v>194</v>
       </c>
-      <c r="E2" s="74" t="s">
-        <v>196</v>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="79" t="s">
+        <v>195</v>
       </c>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="75" t="s">
-        <v>197</v>
-      </c>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75" t="s">
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="75"/>
-      <c r="O2" s="75"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
       <c r="P2" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="76" t="s">
-        <v>62</v>
+      <c r="Q2" s="80" t="s">
+        <v>61</v>
       </c>
-      <c r="R2" s="78"/>
-      <c r="S2" s="75" t="s">
-        <v>170</v>
+      <c r="R2" s="82"/>
+      <c r="S2" s="79" t="s">
+        <v>168</v>
       </c>
-      <c r="T2" s="75"/>
-      <c r="U2" s="75" t="s">
-        <v>171</v>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79" t="s">
+        <v>169</v>
       </c>
-      <c r="V2" s="75"/>
-      <c r="W2" s="75"/>
-      <c r="X2" s="75"/>
-      <c r="Y2" s="75"/>
-      <c r="Z2" s="75"/>
-      <c r="AA2" s="75"/>
+      <c r="V2" s="79"/>
+      <c r="W2" s="79"/>
+      <c r="X2" s="79"/>
+      <c r="Y2" s="79"/>
+      <c r="Z2" s="79"/>
+      <c r="AA2" s="79"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="130"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="101"/>
+      <c r="A3" s="138"/>
+      <c r="B3" s="138"/>
+      <c r="C3" s="138"/>
+      <c r="D3" s="98"/>
       <c r="E3" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F3" s="45" t="s">
         <v>36</v>
       </c>
       <c r="G3" s="55" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H3" s="45" t="s">
         <v>46</v>
       </c>
       <c r="I3" s="49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J3" s="46" t="s">
         <v>36</v>
       </c>
       <c r="K3" s="49" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L3" s="46" t="s">
         <v>46</v>
       </c>
       <c r="M3" s="49" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="N3" s="46" t="s">
         <v>35</v>
       </c>
       <c r="O3" s="49" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
-      <c r="P3" s="94"/>
+      <c r="P3" s="95"/>
       <c r="Q3" s="48" t="s">
+        <v>62</v>
+      </c>
+      <c r="R3" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="R3" s="48" t="s">
-        <v>64</v>
-      </c>
       <c r="S3" s="58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T3" s="46" t="s">
         <v>38</v>
@@ -4353,7 +4365,7 @@
         <v>40</v>
       </c>
       <c r="W3" s="49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="X3" s="46" t="s">
         <v>41</v>
@@ -4362,10 +4374,10 @@
         <v>42</v>
       </c>
       <c r="Z3" s="46" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AA3" s="46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -10169,7 +10181,7 @@
       <c r="AA203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="jbmvzB2N6rnp3+5rdxIfofisN6mcHQQvDBWGvTjpIl5PFoc7bVM6j2cNQWnPhxa9QYnyvLZnYTfFA1LuaeCCKQ==" saltValue="MoHkHgA/6T44FfWehpstFA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
@@ -10229,82 +10241,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="139" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
+      <c r="H1" s="140"/>
+      <c r="I1" s="140"/>
+      <c r="J1" s="140"/>
+      <c r="K1" s="140"/>
+      <c r="L1" s="141"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="61"/>
+      <c r="C2" s="80" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="80" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="81"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="133"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="81" t="s">
+      <c r="J2" s="114"/>
+      <c r="K2" s="142" t="s">
+        <v>86</v>
+      </c>
+      <c r="L2" s="79" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="143"/>
+      <c r="B3" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="76" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="76" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="77"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="107" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="108"/>
-      <c r="K2" s="134" t="s">
-        <v>88</v>
-      </c>
-      <c r="L2" s="75" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="135"/>
-      <c r="B3" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" s="103" t="s">
+      <c r="C3" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75" t="s">
+      <c r="E3" s="79"/>
+      <c r="F3" s="79" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="79" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="75"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="80"/>
-      <c r="K3" s="134"/>
-      <c r="L3" s="75"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="79"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="82"/>
+      <c r="A4" s="86"/>
       <c r="B4" s="63"/>
-      <c r="C4" s="103"/>
+      <c r="C4" s="109"/>
       <c r="D4" s="46" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="75"/>
+      <c r="F4" s="79"/>
       <c r="G4" s="46" t="s">
         <v>0</v>
       </c>
@@ -10315,10 +10327,10 @@
         <v>18</v>
       </c>
       <c r="J4" s="60" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
-      <c r="K4" s="134"/>
-      <c r="L4" s="75"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="79"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -13121,7 +13133,7 @@
       <c r="L204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/AVUnfjTnorQL1RDL+hRIDmLQoIV0DUmeJBhuJdPjFuxRJuT2rSlUHCz4336HYOj93HQegMm3ggYwlysNcvMqw==" saltValue="4kCq8AnEwXvxULYWNpaZUA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C2:E2"/>
@@ -13149,1051 +13161,1257 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:C203"/>
+  <dimension ref="A1:D203"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" style="3" customWidth="1"/>
+    <col min="2" max="3" width="21.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="38.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="75" t="s">
+      <c r="D1" s="12"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="136" t="s">
-        <v>60</v>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="64" t="s">
+        <v>166</v>
       </c>
-      <c r="C2" s="98" t="s">
-        <v>169</v>
+      <c r="B3" s="144" t="s">
+        <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="75"/>
-      <c r="B3" s="136"/>
-      <c r="C3" s="99"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="145" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="146" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" s="2"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" s="2"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" s="2"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" s="2"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" s="2"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" s="2"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" s="2"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" s="2"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" s="2"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" s="2"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" s="2"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" s="2"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" s="2"/>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" s="2"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" s="2"/>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" s="2"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" s="2"/>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" s="2"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" s="2"/>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" s="2"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" s="2"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" s="2"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" s="2"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" s="2"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" s="2"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" s="2"/>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" s="2"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" s="2"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" s="2"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" s="2"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" s="2"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" s="2"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" s="2"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" s="2"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" s="2"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" s="2"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" s="2"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" s="2"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" s="2"/>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" s="2"/>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" s="2"/>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" s="2"/>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" s="2"/>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" s="2"/>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" s="2"/>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" s="2"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" s="2"/>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" s="2"/>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" s="2"/>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" s="2"/>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" s="2"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" s="2"/>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" s="2"/>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" s="2"/>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" s="2"/>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" s="2"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" s="2"/>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" s="2"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" s="2"/>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" s="2"/>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" s="2"/>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" s="2"/>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" s="2"/>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" s="2"/>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" s="2"/>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" s="2"/>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" s="2"/>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" s="2"/>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" s="2"/>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" s="2"/>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" s="2"/>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" s="2"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" s="2"/>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" s="2"/>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" s="2"/>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" s="2"/>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" s="2"/>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" s="2"/>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" s="2"/>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" s="2"/>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" s="2"/>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" s="2"/>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" s="2"/>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" s="2"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" s="2"/>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" s="2"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" s="2"/>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" s="2"/>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" s="2"/>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" s="2"/>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" s="2"/>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" s="2"/>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" s="2"/>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" s="2"/>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" s="2"/>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" s="2"/>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D158" s="2"/>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D159" s="2"/>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D160" s="2"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D161" s="2"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D162" s="2"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D163" s="2"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D164" s="2"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D165" s="2"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D166" s="2"/>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D167" s="2"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D168" s="2"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D169" s="2"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
-    </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D170" s="2"/>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D171" s="2"/>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D172" s="2"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
-    </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D173" s="2"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
-    </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D174" s="2"/>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D175" s="2"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D176" s="2"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D177" s="2"/>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D178" s="2"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D179" s="2"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D180" s="2"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D181" s="2"/>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D182" s="2"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D183" s="2"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D184" s="2"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D185" s="2"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D186" s="2"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D187" s="2"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D188" s="2"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D189" s="2"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D190" s="2"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D191" s="2"/>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D192" s="2"/>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
-    </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D193" s="2"/>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
-    </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D194" s="2"/>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D195" s="2"/>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D196" s="2"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D197" s="2"/>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D198" s="2"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D199" s="2"/>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D200" s="2"/>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D201" s="2"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D202" s="2"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Duipbw6/iA29MxwgVj4tKcJrHzyZkC6uGBTbSN43hRLlsV57ZRo3rMebkD2QlwbUYgRokqzqwCieixB9q4uHBA==" saltValue="72umP9rt0Mq33pdn0bGOzA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C3" xr:uid="{7225598A-9FB2-4A8E-83F8-C019E42E3CA2}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 A3" xr:uid="{7225598A-9FB2-4A8E-83F8-C019E42E3CA2}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{12E3C839-C868-420D-A22A-8D4B6C11C5B1}"/>
+    <hyperlink ref="D3" r:id="rId1" location="weightEstimationMethods" display="ESTIMATION_METHOD_CODE" xr:uid="{12E3C839-C868-420D-A22A-8D4B6C11C5B1}"/>
+    <hyperlink ref="A3" r:id="rId2" location="weightMeasurements" xr:uid="{FCB320D5-74D7-4332-A1DA-5A2B732951CB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14217,7 +14435,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -14228,35 +14446,35 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="93" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="85" t="s">
         <v>43</v>
       </c>
       <c r="C2" s="93" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D2" s="93" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E2" s="93" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="85" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="81" t="s">
+      <c r="G2" s="85" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="94"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="94"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -16059,7 +16277,7 @@
       <c r="G203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ARTpSh0oApwl9TNOCTxm2HmmU6tAXdesKn+g9853QmVEEDoH/xm1ezQ7+XxJ7omdGFujG+UURXsMXFGaeFoKqw==" saltValue="SCN9O8hYMPVmW9/GyXv5RA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A2:A3"/>
@@ -16090,25 +16308,26 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E204"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="15.7109375" style="3" customWidth="1"/>
+    <col min="2" max="6" width="15.7109375" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E1" s="7"/>
+      <c r="F1" s="8"/>
+    </row>
+    <row r="2" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B2" s="45" t="s">
         <v>54</v>
@@ -16119,1426 +16338,1634 @@
       <c r="D2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="65" t="s">
+        <v>205</v>
+      </c>
+      <c r="F2" s="46" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13"/>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="2"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="2"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="2"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="2"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="2"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="2"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="2"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="2"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="2"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="2"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="2"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="2"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="2"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="2"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="2"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="2"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="2"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70" s="2"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71" s="2"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72" s="2"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73" s="2"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74" s="2"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75" s="2"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76" s="2"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77" s="2"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78" s="2"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79" s="2"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80" s="2"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81" s="2"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82" s="2"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83" s="2"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84" s="2"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
       <c r="E85" s="2"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85" s="2"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
       <c r="E86" s="2"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86" s="2"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
       <c r="E87" s="2"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87" s="2"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
       <c r="E88" s="2"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88" s="2"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
       <c r="E89" s="2"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89" s="2"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90" s="2"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91" s="2"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92" s="2"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
       <c r="E93" s="2"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93" s="2"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94" s="2"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
       <c r="E95" s="2"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95" s="2"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="2"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96" s="2"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="2"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97" s="2"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="2"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98" s="2"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99" s="2"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="2"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100" s="2"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="2"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101" s="2"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102" s="2"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
       <c r="E103" s="2"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103" s="2"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104" s="2"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105" s="2"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="2"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F106" s="2"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F107" s="2"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108" s="2"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="2"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F109" s="2"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="2"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F110" s="2"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
       <c r="E111" s="2"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111" s="2"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
       <c r="E112" s="2"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F112" s="2"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
       <c r="E113" s="2"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113" s="2"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
       <c r="E114" s="2"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114" s="2"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
       <c r="E115" s="2"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115" s="2"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116" s="2"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
       <c r="E117" s="2"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117" s="2"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
       <c r="D118" s="2"/>
       <c r="E118" s="2"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118" s="2"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
       <c r="D119" s="2"/>
       <c r="E119" s="2"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119" s="2"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
       <c r="E120" s="2"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120" s="2"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
       <c r="E121" s="2"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121" s="2"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
       <c r="E122" s="2"/>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122" s="2"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
       <c r="E123" s="2"/>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123" s="2"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
       <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124" s="2"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
       <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125" s="2"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
       <c r="E126" s="2"/>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F126" s="2"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
       <c r="D127" s="2"/>
       <c r="E127" s="2"/>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127" s="2"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
       <c r="E128" s="2"/>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128" s="2"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129" s="2"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
       <c r="E130" s="2"/>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130" s="2"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131" s="2"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
       <c r="D132" s="2"/>
       <c r="E132" s="2"/>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132" s="2"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
       <c r="D133" s="2"/>
       <c r="E133" s="2"/>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133" s="2"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
       <c r="D134" s="2"/>
       <c r="E134" s="2"/>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134" s="2"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
       <c r="D135" s="2"/>
       <c r="E135" s="2"/>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135" s="2"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
       <c r="D136" s="2"/>
       <c r="E136" s="2"/>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136" s="2"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
       <c r="D137" s="2"/>
       <c r="E137" s="2"/>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137" s="2"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
       <c r="D138" s="2"/>
       <c r="E138" s="2"/>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138" s="2"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
       <c r="D139" s="2"/>
       <c r="E139" s="2"/>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139" s="2"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="2"/>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140" s="2"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="2"/>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141" s="2"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
       <c r="E142" s="2"/>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142" s="2"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="2"/>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143" s="2"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
       <c r="E144" s="2"/>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144" s="2"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="2"/>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145" s="2"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
       <c r="D146" s="2"/>
       <c r="E146" s="2"/>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146" s="2"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
       <c r="D147" s="2"/>
       <c r="E147" s="2"/>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147" s="2"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
       <c r="E148" s="2"/>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148" s="2"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
       <c r="E149" s="2"/>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149" s="2"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="2"/>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150" s="2"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151" s="2"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
       <c r="E152" s="2"/>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152" s="2"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
       <c r="E153" s="2"/>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153" s="2"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154" s="2"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
       <c r="D155" s="2"/>
       <c r="E155" s="2"/>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155" s="2"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156" s="2"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
       <c r="E157" s="2"/>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157" s="2"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
       <c r="E158" s="2"/>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158" s="2"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
       <c r="D159" s="2"/>
       <c r="E159" s="2"/>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159" s="2"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160" s="2"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
       <c r="E161" s="2"/>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161" s="2"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
       <c r="E162" s="2"/>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162" s="2"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
       <c r="E163" s="2"/>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F163" s="2"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
       <c r="E164" s="2"/>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164" s="2"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
       <c r="D165" s="2"/>
       <c r="E165" s="2"/>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165" s="2"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
       <c r="D166" s="2"/>
       <c r="E166" s="2"/>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166" s="2"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
       <c r="E167" s="2"/>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167" s="2"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168" s="2"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
       <c r="D169" s="2"/>
       <c r="E169" s="2"/>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169" s="2"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
       <c r="E170" s="2"/>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170" s="2"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
       <c r="E171" s="2"/>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171" s="2"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F172" s="2"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F173" s="2"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F174" s="2"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F175" s="2"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F176" s="2"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
       <c r="E177" s="2"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F177" s="2"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
       <c r="E178" s="2"/>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F178" s="2"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
       <c r="D179" s="2"/>
       <c r="E179" s="2"/>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F179" s="2"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F180" s="2"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F181" s="2"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F182" s="2"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F183" s="2"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F184" s="2"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F185" s="2"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F186" s="2"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F187" s="2"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F188" s="2"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F189" s="2"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F190" s="2"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F191" s="2"/>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F192" s="2"/>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F193" s="2"/>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F194" s="2"/>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F195" s="2"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F196" s="2"/>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F197" s="2"/>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F198" s="2"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F199" s="2"/>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F200" s="2"/>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F201" s="2"/>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F202" s="2"/>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F203" s="2"/>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fUJQpTmfk3fQcmDfjKBS8ty6Ld31zauJ5dyElb09yHM9Zws0ZSfMDELQItAG7qij67mkNyt8HerkeouhUOSOOQ==" saltValue="Q3J8NTvP20OfjgQUKJxM3Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" location="surfaceFisheryActivityTypes" xr:uid="{3659540C-53C8-4CD5-9B75-E086E42A4EF1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17603,125 +18030,125 @@
       <c r="X1" s="40"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="74" t="s">
-        <v>83</v>
+      <c r="A2" s="78" t="s">
+        <v>81</v>
       </c>
-      <c r="B2" s="74" t="s">
-        <v>182</v>
-      </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="75" t="s">
-        <v>181</v>
-      </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="74" t="s">
+      <c r="B2" s="78" t="s">
         <v>180</v>
       </c>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="74"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="74"/>
-      <c r="V2" s="74"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="74"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="79" t="s">
+        <v>179</v>
+      </c>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="O2" s="78"/>
+      <c r="P2" s="78"/>
+      <c r="Q2" s="78"/>
+      <c r="R2" s="78"/>
+      <c r="S2" s="78"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="78"/>
+      <c r="V2" s="78"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="78"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="76" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="78"/>
-      <c r="I3" s="76" t="s">
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="80" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="78"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
-      <c r="P3" s="74"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="74"/>
-      <c r="S3" s="74"/>
-      <c r="T3" s="74"/>
-      <c r="U3" s="74"/>
-      <c r="V3" s="74"/>
-      <c r="W3" s="74"/>
-      <c r="X3" s="74"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="82"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="74"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="79" t="s">
-        <v>179</v>
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="83" t="s">
+        <v>177</v>
       </c>
-      <c r="E4" s="80"/>
-      <c r="F4" s="79" t="s">
-        <v>178</v>
+      <c r="E4" s="84"/>
+      <c r="F4" s="83" t="s">
+        <v>176</v>
       </c>
-      <c r="G4" s="80"/>
-      <c r="H4" s="81" t="s">
+      <c r="G4" s="84"/>
+      <c r="H4" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="79" t="s">
-        <v>179</v>
+      <c r="I4" s="83" t="s">
+        <v>177</v>
       </c>
-      <c r="J4" s="80"/>
-      <c r="K4" s="79" t="s">
-        <v>178</v>
+      <c r="J4" s="84"/>
+      <c r="K4" s="83" t="s">
+        <v>176</v>
       </c>
-      <c r="L4" s="80"/>
-      <c r="M4" s="81" t="s">
+      <c r="L4" s="84"/>
+      <c r="M4" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="74" t="s">
-        <v>177</v>
-      </c>
-      <c r="O4" s="74"/>
-      <c r="P4" s="75" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="75"/>
-      <c r="S4" s="75"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="75" t="s">
+      <c r="N4" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="V4" s="75"/>
-      <c r="W4" s="75"/>
-      <c r="X4" s="75"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="79" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="79" t="s">
+        <v>173</v>
+      </c>
+      <c r="V4" s="79"/>
+      <c r="W4" s="79"/>
+      <c r="X4" s="79"/>
     </row>
     <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
+      <c r="A5" s="78"/>
       <c r="B5" s="45" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C5" s="46" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E5" s="49" t="s">
         <v>4</v>
@@ -17732,9 +18159,9 @@
       <c r="G5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="82"/>
+      <c r="H5" s="86"/>
       <c r="I5" s="49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="J5" s="49" t="s">
         <v>4</v>
@@ -17745,7 +18172,7 @@
       <c r="L5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="82"/>
+      <c r="M5" s="86"/>
       <c r="N5" s="45" t="s">
         <v>5</v>
       </c>
@@ -17768,16 +18195,16 @@
         <v>10</v>
       </c>
       <c r="U5" s="49" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V5" s="49" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="W5" s="49" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="X5" s="49" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
@@ -23040,100 +23467,100 @@
       <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
-        <v>83</v>
+      <c r="A2" s="87" t="s">
+        <v>81</v>
       </c>
-      <c r="B2" s="83" t="s">
+      <c r="B2" s="99" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="86" t="s">
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="87"/>
-      <c r="I2" s="88"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="104"/>
       <c r="J2" s="93" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
-      <c r="K2" s="100" t="s">
-        <v>118</v>
+      <c r="K2" s="96" t="s">
+        <v>116</v>
       </c>
-      <c r="L2" s="83" t="s">
-        <v>107</v>
+      <c r="L2" s="99" t="s">
+        <v>105</v>
       </c>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="85"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+      <c r="O2" s="100"/>
+      <c r="P2" s="101"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="96"/>
-      <c r="B3" s="74" t="s">
+      <c r="A3" s="88"/>
+      <c r="B3" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="89" t="s">
-        <v>112</v>
+      <c r="C3" s="105" t="s">
+        <v>110</v>
       </c>
-      <c r="D3" s="90" t="s">
+      <c r="D3" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="81" t="s">
+      <c r="E3" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="91" t="s">
-        <v>111</v>
+      <c r="G3" s="107" t="s">
+        <v>109</v>
       </c>
       <c r="H3" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="137" t="s">
-        <v>198</v>
+      <c r="I3" s="90" t="s">
+        <v>196</v>
       </c>
-      <c r="J3" s="139"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="102" t="s">
-        <v>183</v>
+      <c r="J3" s="94"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="92" t="s">
+        <v>181</v>
       </c>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102" t="s">
-        <v>184</v>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92" t="s">
+        <v>182</v>
       </c>
-      <c r="O3" s="102"/>
-      <c r="P3" s="92" t="s">
+      <c r="O3" s="92"/>
+      <c r="P3" s="108" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="94"/>
-      <c r="K4" s="101"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="95"/>
+      <c r="I4" s="91"/>
+      <c r="J4" s="95"/>
+      <c r="K4" s="98"/>
       <c r="L4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="M4" s="56" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N4" s="53" t="s">
         <v>3</v>
       </c>
       <c r="O4" s="56" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
-      <c r="P4" s="92"/>
+      <c r="P4" s="108"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -26738,6 +27165,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="loCcDutONBiXlJqS7jFwjpcmO121MZrDewcncGPPRVgUv73enkrcRPZs4v6OMfPiFQDnf3etYloi77X9bD5i6w==" saltValue="cVv4QLimhWO21UvJ9LYbUQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="N3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="L3:M3"/>
@@ -26754,7 +27182,6 @@
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="H3:H4"/>
-    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 C3:C4 G3:H4 O5 J2:K2" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
@@ -26810,49 +27237,49 @@
       <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
-        <v>83</v>
+      <c r="A2" s="87" t="s">
+        <v>81</v>
       </c>
-      <c r="B2" s="103" t="s">
-        <v>185</v>
+      <c r="B2" s="109" t="s">
+        <v>183</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103" t="s">
-        <v>186</v>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109" t="s">
+        <v>184</v>
       </c>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+      <c r="K2" s="109"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="96"/>
-      <c r="B3" s="76" t="s">
-        <v>179</v>
+      <c r="A3" s="88"/>
+      <c r="B3" s="80" t="s">
+        <v>177</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="81" t="s">
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="76" t="s">
-        <v>179</v>
+      <c r="G3" s="80" t="s">
+        <v>177</v>
       </c>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="78"/>
-      <c r="K3" s="81" t="s">
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="85" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
+      <c r="A4" s="89"/>
       <c r="B4" s="49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" s="49" t="s">
         <v>4</v>
@@ -26863,9 +27290,9 @@
       <c r="E4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="82"/>
+      <c r="F4" s="86"/>
       <c r="G4" s="49" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="H4" s="49" t="s">
         <v>4</v>
@@ -26876,7 +27303,7 @@
       <c r="J4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="82"/>
+      <c r="K4" s="86"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -29593,156 +30020,156 @@
       <c r="AO1" s="39"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
-        <v>83</v>
+      <c r="A2" s="87" t="s">
+        <v>81</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="80" t="s">
+        <v>141</v>
+      </c>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="82"/>
+      <c r="U2" s="80" t="s">
+        <v>140</v>
+      </c>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
+      <c r="Y2" s="81"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="81"/>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="81"/>
+      <c r="AE2" s="81"/>
+      <c r="AF2" s="81"/>
+      <c r="AG2" s="82"/>
+      <c r="AH2" s="80" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI2" s="81"/>
+      <c r="AJ2" s="81"/>
+      <c r="AK2" s="81"/>
+      <c r="AL2" s="81"/>
+      <c r="AM2" s="81"/>
+      <c r="AN2" s="81"/>
+      <c r="AO2" s="81"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3" s="88"/>
+      <c r="B3" s="85" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="85" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="93" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79" t="s">
         <v>143</v>
       </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="77"/>
-      <c r="Q2" s="77"/>
-      <c r="R2" s="77"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="76" t="s">
-        <v>142</v>
+      <c r="I3" s="79"/>
+      <c r="J3" s="79"/>
+      <c r="K3" s="85" t="s">
+        <v>107</v>
       </c>
-      <c r="V2" s="77"/>
-      <c r="W2" s="77"/>
-      <c r="X2" s="77"/>
-      <c r="Y2" s="77"/>
-      <c r="Z2" s="77"/>
-      <c r="AA2" s="77"/>
-      <c r="AB2" s="77"/>
-      <c r="AC2" s="77"/>
-      <c r="AD2" s="77"/>
-      <c r="AE2" s="77"/>
-      <c r="AF2" s="77"/>
-      <c r="AG2" s="78"/>
-      <c r="AH2" s="76" t="s">
-        <v>187</v>
-      </c>
-      <c r="AI2" s="77"/>
-      <c r="AJ2" s="77"/>
-      <c r="AK2" s="77"/>
-      <c r="AL2" s="77"/>
-      <c r="AM2" s="77"/>
-      <c r="AN2" s="77"/>
-      <c r="AO2" s="77"/>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="96"/>
-      <c r="B3" s="81" t="s">
-        <v>200</v>
-      </c>
-      <c r="C3" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="D3" s="93" t="s">
-        <v>120</v>
-      </c>
-      <c r="E3" s="75" t="s">
+      <c r="L3" s="80" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75" t="s">
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="82"/>
+      <c r="P3" s="80" t="s">
         <v>145</v>
       </c>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="L3" s="76" t="s">
-        <v>146</v>
-      </c>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="76" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="76" t="s">
+      <c r="Q3" s="81"/>
+      <c r="R3" s="82"/>
+      <c r="S3" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="78"/>
-      <c r="U3" s="75" t="s">
-        <v>131</v>
+      <c r="T3" s="82"/>
+      <c r="U3" s="79" t="s">
+        <v>129</v>
       </c>
-      <c r="V3" s="75" t="s">
+      <c r="V3" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="W3" s="75" t="s">
+      <c r="W3" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="X3" s="75" t="s">
+      <c r="X3" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" s="75" t="s">
+      <c r="Y3" s="79" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="75" t="s">
+      <c r="Z3" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="AA3" s="75" t="s">
+      <c r="AA3" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="AB3" s="75" t="s">
+      <c r="AB3" s="79" t="s">
         <v>27</v>
       </c>
-      <c r="AC3" s="75" t="s">
+      <c r="AC3" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="AD3" s="75" t="s">
+      <c r="AD3" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="AE3" s="75" t="s">
+      <c r="AE3" s="79" t="s">
         <v>30</v>
       </c>
-      <c r="AF3" s="75" t="s">
+      <c r="AF3" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="AG3" s="75" t="s">
+      <c r="AG3" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="AH3" s="86" t="s">
+      <c r="AH3" s="102" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI3" s="104"/>
+      <c r="AJ3" s="102" t="s">
+        <v>137</v>
+      </c>
+      <c r="AK3" s="104"/>
+      <c r="AL3" s="102" t="s">
         <v>138</v>
       </c>
-      <c r="AI3" s="88"/>
-      <c r="AJ3" s="86" t="s">
+      <c r="AM3" s="104"/>
+      <c r="AN3" s="102" t="s">
         <v>139</v>
       </c>
-      <c r="AK3" s="88"/>
-      <c r="AL3" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="AM3" s="88"/>
-      <c r="AN3" s="86" t="s">
-        <v>141</v>
-      </c>
-      <c r="AO3" s="88"/>
+      <c r="AO3" s="104"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="94"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="57" t="s">
         <v>19</v>
       </c>
@@ -29750,7 +30177,7 @@
         <v>20</v>
       </c>
       <c r="G4" s="58" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H4" s="57" t="s">
         <v>19</v>
@@ -29759,72 +30186,72 @@
         <v>20</v>
       </c>
       <c r="J4" s="58" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
-      <c r="K4" s="82"/>
+      <c r="K4" s="86"/>
       <c r="L4" s="49" t="s">
+        <v>120</v>
+      </c>
+      <c r="M4" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="N4" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="M4" s="49" t="s">
+      <c r="O4" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="N4" s="49" t="s">
+      <c r="P4" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="O4" s="49" t="s">
+      <c r="Q4" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="P4" s="49" t="s">
+      <c r="R4" s="49" t="s">
         <v>126</v>
-      </c>
-      <c r="Q4" s="49" t="s">
-        <v>127</v>
-      </c>
-      <c r="R4" s="49" t="s">
-        <v>128</v>
       </c>
       <c r="S4" s="46" t="s">
         <v>18</v>
       </c>
       <c r="T4" s="60" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
-      <c r="U4" s="75"/>
-      <c r="V4" s="75"/>
-      <c r="W4" s="75"/>
-      <c r="X4" s="75"/>
-      <c r="Y4" s="75"/>
-      <c r="Z4" s="75"/>
-      <c r="AA4" s="75"/>
-      <c r="AB4" s="75"/>
-      <c r="AC4" s="75"/>
-      <c r="AD4" s="75"/>
-      <c r="AE4" s="75"/>
-      <c r="AF4" s="75"/>
-      <c r="AG4" s="75"/>
+      <c r="U4" s="79"/>
+      <c r="V4" s="79"/>
+      <c r="W4" s="79"/>
+      <c r="X4" s="79"/>
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="79"/>
+      <c r="AA4" s="79"/>
+      <c r="AB4" s="79"/>
+      <c r="AC4" s="79"/>
+      <c r="AD4" s="79"/>
+      <c r="AE4" s="79"/>
+      <c r="AF4" s="79"/>
+      <c r="AG4" s="79"/>
       <c r="AH4" s="59" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AI4" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="AJ4" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="AJ4" s="50" t="s">
+      <c r="AK4" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="AL4" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="AK4" s="50" t="s">
+      <c r="AM4" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="AL4" s="50" t="s">
+      <c r="AN4" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="AM4" s="50" t="s">
+      <c r="AO4" s="50" t="s">
         <v>135</v>
-      </c>
-      <c r="AN4" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="AO4" s="50" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.25">
@@ -38430,20 +38857,6 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="8bHlaJi3U8HDWWQ8OCWi25V/b80PL4HwFKcOKS/16PdUN4au/xhycep9yQjaF4zHWMHGim6f0LJ0nfZeKGdm3g==" saltValue="UJ23crOsxF9zWozuSSobSw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="AB3:AB4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="AN3:AO3"/>
@@ -38460,6 +38873,20 @@
     <mergeCell ref="AC3:AC4"/>
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="P3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 L4:R4 AH4:AO4" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -38509,93 +38936,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="104" t="s">
-        <v>68</v>
+      <c r="A1" s="110" t="s">
+        <v>67</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="106"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="112"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
-        <v>83</v>
+      <c r="A2" s="89" t="s">
+        <v>81</v>
       </c>
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="89" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="89"/>
+      <c r="D2" s="99" t="s">
+        <v>189</v>
+      </c>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="101"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="78" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="87" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="83" t="s">
-        <v>191</v>
+      <c r="E3" s="113" t="s">
+        <v>187</v>
       </c>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="85"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74" t="s">
+      <c r="F3" s="114"/>
+      <c r="G3" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="74" t="s">
-        <v>203</v>
-      </c>
-      <c r="D3" s="95" t="s">
-        <v>192</v>
-      </c>
-      <c r="E3" s="107" t="s">
-        <v>189</v>
-      </c>
-      <c r="F3" s="108"/>
-      <c r="G3" s="107" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="108"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="114"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="74"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="84"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="97"/>
+      <c r="A5" s="78"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="89"/>
       <c r="E5" s="49" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F5" s="58" t="s">
         <v>55</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I5" s="49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J5" s="49" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -41054,146 +41481,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="104" t="s">
+      <c r="A1" s="110" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="111"/>
+      <c r="J1" s="111"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="111"/>
+      <c r="O1" s="111"/>
+      <c r="P1" s="111"/>
+      <c r="Q1" s="111"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="111"/>
+      <c r="T1" s="112"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="87" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="126" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="128"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="G2" s="113" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="115"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="120" t="s">
+        <v>149</v>
+      </c>
+      <c r="K2" s="121"/>
+      <c r="L2" s="121"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-      <c r="K1" s="105"/>
-      <c r="L1" s="105"/>
-      <c r="M1" s="105"/>
-      <c r="N1" s="105"/>
-      <c r="O1" s="105"/>
-      <c r="P1" s="105"/>
-      <c r="Q1" s="105"/>
-      <c r="R1" s="105"/>
-      <c r="S1" s="105"/>
-      <c r="T1" s="106"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="95" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="120" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="122"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="107" t="s">
-        <v>150</v>
-      </c>
-      <c r="H2" s="109"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="114" t="s">
-        <v>151</v>
-      </c>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="74" t="s">
+      <c r="O2" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="O2" s="107" t="s">
-        <v>71</v>
+      <c r="P2" s="115"/>
+      <c r="Q2" s="115"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="79" t="s">
+        <v>203</v>
       </c>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="75" t="s">
-        <v>205</v>
+      <c r="T2" s="117" t="s">
+        <v>80</v>
       </c>
-      <c r="T2" s="111" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="96"/>
-      <c r="B3" s="96"/>
-      <c r="C3" s="90" t="s">
+      <c r="A3" s="88"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="120" t="s">
+      <c r="D3" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="121"/>
-      <c r="F3" s="90" t="s">
+      <c r="E3" s="127"/>
+      <c r="F3" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="79"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="80"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="118"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="119"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="79"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="112"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="116"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="124"/>
+      <c r="L3" s="124"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="116"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="97"/>
-      <c r="B4" s="97"/>
-      <c r="C4" s="90"/>
+      <c r="A4" s="89"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="106"/>
       <c r="D4" s="47" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="90"/>
+      <c r="F4" s="106"/>
       <c r="G4" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="I4" s="49" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="49" t="s">
+      <c r="J4" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="K4" s="55" t="s">
         <v>153</v>
       </c>
-      <c r="I4" s="49" t="s">
+      <c r="L4" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="J4" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="K4" s="55" t="s">
+      <c r="M4" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="L4" s="55" t="s">
+      <c r="N4" s="78"/>
+      <c r="O4" s="48" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="49" t="s">
         <v>156</v>
       </c>
-      <c r="M4" s="55" t="s">
+      <c r="Q4" s="49" t="s">
         <v>157</v>
-      </c>
-      <c r="N4" s="74"/>
-      <c r="O4" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="P4" s="49" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q4" s="49" t="s">
-        <v>159</v>
       </c>
       <c r="R4" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="75"/>
-      <c r="T4" s="113"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="119"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -45652,7 +46079,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -45664,47 +46091,47 @@
       <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
-        <v>83</v>
+      <c r="A2" s="87" t="s">
+        <v>81</v>
       </c>
-      <c r="B2" s="100" t="s">
+      <c r="B2" s="96" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="129" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="130"/>
+      <c r="E2" s="96" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="87" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="123" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="100" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="95" t="s">
-        <v>161</v>
-      </c>
-      <c r="G2" s="114" t="s">
+      <c r="G2" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="115"/>
-      <c r="I2" s="116"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="122"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="101"/>
+      <c r="A3" s="89"/>
+      <c r="B3" s="98"/>
       <c r="C3" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" s="55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
-      <c r="E3" s="101"/>
-      <c r="F3" s="97"/>
-      <c r="G3" s="141" t="s">
-        <v>168</v>
+      <c r="E3" s="98"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="65" t="s">
+        <v>166</v>
       </c>
       <c r="H3" s="45" t="s">
         <v>35</v>
       </c>
       <c r="I3" s="55" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -47957,94 +48384,94 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="131" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="132"/>
+      <c r="K1" s="132"/>
+      <c r="L1" s="132"/>
+      <c r="M1" s="132"/>
+      <c r="N1" s="132"/>
+      <c r="O1" s="132"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="87" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="85" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="95" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="81" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="81" t="s">
-        <v>84</v>
+      <c r="C2" s="85" t="s">
+        <v>82</v>
       </c>
       <c r="D2" s="93" t="s">
+        <v>157</v>
+      </c>
+      <c r="E2" s="133" t="s">
+        <v>75</v>
+      </c>
+      <c r="F2" s="134"/>
+      <c r="G2" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="135" t="s">
         <v>159</v>
       </c>
-      <c r="E2" s="127" t="s">
-        <v>77</v>
+      <c r="I2" s="80" t="s">
+        <v>34</v>
       </c>
-      <c r="F2" s="128"/>
-      <c r="G2" s="93" t="s">
+      <c r="J2" s="82"/>
+      <c r="K2" s="93" t="s">
         <v>160</v>
       </c>
-      <c r="H2" s="143" t="s">
+      <c r="L2" s="80" t="s">
+        <v>191</v>
+      </c>
+      <c r="M2" s="82"/>
+      <c r="N2" s="102" t="s">
+        <v>192</v>
+      </c>
+      <c r="O2" s="104"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="89"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="95"/>
+      <c r="H3" s="136"/>
+      <c r="I3" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="J3" s="66" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="95"/>
+      <c r="L3" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="I2" s="76" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="78"/>
-      <c r="K2" s="93" t="s">
+      <c r="M3" s="49" t="s">
         <v>162</v>
       </c>
-      <c r="L2" s="76" t="s">
-        <v>193</v>
-      </c>
-      <c r="M2" s="78"/>
-      <c r="N2" s="86" t="s">
-        <v>194</v>
-      </c>
-      <c r="O2" s="88"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="97"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="94"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="145" t="s">
-        <v>168</v>
-      </c>
-      <c r="J3" s="144" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="94"/>
-      <c r="L3" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="M3" s="49" t="s">
-        <v>164</v>
-      </c>
       <c r="N3" s="49" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="O3" s="49" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73335974-F38C-4FBA-B999-5F546D3C86B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605AC66D-78C5-4FC4-930E-789A1AE0F3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29085" yWindow="495" windowWidth="27705" windowHeight="15090" tabRatio="803" firstSheet="8" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="803" firstSheet="8" activeTab="14" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="35" r:id="rId1"/>
@@ -1213,6 +1213,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1273,6 +1283,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1289,9 +1302,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1458,16 +1468,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1800,24 +1800,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="70"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="73"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="71"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="73"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="76"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="14"/>
@@ -1867,15 +1867,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="20"/>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="D8" s="74"/>
+      <c r="D8" s="77"/>
       <c r="E8" s="21"/>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="77" t="s">
         <v>94</v>
       </c>
-      <c r="G8" s="74"/>
+      <c r="G8" s="77"/>
       <c r="H8" s="22"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2057,11 +2057,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="20"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="77"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="79"/>
+      <c r="G26" s="80"/>
       <c r="H26" s="22"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2130,40 +2130,40 @@
       <c r="H1" s="11"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="140" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="140" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="140" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="93" t="s">
+      <c r="D2" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="93" t="s">
+      <c r="F2" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="85" t="s">
+      <c r="H2" s="88" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="138"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="86"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="86"/>
-      <c r="H3" s="86"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="89"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="89"/>
+      <c r="H3" s="89"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -4226,92 +4226,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="113" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="111"/>
-      <c r="U1" s="111"/>
-      <c r="V1" s="111"/>
-      <c r="W1" s="111"/>
-      <c r="X1" s="111"/>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
+      <c r="V1" s="114"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
+      <c r="Y1" s="114"/>
+      <c r="Z1" s="114"/>
+      <c r="AA1" s="115"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="140" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="140" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="140" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="96" t="s">
+      <c r="D2" s="99" t="s">
         <v>158</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="81" t="s">
         <v>194</v>
       </c>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="79" t="s">
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79" t="s">
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="93" t="s">
+      <c r="N2" s="82"/>
+      <c r="O2" s="82"/>
+      <c r="P2" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="80" t="s">
+      <c r="Q2" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="R2" s="82"/>
-      <c r="S2" s="79" t="s">
+      <c r="R2" s="85"/>
+      <c r="S2" s="82" t="s">
         <v>168</v>
       </c>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79" t="s">
+      <c r="T2" s="82"/>
+      <c r="U2" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="V2" s="79"/>
-      <c r="W2" s="79"/>
-      <c r="X2" s="79"/>
-      <c r="Y2" s="79"/>
-      <c r="Z2" s="79"/>
-      <c r="AA2" s="79"/>
+      <c r="V2" s="82"/>
+      <c r="W2" s="82"/>
+      <c r="X2" s="82"/>
+      <c r="Y2" s="82"/>
+      <c r="Z2" s="82"/>
+      <c r="AA2" s="82"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="138"/>
-      <c r="B3" s="138"/>
-      <c r="C3" s="138"/>
-      <c r="D3" s="98"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="141"/>
+      <c r="C3" s="141"/>
+      <c r="D3" s="101"/>
       <c r="E3" s="55" t="s">
         <v>60</v>
       </c>
@@ -4345,7 +4345,7 @@
       <c r="O3" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="P3" s="95"/>
+      <c r="P3" s="98"/>
       <c r="Q3" s="48" t="s">
         <v>62</v>
       </c>
@@ -10241,82 +10241,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="140"/>
-      <c r="K1" s="140"/>
-      <c r="L1" s="141"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
+      <c r="D1" s="143"/>
+      <c r="E1" s="143"/>
+      <c r="F1" s="143"/>
+      <c r="G1" s="143"/>
+      <c r="H1" s="143"/>
+      <c r="I1" s="143"/>
+      <c r="J1" s="143"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="144"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="88" t="s">
         <v>81</v>
       </c>
       <c r="B2" s="61"/>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="83" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="80" t="s">
+      <c r="D2" s="84"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="83" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="81"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="113" t="s">
+      <c r="G2" s="84"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="114"/>
-      <c r="K2" s="142" t="s">
+      <c r="J2" s="117"/>
+      <c r="K2" s="145" t="s">
         <v>86</v>
       </c>
-      <c r="L2" s="79" t="s">
+      <c r="L2" s="82" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="143"/>
+      <c r="A3" s="146"/>
       <c r="B3" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="109" t="s">
+      <c r="C3" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79" t="s">
+      <c r="E3" s="82"/>
+      <c r="F3" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="79"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="142"/>
-      <c r="L3" s="79"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="86"/>
+      <c r="J3" s="87"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="82"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
+      <c r="A4" s="89"/>
       <c r="B4" s="63"/>
-      <c r="C4" s="109"/>
+      <c r="C4" s="112"/>
       <c r="D4" s="46" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="79"/>
+      <c r="F4" s="82"/>
       <c r="G4" s="46" t="s">
         <v>0</v>
       </c>
@@ -10329,8 +10329,8 @@
       <c r="J4" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="K4" s="142"/>
-      <c r="L4" s="79"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="82"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -13178,24 +13178,24 @@
       <c r="D1" s="12"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="144" t="s">
+      <c r="B3" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="145" t="s">
+      <c r="C3" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="D3" s="146" t="s">
+      <c r="D3" s="70" t="s">
         <v>167</v>
       </c>
     </row>
@@ -14445,36 +14445,36 @@
       <c r="G1" s="11"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="96" t="s">
         <v>163</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="93" t="s">
+      <c r="C2" s="96" t="s">
         <v>164</v>
       </c>
-      <c r="D2" s="93" t="s">
+      <c r="D2" s="96" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="93" t="s">
+      <c r="E2" s="96" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="85" t="s">
+      <c r="G2" s="88" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="95"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="86"/>
-      <c r="G3" s="86"/>
+      <c r="A3" s="98"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="89"/>
+      <c r="G3" s="89"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -18030,117 +18030,117 @@
       <c r="X1" s="40"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="81" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="81" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="78"/>
-      <c r="D2" s="79" t="s">
+      <c r="C2" s="81"/>
+      <c r="D2" s="82" t="s">
         <v>179</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="78" t="s">
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="82"/>
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="81" t="s">
         <v>178</v>
       </c>
-      <c r="O2" s="78"/>
-      <c r="P2" s="78"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="78"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="78"/>
-      <c r="U2" s="78"/>
-      <c r="V2" s="78"/>
-      <c r="W2" s="78"/>
-      <c r="X2" s="78"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="78"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="80" t="s">
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="80" t="s">
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
-      <c r="L3" s="81"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
-      <c r="V3" s="78"/>
-      <c r="W3" s="78"/>
-      <c r="X3" s="78"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="85"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
       <c r="Y3" s="4"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="78"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="83" t="s">
+      <c r="A4" s="81"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="E4" s="84"/>
-      <c r="F4" s="83" t="s">
+      <c r="E4" s="87"/>
+      <c r="F4" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="G4" s="84"/>
-      <c r="H4" s="85" t="s">
+      <c r="G4" s="87"/>
+      <c r="H4" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="83" t="s">
+      <c r="I4" s="86" t="s">
         <v>177</v>
       </c>
-      <c r="J4" s="84"/>
-      <c r="K4" s="83" t="s">
+      <c r="J4" s="87"/>
+      <c r="K4" s="86" t="s">
         <v>176</v>
       </c>
-      <c r="L4" s="84"/>
-      <c r="M4" s="85" t="s">
+      <c r="L4" s="87"/>
+      <c r="M4" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="N4" s="78" t="s">
+      <c r="N4" s="81" t="s">
         <v>175</v>
       </c>
-      <c r="O4" s="78"/>
-      <c r="P4" s="79" t="s">
+      <c r="O4" s="81"/>
+      <c r="P4" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="79"/>
-      <c r="U4" s="79" t="s">
+      <c r="Q4" s="82"/>
+      <c r="R4" s="82"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="82"/>
+      <c r="U4" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="V4" s="79"/>
-      <c r="W4" s="79"/>
-      <c r="X4" s="79"/>
+      <c r="V4" s="82"/>
+      <c r="W4" s="82"/>
+      <c r="X4" s="82"/>
     </row>
     <row r="5" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="78"/>
+      <c r="A5" s="81"/>
       <c r="B5" s="45" t="s">
         <v>104</v>
       </c>
@@ -18159,7 +18159,7 @@
       <c r="G5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="86"/>
+      <c r="H5" s="89"/>
       <c r="I5" s="49" t="s">
         <v>109</v>
       </c>
@@ -18172,7 +18172,7 @@
       <c r="L5" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="M5" s="86"/>
+      <c r="M5" s="89"/>
       <c r="N5" s="45" t="s">
         <v>5</v>
       </c>
@@ -23467,87 +23467,87 @@
       <c r="P1" s="40"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="99" t="s">
+      <c r="B2" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="102" t="s">
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="103"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="93" t="s">
+      <c r="H2" s="106"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="96" t="s">
         <v>197</v>
       </c>
-      <c r="K2" s="96" t="s">
+      <c r="K2" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="L2" s="99" t="s">
+      <c r="L2" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="101"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="104"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="88"/>
-      <c r="B3" s="78" t="s">
+      <c r="A3" s="92"/>
+      <c r="B3" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="105" t="s">
+      <c r="C3" s="108" t="s">
         <v>110</v>
       </c>
-      <c r="D3" s="106" t="s">
+      <c r="D3" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="82" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="107" t="s">
+      <c r="G3" s="110" t="s">
         <v>109</v>
       </c>
-      <c r="H3" s="93" t="s">
+      <c r="H3" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="90" t="s">
+      <c r="I3" s="94" t="s">
         <v>196</v>
       </c>
-      <c r="J3" s="94"/>
-      <c r="K3" s="97"/>
-      <c r="L3" s="92" t="s">
+      <c r="J3" s="97"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="M3" s="92"/>
-      <c r="N3" s="92" t="s">
+      <c r="M3" s="90"/>
+      <c r="N3" s="90" t="s">
         <v>182</v>
       </c>
-      <c r="O3" s="92"/>
-      <c r="P3" s="108" t="s">
+      <c r="O3" s="90"/>
+      <c r="P3" s="111" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="89"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="95"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="98"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="95"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="101"/>
       <c r="L4" s="52" t="s">
         <v>3</v>
       </c>
@@ -23560,7 +23560,7 @@
       <c r="O4" s="56" t="s">
         <v>117</v>
       </c>
-      <c r="P4" s="108"/>
+      <c r="P4" s="111"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -27165,6 +27165,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="loCcDutONBiXlJqS7jFwjpcmO121MZrDewcncGPPRVgUv73enkrcRPZs4v6OMfPiFQDnf3etYloi77X9bD5i6w==" saltValue="cVv4QLimhWO21UvJ9LYbUQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="H3:H4"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="I3:I4"/>
@@ -27181,7 +27182,6 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="P3:P4"/>
-    <mergeCell ref="H3:H4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M4 C3:C4 G3:H4 O5 J2:K2" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
@@ -27237,47 +27237,47 @@
       <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="112" t="s">
         <v>183</v>
       </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109" t="s">
+      <c r="C2" s="112"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112" t="s">
         <v>184</v>
       </c>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="88"/>
-      <c r="B3" s="80" t="s">
+      <c r="A3" s="92"/>
+      <c r="B3" s="83" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="85" t="s">
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="80" t="s">
+      <c r="G3" s="83" t="s">
         <v>177</v>
       </c>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="85" t="s">
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="88" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="89"/>
+      <c r="A4" s="93"/>
       <c r="B4" s="49" t="s">
         <v>109</v>
       </c>
@@ -27290,7 +27290,7 @@
       <c r="E4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="86"/>
+      <c r="F4" s="89"/>
       <c r="G4" s="49" t="s">
         <v>109</v>
       </c>
@@ -27303,7 +27303,7 @@
       <c r="J4" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="K4" s="86"/>
+      <c r="K4" s="89"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -30020,156 +30020,156 @@
       <c r="AO1" s="39"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="83" t="s">
         <v>141</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="82"/>
-      <c r="U2" s="80" t="s">
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="T2" s="85"/>
+      <c r="U2" s="83" t="s">
         <v>140</v>
       </c>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="81"/>
-      <c r="Y2" s="81"/>
-      <c r="Z2" s="81"/>
-      <c r="AA2" s="81"/>
-      <c r="AB2" s="81"/>
-      <c r="AC2" s="81"/>
-      <c r="AD2" s="81"/>
-      <c r="AE2" s="81"/>
-      <c r="AF2" s="81"/>
-      <c r="AG2" s="82"/>
-      <c r="AH2" s="80" t="s">
+      <c r="V2" s="84"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="84"/>
+      <c r="Y2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AD2" s="84"/>
+      <c r="AE2" s="84"/>
+      <c r="AF2" s="84"/>
+      <c r="AG2" s="85"/>
+      <c r="AH2" s="83" t="s">
         <v>185</v>
       </c>
-      <c r="AI2" s="81"/>
-      <c r="AJ2" s="81"/>
-      <c r="AK2" s="81"/>
-      <c r="AL2" s="81"/>
-      <c r="AM2" s="81"/>
-      <c r="AN2" s="81"/>
-      <c r="AO2" s="81"/>
+      <c r="AI2" s="84"/>
+      <c r="AJ2" s="84"/>
+      <c r="AK2" s="84"/>
+      <c r="AL2" s="84"/>
+      <c r="AM2" s="84"/>
+      <c r="AN2" s="84"/>
+      <c r="AO2" s="84"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="88"/>
-      <c r="B3" s="85" t="s">
+      <c r="A3" s="92"/>
+      <c r="B3" s="88" t="s">
         <v>198</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="88" t="s">
         <v>199</v>
       </c>
-      <c r="D3" s="93" t="s">
+      <c r="D3" s="96" t="s">
         <v>118</v>
       </c>
-      <c r="E3" s="79" t="s">
+      <c r="E3" s="82" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79" t="s">
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82" t="s">
         <v>143</v>
       </c>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="85" t="s">
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="L3" s="80" t="s">
+      <c r="L3" s="83" t="s">
         <v>144</v>
       </c>
-      <c r="M3" s="81"/>
-      <c r="N3" s="81"/>
-      <c r="O3" s="82"/>
-      <c r="P3" s="80" t="s">
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="83" t="s">
         <v>145</v>
       </c>
-      <c r="Q3" s="81"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="80" t="s">
+      <c r="Q3" s="84"/>
+      <c r="R3" s="85"/>
+      <c r="S3" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="T3" s="82"/>
-      <c r="U3" s="79" t="s">
+      <c r="T3" s="85"/>
+      <c r="U3" s="82" t="s">
         <v>129</v>
       </c>
-      <c r="V3" s="79" t="s">
+      <c r="V3" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="W3" s="79" t="s">
+      <c r="W3" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="X3" s="79" t="s">
+      <c r="X3" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="Y3" s="79" t="s">
+      <c r="Y3" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="Z3" s="79" t="s">
+      <c r="Z3" s="82" t="s">
         <v>25</v>
       </c>
-      <c r="AA3" s="79" t="s">
+      <c r="AA3" s="82" t="s">
         <v>26</v>
       </c>
-      <c r="AB3" s="79" t="s">
+      <c r="AB3" s="82" t="s">
         <v>27</v>
       </c>
-      <c r="AC3" s="79" t="s">
+      <c r="AC3" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="AD3" s="79" t="s">
+      <c r="AD3" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="AE3" s="79" t="s">
+      <c r="AE3" s="82" t="s">
         <v>30</v>
       </c>
-      <c r="AF3" s="79" t="s">
+      <c r="AF3" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="AG3" s="79" t="s">
+      <c r="AG3" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="AH3" s="102" t="s">
+      <c r="AH3" s="105" t="s">
         <v>136</v>
       </c>
-      <c r="AI3" s="104"/>
-      <c r="AJ3" s="102" t="s">
+      <c r="AI3" s="107"/>
+      <c r="AJ3" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="AK3" s="104"/>
-      <c r="AL3" s="102" t="s">
+      <c r="AK3" s="107"/>
+      <c r="AL3" s="105" t="s">
         <v>138</v>
       </c>
-      <c r="AM3" s="104"/>
-      <c r="AN3" s="102" t="s">
+      <c r="AM3" s="107"/>
+      <c r="AN3" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="AO3" s="104"/>
+      <c r="AO3" s="107"/>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A4" s="89"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="95"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="57" t="s">
         <v>19</v>
       </c>
@@ -30188,7 +30188,7 @@
       <c r="J4" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="K4" s="86"/>
+      <c r="K4" s="89"/>
       <c r="L4" s="49" t="s">
         <v>120</v>
       </c>
@@ -30216,19 +30216,19 @@
       <c r="T4" s="60" t="s">
         <v>119</v>
       </c>
-      <c r="U4" s="79"/>
-      <c r="V4" s="79"/>
-      <c r="W4" s="79"/>
-      <c r="X4" s="79"/>
-      <c r="Y4" s="79"/>
-      <c r="Z4" s="79"/>
-      <c r="AA4" s="79"/>
-      <c r="AB4" s="79"/>
-      <c r="AC4" s="79"/>
-      <c r="AD4" s="79"/>
-      <c r="AE4" s="79"/>
-      <c r="AF4" s="79"/>
-      <c r="AG4" s="79"/>
+      <c r="U4" s="82"/>
+      <c r="V4" s="82"/>
+      <c r="W4" s="82"/>
+      <c r="X4" s="82"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="82"/>
+      <c r="AA4" s="82"/>
+      <c r="AB4" s="82"/>
+      <c r="AC4" s="82"/>
+      <c r="AD4" s="82"/>
+      <c r="AE4" s="82"/>
+      <c r="AF4" s="82"/>
+      <c r="AG4" s="82"/>
       <c r="AH4" s="59" t="s">
         <v>127</v>
       </c>
@@ -38857,6 +38857,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="8bHlaJi3U8HDWWQ8OCWi25V/b80PL4HwFKcOKS/16PdUN4au/xhycep9yQjaF4zHWMHGim6f0LJ0nfZeKGdm3g==" saltValue="UJ23crOsxF9zWozuSSobSw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AG3:AG4"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="Z3:Z4"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="AB3:AB4"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:T2"/>
     <mergeCell ref="AN3:AO3"/>
@@ -38873,20 +38887,6 @@
     <mergeCell ref="AC3:AC4"/>
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="P3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AG3:AG4"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Y4"/>
-    <mergeCell ref="Z3:Z4"/>
-    <mergeCell ref="AA3:AA4"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3:D4 L4:R4 AH4:AO4" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -38936,76 +38936,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="115"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="93" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="93" t="s">
         <v>188</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="99" t="s">
+      <c r="C2" s="93"/>
+      <c r="D2" s="102" t="s">
         <v>189</v>
       </c>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="101"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="104"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="78"/>
-      <c r="B3" s="78" t="s">
+      <c r="A3" s="81"/>
+      <c r="B3" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="C3" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="87" t="s">
+      <c r="D3" s="91" t="s">
         <v>190</v>
       </c>
-      <c r="E3" s="113" t="s">
+      <c r="E3" s="116" t="s">
         <v>187</v>
       </c>
-      <c r="F3" s="114"/>
-      <c r="G3" s="113" t="s">
+      <c r="F3" s="117"/>
+      <c r="G3" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="H3" s="115"/>
-      <c r="I3" s="115"/>
-      <c r="J3" s="114"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+      <c r="J3" s="117"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="78"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="78"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="116"/>
-      <c r="I4" s="116"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="119"/>
+      <c r="I4" s="119"/>
+      <c r="J4" s="87"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="78"/>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="89"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="93"/>
       <c r="E5" s="49" t="s">
         <v>186</v>
       </c>
@@ -41481,110 +41481,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="113" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="111"/>
-      <c r="C1" s="111"/>
-      <c r="D1" s="111"/>
-      <c r="E1" s="111"/>
-      <c r="F1" s="111"/>
-      <c r="G1" s="111"/>
-      <c r="H1" s="111"/>
-      <c r="I1" s="111"/>
-      <c r="J1" s="111"/>
-      <c r="K1" s="111"/>
-      <c r="L1" s="111"/>
-      <c r="M1" s="111"/>
-      <c r="N1" s="111"/>
-      <c r="O1" s="111"/>
-      <c r="P1" s="111"/>
-      <c r="Q1" s="111"/>
-      <c r="R1" s="111"/>
-      <c r="S1" s="111"/>
-      <c r="T1" s="112"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="115"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="91" t="s">
         <v>106</v>
       </c>
-      <c r="C2" s="126" t="s">
+      <c r="C2" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="D2" s="128"/>
-      <c r="E2" s="127"/>
+      <c r="D2" s="131"/>
+      <c r="E2" s="130"/>
       <c r="F2" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="G2" s="113" t="s">
+      <c r="G2" s="116" t="s">
         <v>148</v>
       </c>
-      <c r="H2" s="115"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="120" t="s">
+      <c r="H2" s="118"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="123" t="s">
         <v>149</v>
       </c>
-      <c r="K2" s="121"/>
-      <c r="L2" s="121"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="78" t="s">
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="81" t="s">
         <v>69</v>
       </c>
-      <c r="O2" s="113" t="s">
+      <c r="O2" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="P2" s="115"/>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="79" t="s">
+      <c r="P2" s="118"/>
+      <c r="Q2" s="118"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="T2" s="117" t="s">
+      <c r="T2" s="120" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="88"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="106" t="s">
+      <c r="A3" s="92"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="126" t="s">
+      <c r="D3" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="127"/>
-      <c r="F3" s="106" t="s">
+      <c r="E3" s="130"/>
+      <c r="F3" s="109" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="116"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="124"/>
-      <c r="L3" s="124"/>
-      <c r="M3" s="125"/>
-      <c r="N3" s="78"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="84"/>
-      <c r="S3" s="79"/>
-      <c r="T3" s="118"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="119"/>
+      <c r="I3" s="87"/>
+      <c r="J3" s="126"/>
+      <c r="K3" s="127"/>
+      <c r="L3" s="127"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="119"/>
+      <c r="Q3" s="119"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="82"/>
+      <c r="T3" s="121"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="89"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="106"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="109"/>
       <c r="D4" s="47" t="s">
         <v>0</v>
       </c>
       <c r="E4" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="106"/>
+      <c r="F4" s="109"/>
       <c r="G4" s="49" t="s">
         <v>150</v>
       </c>
@@ -41606,7 +41606,7 @@
       <c r="M4" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="N4" s="78"/>
+      <c r="N4" s="81"/>
       <c r="O4" s="48" t="s">
         <v>66</v>
       </c>
@@ -41619,8 +41619,8 @@
       <c r="R4" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="79"/>
-      <c r="T4" s="119"/>
+      <c r="S4" s="82"/>
+      <c r="T4" s="122"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
@@ -46091,39 +46091,39 @@
       <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="99" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="129" t="s">
+      <c r="C2" s="132" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="130"/>
-      <c r="E2" s="96" t="s">
+      <c r="D2" s="133"/>
+      <c r="E2" s="99" t="s">
         <v>158</v>
       </c>
-      <c r="F2" s="87" t="s">
+      <c r="F2" s="91" t="s">
         <v>159</v>
       </c>
-      <c r="G2" s="120" t="s">
+      <c r="G2" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="121"/>
-      <c r="I2" s="122"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="125"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="89"/>
-      <c r="B3" s="98"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="101"/>
       <c r="C3" s="55" t="s">
         <v>60</v>
       </c>
       <c r="D3" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="98"/>
-      <c r="F3" s="89"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="93"/>
       <c r="G3" s="65" t="s">
         <v>166</v>
       </c>
@@ -48384,83 +48384,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="131" t="s">
+      <c r="A1" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="132"/>
-      <c r="I1" s="132"/>
-      <c r="J1" s="132"/>
-      <c r="K1" s="132"/>
-      <c r="L1" s="132"/>
-      <c r="M1" s="132"/>
-      <c r="N1" s="132"/>
-      <c r="O1" s="132"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
+      <c r="O1" s="135"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="87" t="s">
+      <c r="A2" s="91" t="s">
         <v>81</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="88" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="93" t="s">
+      <c r="D2" s="96" t="s">
         <v>157</v>
       </c>
-      <c r="E2" s="133" t="s">
+      <c r="E2" s="136" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="134"/>
-      <c r="G2" s="93" t="s">
+      <c r="F2" s="137"/>
+      <c r="G2" s="96" t="s">
         <v>158</v>
       </c>
-      <c r="H2" s="135" t="s">
+      <c r="H2" s="138" t="s">
         <v>159</v>
       </c>
-      <c r="I2" s="80" t="s">
+      <c r="I2" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="82"/>
-      <c r="K2" s="93" t="s">
+      <c r="J2" s="85"/>
+      <c r="K2" s="96" t="s">
         <v>160</v>
       </c>
-      <c r="L2" s="80" t="s">
+      <c r="L2" s="83" t="s">
         <v>191</v>
       </c>
-      <c r="M2" s="82"/>
-      <c r="N2" s="102" t="s">
+      <c r="M2" s="85"/>
+      <c r="N2" s="105" t="s">
         <v>192</v>
       </c>
-      <c r="O2" s="104"/>
+      <c r="O2" s="107"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="89"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="86"/>
-      <c r="D3" s="95"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="98"/>
       <c r="E3" s="49" t="s">
         <v>60</v>
       </c>
       <c r="F3" s="49" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="95"/>
-      <c r="H3" s="136"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="139"/>
       <c r="I3" s="67" t="s">
         <v>166</v>
       </c>
       <c r="J3" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="95"/>
+      <c r="K3" s="98"/>
       <c r="L3" s="49" t="s">
         <v>161</v>
       </c>

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schirico\Repositories\iotc-reference-forms\form_reporting_templates\ros\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\ros\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF917E31-4C8B-4597-8D57-13EF6A725296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA53A2B6-98F8-4C88-B05F-9B9C72E2A801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" tabRatio="803" firstSheet="8" activeTab="8" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="803" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="35" r:id="rId1"/>
@@ -589,9 +589,6 @@
     <t>REGISTRATION_NUMBER</t>
   </si>
   <si>
-    <t>LICESNED_TARGET_SPECIES</t>
-  </si>
-  <si>
     <t>GROSS_TONNAGE</t>
   </si>
   <si>
@@ -626,6 +623,9 @@
   </si>
   <si>
     <t>CATCH_ID</t>
+  </si>
+  <si>
+    <t>LICENSED_TARGET_SPECIES</t>
   </si>
 </sst>
 </file>
@@ -1067,9 +1067,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1220,6 +1217,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1236,9 +1236,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1299,15 +1296,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1350,10 +1338,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1370,12 +1373,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1388,6 +1385,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1719,24 +1717,24 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="63"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="64"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="66"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
@@ -1786,15 +1784,15 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="13"/>
-      <c r="C8" s="67" t="s">
+      <c r="C8" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="67"/>
+      <c r="D8" s="66"/>
       <c r="E8" s="14"/>
-      <c r="F8" s="67" t="s">
+      <c r="F8" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="67"/>
+      <c r="G8" s="66"/>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1916,7 +1914,7 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="13"/>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="24" t="s">
         <v>53</v>
       </c>
       <c r="D20" s="23"/>
@@ -1927,7 +1925,7 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="13"/>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="130" t="s">
         <v>87</v>
       </c>
       <c r="D21" s="23"/>
@@ -1976,11 +1974,11 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="69"/>
-      <c r="F26" s="69"/>
-      <c r="G26" s="70"/>
+      <c r="C26" s="67"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="69"/>
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1997,7 +1995,7 @@
       <c r="D28" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="QXspNp+1PSaoV+3Ex0NtX0ciQUE5017lUR6TNqS4/BWWl8yEi5vIO2XdkGQisIEyujfnCKqy/tmCLCQiiwT+2g==" saltValue="Y9jBrA7Hhv8OsMSdHMh9/g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="L0Y8Wko3eP5Yq8pEijOk1nzB+1M0apYi9uBJGWynVndNbEc8Y6vufqElebv2iCkLeSg4rtJpaBGk29mbM06vBw==" saltValue="fXrIfiTxdhPO9Ilm54xaVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2012,9 +2010,10 @@
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="entities" xr:uid="{08CB1E5C-74F0-4212-8433-945855227E6E}"/>
     <hyperlink ref="C20" r:id="rId2" location="fleets" xr:uid="{897BF8BC-F2E3-4772-BA0F-742223734F76}"/>
+    <hyperlink ref="C21" r:id="rId3" location="sourcesRO" xr:uid="{188C1042-2B0D-43BD-AF8E-49D3485511D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -2055,130 +2054,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="126" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="127" t="s">
+      <c r="C1" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="89" t="s">
+      <c r="D1" s="88" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="71" t="s">
+      <c r="E1" s="70" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="72" t="s">
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72" t="s">
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="72"/>
-      <c r="O1" s="72"/>
-      <c r="P1" s="86" t="s">
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="Q1" s="73" t="s">
+      <c r="Q1" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="75"/>
-      <c r="S1" s="72" t="s">
+      <c r="R1" s="74"/>
+      <c r="S1" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72" t="s">
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
-      <c r="Y1" s="72"/>
-      <c r="Z1" s="72"/>
-      <c r="AA1" s="72"/>
-      <c r="AB1" s="72"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
+      <c r="Y1" s="71"/>
+      <c r="Z1" s="71"/>
+      <c r="AA1" s="71"/>
+      <c r="AB1" s="71"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="128"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="42" t="s">
+      <c r="A2" s="127"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="42" t="s">
+      <c r="G2" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="I2" s="36" t="s">
+      <c r="I2" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="33" t="s">
+      <c r="J2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="36" t="s">
+      <c r="O2" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="P2" s="88"/>
-      <c r="Q2" s="35" t="s">
+      <c r="P2" s="87"/>
+      <c r="Q2" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="R2" s="58" t="s">
+      <c r="R2" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="S2" s="60" t="s">
+      <c r="S2" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="T2" s="60" t="s">
+      <c r="T2" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="U2" s="59" t="s">
-        <v>190</v>
+      <c r="U2" s="58" t="s">
+        <v>189</v>
       </c>
-      <c r="V2" s="33" t="s">
+      <c r="V2" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="W2" s="33" t="s">
+      <c r="W2" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="X2" s="36" t="s">
+      <c r="X2" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="Y2" s="33" t="s">
+      <c r="Y2" s="32" t="s">
+        <v>187</v>
+      </c>
+      <c r="Z2" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="Z2" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA2" s="33" t="s">
+      <c r="AA2" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" s="33" t="s">
+      <c r="AB2" s="32" t="s">
         <v>70</v>
       </c>
     </row>
@@ -8185,17 +8184,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="QfkjKQojhZfz29mQ5SGEahbHtW+1jF5g9wReJHClQmskz9aWoQpvW8D4HSYsV3MGU/4uNm+mOPzdYbNdiaqmZA==" saltValue="H9ewSGx8i6TuVkuFlH9FJg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:U1"/>
     <mergeCell ref="V1:AB1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:O1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:R1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 D1:D2 E2 G2 I2 K2 P1:P2" xr:uid="{5E4B3162-4EBB-4AB5-B30D-164A47D38785}">
@@ -8243,48 +8242,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="127" t="s">
+      <c r="A1" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="126" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="127" t="s">
+      <c r="C1" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="86" t="s">
+      <c r="D1" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="E1" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="86" t="s">
+      <c r="F1" s="85" t="s">
         <v>149</v>
       </c>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="78" t="s">
+      <c r="H1" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="95" t="s">
+      <c r="I1" s="94" t="s">
         <v>175</v>
       </c>
-      <c r="J1" s="97"/>
+      <c r="J1" s="96"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="128"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="128"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="36" t="s">
+      <c r="A2" s="127"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="87"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="36" t="s">
+      <c r="J2" s="35" t="s">
         <v>73</v>
       </c>
     </row>
@@ -10730,80 +10729,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="73" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="72" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="74"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="73" t="s">
+      <c r="D1" s="73"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="72" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="74"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="106" t="s">
+      <c r="G1" s="73"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="108"/>
-      <c r="K1" s="130" t="s">
+      <c r="J1" s="104"/>
+      <c r="K1" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="L1" s="72" t="s">
+      <c r="L1" s="71" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="129"/>
-      <c r="B2" s="49" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="48" t="s">
         <v>91</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="72" t="s">
+      <c r="D2" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72" t="s">
+      <c r="E2" s="71"/>
+      <c r="F2" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="72" t="s">
+      <c r="G2" s="71" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="72"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="72"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="71"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="79"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="33" t="s">
+      <c r="A3" s="78"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="72"/>
-      <c r="G3" s="33" t="s">
+      <c r="F3" s="71"/>
+      <c r="G3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="47" t="s">
+      <c r="J3" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="K3" s="130"/>
-      <c r="L3" s="72"/>
+      <c r="K3" s="129"/>
+      <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -13642,24 +13641,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="56" t="s">
-        <v>186</v>
+      <c r="C2" s="55" t="s">
+        <v>185</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="56" t="s">
         <v>145</v>
       </c>
     </row>
@@ -14898,36 +14897,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="86" t="s">
+      <c r="A1" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="86" t="s">
+      <c r="C1" s="85" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="86" t="s">
+      <c r="D1" s="85" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="86" t="s">
+      <c r="E1" s="85" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="78" t="s">
+      <c r="F1" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="78" t="s">
+      <c r="G1" s="77" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="88"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
+      <c r="A2" s="87"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="87"/>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
@@ -16771,19 +16770,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="33" t="s">
+      <c r="E1" s="32" t="s">
         <v>50</v>
       </c>
     </row>
@@ -18239,208 +18238,208 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="70" t="s">
         <v>163</v>
       </c>
-      <c r="C1" s="71"/>
-      <c r="D1" s="72" t="s">
+      <c r="C1" s="70"/>
+      <c r="D1" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="71" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="70" t="s">
         <v>161</v>
       </c>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="71"/>
-      <c r="T1" s="71"/>
-      <c r="U1" s="71"/>
-      <c r="V1" s="71"/>
-      <c r="W1" s="71"/>
-      <c r="X1" s="71"/>
+      <c r="O1" s="70"/>
+      <c r="P1" s="70"/>
+      <c r="Q1" s="70"/>
+      <c r="R1" s="70"/>
+      <c r="S1" s="70"/>
+      <c r="T1" s="70"/>
+      <c r="U1" s="70"/>
+      <c r="V1" s="70"/>
+      <c r="W1" s="70"/>
+      <c r="X1" s="70"/>
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="71"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="73" t="s">
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="73" t="s">
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="75"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="71"/>
-      <c r="P2" s="71"/>
-      <c r="Q2" s="71"/>
-      <c r="R2" s="71"/>
-      <c r="S2" s="71"/>
-      <c r="T2" s="71"/>
-      <c r="U2" s="71"/>
-      <c r="V2" s="71"/>
-      <c r="W2" s="71"/>
-      <c r="X2" s="71"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="74"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="70"/>
+      <c r="U2" s="70"/>
+      <c r="V2" s="70"/>
+      <c r="W2" s="70"/>
+      <c r="X2" s="70"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="76" t="s">
+      <c r="A3" s="70"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="E3" s="77"/>
-      <c r="F3" s="76" t="s">
+      <c r="E3" s="76"/>
+      <c r="F3" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="77"/>
-      <c r="H3" s="78" t="s">
+      <c r="G3" s="76"/>
+      <c r="H3" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="76" t="s">
+      <c r="I3" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="J3" s="77"/>
-      <c r="K3" s="76" t="s">
+      <c r="J3" s="76"/>
+      <c r="K3" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="L3" s="77"/>
-      <c r="M3" s="78" t="s">
+      <c r="L3" s="76"/>
+      <c r="M3" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="N3" s="71" t="s">
+      <c r="N3" s="70" t="s">
         <v>158</v>
       </c>
-      <c r="O3" s="71"/>
-      <c r="P3" s="71" t="s">
+      <c r="O3" s="70"/>
+      <c r="P3" s="70" t="s">
         <v>157</v>
       </c>
-      <c r="Q3" s="71"/>
-      <c r="R3" s="71"/>
-      <c r="S3" s="71"/>
-      <c r="T3" s="71"/>
-      <c r="U3" s="72" t="s">
+      <c r="Q3" s="70"/>
+      <c r="R3" s="70"/>
+      <c r="S3" s="70"/>
+      <c r="T3" s="70"/>
+      <c r="U3" s="71" t="s">
         <v>156</v>
       </c>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
     </row>
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="32" t="s">
+      <c r="A4" s="70"/>
+      <c r="B4" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="33" t="s">
+      <c r="F4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="79"/>
-      <c r="I4" s="36" t="s">
+      <c r="H4" s="78"/>
+      <c r="I4" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="33" t="s">
+      <c r="K4" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="33" t="s">
+      <c r="L4" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="79"/>
-      <c r="N4" s="32" t="s">
+      <c r="M4" s="78"/>
+      <c r="N4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="32" t="s">
+      <c r="O4" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="P4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="32" t="s">
+      <c r="Q4" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="33" t="s">
+      <c r="R4" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="33" t="s">
+      <c r="S4" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="T4" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="36" t="s">
+      <c r="U4" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="V4" s="36" t="s">
+      <c r="V4" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="W4" s="36" t="s">
+      <c r="W4" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="X4" s="36" t="s">
+      <c r="X4" s="35" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="38"/>
-      <c r="M5" s="38"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="38"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="38"/>
-      <c r="S5" s="38"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="38"/>
-      <c r="V5" s="38"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="38"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="37"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="37"/>
+      <c r="M5" s="37"/>
+      <c r="N5" s="37"/>
+      <c r="O5" s="37"/>
+      <c r="P5" s="37"/>
+      <c r="Q5" s="37"/>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="37"/>
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="37"/>
+      <c r="X5" s="37"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -23659,97 +23658,97 @@
       <c r="A1" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="95" t="s">
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="96"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="86" t="s">
-        <v>179</v>
+      <c r="H1" s="95"/>
+      <c r="I1" s="96"/>
+      <c r="J1" s="85" t="s">
+        <v>191</v>
       </c>
-      <c r="K1" s="89" t="s">
+      <c r="K1" s="88" t="s">
         <v>101</v>
       </c>
-      <c r="L1" s="92" t="s">
+      <c r="L1" s="91" t="s">
         <v>90</v>
       </c>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="94"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="93"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="81"/>
-      <c r="B2" s="71" t="s">
+      <c r="B2" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="98" t="s">
+      <c r="C2" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="99" t="s">
+      <c r="D2" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="78" t="s">
+      <c r="E2" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="100" t="s">
+      <c r="G2" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="H2" s="86" t="s">
+      <c r="H2" s="85" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="83" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="87"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="85" t="s">
+      <c r="J2" s="86"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="79" t="s">
         <v>164</v>
       </c>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85" t="s">
+      <c r="M2" s="79"/>
+      <c r="N2" s="79" t="s">
         <v>165</v>
       </c>
-      <c r="O2" s="85"/>
-      <c r="P2" s="101" t="s">
+      <c r="O2" s="79"/>
+      <c r="P2" s="100" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
-      <c r="B3" s="71"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="88"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="97"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="99"/>
+      <c r="H3" s="87"/>
       <c r="I3" s="84"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="39" t="s">
+      <c r="J3" s="87"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="43" t="s">
+      <c r="M3" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="N3" s="40" t="s">
+      <c r="N3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="43" t="s">
+      <c r="O3" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="P3" s="101"/>
+      <c r="P3" s="100"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -27352,8 +27351,9 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="XU08Log8a/6RzgCsAhCXVIUqBOPndw88iopL79hr8n8v2SOtQSJ43xiEPZlqn5cTto2h5aq/Geyvk+whPFWbjQ==" saltValue="FSak44J43nTVSiht1VpXBQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="H2:H3"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="I2:I3"/>
@@ -27370,10 +27370,9 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="P2:P3"/>
-    <mergeCell ref="H2:H3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 C2:C3 G2:H3 O4 J1:K1" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 C2:C3 G2:H3 O4 K1 J1:J3" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -27418,70 +27417,70 @@
       <c r="A1" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="102" t="s">
+      <c r="B1" s="101" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102" t="s">
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101" t="s">
         <v>167</v>
       </c>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="81"/>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="78" t="s">
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="73" t="s">
+      <c r="G2" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="75"/>
-      <c r="K2" s="78" t="s">
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="77" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="79"/>
-      <c r="G3" s="36" t="s">
+      <c r="F3" s="78"/>
+      <c r="G3" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="33" t="s">
+      <c r="I3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="79"/>
+      <c r="K3" s="78"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -30156,234 +30155,234 @@
       <c r="A1" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="72" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="74"/>
-      <c r="K1" s="74"/>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="74"/>
-      <c r="O1" s="74"/>
-      <c r="P1" s="74"/>
-      <c r="Q1" s="74"/>
-      <c r="R1" s="74"/>
-      <c r="S1" s="74"/>
-      <c r="T1" s="75"/>
-      <c r="U1" s="73" t="s">
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="73"/>
+      <c r="O1" s="73"/>
+      <c r="P1" s="73"/>
+      <c r="Q1" s="73"/>
+      <c r="R1" s="73"/>
+      <c r="S1" s="73"/>
+      <c r="T1" s="74"/>
+      <c r="U1" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="V1" s="74"/>
-      <c r="W1" s="74"/>
-      <c r="X1" s="74"/>
-      <c r="Y1" s="74"/>
-      <c r="Z1" s="74"/>
-      <c r="AA1" s="74"/>
-      <c r="AB1" s="74"/>
-      <c r="AC1" s="74"/>
-      <c r="AD1" s="74"/>
-      <c r="AE1" s="74"/>
-      <c r="AF1" s="74"/>
-      <c r="AG1" s="75"/>
-      <c r="AH1" s="73" t="s">
+      <c r="V1" s="73"/>
+      <c r="W1" s="73"/>
+      <c r="X1" s="73"/>
+      <c r="Y1" s="73"/>
+      <c r="Z1" s="73"/>
+      <c r="AA1" s="73"/>
+      <c r="AB1" s="73"/>
+      <c r="AC1" s="73"/>
+      <c r="AD1" s="73"/>
+      <c r="AE1" s="73"/>
+      <c r="AF1" s="73"/>
+      <c r="AG1" s="74"/>
+      <c r="AH1" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="AI1" s="74"/>
-      <c r="AJ1" s="74"/>
-      <c r="AK1" s="74"/>
-      <c r="AL1" s="74"/>
-      <c r="AM1" s="74"/>
-      <c r="AN1" s="74"/>
-      <c r="AO1" s="74"/>
+      <c r="AI1" s="73"/>
+      <c r="AJ1" s="73"/>
+      <c r="AK1" s="73"/>
+      <c r="AL1" s="73"/>
+      <c r="AM1" s="73"/>
+      <c r="AN1" s="73"/>
+      <c r="AO1" s="73"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="81"/>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="77" t="s">
         <v>180</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="D2" s="85" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="77" t="s">
+        <v>92</v>
+      </c>
+      <c r="L2" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="72" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="74"/>
+      <c r="U2" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="V2" s="71" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="71" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="71" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="71" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="71" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF2" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG2" s="71" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH2" s="94" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI2" s="96"/>
+      <c r="AJ2" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="AK2" s="96"/>
+      <c r="AL2" s="94" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM2" s="96"/>
+      <c r="AN2" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="AO2" s="96"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="A3" s="82"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="78"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="44" t="s">
         <v>181</v>
       </c>
-      <c r="D2" s="86" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="72" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="78" t="s">
-        <v>92</v>
-      </c>
-      <c r="L2" s="73" t="s">
-        <v>129</v>
-      </c>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="75"/>
-      <c r="P2" s="73" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="75"/>
-      <c r="S2" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="75"/>
-      <c r="U2" s="72" t="s">
-        <v>114</v>
-      </c>
-      <c r="V2" s="72" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" s="72" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2" s="72" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="72" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB2" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC2" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD2" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE2" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF2" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG2" s="72" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH2" s="95" t="s">
-        <v>121</v>
-      </c>
-      <c r="AI2" s="97"/>
-      <c r="AJ2" s="95" t="s">
-        <v>122</v>
-      </c>
-      <c r="AK2" s="97"/>
-      <c r="AL2" s="95" t="s">
-        <v>123</v>
-      </c>
-      <c r="AM2" s="97"/>
-      <c r="AN2" s="95" t="s">
-        <v>124</v>
-      </c>
-      <c r="AO2" s="97"/>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A3" s="82"/>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="44" t="s">
+      <c r="H3" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="I3" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="45" t="s">
-        <v>182</v>
+      <c r="J3" s="44" t="s">
+        <v>181</v>
       </c>
-      <c r="H3" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="K3" s="79"/>
-      <c r="L3" s="36" t="s">
+      <c r="K3" s="78"/>
+      <c r="L3" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="M3" s="36" t="s">
+      <c r="M3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="N3" s="36" t="s">
+      <c r="N3" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="O3" s="36" t="s">
+      <c r="O3" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="36" t="s">
+      <c r="P3" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="Q3" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="R3" s="36" t="s">
+      <c r="R3" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="S3" s="33" t="s">
+      <c r="S3" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="47" t="s">
+      <c r="T3" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="46" t="s">
+      <c r="U3" s="71"/>
+      <c r="V3" s="71"/>
+      <c r="W3" s="71"/>
+      <c r="X3" s="71"/>
+      <c r="Y3" s="71"/>
+      <c r="Z3" s="71"/>
+      <c r="AA3" s="71"/>
+      <c r="AB3" s="71"/>
+      <c r="AC3" s="71"/>
+      <c r="AD3" s="71"/>
+      <c r="AE3" s="71"/>
+      <c r="AF3" s="71"/>
+      <c r="AG3" s="71"/>
+      <c r="AH3" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="AI3" s="37" t="s">
+      <c r="AI3" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="AJ3" s="37" t="s">
+      <c r="AJ3" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="AK3" s="37" t="s">
+      <c r="AK3" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="AL3" s="37" t="s">
+      <c r="AL3" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="AM3" s="37" t="s">
+      <c r="AM3" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="AN3" s="37" t="s">
+      <c r="AN3" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="AO3" s="37" t="s">
+      <c r="AO3" s="36" t="s">
         <v>120</v>
       </c>
     </row>
@@ -38990,6 +38989,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="lNt5LYbnuQ08vRpkZezsxMNggYZu4PC+fh7ck+AE/9pVc6iyvdVLeNMHFu+xdNyS1TM0avJP5Y70ZRHmYVjgdg==" saltValue="C7Hm9uOiHYDLx4CIc3b8bw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="AB2:AB3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="AN2:AO2"/>
@@ -39006,20 +39019,6 @@
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 L3:R3 AH3:AO3" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -39076,15 +39075,15 @@
         <v>171</v>
       </c>
       <c r="C1" s="82"/>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="91" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="94"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="81"/>
@@ -39092,44 +39091,44 @@
         <v>58</v>
       </c>
       <c r="C2" s="80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D2" s="80" t="s">
         <v>173</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="F2" s="75"/>
-      <c r="G2" s="73" t="s">
+      <c r="F2" s="74"/>
+      <c r="G2" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="75"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="74"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="82"/>
       <c r="D3" s="82"/>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="J3" s="36" t="s">
-        <v>184</v>
+      <c r="J3" s="35" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -41594,39 +41593,39 @@
       <c r="B1" s="80" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="103" t="s">
+      <c r="C1" s="115" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="105"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="32" t="s">
+      <c r="D1" s="117"/>
+      <c r="E1" s="116"/>
+      <c r="F1" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="G1" s="102" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="107"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="113" t="s">
+      <c r="H1" s="103"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="109" t="s">
         <v>134</v>
       </c>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="71" t="s">
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="111"/>
+      <c r="N1" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="106" t="s">
+      <c r="O1" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="108"/>
-      <c r="T1" s="72" t="s">
-        <v>185</v>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
+      <c r="S1" s="104"/>
+      <c r="T1" s="71" t="s">
+        <v>184</v>
       </c>
-      <c r="U1" s="110" t="s">
+      <c r="U1" s="106" t="s">
         <v>66</v>
       </c>
     </row>
@@ -41636,79 +41635,79 @@
       <c r="C2" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="103" t="s">
+      <c r="D2" s="115" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="104"/>
+      <c r="E2" s="116"/>
       <c r="F2" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="76"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="71"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
-      <c r="S2" s="77"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="111"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="70"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="107"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="82"/>
       <c r="B3" s="82"/>
       <c r="C3" s="82"/>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="33" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="82"/>
-      <c r="G3" s="36" t="s">
+      <c r="G3" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="36" t="s">
+      <c r="I3" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="J3" s="42" t="s">
+      <c r="J3" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="K3" s="42" t="s">
+      <c r="K3" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="L3" s="42" t="s">
+      <c r="L3" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="M3" s="42" t="s">
+      <c r="M3" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="N3" s="71"/>
-      <c r="O3" s="35" t="s">
+      <c r="N3" s="70"/>
+      <c r="O3" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="P3" s="58" t="s">
-        <v>187</v>
+      <c r="P3" s="57" t="s">
+        <v>186</v>
       </c>
-      <c r="Q3" s="36" t="s">
+      <c r="Q3" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="R3" s="36" t="s">
+      <c r="R3" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="S3" s="33" t="s">
+      <c r="S3" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="72"/>
-      <c r="U3" s="112"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="108"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
@@ -46314,18 +46313,18 @@
   <sheetProtection algorithmName="SHA-512" hashValue="IdgVTozWVwbzHSzNaqZaK0q5uHocEAzKK+AkRaHish6a5TyEsCDFLTUuxoR50I9TB+atOI1LaAB25kwX5+RoHw==" saltValue="QAr/RWj4fd8bRZOT5I76lw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="12">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G1:I2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="O1:S2"/>
     <mergeCell ref="U1:U3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="T1:T3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G1:I2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" sqref="U1:U3 Q3:R3 G3:M3" xr:uid="{AF5AE5B6-046A-4AF7-91CF-4FE32EB3CEA6}">
@@ -46369,43 +46368,43 @@
       <c r="A1" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="B1" s="88" t="s">
         <v>142</v>
       </c>
-      <c r="C1" s="119" t="s">
+      <c r="C1" s="118" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="120"/>
-      <c r="E1" s="89" t="s">
+      <c r="D1" s="119"/>
+      <c r="E1" s="88" t="s">
         <v>143</v>
       </c>
       <c r="F1" s="80" t="s">
         <v>144</v>
       </c>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="114"/>
-      <c r="I1" s="115"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="111"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="82"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="42" t="s">
+      <c r="B2" s="90"/>
+      <c r="C2" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="91"/>
+      <c r="E2" s="90"/>
       <c r="F2" s="82"/>
-      <c r="G2" s="52" t="s">
+      <c r="G2" s="51" t="s">
         <v>151</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="42" t="s">
+      <c r="I2" s="41" t="s">
         <v>145</v>
       </c>
     </row>
@@ -48663,61 +48662,61 @@
       <c r="A1" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B1" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="78" t="s">
-        <v>191</v>
+      <c r="C1" s="77" t="s">
+        <v>190</v>
       </c>
-      <c r="D1" s="123" t="s">
+      <c r="D1" s="124" t="s">
         <v>142</v>
       </c>
-      <c r="E1" s="125" t="s">
+      <c r="E1" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="126"/>
-      <c r="G1" s="86" t="s">
+      <c r="F1" s="121"/>
+      <c r="G1" s="85" t="s">
         <v>143</v>
       </c>
-      <c r="H1" s="121" t="s">
+      <c r="H1" s="122" t="s">
         <v>144</v>
       </c>
-      <c r="I1" s="73" t="s">
+      <c r="I1" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="75"/>
-      <c r="K1" s="86" t="s">
+      <c r="J1" s="74"/>
+      <c r="K1" s="85" t="s">
         <v>145</v>
       </c>
-      <c r="L1" s="73" t="s">
+      <c r="L1" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="M1" s="75"/>
+      <c r="M1" s="74"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="82"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="36" t="s">
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="88"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="54" t="s">
+      <c r="G2" s="87"/>
+      <c r="H2" s="123"/>
+      <c r="I2" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="J2" s="53" t="s">
+      <c r="J2" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="88"/>
-      <c r="L2" s="36" t="s">
+      <c r="K2" s="87"/>
+      <c r="L2" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="M2" s="36" t="s">
+      <c r="M2" s="35" t="s">
         <v>147</v>
       </c>
     </row>
@@ -51724,16 +51723,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="0x3j3ozqD1rkznmKKx/nvwqLY5+BmSrFwYHx5i3QnYCmWvB+J2nRzoVTNuX5eJNsG3YD1voaeXBMhU4esk6mcA==" saltValue="zYYWMnMjhZY6XAGfe+td2A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="10">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="L1:M1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2 L2" xr:uid="{2F2D812A-9500-497F-8725-7E6E70DDE170}">

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699AC24F-3C11-4643-9C8D-35FF3161F88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439D3E0E-A178-EE43-B975-D79DB46C2DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="24660" windowHeight="16840" tabRatio="803" firstSheet="10" activeTab="14" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="24660" windowHeight="16740" tabRatio="803" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="35" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="191">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>Version</t>
-  </si>
-  <si>
-    <t>2.0.0</t>
   </si>
   <si>
     <t>Submission information</t>
@@ -1218,6 +1215,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1292,19 +1292,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1346,6 +1334,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1718,7 +1715,7 @@
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B2" s="61" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
@@ -1742,14 +1739,14 @@
         <v>74</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>76</v>
+      <c r="G4" s="11">
+        <v>4</v>
       </c>
       <c r="H4" s="12"/>
     </row>
@@ -1765,7 +1762,7 @@
     <row r="6" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
       <c r="C6" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -1785,12 +1782,12 @@
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="13"/>
       <c r="C8" s="67" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D8" s="67"/>
       <c r="E8" s="14"/>
       <c r="F8" s="67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G8" s="67"/>
       <c r="H8" s="15"/>
@@ -1798,12 +1795,12 @@
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="13"/>
       <c r="C9" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="14"/>
       <c r="F9" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="15"/>
@@ -1811,12 +1808,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="13"/>
       <c r="C10" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="15"/>
@@ -1833,7 +1830,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="14"/>
@@ -1873,7 +1870,7 @@
     <row r="16" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
       <c r="C16" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
@@ -1893,7 +1890,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18" s="19" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="14"/>
@@ -1904,7 +1901,7 @@
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
       <c r="C19" s="24" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="14"/>
@@ -1926,7 +1923,7 @@
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="13"/>
       <c r="C21" s="60" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="14"/>
@@ -1995,7 +1992,7 @@
       <c r="D28" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="L0Y8Wko3eP5Yq8pEijOk1nzB+1M0apYi9uBJGWynVndNbEc8Y6vufqElebv2iCkLeSg4rtJpaBGk29mbM06vBw==" saltValue="fXrIfiTxdhPO9Ilm54xaVw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="bIHVKW/9SYUEMp5j00ENytYaPcpDZDdTvNpX4KPu4yNeLRi4urPwZ63Qp8YGQoDSk/Z/SXtQUbNTdTTgzVQUtg==" saltValue="8yroYgwpWbBbiCqQQUDBsg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2058,22 +2055,22 @@
         <v>67</v>
       </c>
       <c r="B1" s="127" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C1" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="89" t="s">
-        <v>143</v>
+      <c r="D1" s="90" t="s">
+        <v>142</v>
       </c>
       <c r="E1" s="71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F1" s="71"/>
       <c r="G1" s="71"/>
       <c r="H1" s="71"/>
       <c r="I1" s="72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J1" s="72"/>
       <c r="K1" s="72"/>
@@ -2083,7 +2080,7 @@
       </c>
       <c r="N1" s="72"/>
       <c r="O1" s="72"/>
-      <c r="P1" s="80" t="s">
+      <c r="P1" s="81" t="s">
         <v>37</v>
       </c>
       <c r="Q1" s="73" t="s">
@@ -2091,12 +2088,12 @@
       </c>
       <c r="R1" s="75"/>
       <c r="S1" s="72" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T1" s="72"/>
       <c r="U1" s="72"/>
       <c r="V1" s="72" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="W1" s="72"/>
       <c r="X1" s="72"/>
@@ -2109,7 +2106,7 @@
       <c r="A2" s="128"/>
       <c r="B2" s="128"/>
       <c r="C2" s="128"/>
-      <c r="D2" s="91"/>
+      <c r="D2" s="92"/>
       <c r="E2" s="41" t="s">
         <v>54</v>
       </c>
@@ -2117,7 +2114,7 @@
         <v>36</v>
       </c>
       <c r="G2" s="41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H2" s="31" t="s">
         <v>44</v>
@@ -2129,21 +2126,21 @@
         <v>36</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L2" s="32" t="s">
         <v>44</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N2" s="32" t="s">
         <v>35</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
-      <c r="P2" s="81"/>
+      <c r="P2" s="82"/>
       <c r="Q2" s="34" t="s">
         <v>56</v>
       </c>
@@ -2157,7 +2154,7 @@
         <v>38</v>
       </c>
       <c r="U2" s="58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V2" s="32" t="s">
         <v>39</v>
@@ -2169,10 +2166,10 @@
         <v>54</v>
       </c>
       <c r="Y2" s="32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AA2" s="32" t="s">
         <v>69</v>
@@ -8184,17 +8181,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="HslEuID6IjZtZdKCUOojygIr7JEfDdTW3xXhdfKVBBZXMUg8BpmKsrISBeACUnUATtRkRZOGAip7oxU+3PrcFA==" saltValue="p7kZbF4A7qKywshOKE8NhA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:R1"/>
     <mergeCell ref="S1:U1"/>
     <mergeCell ref="V1:AB1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:H1"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="M1:O1"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:R1"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2 D1:D2 E2 G2 I2 K2 P1:P2" xr:uid="{5E4B3162-4EBB-4AB5-B30D-164A47D38785}">
@@ -8246,19 +8243,19 @@
         <v>67</v>
       </c>
       <c r="B1" s="127" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C1" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="80" t="s">
-        <v>148</v>
+      <c r="D1" s="81" t="s">
+        <v>147</v>
       </c>
       <c r="E1" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="80" t="s">
-        <v>149</v>
+      <c r="F1" s="81" t="s">
+        <v>148</v>
       </c>
       <c r="G1" s="78" t="s">
         <v>42</v>
@@ -8266,18 +8263,18 @@
       <c r="H1" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="95" t="s">
-        <v>175</v>
+      <c r="I1" s="96" t="s">
+        <v>174</v>
       </c>
-      <c r="J1" s="97"/>
+      <c r="J1" s="98"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="128"/>
       <c r="B2" s="128"/>
       <c r="C2" s="128"/>
-      <c r="D2" s="81"/>
+      <c r="D2" s="82"/>
       <c r="E2" s="79"/>
-      <c r="F2" s="81"/>
+      <c r="F2" s="82"/>
       <c r="G2" s="79"/>
       <c r="H2" s="79"/>
       <c r="I2" s="35" t="s">
@@ -10734,30 +10731,30 @@
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="73" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D1" s="74"/>
       <c r="E1" s="75"/>
       <c r="F1" s="73" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G1" s="74"/>
       <c r="H1" s="75"/>
-      <c r="I1" s="106" t="s">
+      <c r="I1" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="J1" s="108"/>
+      <c r="J1" s="105"/>
       <c r="K1" s="130" t="s">
         <v>71</v>
       </c>
       <c r="L1" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="129"/>
       <c r="B2" s="48" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C2" s="72" t="s">
         <v>48</v>
@@ -10799,7 +10796,7 @@
         <v>18</v>
       </c>
       <c r="J3" s="46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K3" s="130"/>
       <c r="L3" s="72"/>
@@ -13650,16 +13647,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="50" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B2" s="54" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -14897,19 +14894,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
-        <v>148</v>
+      <c r="A1" s="81" t="s">
+        <v>147</v>
       </c>
       <c r="B1" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="80" t="s">
-        <v>149</v>
+      <c r="C1" s="81" t="s">
+        <v>148</v>
       </c>
-      <c r="D1" s="80" t="s">
+      <c r="D1" s="81" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="80" t="s">
+      <c r="E1" s="81" t="s">
         <v>73</v>
       </c>
       <c r="F1" s="78" t="s">
@@ -14920,11 +14917,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="81"/>
+      <c r="A2" s="82"/>
       <c r="B2" s="79"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
       <c r="F2" s="79"/>
       <c r="G2" s="79"/>
     </row>
@@ -18242,11 +18239,11 @@
         <v>67</v>
       </c>
       <c r="B1" s="71" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C1" s="71"/>
       <c r="D1" s="72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="72"/>
       <c r="F1" s="72"/>
@@ -18258,7 +18255,7 @@
       <c r="L1" s="72"/>
       <c r="M1" s="72"/>
       <c r="N1" s="71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O1" s="71"/>
       <c r="P1" s="71"/>
@@ -18308,40 +18305,40 @@
       <c r="B3" s="71"/>
       <c r="C3" s="71"/>
       <c r="D3" s="76" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E3" s="77"/>
       <c r="F3" s="76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G3" s="77"/>
       <c r="H3" s="78" t="s">
         <v>48</v>
       </c>
       <c r="I3" s="76" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J3" s="77"/>
       <c r="K3" s="76" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L3" s="77"/>
       <c r="M3" s="78" t="s">
         <v>48</v>
       </c>
       <c r="N3" s="71" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O3" s="71"/>
       <c r="P3" s="71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q3" s="71"/>
       <c r="R3" s="71"/>
       <c r="S3" s="71"/>
       <c r="T3" s="71"/>
       <c r="U3" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="V3" s="72"/>
       <c r="W3" s="72"/>
@@ -18350,13 +18347,13 @@
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="71"/>
       <c r="B4" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E4" s="35" t="s">
         <v>4</v>
@@ -18369,7 +18366,7 @@
       </c>
       <c r="H4" s="79"/>
       <c r="I4" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J4" s="35" t="s">
         <v>4</v>
@@ -18403,16 +18400,16 @@
         <v>10</v>
       </c>
       <c r="U4" s="35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="V4" s="35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="W4" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X4" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
@@ -23655,44 +23652,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="92" t="s">
+      <c r="B1" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="95" t="s">
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="96"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="80" t="s">
-        <v>191</v>
+      <c r="H1" s="97"/>
+      <c r="I1" s="98"/>
+      <c r="J1" s="81" t="s">
+        <v>190</v>
       </c>
-      <c r="K1" s="89" t="s">
-        <v>101</v>
+      <c r="K1" s="90" t="s">
+        <v>100</v>
       </c>
-      <c r="L1" s="92" t="s">
-        <v>90</v>
+      <c r="L1" s="93" t="s">
+        <v>89</v>
       </c>
-      <c r="M1" s="93"/>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
+      <c r="O1" s="94"/>
+      <c r="P1" s="95"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="84"/>
+      <c r="A2" s="85"/>
       <c r="B2" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="98" t="s">
-        <v>95</v>
+      <c r="C2" s="99" t="s">
+        <v>94</v>
       </c>
-      <c r="D2" s="99" t="s">
+      <c r="D2" s="100" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="78" t="s">
@@ -23701,54 +23698,54 @@
       <c r="F2" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="100" t="s">
-        <v>94</v>
+      <c r="G2" s="101" t="s">
+        <v>93</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="81" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="86" t="s">
-        <v>178</v>
+      <c r="I2" s="87" t="s">
+        <v>177</v>
       </c>
-      <c r="J2" s="88"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="82" t="s">
+      <c r="J2" s="89"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="83" t="s">
+        <v>163</v>
+      </c>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83" t="s">
         <v>164</v>
       </c>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82" t="s">
-        <v>165</v>
-      </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="101" t="s">
+      <c r="O2" s="83"/>
+      <c r="P2" s="80" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
+      <c r="A3" s="86"/>
       <c r="B3" s="71"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="99"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="79"/>
       <c r="F3" s="72"/>
-      <c r="G3" s="100"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="87"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="91"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="92"/>
       <c r="L3" s="38" t="s">
         <v>3</v>
       </c>
       <c r="M3" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N3" s="39" t="s">
         <v>3</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
-      <c r="P3" s="101"/>
+      <c r="P3" s="80"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -27353,6 +27350,7 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="qEGKRn65ciVDbmHEo86MTKkORNnkHlArZ7cMC5oUrnKH3puj0UsvJ2HCr2az9DaWSJb9lX+VmSVn49E01kPxMg==" saltValue="vQ5Ac/JH37NsP5rCz6/aCw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="G2:G3"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="N2:O2"/>
@@ -27369,7 +27367,6 @@
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 C2:C3 G2:H3 O4 K1 J1:J3" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
@@ -27414,18 +27411,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="102" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C1" s="102"/>
       <c r="D1" s="102"/>
       <c r="E1" s="102"/>
       <c r="F1" s="102"/>
       <c r="G1" s="102" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H1" s="102"/>
       <c r="I1" s="102"/>
@@ -27433,9 +27430,9 @@
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="84"/>
+      <c r="A2" s="85"/>
       <c r="B2" s="73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C2" s="74"/>
       <c r="D2" s="74"/>
@@ -27444,7 +27441,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H2" s="74"/>
       <c r="I2" s="74"/>
@@ -27454,9 +27451,9 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
+      <c r="A3" s="86"/>
       <c r="B3" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>4</v>
@@ -27469,7 +27466,7 @@
       </c>
       <c r="F3" s="79"/>
       <c r="G3" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H3" s="35" t="s">
         <v>4</v>
@@ -30152,11 +30149,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="73" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C1" s="74"/>
       <c r="D1" s="74"/>
@@ -30177,7 +30174,7 @@
       <c r="S1" s="74"/>
       <c r="T1" s="75"/>
       <c r="U1" s="73" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V1" s="74"/>
       <c r="W1" s="74"/>
@@ -30192,7 +30189,7 @@
       <c r="AF1" s="74"/>
       <c r="AG1" s="75"/>
       <c r="AH1" s="73" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AI1" s="74"/>
       <c r="AJ1" s="74"/>
@@ -30203,37 +30200,37 @@
       <c r="AO1" s="74"/>
     </row>
     <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="84"/>
+      <c r="A2" s="85"/>
       <c r="B2" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="C2" s="78" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="80" t="s">
-        <v>103</v>
+      <c r="D2" s="81" t="s">
+        <v>102</v>
       </c>
       <c r="E2" s="72" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F2" s="72"/>
       <c r="G2" s="72"/>
       <c r="H2" s="72" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I2" s="72"/>
       <c r="J2" s="72"/>
       <c r="K2" s="78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L2" s="73" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M2" s="74"/>
       <c r="N2" s="74"/>
       <c r="O2" s="75"/>
       <c r="P2" s="73" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q2" s="74"/>
       <c r="R2" s="75"/>
@@ -30242,7 +30239,7 @@
       </c>
       <c r="T2" s="75"/>
       <c r="U2" s="72" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="V2" s="72" t="s">
         <v>22</v>
@@ -30280,28 +30277,28 @@
       <c r="AG2" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="AH2" s="95" t="s">
+      <c r="AH2" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI2" s="98"/>
+      <c r="AJ2" s="96" t="s">
         <v>121</v>
       </c>
-      <c r="AI2" s="97"/>
-      <c r="AJ2" s="95" t="s">
+      <c r="AK2" s="98"/>
+      <c r="AL2" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="AK2" s="97"/>
-      <c r="AL2" s="95" t="s">
+      <c r="AM2" s="98"/>
+      <c r="AN2" s="96" t="s">
         <v>123</v>
       </c>
-      <c r="AM2" s="97"/>
-      <c r="AN2" s="95" t="s">
-        <v>124</v>
-      </c>
-      <c r="AO2" s="97"/>
+      <c r="AO2" s="98"/>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
+      <c r="A3" s="86"/>
       <c r="B3" s="79"/>
       <c r="C3" s="79"/>
-      <c r="D3" s="81"/>
+      <c r="D3" s="82"/>
       <c r="E3" s="43" t="s">
         <v>19</v>
       </c>
@@ -30309,7 +30306,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H3" s="43" t="s">
         <v>19</v>
@@ -30318,35 +30315,35 @@
         <v>20</v>
       </c>
       <c r="J3" s="44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K3" s="79"/>
       <c r="L3" s="35" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="M3" s="35" t="s">
+      <c r="N3" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="O3" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="P3" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="Q3" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="Q3" s="35" t="s">
+      <c r="R3" s="35" t="s">
         <v>110</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>111</v>
       </c>
       <c r="S3" s="32" t="s">
         <v>18</v>
       </c>
       <c r="T3" s="46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="U3" s="72"/>
       <c r="V3" s="72"/>
@@ -30362,28 +30359,28 @@
       <c r="AF3" s="72"/>
       <c r="AG3" s="72"/>
       <c r="AH3" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI3" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="AI3" s="36" t="s">
-        <v>113</v>
+      <c r="AJ3" s="36" t="s">
+        <v>114</v>
       </c>
-      <c r="AJ3" s="36" t="s">
+      <c r="AK3" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="AK3" s="36" t="s">
+      <c r="AL3" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="AL3" s="36" t="s">
+      <c r="AM3" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="AM3" s="36" t="s">
+      <c r="AN3" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="AN3" s="36" t="s">
+      <c r="AO3" s="36" t="s">
         <v>119</v>
-      </c>
-      <c r="AO3" s="36" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -38989,6 +38986,20 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="in9HWhrbfPeQLKOphe9HcQ3ZWSvu9v4Chn7tSlbMDS+5w+WrRSh6fFRY7HaRetWtqRaeTChN5KnyLnOrPZ3pZA==" saltValue="7WB/oWTeA55ZXeyLP0lXUw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="AB2:AB3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="AN2:AO2"/>
@@ -39005,20 +39016,6 @@
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 L3:R3 AH3:AO3" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -39068,36 +39065,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="86" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="86"/>
+      <c r="D1" s="93" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="85"/>
-      <c r="D1" s="92" t="s">
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="95"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="85"/>
+      <c r="B2" s="84" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="84" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" s="84" t="s">
         <v>172</v>
       </c>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-      <c r="H1" s="93"/>
-      <c r="I1" s="93"/>
-      <c r="J1" s="94"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="84"/>
-      <c r="B2" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="83" t="s">
-        <v>182</v>
-      </c>
-      <c r="D2" s="83" t="s">
-        <v>173</v>
-      </c>
       <c r="E2" s="73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F2" s="75"/>
       <c r="G2" s="73" t="s">
@@ -39108,12 +39105,12 @@
       <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
-      <c r="D3" s="85"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
       <c r="E3" s="35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F3" s="44" t="s">
         <v>49</v>
@@ -39122,13 +39119,13 @@
         <v>54</v>
       </c>
       <c r="H3" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="35" t="s">
-        <v>111</v>
-      </c>
       <c r="J3" s="35" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -41587,127 +41584,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="83" t="s">
-        <v>91</v>
+      <c r="B1" s="84" t="s">
+        <v>90</v>
       </c>
-      <c r="C1" s="103" t="s">
+      <c r="C1" s="116" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="118"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="D1" s="105"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="31" t="s">
+      <c r="G1" s="103" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="H1" s="104"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="107"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="113" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="114"/>
-      <c r="L1" s="114"/>
-      <c r="M1" s="115"/>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="112"/>
       <c r="N1" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="106" t="s">
+      <c r="O1" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="108"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
       <c r="T1" s="72" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
-      <c r="U1" s="110" t="s">
+      <c r="U1" s="107" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
-      <c r="C2" s="83" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="103" t="s">
+      <c r="D2" s="116" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="104"/>
-      <c r="F2" s="83" t="s">
+      <c r="E2" s="117"/>
+      <c r="F2" s="84" t="s">
         <v>48</v>
       </c>
       <c r="G2" s="76"/>
-      <c r="H2" s="109"/>
+      <c r="H2" s="106"/>
       <c r="I2" s="77"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="118"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="115"/>
       <c r="N2" s="71"/>
       <c r="O2" s="76"/>
-      <c r="P2" s="109"/>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="109"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
       <c r="S2" s="77"/>
       <c r="T2" s="72"/>
-      <c r="U2" s="111"/>
+      <c r="U2" s="108"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="85"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
       <c r="D3" s="33" t="s">
         <v>0</v>
       </c>
       <c r="E3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="85"/>
+      <c r="F3" s="86"/>
       <c r="G3" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="I3" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="J3" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="K3" s="41" t="s">
         <v>137</v>
       </c>
-      <c r="J3" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="K3" s="41" t="s">
+      <c r="L3" s="41" t="s">
         <v>138</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="M3" s="41" t="s">
         <v>139</v>
-      </c>
-      <c r="M3" s="41" t="s">
-        <v>140</v>
       </c>
       <c r="N3" s="71"/>
       <c r="O3" s="34" t="s">
         <v>60</v>
       </c>
       <c r="P3" s="57" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="R3" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S3" s="32" t="s">
         <v>34</v>
       </c>
       <c r="T3" s="72"/>
-      <c r="U3" s="112"/>
+      <c r="U3" s="109"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -46313,18 +46310,18 @@
   <sheetProtection algorithmName="SHA-512" hashValue="vb3l2GPyTmOeMpvedAjZ5so+j03iBDjWx3ozUq1oM5QjY9AJ+7qSyqXmIAxigMK0wo/0kW2bwbQpgi37D24U6w==" saltValue="804oboBvFb3X5NzoXiRygQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="12">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G1:I2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="O1:S2"/>
     <mergeCell ref="U1:U3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="T1:T3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G1:I2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" sqref="U1:U3 Q3:R3 G3:M3" xr:uid="{AF5AE5B6-046A-4AF7-91CF-4FE32EB3CEA6}">
@@ -46365,47 +46362,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="89" t="s">
-        <v>142</v>
+      <c r="B1" s="90" t="s">
+        <v>141</v>
       </c>
       <c r="C1" s="119" t="s">
         <v>64</v>
       </c>
       <c r="D1" s="120"/>
-      <c r="E1" s="89" t="s">
+      <c r="E1" s="90" t="s">
+        <v>142</v>
+      </c>
+      <c r="F1" s="84" t="s">
         <v>143</v>
       </c>
-      <c r="F1" s="83" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="113" t="s">
+      <c r="G1" s="110" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="114"/>
-      <c r="I1" s="115"/>
+      <c r="H1" s="111"/>
+      <c r="I1" s="112"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="85"/>
-      <c r="B2" s="91"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="92"/>
       <c r="C2" s="41" t="s">
         <v>54</v>
       </c>
       <c r="D2" s="41" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="91"/>
-      <c r="F2" s="85"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="86"/>
       <c r="G2" s="51" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H2" s="31" t="s">
         <v>35</v>
       </c>
       <c r="I2" s="41" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -48659,42 +48656,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D1" s="123" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E1" s="125" t="s">
         <v>64</v>
       </c>
       <c r="F1" s="126"/>
-      <c r="G1" s="80" t="s">
-        <v>143</v>
+      <c r="G1" s="81" t="s">
+        <v>142</v>
       </c>
       <c r="H1" s="121" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I1" s="73" t="s">
         <v>34</v>
       </c>
       <c r="J1" s="75"/>
-      <c r="K1" s="80" t="s">
-        <v>145</v>
+      <c r="K1" s="81" t="s">
+        <v>144</v>
       </c>
       <c r="L1" s="73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M1" s="75"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="85"/>
+      <c r="A2" s="86"/>
       <c r="B2" s="79"/>
       <c r="C2" s="79"/>
       <c r="D2" s="124"/>
@@ -48704,20 +48701,20 @@
       <c r="F2" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="81"/>
+      <c r="G2" s="82"/>
       <c r="H2" s="122"/>
       <c r="I2" s="53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J2" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="81"/>
+      <c r="K2" s="82"/>
       <c r="L2" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">

--- a/form_reporting_templates/ros/Form-ROS-PL.xlsx
+++ b/form_reporting_templates/ros/Form-ROS-PL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/schirico/IOTC/IOTC_reference_forms/form_reporting_templates/ros/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327716A2-D25D-FA41-B20F-CF48C8AAAD97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A25160-A3A4-7345-BCA7-4EB56D203353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="740" windowWidth="22500" windowHeight="16780" tabRatio="803" firstSheet="10" activeTab="13" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
+    <workbookView xWindow="14200" yWindow="740" windowWidth="15200" windowHeight="16740" tabRatio="803" firstSheet="8" activeTab="9" xr2:uid="{EFC17563-B14E-425F-8BEA-A9EB7F2C43CD}"/>
   </bookViews>
   <sheets>
     <sheet name="META" sheetId="35" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="191">
   <si>
     <t>LATITUDE</t>
   </si>
@@ -182,9 +182,6 @@
   </si>
   <si>
     <t>PHOTO_ID</t>
-  </si>
-  <si>
-    <t>IS_STRAIGHT</t>
   </si>
   <si>
     <t>EMBARKATION</t>
@@ -624,6 +621,9 @@
   <si>
     <t>LICENSED_TARGET_SPECIES</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -633,7 +633,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -678,15 +678,6 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1003,7 +994,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyProtection="1">
@@ -1053,9 +1044,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1103,17 +1091,14 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1124,16 +1109,16 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1158,6 +1143,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1218,6 +1204,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1227,16 +1216,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1297,15 +1283,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1318,15 +1295,15 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1348,17 +1325,26 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1368,16 +1354,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1394,7 +1380,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1726,36 +1714,36 @@
   <sheetData>
     <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B2" s="62" t="s">
-        <v>92</v>
+      <c r="B2" s="61" t="s">
+        <v>91</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="64"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="63"/>
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="65"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="67"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="66"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B4" s="7"/>
       <c r="C4" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G4" s="11">
         <v>4</v>
@@ -1774,7 +1762,7 @@
     <row r="6" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B6" s="13"/>
       <c r="C6" s="16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
@@ -1793,26 +1781,26 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" s="13"/>
-      <c r="C8" s="68" t="s">
+      <c r="C8" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="67"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="67" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="68"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8" s="68"/>
+      <c r="G8" s="67"/>
       <c r="H8" s="15"/>
     </row>
     <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B9" s="13"/>
       <c r="C9" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D9" s="18"/>
       <c r="E9" s="14"/>
       <c r="F9" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G9" s="18"/>
       <c r="H9" s="15"/>
@@ -1820,12 +1808,12 @@
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" s="13"/>
       <c r="C10" s="19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" s="18"/>
       <c r="E10" s="14"/>
       <c r="F10" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G10" s="18"/>
       <c r="H10" s="15"/>
@@ -1842,7 +1830,7 @@
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" s="13"/>
       <c r="C12" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" s="21"/>
       <c r="E12" s="14"/>
@@ -1853,7 +1841,7 @@
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B13" s="13"/>
       <c r="C13" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="14"/>
@@ -1882,7 +1870,7 @@
     <row r="16" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B16" s="13"/>
       <c r="C16" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="14"/>
       <c r="E16" s="14"/>
@@ -1902,7 +1890,7 @@
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" s="13"/>
       <c r="C18" s="19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D18" s="23"/>
       <c r="E18" s="14"/>
@@ -1912,8 +1900,8 @@
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" s="13"/>
-      <c r="C19" s="24" t="s">
-        <v>85</v>
+      <c r="C19" s="133" t="s">
+        <v>84</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="14"/>
@@ -1923,8 +1911,8 @@
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" s="13"/>
-      <c r="C20" s="24" t="s">
-        <v>53</v>
+      <c r="C20" s="133" t="s">
+        <v>52</v>
       </c>
       <c r="D20" s="23"/>
       <c r="E20" s="14"/>
@@ -1934,8 +1922,8 @@
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" s="13"/>
-      <c r="C21" s="134" t="s">
-        <v>86</v>
+      <c r="C21" s="60" t="s">
+        <v>85</v>
       </c>
       <c r="D21" s="23"/>
       <c r="E21" s="14"/>
@@ -1954,8 +1942,8 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" s="13"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="25"/>
       <c r="E23" s="22"/>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -1964,7 +1952,7 @@
     <row r="24" spans="2:8" ht="19" x14ac:dyDescent="0.25">
       <c r="B24" s="13"/>
       <c r="C24" s="16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="14"/>
@@ -1983,28 +1971,28 @@
     </row>
     <row r="26" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="13"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="71"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69"/>
+      <c r="G26" s="70"/>
       <c r="H26" s="15"/>
     </row>
     <row r="27" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="27"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="29"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="28"/>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C28" s="1"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KZMRB4JWG/ZNMkWaEXj5a9cXMjqZzpgPnx4ubrHaZYsPCEEcBzlQkGqgJfGJAYdjJtsDJUHl6tin0Qs4OatS0g==" saltValue="yiOjG1PRXXt+VkoaBKNG7g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="01UCOy5BIdb+BJK7nkusT4MtmFkIA2gUeMocibGwP3/7JKYAGepMdzwCjw3xo9eAnQXfZ44dPDKA9gplq0k0sg==" saltValue="ntL7Xjz1pvPsP5t27WnjJw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="C8:D8"/>
@@ -2037,7 +2025,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:AC202"/>
+  <dimension ref="A1:AA202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.6640625" style="3" customWidth="1"/>
@@ -2047,160 +2035,150 @@
     <col min="6" max="6" width="11" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="27.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="9.1640625" style="3"/>
-    <col min="19" max="19" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.5" style="3" customWidth="1"/>
-    <col min="22" max="22" width="24" style="3" customWidth="1"/>
-    <col min="23" max="23" width="9.1640625" style="3"/>
-    <col min="24" max="24" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11" style="3" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="15.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.5" style="3" customWidth="1"/>
-    <col min="29" max="29" width="37.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1640625" style="3"/>
+    <col min="17" max="17" width="16.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.5" style="3" customWidth="1"/>
+    <col min="20" max="20" width="24" style="3" customWidth="1"/>
+    <col min="21" max="21" width="9.1640625" style="3"/>
+    <col min="22" max="22" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="15.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.5" style="3" customWidth="1"/>
+    <col min="27" max="27" width="37.33203125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A1" s="128" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A1" s="127" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="127" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="128" t="s">
-        <v>90</v>
+      <c r="E1" s="89" t="s">
+        <v>141</v>
       </c>
-      <c r="C1" s="128" t="s">
-        <v>189</v>
+      <c r="F1" s="71" t="s">
+        <v>174</v>
       </c>
-      <c r="D1" s="128" t="s">
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="72" t="s">
+        <v>175</v>
+      </c>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="72"/>
+      <c r="N1" s="72"/>
+      <c r="O1" s="86" t="s">
+        <v>37</v>
+      </c>
+      <c r="P1" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q1" s="75"/>
+      <c r="R1" s="72" t="s">
+        <v>151</v>
+      </c>
+      <c r="S1" s="72"/>
+      <c r="T1" s="72"/>
+      <c r="U1" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="V1" s="72"/>
+      <c r="W1" s="72"/>
+      <c r="X1" s="72"/>
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="72"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A2" s="128"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="L2" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="M2" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="O2" s="88"/>
+      <c r="P2" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" s="54" t="s">
+        <v>56</v>
+      </c>
+      <c r="R2" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="S2" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="U2" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="V2" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="W2" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="Y2" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="Z2" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="90" t="s">
-        <v>142</v>
-      </c>
-      <c r="F1" s="72" t="s">
-        <v>175</v>
-      </c>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="73" t="s">
-        <v>176</v>
-      </c>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="O1" s="73"/>
-      <c r="P1" s="73"/>
-      <c r="Q1" s="87" t="s">
-        <v>37</v>
-      </c>
-      <c r="R1" s="74" t="s">
-        <v>55</v>
-      </c>
-      <c r="S1" s="76"/>
-      <c r="T1" s="73" t="s">
-        <v>152</v>
-      </c>
-      <c r="U1" s="73"/>
-      <c r="V1" s="73"/>
-      <c r="W1" s="73" t="s">
-        <v>153</v>
-      </c>
-      <c r="X1" s="73"/>
-      <c r="Y1" s="73"/>
-      <c r="Z1" s="73"/>
-      <c r="AA1" s="73"/>
-      <c r="AB1" s="73"/>
-      <c r="AC1" s="73"/>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A2" s="129"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="41" t="s">
-        <v>149</v>
-      </c>
-      <c r="I2" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="M2" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="S2" s="56" t="s">
-        <v>57</v>
-      </c>
-      <c r="T2" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="U2" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="W2" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="X2" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z2" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA2" s="32" t="s">
-        <v>187</v>
-      </c>
-      <c r="AB2" s="32" t="s">
+      <c r="AA2" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="AC2" s="32" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -2228,10 +2206,8 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
       <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2259,10 +2235,8 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
       <c r="AA4" s="2"/>
-      <c r="AB4" s="2"/>
-      <c r="AC4" s="2"/>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2290,10 +2264,8 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
       <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2321,10 +2293,8 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
       <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -2352,10 +2322,8 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -2383,10 +2351,8 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
       <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -2414,10 +2380,8 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
       <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -2445,10 +2409,8 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
       <c r="AA10" s="2"/>
-      <c r="AB10" s="2"/>
-      <c r="AC10" s="2"/>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2476,10 +2438,8 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2507,10 +2467,8 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2538,10 +2496,8 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
       <c r="AA13" s="2"/>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -2569,10 +2525,8 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
       <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2600,10 +2554,8 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
       <c r="AA15" s="2"/>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="2"/>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -2631,10 +2583,8 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
-      <c r="AB16" s="2"/>
-      <c r="AC16" s="2"/>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -2662,10 +2612,8 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2"/>
-    </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -2693,10 +2641,8 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2724,10 +2670,8 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-    </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2755,10 +2699,8 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
-    </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2786,10 +2728,8 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-    </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2817,10 +2757,8 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-      <c r="AC22" s="2"/>
-    </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2848,10 +2786,8 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
-      <c r="AC23" s="2"/>
-    </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2879,10 +2815,8 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-    </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2910,10 +2844,8 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="2"/>
-    </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2941,10 +2873,8 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
       <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
-      <c r="AC26" s="2"/>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -2972,10 +2902,8 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
-      <c r="AB27" s="2"/>
-      <c r="AC27" s="2"/>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3003,10 +2931,8 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
-      <c r="AB28" s="2"/>
-      <c r="AC28" s="2"/>
-    </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3034,10 +2960,8 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
-      <c r="AB29" s="2"/>
-      <c r="AC29" s="2"/>
-    </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3065,10 +2989,8 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
       <c r="AA30" s="2"/>
-      <c r="AB30" s="2"/>
-      <c r="AC30" s="2"/>
-    </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3096,10 +3018,8 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
       <c r="AA31" s="2"/>
-      <c r="AB31" s="2"/>
-      <c r="AC31" s="2"/>
-    </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3127,10 +3047,8 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
-      <c r="AB32" s="2"/>
-      <c r="AC32" s="2"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3158,10 +3076,8 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
-      <c r="AB33" s="2"/>
-      <c r="AC33" s="2"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3189,10 +3105,8 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
-      <c r="AB34" s="2"/>
-      <c r="AC34" s="2"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3220,10 +3134,8 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
-      <c r="AB35" s="2"/>
-      <c r="AC35" s="2"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3251,10 +3163,8 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
-      <c r="AB36" s="2"/>
-      <c r="AC36" s="2"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3282,10 +3192,8 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
-      <c r="AB37" s="2"/>
-      <c r="AC37" s="2"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3313,10 +3221,8 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
-      <c r="AB38" s="2"/>
-      <c r="AC38" s="2"/>
-    </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -3344,10 +3250,8 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
-      <c r="AB39" s="2"/>
-      <c r="AC39" s="2"/>
-    </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -3375,10 +3279,8 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
-      <c r="AB40" s="2"/>
-      <c r="AC40" s="2"/>
-    </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -3406,10 +3308,8 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
-      <c r="AB41" s="2"/>
-      <c r="AC41" s="2"/>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -3437,10 +3337,8 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
-      <c r="AB42" s="2"/>
-      <c r="AC42" s="2"/>
-    </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -3468,10 +3366,8 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
-      <c r="AB43" s="2"/>
-      <c r="AC43" s="2"/>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -3499,10 +3395,8 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
-      <c r="AB44" s="2"/>
-      <c r="AC44" s="2"/>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -3530,10 +3424,8 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
-      <c r="AB45" s="2"/>
-      <c r="AC45" s="2"/>
-    </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -3561,10 +3453,8 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
-      <c r="AB46" s="2"/>
-      <c r="AC46" s="2"/>
-    </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -3592,10 +3482,8 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
-      <c r="AB47" s="2"/>
-      <c r="AC47" s="2"/>
-    </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -3623,10 +3511,8 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
       <c r="AA48" s="2"/>
-      <c r="AB48" s="2"/>
-      <c r="AC48" s="2"/>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -3654,10 +3540,8 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
       <c r="AA49" s="2"/>
-      <c r="AB49" s="2"/>
-      <c r="AC49" s="2"/>
-    </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -3685,10 +3569,8 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
       <c r="AA50" s="2"/>
-      <c r="AB50" s="2"/>
-      <c r="AC50" s="2"/>
-    </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3716,10 +3598,8 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
       <c r="AA51" s="2"/>
-      <c r="AB51" s="2"/>
-      <c r="AC51" s="2"/>
-    </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3747,10 +3627,8 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
       <c r="AA52" s="2"/>
-      <c r="AB52" s="2"/>
-      <c r="AC52" s="2"/>
-    </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -3778,10 +3656,8 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
       <c r="AA53" s="2"/>
-      <c r="AB53" s="2"/>
-      <c r="AC53" s="2"/>
-    </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -3809,10 +3685,8 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
       <c r="AA54" s="2"/>
-      <c r="AB54" s="2"/>
-      <c r="AC54" s="2"/>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -3840,10 +3714,8 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
       <c r="AA55" s="2"/>
-      <c r="AB55" s="2"/>
-      <c r="AC55" s="2"/>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -3871,10 +3743,8 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
       <c r="AA56" s="2"/>
-      <c r="AB56" s="2"/>
-      <c r="AC56" s="2"/>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -3902,10 +3772,8 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
-      <c r="AB57" s="2"/>
-      <c r="AC57" s="2"/>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -3933,10 +3801,8 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
       <c r="AA58" s="2"/>
-      <c r="AB58" s="2"/>
-      <c r="AC58" s="2"/>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -3964,10 +3830,8 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
       <c r="AA59" s="2"/>
-      <c r="AB59" s="2"/>
-      <c r="AC59" s="2"/>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -3995,10 +3859,8 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
       <c r="AA60" s="2"/>
-      <c r="AB60" s="2"/>
-      <c r="AC60" s="2"/>
-    </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -4026,10 +3888,8 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
       <c r="AA61" s="2"/>
-      <c r="AB61" s="2"/>
-      <c r="AC61" s="2"/>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -4057,10 +3917,8 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
       <c r="AA62" s="2"/>
-      <c r="AB62" s="2"/>
-      <c r="AC62" s="2"/>
-    </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -4088,10 +3946,8 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
       <c r="AA63" s="2"/>
-      <c r="AB63" s="2"/>
-      <c r="AC63" s="2"/>
-    </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -4119,10 +3975,8 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
       <c r="AA64" s="2"/>
-      <c r="AB64" s="2"/>
-      <c r="AC64" s="2"/>
-    </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -4150,10 +4004,8 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
       <c r="AA65" s="2"/>
-      <c r="AB65" s="2"/>
-      <c r="AC65" s="2"/>
-    </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -4181,10 +4033,8 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
       <c r="AA66" s="2"/>
-      <c r="AB66" s="2"/>
-      <c r="AC66" s="2"/>
-    </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -4212,10 +4062,8 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
       <c r="AA67" s="2"/>
-      <c r="AB67" s="2"/>
-      <c r="AC67" s="2"/>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -4243,10 +4091,8 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
       <c r="AA68" s="2"/>
-      <c r="AB68" s="2"/>
-      <c r="AC68" s="2"/>
-    </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -4274,10 +4120,8 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
-      <c r="AB69" s="2"/>
-      <c r="AC69" s="2"/>
-    </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -4305,10 +4149,8 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
-      <c r="AB70" s="2"/>
-      <c r="AC70" s="2"/>
-    </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -4336,10 +4178,8 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
       <c r="AA71" s="2"/>
-      <c r="AB71" s="2"/>
-      <c r="AC71" s="2"/>
-    </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -4367,10 +4207,8 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
       <c r="AA72" s="2"/>
-      <c r="AB72" s="2"/>
-      <c r="AC72" s="2"/>
-    </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -4398,10 +4236,8 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
       <c r="AA73" s="2"/>
-      <c r="AB73" s="2"/>
-      <c r="AC73" s="2"/>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -4429,10 +4265,8 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
       <c r="AA74" s="2"/>
-      <c r="AB74" s="2"/>
-      <c r="AC74" s="2"/>
-    </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -4460,10 +4294,8 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
       <c r="AA75" s="2"/>
-      <c r="AB75" s="2"/>
-      <c r="AC75" s="2"/>
-    </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -4491,10 +4323,8 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
       <c r="AA76" s="2"/>
-      <c r="AB76" s="2"/>
-      <c r="AC76" s="2"/>
-    </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -4522,10 +4352,8 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
       <c r="AA77" s="2"/>
-      <c r="AB77" s="2"/>
-      <c r="AC77" s="2"/>
-    </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -4553,10 +4381,8 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
       <c r="AA78" s="2"/>
-      <c r="AB78" s="2"/>
-      <c r="AC78" s="2"/>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -4584,10 +4410,8 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
       <c r="AA79" s="2"/>
-      <c r="AB79" s="2"/>
-      <c r="AC79" s="2"/>
-    </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -4615,10 +4439,8 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
       <c r="AA80" s="2"/>
-      <c r="AB80" s="2"/>
-      <c r="AC80" s="2"/>
-    </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -4646,10 +4468,8 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
       <c r="AA81" s="2"/>
-      <c r="AB81" s="2"/>
-      <c r="AC81" s="2"/>
-    </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -4677,10 +4497,8 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
       <c r="AA82" s="2"/>
-      <c r="AB82" s="2"/>
-      <c r="AC82" s="2"/>
-    </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -4708,10 +4526,8 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
       <c r="AA83" s="2"/>
-      <c r="AB83" s="2"/>
-      <c r="AC83" s="2"/>
-    </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -4739,10 +4555,8 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
       <c r="AA84" s="2"/>
-      <c r="AB84" s="2"/>
-      <c r="AC84" s="2"/>
-    </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -4770,10 +4584,8 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
       <c r="AA85" s="2"/>
-      <c r="AB85" s="2"/>
-      <c r="AC85" s="2"/>
-    </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -4801,10 +4613,8 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
       <c r="AA86" s="2"/>
-      <c r="AB86" s="2"/>
-      <c r="AC86" s="2"/>
-    </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -4832,10 +4642,8 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
       <c r="AA87" s="2"/>
-      <c r="AB87" s="2"/>
-      <c r="AC87" s="2"/>
-    </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -4863,10 +4671,8 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
       <c r="AA88" s="2"/>
-      <c r="AB88" s="2"/>
-      <c r="AC88" s="2"/>
-    </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -4894,10 +4700,8 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
       <c r="AA89" s="2"/>
-      <c r="AB89" s="2"/>
-      <c r="AC89" s="2"/>
-    </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -4925,10 +4729,8 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
       <c r="AA90" s="2"/>
-      <c r="AB90" s="2"/>
-      <c r="AC90" s="2"/>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -4956,10 +4758,8 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
       <c r="AA91" s="2"/>
-      <c r="AB91" s="2"/>
-      <c r="AC91" s="2"/>
-    </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -4987,10 +4787,8 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
       <c r="AA92" s="2"/>
-      <c r="AB92" s="2"/>
-      <c r="AC92" s="2"/>
-    </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -5018,10 +4816,8 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
       <c r="AA93" s="2"/>
-      <c r="AB93" s="2"/>
-      <c r="AC93" s="2"/>
-    </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -5049,10 +4845,8 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
       <c r="AA94" s="2"/>
-      <c r="AB94" s="2"/>
-      <c r="AC94" s="2"/>
-    </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -5080,10 +4874,8 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
       <c r="AA95" s="2"/>
-      <c r="AB95" s="2"/>
-      <c r="AC95" s="2"/>
-    </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -5111,10 +4903,8 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
       <c r="AA96" s="2"/>
-      <c r="AB96" s="2"/>
-      <c r="AC96" s="2"/>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -5142,10 +4932,8 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
       <c r="AA97" s="2"/>
-      <c r="AB97" s="2"/>
-      <c r="AC97" s="2"/>
-    </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -5173,10 +4961,8 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
       <c r="AA98" s="2"/>
-      <c r="AB98" s="2"/>
-      <c r="AC98" s="2"/>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -5204,10 +4990,8 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
       <c r="AA99" s="2"/>
-      <c r="AB99" s="2"/>
-      <c r="AC99" s="2"/>
-    </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -5235,10 +5019,8 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
       <c r="AA100" s="2"/>
-      <c r="AB100" s="2"/>
-      <c r="AC100" s="2"/>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -5266,10 +5048,8 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
       <c r="AA101" s="2"/>
-      <c r="AB101" s="2"/>
-      <c r="AC101" s="2"/>
-    </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -5297,10 +5077,8 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
       <c r="AA102" s="2"/>
-      <c r="AB102" s="2"/>
-      <c r="AC102" s="2"/>
-    </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -5328,10 +5106,8 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
       <c r="AA103" s="2"/>
-      <c r="AB103" s="2"/>
-      <c r="AC103" s="2"/>
-    </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -5359,10 +5135,8 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
       <c r="AA104" s="2"/>
-      <c r="AB104" s="2"/>
-      <c r="AC104" s="2"/>
-    </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -5390,10 +5164,8 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
       <c r="AA105" s="2"/>
-      <c r="AB105" s="2"/>
-      <c r="AC105" s="2"/>
-    </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -5421,10 +5193,8 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
       <c r="AA106" s="2"/>
-      <c r="AB106" s="2"/>
-      <c r="AC106" s="2"/>
-    </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -5452,10 +5222,8 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
       <c r="AA107" s="2"/>
-      <c r="AB107" s="2"/>
-      <c r="AC107" s="2"/>
-    </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -5483,10 +5251,8 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
       <c r="AA108" s="2"/>
-      <c r="AB108" s="2"/>
-      <c r="AC108" s="2"/>
-    </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -5514,10 +5280,8 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
       <c r="AA109" s="2"/>
-      <c r="AB109" s="2"/>
-      <c r="AC109" s="2"/>
-    </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -5545,10 +5309,8 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
       <c r="AA110" s="2"/>
-      <c r="AB110" s="2"/>
-      <c r="AC110" s="2"/>
-    </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -5576,10 +5338,8 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
       <c r="AA111" s="2"/>
-      <c r="AB111" s="2"/>
-      <c r="AC111" s="2"/>
-    </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -5607,10 +5367,8 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
       <c r="AA112" s="2"/>
-      <c r="AB112" s="2"/>
-      <c r="AC112" s="2"/>
-    </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -5638,10 +5396,8 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
       <c r="AA113" s="2"/>
-      <c r="AB113" s="2"/>
-      <c r="AC113" s="2"/>
-    </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -5669,10 +5425,8 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
       <c r="AA114" s="2"/>
-      <c r="AB114" s="2"/>
-      <c r="AC114" s="2"/>
-    </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -5700,10 +5454,8 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
       <c r="AA115" s="2"/>
-      <c r="AB115" s="2"/>
-      <c r="AC115" s="2"/>
-    </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -5731,10 +5483,8 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
       <c r="AA116" s="2"/>
-      <c r="AB116" s="2"/>
-      <c r="AC116" s="2"/>
-    </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -5762,10 +5512,8 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
-      <c r="AB117" s="2"/>
-      <c r="AC117" s="2"/>
-    </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -5793,10 +5541,8 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
-      <c r="AB118" s="2"/>
-      <c r="AC118" s="2"/>
-    </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -5824,10 +5570,8 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
       <c r="AA119" s="2"/>
-      <c r="AB119" s="2"/>
-      <c r="AC119" s="2"/>
-    </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -5855,10 +5599,8 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
       <c r="AA120" s="2"/>
-      <c r="AB120" s="2"/>
-      <c r="AC120" s="2"/>
-    </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -5886,10 +5628,8 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
       <c r="AA121" s="2"/>
-      <c r="AB121" s="2"/>
-      <c r="AC121" s="2"/>
-    </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -5917,10 +5657,8 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
       <c r="AA122" s="2"/>
-      <c r="AB122" s="2"/>
-      <c r="AC122" s="2"/>
-    </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -5948,10 +5686,8 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
       <c r="AA123" s="2"/>
-      <c r="AB123" s="2"/>
-      <c r="AC123" s="2"/>
-    </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -5979,10 +5715,8 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
       <c r="AA124" s="2"/>
-      <c r="AB124" s="2"/>
-      <c r="AC124" s="2"/>
-    </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -6010,10 +5744,8 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
       <c r="AA125" s="2"/>
-      <c r="AB125" s="2"/>
-      <c r="AC125" s="2"/>
-    </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -6041,10 +5773,8 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
       <c r="AA126" s="2"/>
-      <c r="AB126" s="2"/>
-      <c r="AC126" s="2"/>
-    </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -6072,10 +5802,8 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
       <c r="AA127" s="2"/>
-      <c r="AB127" s="2"/>
-      <c r="AC127" s="2"/>
-    </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -6103,10 +5831,8 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
       <c r="AA128" s="2"/>
-      <c r="AB128" s="2"/>
-      <c r="AC128" s="2"/>
-    </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -6134,10 +5860,8 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
       <c r="AA129" s="2"/>
-      <c r="AB129" s="2"/>
-      <c r="AC129" s="2"/>
-    </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -6165,10 +5889,8 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
       <c r="AA130" s="2"/>
-      <c r="AB130" s="2"/>
-      <c r="AC130" s="2"/>
-    </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -6196,10 +5918,8 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
       <c r="AA131" s="2"/>
-      <c r="AB131" s="2"/>
-      <c r="AC131" s="2"/>
-    </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -6227,10 +5947,8 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
       <c r="AA132" s="2"/>
-      <c r="AB132" s="2"/>
-      <c r="AC132" s="2"/>
-    </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -6258,10 +5976,8 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
       <c r="AA133" s="2"/>
-      <c r="AB133" s="2"/>
-      <c r="AC133" s="2"/>
-    </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -6289,10 +6005,8 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
       <c r="AA134" s="2"/>
-      <c r="AB134" s="2"/>
-      <c r="AC134" s="2"/>
-    </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -6320,10 +6034,8 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
       <c r="AA135" s="2"/>
-      <c r="AB135" s="2"/>
-      <c r="AC135" s="2"/>
-    </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -6351,10 +6063,8 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
       <c r="AA136" s="2"/>
-      <c r="AB136" s="2"/>
-      <c r="AC136" s="2"/>
-    </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -6382,10 +6092,8 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
       <c r="AA137" s="2"/>
-      <c r="AB137" s="2"/>
-      <c r="AC137" s="2"/>
-    </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -6413,10 +6121,8 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
       <c r="AA138" s="2"/>
-      <c r="AB138" s="2"/>
-      <c r="AC138" s="2"/>
-    </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -6444,10 +6150,8 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
       <c r="AA139" s="2"/>
-      <c r="AB139" s="2"/>
-      <c r="AC139" s="2"/>
-    </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -6475,10 +6179,8 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
       <c r="AA140" s="2"/>
-      <c r="AB140" s="2"/>
-      <c r="AC140" s="2"/>
-    </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -6506,10 +6208,8 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
       <c r="AA141" s="2"/>
-      <c r="AB141" s="2"/>
-      <c r="AC141" s="2"/>
-    </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -6537,10 +6237,8 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
       <c r="AA142" s="2"/>
-      <c r="AB142" s="2"/>
-      <c r="AC142" s="2"/>
-    </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -6568,10 +6266,8 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
       <c r="AA143" s="2"/>
-      <c r="AB143" s="2"/>
-      <c r="AC143" s="2"/>
-    </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -6599,10 +6295,8 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
       <c r="AA144" s="2"/>
-      <c r="AB144" s="2"/>
-      <c r="AC144" s="2"/>
-    </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -6630,10 +6324,8 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
       <c r="AA145" s="2"/>
-      <c r="AB145" s="2"/>
-      <c r="AC145" s="2"/>
-    </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -6661,10 +6353,8 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
       <c r="AA146" s="2"/>
-      <c r="AB146" s="2"/>
-      <c r="AC146" s="2"/>
-    </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -6692,10 +6382,8 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
       <c r="AA147" s="2"/>
-      <c r="AB147" s="2"/>
-      <c r="AC147" s="2"/>
-    </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -6723,10 +6411,8 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
       <c r="AA148" s="2"/>
-      <c r="AB148" s="2"/>
-      <c r="AC148" s="2"/>
-    </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -6754,10 +6440,8 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
       <c r="AA149" s="2"/>
-      <c r="AB149" s="2"/>
-      <c r="AC149" s="2"/>
-    </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -6785,10 +6469,8 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
       <c r="AA150" s="2"/>
-      <c r="AB150" s="2"/>
-      <c r="AC150" s="2"/>
-    </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -6816,10 +6498,8 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
       <c r="AA151" s="2"/>
-      <c r="AB151" s="2"/>
-      <c r="AC151" s="2"/>
-    </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -6847,10 +6527,8 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
       <c r="AA152" s="2"/>
-      <c r="AB152" s="2"/>
-      <c r="AC152" s="2"/>
-    </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -6878,10 +6556,8 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
       <c r="AA153" s="2"/>
-      <c r="AB153" s="2"/>
-      <c r="AC153" s="2"/>
-    </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -6909,10 +6585,8 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
       <c r="AA154" s="2"/>
-      <c r="AB154" s="2"/>
-      <c r="AC154" s="2"/>
-    </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -6940,10 +6614,8 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
       <c r="AA155" s="2"/>
-      <c r="AB155" s="2"/>
-      <c r="AC155" s="2"/>
-    </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -6971,10 +6643,8 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
       <c r="AA156" s="2"/>
-      <c r="AB156" s="2"/>
-      <c r="AC156" s="2"/>
-    </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -7002,10 +6672,8 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
       <c r="AA157" s="2"/>
-      <c r="AB157" s="2"/>
-      <c r="AC157" s="2"/>
-    </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -7033,10 +6701,8 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
       <c r="AA158" s="2"/>
-      <c r="AB158" s="2"/>
-      <c r="AC158" s="2"/>
-    </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -7064,10 +6730,8 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
       <c r="AA159" s="2"/>
-      <c r="AB159" s="2"/>
-      <c r="AC159" s="2"/>
-    </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -7095,10 +6759,8 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
       <c r="AA160" s="2"/>
-      <c r="AB160" s="2"/>
-      <c r="AC160" s="2"/>
-    </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -7126,10 +6788,8 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
       <c r="AA161" s="2"/>
-      <c r="AB161" s="2"/>
-      <c r="AC161" s="2"/>
-    </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -7157,10 +6817,8 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
       <c r="AA162" s="2"/>
-      <c r="AB162" s="2"/>
-      <c r="AC162" s="2"/>
-    </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -7188,10 +6846,8 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
       <c r="AA163" s="2"/>
-      <c r="AB163" s="2"/>
-      <c r="AC163" s="2"/>
-    </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -7219,10 +6875,8 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
       <c r="AA164" s="2"/>
-      <c r="AB164" s="2"/>
-      <c r="AC164" s="2"/>
-    </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -7250,10 +6904,8 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
       <c r="AA165" s="2"/>
-      <c r="AB165" s="2"/>
-      <c r="AC165" s="2"/>
-    </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -7281,10 +6933,8 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
       <c r="AA166" s="2"/>
-      <c r="AB166" s="2"/>
-      <c r="AC166" s="2"/>
-    </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -7312,10 +6962,8 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
       <c r="AA167" s="2"/>
-      <c r="AB167" s="2"/>
-      <c r="AC167" s="2"/>
-    </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -7343,10 +6991,8 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
       <c r="AA168" s="2"/>
-      <c r="AB168" s="2"/>
-      <c r="AC168" s="2"/>
-    </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -7374,10 +7020,8 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
       <c r="AA169" s="2"/>
-      <c r="AB169" s="2"/>
-      <c r="AC169" s="2"/>
-    </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -7405,10 +7049,8 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
       <c r="AA170" s="2"/>
-      <c r="AB170" s="2"/>
-      <c r="AC170" s="2"/>
-    </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -7436,10 +7078,8 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
       <c r="AA171" s="2"/>
-      <c r="AB171" s="2"/>
-      <c r="AC171" s="2"/>
-    </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -7467,10 +7107,8 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
       <c r="AA172" s="2"/>
-      <c r="AB172" s="2"/>
-      <c r="AC172" s="2"/>
-    </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -7498,10 +7136,8 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
       <c r="AA173" s="2"/>
-      <c r="AB173" s="2"/>
-      <c r="AC173" s="2"/>
-    </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -7529,10 +7165,8 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
       <c r="AA174" s="2"/>
-      <c r="AB174" s="2"/>
-      <c r="AC174" s="2"/>
-    </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -7560,10 +7194,8 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
       <c r="AA175" s="2"/>
-      <c r="AB175" s="2"/>
-      <c r="AC175" s="2"/>
-    </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -7591,10 +7223,8 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
-      <c r="AB176" s="2"/>
-      <c r="AC176" s="2"/>
-    </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -7622,10 +7252,8 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
       <c r="AA177" s="2"/>
-      <c r="AB177" s="2"/>
-      <c r="AC177" s="2"/>
-    </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -7653,10 +7281,8 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
       <c r="AA178" s="2"/>
-      <c r="AB178" s="2"/>
-      <c r="AC178" s="2"/>
-    </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -7684,10 +7310,8 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
       <c r="AA179" s="2"/>
-      <c r="AB179" s="2"/>
-      <c r="AC179" s="2"/>
-    </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -7715,10 +7339,8 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
       <c r="AA180" s="2"/>
-      <c r="AB180" s="2"/>
-      <c r="AC180" s="2"/>
-    </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -7746,10 +7368,8 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
       <c r="AA181" s="2"/>
-      <c r="AB181" s="2"/>
-      <c r="AC181" s="2"/>
-    </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -7777,10 +7397,8 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
       <c r="AA182" s="2"/>
-      <c r="AB182" s="2"/>
-      <c r="AC182" s="2"/>
-    </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -7808,10 +7426,8 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
       <c r="AA183" s="2"/>
-      <c r="AB183" s="2"/>
-      <c r="AC183" s="2"/>
-    </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -7839,10 +7455,8 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
       <c r="AA184" s="2"/>
-      <c r="AB184" s="2"/>
-      <c r="AC184" s="2"/>
-    </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -7870,10 +7484,8 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
       <c r="AA185" s="2"/>
-      <c r="AB185" s="2"/>
-      <c r="AC185" s="2"/>
-    </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -7901,10 +7513,8 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
       <c r="AA186" s="2"/>
-      <c r="AB186" s="2"/>
-      <c r="AC186" s="2"/>
-    </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -7932,10 +7542,8 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
       <c r="AA187" s="2"/>
-      <c r="AB187" s="2"/>
-      <c r="AC187" s="2"/>
-    </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -7963,10 +7571,8 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
       <c r="AA188" s="2"/>
-      <c r="AB188" s="2"/>
-      <c r="AC188" s="2"/>
-    </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -7994,10 +7600,8 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
       <c r="AA189" s="2"/>
-      <c r="AB189" s="2"/>
-      <c r="AC189" s="2"/>
-    </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -8025,10 +7629,8 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
       <c r="AA190" s="2"/>
-      <c r="AB190" s="2"/>
-      <c r="AC190" s="2"/>
-    </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -8056,10 +7658,8 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
       <c r="AA191" s="2"/>
-      <c r="AB191" s="2"/>
-      <c r="AC191" s="2"/>
-    </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -8087,10 +7687,8 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
       <c r="AA192" s="2"/>
-      <c r="AB192" s="2"/>
-      <c r="AC192" s="2"/>
-    </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -8118,10 +7716,8 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
       <c r="AA193" s="2"/>
-      <c r="AB193" s="2"/>
-      <c r="AC193" s="2"/>
-    </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -8149,10 +7745,8 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
       <c r="AA194" s="2"/>
-      <c r="AB194" s="2"/>
-      <c r="AC194" s="2"/>
-    </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -8180,10 +7774,8 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
       <c r="AA195" s="2"/>
-      <c r="AB195" s="2"/>
-      <c r="AC195" s="2"/>
-    </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -8211,10 +7803,8 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
       <c r="AA196" s="2"/>
-      <c r="AB196" s="2"/>
-      <c r="AC196" s="2"/>
-    </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -8242,10 +7832,8 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
       <c r="AA197" s="2"/>
-      <c r="AB197" s="2"/>
-      <c r="AC197" s="2"/>
-    </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -8273,10 +7861,8 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
       <c r="AA198" s="2"/>
-      <c r="AB198" s="2"/>
-      <c r="AC198" s="2"/>
-    </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -8304,10 +7890,8 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
       <c r="AA199" s="2"/>
-      <c r="AB199" s="2"/>
-      <c r="AC199" s="2"/>
-    </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -8335,10 +7919,8 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
       <c r="AA200" s="2"/>
-      <c r="AB200" s="2"/>
-      <c r="AC200" s="2"/>
-    </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -8366,10 +7948,8 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
       <c r="AA201" s="2"/>
-      <c r="AB201" s="2"/>
-      <c r="AC201" s="2"/>
-    </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.2">
+    </row>
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -8397,46 +7977,44 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
       <c r="AA202" s="2"/>
-      <c r="AB202" s="2"/>
-      <c r="AC202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="4CnJFioDufauFlcuVYVUM3zx/XrFCj+MsvmDJD6RokHnryudMK/Xvx58l7ZP3igFAK8w35WXBagaz/w6PPWUEw==" saltValue="IeXYY1GNltMDdzxKZUakBg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="4Qur3f6B0edmuNwV5Ruzg/FsJKKWXnH+vIni1KOWOxsF8QzNDUbMj1ER2FnRrTjlqnkNsjDHIF1bEBaU5ljcMA==" saltValue="+2DyvWDjTfVT7T1WG/taeg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="12">
+    <mergeCell ref="R1:T1"/>
+    <mergeCell ref="U1:AA1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:N1"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:Q1"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="T1:V1"/>
-    <mergeCell ref="W1:AC1"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="N1:P1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2 E1:E2 F2 H2 J2 L2 Q1:Q2" xr:uid="{5E4B3162-4EBB-4AB5-B30D-164A47D38785}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 E1:E2 F2 H2 I2 K2 O1:O2" xr:uid="{5E4B3162-4EBB-4AB5-B30D-164A47D38785}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
-    <dataValidation type="custom" sqref="P2" xr:uid="{0C4A21EA-2076-49C9-9297-5A1258997CF8}">
+    <dataValidation type="custom" sqref="N2" xr:uid="{0C4A21EA-2076-49C9-9297-5A1258997CF8}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="E1:E2" r:id="rId1" location="samplingMethodsForSamplingCollection" display="SAMPLING_METHOD" xr:uid="{BFD2684A-F255-4A45-936A-FA04BB028BCC}"/>
     <hyperlink ref="H2" r:id="rId2" location="lengthMeasurementTools" xr:uid="{C4FA29B3-2C8D-4339-B3D8-F0EA1EB90752}"/>
-    <hyperlink ref="L2" r:id="rId3" location="lengthMeasurementTools" xr:uid="{75603697-09CE-4919-BF4D-3EBC3F8E1252}"/>
+    <hyperlink ref="K2" r:id="rId3" location="lengthMeasurementTools" xr:uid="{75603697-09CE-4919-BF4D-3EBC3F8E1252}"/>
     <hyperlink ref="F2" r:id="rId4" location="lengthMeasurements" xr:uid="{2187AEC4-49E1-4244-AA70-A980ABD68A20}"/>
-    <hyperlink ref="J2" r:id="rId5" location="lengthMeasurements" xr:uid="{52978703-518C-4A83-BC90-C27264C77908}"/>
-    <hyperlink ref="N2" r:id="rId6" location="fishProcessingTypes" xr:uid="{D43A58E3-BC87-4BAB-B629-28CC81AB8470}"/>
-    <hyperlink ref="Q1:Q2" r:id="rId7" location="sex" display="SEX" xr:uid="{CF9A9C8D-83EB-473F-A588-FB44C1C23798}"/>
-    <hyperlink ref="Y2" r:id="rId8" location="tagTypes" xr:uid="{EA3855C5-793B-43E7-B8B6-CF9F2C339024}"/>
-    <hyperlink ref="P2" r:id="rId9" location="weightMeasurementTools" xr:uid="{938A134D-B03F-4820-AF1D-1B56AC5AF35E}"/>
-    <hyperlink ref="T2" r:id="rId10" location="biologicalMaterials" xr:uid="{9CA25A94-9E03-42B9-ADD6-BE8860D51622}"/>
-    <hyperlink ref="U2" r:id="rId11" location="Sample_Preservation_Methods" xr:uid="{61EB242F-51D1-4BB7-828F-770517065000}"/>
-    <hyperlink ref="S2" r:id="rId12" location="Maturity_Stages" xr:uid="{6E90A65C-DD1D-4350-8774-23DB81D719E5}"/>
+    <hyperlink ref="I2" r:id="rId5" location="lengthMeasurements" xr:uid="{52978703-518C-4A83-BC90-C27264C77908}"/>
+    <hyperlink ref="L2" r:id="rId6" location="fishProcessingTypes" xr:uid="{D43A58E3-BC87-4BAB-B629-28CC81AB8470}"/>
+    <hyperlink ref="O1:O2" r:id="rId7" location="sex" display="SEX" xr:uid="{CF9A9C8D-83EB-473F-A588-FB44C1C23798}"/>
+    <hyperlink ref="W2" r:id="rId8" location="tagTypes" xr:uid="{EA3855C5-793B-43E7-B8B6-CF9F2C339024}"/>
+    <hyperlink ref="N2" r:id="rId9" location="weightMeasurementTools" xr:uid="{938A134D-B03F-4820-AF1D-1B56AC5AF35E}"/>
+    <hyperlink ref="R2" r:id="rId10" location="biologicalMaterials" xr:uid="{9CA25A94-9E03-42B9-ADD6-BE8860D51622}"/>
+    <hyperlink ref="S2" r:id="rId11" location="Sample_Preservation_Methods" xr:uid="{61EB242F-51D1-4BB7-828F-770517065000}"/>
+    <hyperlink ref="Q2" r:id="rId12" location="Maturity_Stages" xr:uid="{6E90A65C-DD1D-4350-8774-23DB81D719E5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8462,53 +8040,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="127" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="127" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="127" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="128" t="s">
-        <v>90</v>
+      <c r="E1" s="86" t="s">
+        <v>146</v>
       </c>
-      <c r="C1" s="128" t="s">
-        <v>189</v>
+      <c r="F1" s="78" t="s">
+        <v>41</v>
       </c>
-      <c r="D1" s="128" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="87" t="s">
+      <c r="G1" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="79" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="87" t="s">
-        <v>148</v>
-      </c>
-      <c r="H1" s="79" t="s">
+      <c r="H1" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="79" t="s">
+      <c r="I1" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="96" t="s">
-        <v>174</v>
+      <c r="J1" s="95" t="s">
+        <v>173</v>
       </c>
-      <c r="K1" s="98"/>
+      <c r="K1" s="97"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="129"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="35" t="s">
+      <c r="A2" s="128"/>
+      <c r="B2" s="128"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="K2" s="34" t="s">
         <v>72</v>
-      </c>
-      <c r="K2" s="35" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -11103,7 +10681,7 @@
       <c r="K202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6zCDnW+wqfrhaKF9EcUyEoCwaYT4d43eEktL4T5elqQboWNx+1UNYyJBhvetcHTxRHCuwbfBlaIjLeyzohJuTg==" saltValue="f62Nyvbwj8gV8CcFU8H/6A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="OxqJ4YJ3nUOpjSDXzjH9nprQE+NNTbP1AQ8KoCckGCmOd5BDXohmX27doiYEhYQ4QDu+kSSiwY5kcFCaPOIEUg==" saltValue="G/Pm7VL05F8thOmXQO+u1A==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="10">
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="B1:B2"/>
@@ -11126,6 +10704,8 @@
     <hyperlink ref="G1" r:id="rId2" location="handlingMethods" xr:uid="{8BA4CC5E-2A66-4A5F-8835-F30335A7CEAF}"/>
     <hyperlink ref="K2" r:id="rId3" location="individualConditions" xr:uid="{DB79B169-4F6A-4893-B37B-9DE2EE60955D}"/>
     <hyperlink ref="J2" r:id="rId4" location="individualConditions" xr:uid="{89A6A9F8-11B3-4EE1-8EFA-FE80B5E2B5D2}"/>
+    <hyperlink ref="E1:E2" r:id="rId5" location="gearInteractions" display="GEAR_INTERACTION" xr:uid="{BB06400E-FD05-DB43-B719-E4E18432D7AD}"/>
+    <hyperlink ref="G1:G2" r:id="rId6" location="handlingMethods" display="HANDLING_METHOD" xr:uid="{DD2ACD47-DD6A-A243-BDC2-F02691EFDBEA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11153,80 +10733,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="79" t="s">
-        <v>67</v>
+      <c r="A1" s="78" t="s">
+        <v>66</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="74" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="74"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="73" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="75"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="74" t="s">
-        <v>131</v>
+      <c r="G1" s="74"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="103" t="s">
+        <v>62</v>
       </c>
-      <c r="G1" s="75"/>
-      <c r="H1" s="76"/>
-      <c r="I1" s="107" t="s">
-        <v>63</v>
+      <c r="J1" s="105"/>
+      <c r="K1" s="130" t="s">
+        <v>70</v>
       </c>
-      <c r="J1" s="109"/>
-      <c r="K1" s="131" t="s">
-        <v>71</v>
+      <c r="L1" s="72" t="s">
+        <v>153</v>
       </c>
-      <c r="L1" s="73" t="s">
-        <v>154</v>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="129"/>
+      <c r="B2" s="46" t="s">
+        <v>89</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="130"/>
-      <c r="B2" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C2" s="73" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73" t="s">
-        <v>48</v>
+      <c r="D2" s="72" t="s">
+        <v>46</v>
       </c>
-      <c r="G2" s="73" t="s">
+      <c r="E2" s="72"/>
+      <c r="F2" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="73"/>
+      <c r="G2" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="72"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="72"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="80"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="32" t="s">
+      <c r="A3" s="79"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="73"/>
-      <c r="G3" s="32" t="s">
+      <c r="F3" s="72"/>
+      <c r="G3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="46" t="s">
-        <v>103</v>
+      <c r="J3" s="44" t="s">
+        <v>102</v>
       </c>
-      <c r="K3" s="131"/>
-      <c r="L3" s="73"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="72"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -14059,1250 +13639,1250 @@
   <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.83203125" style="61" customWidth="1"/>
-    <col min="2" max="2" width="13" style="61" customWidth="1"/>
-    <col min="3" max="3" width="15.5" style="61" customWidth="1"/>
+    <col min="1" max="1" width="17.83203125" style="59" customWidth="1"/>
+    <col min="2" max="2" width="13" style="59" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="59" customWidth="1"/>
     <col min="4" max="4" width="22.1640625" style="3" customWidth="1"/>
     <col min="5" max="6" width="21.33203125" style="3" customWidth="1"/>
     <col min="7" max="7" width="38.6640625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="79" t="s">
-        <v>67</v>
+      <c r="A1" s="78" t="s">
+        <v>66</v>
       </c>
-      <c r="B1" s="79" t="s">
-        <v>90</v>
+      <c r="B1" s="78" t="s">
+        <v>89</v>
       </c>
-      <c r="C1" s="79" t="s">
-        <v>189</v>
+      <c r="C1" s="78" t="s">
+        <v>188</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="59" t="s">
-        <v>150</v>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="57" t="s">
+        <v>149</v>
       </c>
-      <c r="E2" s="53" t="s">
+      <c r="E2" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="54" t="s">
-        <v>184</v>
+      <c r="F2" s="52" t="s">
+        <v>183</v>
       </c>
-      <c r="G2" s="55" t="s">
-        <v>144</v>
+      <c r="G2" s="53" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D3" s="60"/>
+      <c r="D3" s="58"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D4" s="60"/>
+      <c r="D4" s="58"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D5" s="60"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D6" s="60"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D7" s="60"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D8" s="60"/>
+      <c r="D8" s="58"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D9" s="60"/>
+      <c r="D9" s="58"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D10" s="60"/>
+      <c r="D10" s="58"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D11" s="60"/>
+      <c r="D11" s="58"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D12" s="60"/>
+      <c r="D12" s="58"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D13" s="60"/>
+      <c r="D13" s="58"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D14" s="60"/>
+      <c r="D14" s="58"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D15" s="60"/>
+      <c r="D15" s="58"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="D16" s="60"/>
+      <c r="D16" s="58"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D17" s="60"/>
+      <c r="D17" s="58"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D18" s="60"/>
+      <c r="D18" s="58"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D19" s="60"/>
+      <c r="D19" s="58"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D20" s="60"/>
+      <c r="D20" s="58"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D21" s="60"/>
+      <c r="D21" s="58"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D22" s="60"/>
+      <c r="D22" s="58"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D23" s="60"/>
+      <c r="D23" s="58"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D24" s="60"/>
+      <c r="D24" s="58"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D25" s="60"/>
+      <c r="D25" s="58"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D26" s="60"/>
+      <c r="D26" s="58"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D27" s="60"/>
+      <c r="D27" s="58"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
     </row>
     <row r="28" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D28" s="60"/>
+      <c r="D28" s="58"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
     </row>
     <row r="29" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D29" s="60"/>
+      <c r="D29" s="58"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
     <row r="30" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D30" s="60"/>
+      <c r="D30" s="58"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
     </row>
     <row r="31" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D31" s="60"/>
+      <c r="D31" s="58"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D32" s="60"/>
+      <c r="D32" s="58"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
     </row>
     <row r="33" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D33" s="60"/>
+      <c r="D33" s="58"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
     </row>
     <row r="34" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D34" s="60"/>
+      <c r="D34" s="58"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
     </row>
     <row r="35" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D35" s="60"/>
+      <c r="D35" s="58"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
     </row>
     <row r="36" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D36" s="60"/>
+      <c r="D36" s="58"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D37" s="60"/>
+      <c r="D37" s="58"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
     </row>
     <row r="38" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D38" s="60"/>
+      <c r="D38" s="58"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
     </row>
     <row r="39" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D39" s="60"/>
+      <c r="D39" s="58"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
     </row>
     <row r="40" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D40" s="60"/>
+      <c r="D40" s="58"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
     </row>
     <row r="41" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D41" s="60"/>
+      <c r="D41" s="58"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
     </row>
     <row r="42" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D42" s="60"/>
+      <c r="D42" s="58"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
     </row>
     <row r="43" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D43" s="60"/>
+      <c r="D43" s="58"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
     </row>
     <row r="44" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D44" s="60"/>
+      <c r="D44" s="58"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
     </row>
     <row r="45" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D45" s="60"/>
+      <c r="D45" s="58"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
     </row>
     <row r="46" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D46" s="60"/>
+      <c r="D46" s="58"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
     </row>
     <row r="47" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D47" s="60"/>
+      <c r="D47" s="58"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
     </row>
     <row r="48" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D48" s="60"/>
+      <c r="D48" s="58"/>
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
     <row r="49" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D49" s="60"/>
+      <c r="D49" s="58"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
     <row r="50" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D50" s="60"/>
+      <c r="D50" s="58"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
     </row>
     <row r="51" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D51" s="60"/>
+      <c r="D51" s="58"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
     </row>
     <row r="52" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D52" s="60"/>
+      <c r="D52" s="58"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
     </row>
     <row r="53" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D53" s="60"/>
+      <c r="D53" s="58"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
     </row>
     <row r="54" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D54" s="60"/>
+      <c r="D54" s="58"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
     </row>
     <row r="55" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D55" s="60"/>
+      <c r="D55" s="58"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D56" s="60"/>
+      <c r="D56" s="58"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
     </row>
     <row r="57" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D57" s="60"/>
+      <c r="D57" s="58"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
     </row>
     <row r="58" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D58" s="60"/>
+      <c r="D58" s="58"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
     </row>
     <row r="59" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D59" s="60"/>
+      <c r="D59" s="58"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
     </row>
     <row r="60" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D60" s="60"/>
+      <c r="D60" s="58"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
     </row>
     <row r="61" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D61" s="60"/>
+      <c r="D61" s="58"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
     </row>
     <row r="62" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D62" s="60"/>
+      <c r="D62" s="58"/>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
     </row>
     <row r="63" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D63" s="60"/>
+      <c r="D63" s="58"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
     </row>
     <row r="64" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D64" s="60"/>
+      <c r="D64" s="58"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
     </row>
     <row r="65" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D65" s="60"/>
+      <c r="D65" s="58"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
     </row>
     <row r="66" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D66" s="60"/>
+      <c r="D66" s="58"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D67" s="60"/>
+      <c r="D67" s="58"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
     </row>
     <row r="68" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D68" s="60"/>
+      <c r="D68" s="58"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
     </row>
     <row r="69" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D69" s="60"/>
+      <c r="D69" s="58"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D70" s="60"/>
+      <c r="D70" s="58"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
     </row>
     <row r="71" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D71" s="60"/>
+      <c r="D71" s="58"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
     </row>
     <row r="72" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D72" s="60"/>
+      <c r="D72" s="58"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
     </row>
     <row r="73" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D73" s="60"/>
+      <c r="D73" s="58"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
     </row>
     <row r="74" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D74" s="60"/>
+      <c r="D74" s="58"/>
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
     </row>
     <row r="75" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D75" s="60"/>
+      <c r="D75" s="58"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
     </row>
     <row r="76" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D76" s="60"/>
+      <c r="D76" s="58"/>
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
     </row>
     <row r="77" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D77" s="60"/>
+      <c r="D77" s="58"/>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
     </row>
     <row r="78" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D78" s="60"/>
+      <c r="D78" s="58"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
     </row>
     <row r="79" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D79" s="60"/>
+      <c r="D79" s="58"/>
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
     </row>
     <row r="80" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D80" s="60"/>
+      <c r="D80" s="58"/>
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
     </row>
     <row r="81" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D81" s="60"/>
+      <c r="D81" s="58"/>
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
     </row>
     <row r="82" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D82" s="60"/>
+      <c r="D82" s="58"/>
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
     </row>
     <row r="83" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D83" s="60"/>
+      <c r="D83" s="58"/>
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
     </row>
     <row r="84" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D84" s="60"/>
+      <c r="D84" s="58"/>
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
     </row>
     <row r="85" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D85" s="60"/>
+      <c r="D85" s="58"/>
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
     </row>
     <row r="86" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D86" s="60"/>
+      <c r="D86" s="58"/>
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
     </row>
     <row r="87" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D87" s="60"/>
+      <c r="D87" s="58"/>
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
     </row>
     <row r="88" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D88" s="60"/>
+      <c r="D88" s="58"/>
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
     </row>
     <row r="89" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D89" s="60"/>
+      <c r="D89" s="58"/>
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
     </row>
     <row r="90" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D90" s="60"/>
+      <c r="D90" s="58"/>
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
     </row>
     <row r="91" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D91" s="60"/>
+      <c r="D91" s="58"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
     </row>
     <row r="92" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D92" s="60"/>
+      <c r="D92" s="58"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
     </row>
     <row r="93" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D93" s="60"/>
+      <c r="D93" s="58"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
     </row>
     <row r="94" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D94" s="60"/>
+      <c r="D94" s="58"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
     </row>
     <row r="95" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D95" s="60"/>
+      <c r="D95" s="58"/>
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
     </row>
     <row r="96" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D96" s="60"/>
+      <c r="D96" s="58"/>
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
     </row>
     <row r="97" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D97" s="60"/>
+      <c r="D97" s="58"/>
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
     </row>
     <row r="98" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D98" s="60"/>
+      <c r="D98" s="58"/>
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
     </row>
     <row r="99" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D99" s="60"/>
+      <c r="D99" s="58"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
     </row>
     <row r="100" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D100" s="60"/>
+      <c r="D100" s="58"/>
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
     </row>
     <row r="101" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D101" s="60"/>
+      <c r="D101" s="58"/>
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
     </row>
     <row r="102" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D102" s="60"/>
+      <c r="D102" s="58"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
     </row>
     <row r="103" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D103" s="60"/>
+      <c r="D103" s="58"/>
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
     </row>
     <row r="104" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D104" s="60"/>
+      <c r="D104" s="58"/>
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
     </row>
     <row r="105" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D105" s="60"/>
+      <c r="D105" s="58"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
     </row>
     <row r="106" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D106" s="60"/>
+      <c r="D106" s="58"/>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
     </row>
     <row r="107" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D107" s="60"/>
+      <c r="D107" s="58"/>
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
     </row>
     <row r="108" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D108" s="60"/>
+      <c r="D108" s="58"/>
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
     </row>
     <row r="109" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D109" s="60"/>
+      <c r="D109" s="58"/>
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
     </row>
     <row r="110" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D110" s="60"/>
+      <c r="D110" s="58"/>
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
     </row>
     <row r="111" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D111" s="60"/>
+      <c r="D111" s="58"/>
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
     </row>
     <row r="112" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D112" s="60"/>
+      <c r="D112" s="58"/>
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
     </row>
     <row r="113" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D113" s="60"/>
+      <c r="D113" s="58"/>
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
     </row>
     <row r="114" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D114" s="60"/>
+      <c r="D114" s="58"/>
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
     </row>
     <row r="115" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D115" s="60"/>
+      <c r="D115" s="58"/>
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
     </row>
     <row r="116" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D116" s="60"/>
+      <c r="D116" s="58"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
     </row>
     <row r="117" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D117" s="60"/>
+      <c r="D117" s="58"/>
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
     </row>
     <row r="118" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D118" s="60"/>
+      <c r="D118" s="58"/>
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
     </row>
     <row r="119" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D119" s="60"/>
+      <c r="D119" s="58"/>
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
     </row>
     <row r="120" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D120" s="60"/>
+      <c r="D120" s="58"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
     </row>
     <row r="121" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D121" s="60"/>
+      <c r="D121" s="58"/>
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
     </row>
     <row r="122" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D122" s="60"/>
+      <c r="D122" s="58"/>
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
     </row>
     <row r="123" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D123" s="60"/>
+      <c r="D123" s="58"/>
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
     </row>
     <row r="124" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D124" s="60"/>
+      <c r="D124" s="58"/>
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
     </row>
     <row r="125" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D125" s="60"/>
+      <c r="D125" s="58"/>
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
     </row>
     <row r="126" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D126" s="60"/>
+      <c r="D126" s="58"/>
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
     </row>
     <row r="127" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D127" s="60"/>
+      <c r="D127" s="58"/>
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
     </row>
     <row r="128" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D128" s="60"/>
+      <c r="D128" s="58"/>
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
     </row>
     <row r="129" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D129" s="60"/>
+      <c r="D129" s="58"/>
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
     </row>
     <row r="130" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D130" s="60"/>
+      <c r="D130" s="58"/>
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
     </row>
     <row r="131" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D131" s="60"/>
+      <c r="D131" s="58"/>
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
     </row>
     <row r="132" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D132" s="60"/>
+      <c r="D132" s="58"/>
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
     </row>
     <row r="133" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D133" s="60"/>
+      <c r="D133" s="58"/>
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
     </row>
     <row r="134" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D134" s="60"/>
+      <c r="D134" s="58"/>
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
     </row>
     <row r="135" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D135" s="60"/>
+      <c r="D135" s="58"/>
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
     </row>
     <row r="136" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D136" s="60"/>
+      <c r="D136" s="58"/>
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
     </row>
     <row r="137" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D137" s="60"/>
+      <c r="D137" s="58"/>
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
     </row>
     <row r="138" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D138" s="60"/>
+      <c r="D138" s="58"/>
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
     </row>
     <row r="139" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D139" s="60"/>
+      <c r="D139" s="58"/>
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
     </row>
     <row r="140" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D140" s="60"/>
+      <c r="D140" s="58"/>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
     </row>
     <row r="141" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D141" s="60"/>
+      <c r="D141" s="58"/>
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
     </row>
     <row r="142" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D142" s="60"/>
+      <c r="D142" s="58"/>
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
     </row>
     <row r="143" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D143" s="60"/>
+      <c r="D143" s="58"/>
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
     </row>
     <row r="144" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D144" s="60"/>
+      <c r="D144" s="58"/>
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
     </row>
     <row r="145" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D145" s="60"/>
+      <c r="D145" s="58"/>
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
     </row>
     <row r="146" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D146" s="60"/>
+      <c r="D146" s="58"/>
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
     </row>
     <row r="147" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D147" s="60"/>
+      <c r="D147" s="58"/>
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
     </row>
     <row r="148" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D148" s="60"/>
+      <c r="D148" s="58"/>
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
     </row>
     <row r="149" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D149" s="60"/>
+      <c r="D149" s="58"/>
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
     </row>
     <row r="150" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D150" s="60"/>
+      <c r="D150" s="58"/>
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
     </row>
     <row r="151" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D151" s="60"/>
+      <c r="D151" s="58"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
     </row>
     <row r="152" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D152" s="60"/>
+      <c r="D152" s="58"/>
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
     </row>
     <row r="153" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D153" s="60"/>
+      <c r="D153" s="58"/>
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
     </row>
     <row r="154" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D154" s="60"/>
+      <c r="D154" s="58"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
     </row>
     <row r="155" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D155" s="60"/>
+      <c r="D155" s="58"/>
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
     </row>
     <row r="156" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D156" s="60"/>
+      <c r="D156" s="58"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
     </row>
     <row r="157" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D157" s="60"/>
+      <c r="D157" s="58"/>
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
     </row>
     <row r="158" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D158" s="60"/>
+      <c r="D158" s="58"/>
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
     </row>
     <row r="159" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D159" s="60"/>
+      <c r="D159" s="58"/>
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
     </row>
     <row r="160" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D160" s="60"/>
+      <c r="D160" s="58"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
     </row>
     <row r="161" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D161" s="60"/>
+      <c r="D161" s="58"/>
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
     </row>
     <row r="162" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D162" s="60"/>
+      <c r="D162" s="58"/>
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
     </row>
     <row r="163" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D163" s="60"/>
+      <c r="D163" s="58"/>
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
     </row>
     <row r="164" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D164" s="60"/>
+      <c r="D164" s="58"/>
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
     </row>
     <row r="165" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D165" s="60"/>
+      <c r="D165" s="58"/>
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
     </row>
     <row r="166" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D166" s="60"/>
+      <c r="D166" s="58"/>
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
     </row>
     <row r="167" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D167" s="60"/>
+      <c r="D167" s="58"/>
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
     </row>
     <row r="168" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D168" s="60"/>
+      <c r="D168" s="58"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
     </row>
     <row r="169" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D169" s="60"/>
+      <c r="D169" s="58"/>
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
     </row>
     <row r="170" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D170" s="60"/>
+      <c r="D170" s="58"/>
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
     </row>
     <row r="171" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D171" s="60"/>
+      <c r="D171" s="58"/>
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
     </row>
     <row r="172" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D172" s="60"/>
+      <c r="D172" s="58"/>
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
     </row>
     <row r="173" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D173" s="60"/>
+      <c r="D173" s="58"/>
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
     </row>
     <row r="174" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D174" s="60"/>
+      <c r="D174" s="58"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
     </row>
     <row r="175" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D175" s="60"/>
+      <c r="D175" s="58"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
     </row>
     <row r="176" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D176" s="60"/>
+      <c r="D176" s="58"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
     </row>
     <row r="177" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D177" s="60"/>
+      <c r="D177" s="58"/>
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
     </row>
     <row r="178" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D178" s="60"/>
+      <c r="D178" s="58"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
     </row>
     <row r="179" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D179" s="60"/>
+      <c r="D179" s="58"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
     </row>
     <row r="180" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D180" s="60"/>
+      <c r="D180" s="58"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
     </row>
     <row r="181" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D181" s="60"/>
+      <c r="D181" s="58"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
     </row>
     <row r="182" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D182" s="60"/>
+      <c r="D182" s="58"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
     </row>
     <row r="183" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D183" s="60"/>
+      <c r="D183" s="58"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
     </row>
     <row r="184" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D184" s="60"/>
+      <c r="D184" s="58"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
     </row>
     <row r="185" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D185" s="60"/>
+      <c r="D185" s="58"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
     </row>
     <row r="186" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D186" s="60"/>
+      <c r="D186" s="58"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
     </row>
     <row r="187" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D187" s="60"/>
+      <c r="D187" s="58"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
     </row>
     <row r="188" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D188" s="60"/>
+      <c r="D188" s="58"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
     </row>
     <row r="189" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D189" s="60"/>
+      <c r="D189" s="58"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
     </row>
     <row r="190" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D190" s="60"/>
+      <c r="D190" s="58"/>
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
     </row>
     <row r="191" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D191" s="60"/>
+      <c r="D191" s="58"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
     </row>
     <row r="192" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D192" s="60"/>
+      <c r="D192" s="58"/>
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
     </row>
     <row r="193" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D193" s="60"/>
+      <c r="D193" s="58"/>
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
     </row>
     <row r="194" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D194" s="60"/>
+      <c r="D194" s="58"/>
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
     </row>
     <row r="195" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D195" s="60"/>
+      <c r="D195" s="58"/>
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
     </row>
     <row r="196" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D196" s="60"/>
+      <c r="D196" s="58"/>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
     </row>
     <row r="197" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D197" s="60"/>
+      <c r="D197" s="58"/>
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
     </row>
     <row r="198" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D198" s="60"/>
+      <c r="D198" s="58"/>
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
     </row>
     <row r="199" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D199" s="60"/>
+      <c r="D199" s="58"/>
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
     </row>
     <row r="200" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D200" s="60"/>
+      <c r="D200" s="58"/>
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
     </row>
     <row r="201" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D201" s="60"/>
+      <c r="D201" s="58"/>
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
     </row>
     <row r="202" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D202" s="60"/>
+      <c r="D202" s="58"/>
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+9902GILsXPbcsEW4Ajs2kZ9h5kj+iucmUxoCbdK1wYrWTYMu4avre9lXltew3vm2L0C2xbmiw3w8xGc8rFM8g==" saltValue="7mRvml2HT5q+R4eCphaEWA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7P/KGP8E3MOTPzO9v+ggJG+Ciknvu+Aw0Y7smgbX2Ec1qWRcFxpdDd1+2+nJ2wN8QOcX0yX1d3iV+TxZGFtJ2g==" saltValue="zXe1tgPEThB80cgvwcyqdw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="4">
     <mergeCell ref="D1:G1"/>
     <mergeCell ref="A1:A2"/>
@@ -15330,10 +14910,10 @@
   <dimension ref="A1:K202"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.5" style="61" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" style="61" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" style="61" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" style="61" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="59" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="59" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="59" customWidth="1"/>
+    <col min="4" max="4" width="14.83203125" style="59" customWidth="1"/>
     <col min="5" max="5" width="26.5" style="3" customWidth="1"/>
     <col min="6" max="6" width="21" style="3" customWidth="1"/>
     <col min="7" max="7" width="25.5" style="3" bestFit="1" customWidth="1"/>
@@ -15343,55 +14923,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="78" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="79" t="s">
-        <v>90</v>
+      <c r="E1" s="131" t="s">
+        <v>146</v>
       </c>
-      <c r="C1" s="79" t="s">
-        <v>189</v>
+      <c r="F1" s="78" t="s">
+        <v>41</v>
       </c>
-      <c r="D1" s="79" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="132" t="s">
+      <c r="G1" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="F1" s="79" t="s">
-        <v>41</v>
+      <c r="H1" s="86" t="s">
+        <v>71</v>
       </c>
-      <c r="G1" s="87" t="s">
-        <v>148</v>
-      </c>
-      <c r="H1" s="87" t="s">
+      <c r="I1" s="86" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="87" t="s">
-        <v>73</v>
-      </c>
-      <c r="J1" s="79" t="s">
+      <c r="J1" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="K1" s="79" t="s">
+      <c r="K1" s="78" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="80"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="132"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E3" s="60"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -15400,7 +14980,7 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E4" s="60"/>
+      <c r="E4" s="58"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -15409,7 +14989,7 @@
       <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E5" s="60"/>
+      <c r="E5" s="58"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -15418,7 +14998,7 @@
       <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E6" s="60"/>
+      <c r="E6" s="58"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -15427,7 +15007,7 @@
       <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E7" s="60"/>
+      <c r="E7" s="58"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -15436,7 +15016,7 @@
       <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E8" s="60"/>
+      <c r="E8" s="58"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -15445,7 +15025,7 @@
       <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E9" s="60"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -15454,7 +15034,7 @@
       <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E10" s="60"/>
+      <c r="E10" s="58"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -15463,7 +15043,7 @@
       <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E11" s="60"/>
+      <c r="E11" s="58"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -15472,7 +15052,7 @@
       <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E12" s="60"/>
+      <c r="E12" s="58"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -15481,7 +15061,7 @@
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E13" s="60"/>
+      <c r="E13" s="58"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -15490,7 +15070,7 @@
       <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E14" s="60"/>
+      <c r="E14" s="58"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -15499,7 +15079,7 @@
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E15" s="60"/>
+      <c r="E15" s="58"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -15508,7 +15088,7 @@
       <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E16" s="60"/>
+      <c r="E16" s="58"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -15517,7 +15097,7 @@
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E17" s="60"/>
+      <c r="E17" s="58"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -15526,7 +15106,7 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E18" s="60"/>
+      <c r="E18" s="58"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -15535,7 +15115,7 @@
       <c r="K18" s="2"/>
     </row>
     <row r="19" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E19" s="60"/>
+      <c r="E19" s="58"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -15544,7 +15124,7 @@
       <c r="K19" s="2"/>
     </row>
     <row r="20" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E20" s="60"/>
+      <c r="E20" s="58"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -15553,7 +15133,7 @@
       <c r="K20" s="2"/>
     </row>
     <row r="21" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E21" s="60"/>
+      <c r="E21" s="58"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -15562,7 +15142,7 @@
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E22" s="60"/>
+      <c r="E22" s="58"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -15571,16 +15151,18 @@
       <c r="K22" s="2"/>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E23" s="60"/>
+      <c r="E23" s="58"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
+      <c r="I23" s="2" t="s">
+        <v>190</v>
+      </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
     <row r="24" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E24" s="60"/>
+      <c r="E24" s="58"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -15589,7 +15171,7 @@
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E25" s="60"/>
+      <c r="E25" s="58"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -15598,7 +15180,7 @@
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E26" s="60"/>
+      <c r="E26" s="58"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -15607,7 +15189,7 @@
       <c r="K26" s="2"/>
     </row>
     <row r="27" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E27" s="60"/>
+      <c r="E27" s="58"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -15616,7 +15198,7 @@
       <c r="K27" s="2"/>
     </row>
     <row r="28" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E28" s="60"/>
+      <c r="E28" s="58"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -15625,7 +15207,7 @@
       <c r="K28" s="2"/>
     </row>
     <row r="29" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E29" s="60"/>
+      <c r="E29" s="58"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -15634,7 +15216,7 @@
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E30" s="60"/>
+      <c r="E30" s="58"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -15643,7 +15225,7 @@
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E31" s="60"/>
+      <c r="E31" s="58"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -15652,7 +15234,7 @@
       <c r="K31" s="2"/>
     </row>
     <row r="32" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E32" s="60"/>
+      <c r="E32" s="58"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -15661,7 +15243,7 @@
       <c r="K32" s="2"/>
     </row>
     <row r="33" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E33" s="60"/>
+      <c r="E33" s="58"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -15670,7 +15252,7 @@
       <c r="K33" s="2"/>
     </row>
     <row r="34" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E34" s="60"/>
+      <c r="E34" s="58"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -15679,7 +15261,7 @@
       <c r="K34" s="2"/>
     </row>
     <row r="35" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E35" s="60"/>
+      <c r="E35" s="58"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -15688,7 +15270,7 @@
       <c r="K35" s="2"/>
     </row>
     <row r="36" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E36" s="60"/>
+      <c r="E36" s="58"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -15697,7 +15279,7 @@
       <c r="K36" s="2"/>
     </row>
     <row r="37" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E37" s="60"/>
+      <c r="E37" s="58"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -15706,7 +15288,7 @@
       <c r="K37" s="2"/>
     </row>
     <row r="38" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E38" s="60"/>
+      <c r="E38" s="58"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -15715,7 +15297,7 @@
       <c r="K38" s="2"/>
     </row>
     <row r="39" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E39" s="60"/>
+      <c r="E39" s="58"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -15724,7 +15306,7 @@
       <c r="K39" s="2"/>
     </row>
     <row r="40" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E40" s="60"/>
+      <c r="E40" s="58"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -15733,7 +15315,7 @@
       <c r="K40" s="2"/>
     </row>
     <row r="41" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E41" s="60"/>
+      <c r="E41" s="58"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -15742,7 +15324,7 @@
       <c r="K41" s="2"/>
     </row>
     <row r="42" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E42" s="60"/>
+      <c r="E42" s="58"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -15751,7 +15333,7 @@
       <c r="K42" s="2"/>
     </row>
     <row r="43" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E43" s="60"/>
+      <c r="E43" s="58"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -15760,7 +15342,7 @@
       <c r="K43" s="2"/>
     </row>
     <row r="44" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E44" s="60"/>
+      <c r="E44" s="58"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -15769,7 +15351,7 @@
       <c r="K44" s="2"/>
     </row>
     <row r="45" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E45" s="60"/>
+      <c r="E45" s="58"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -15778,7 +15360,7 @@
       <c r="K45" s="2"/>
     </row>
     <row r="46" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E46" s="60"/>
+      <c r="E46" s="58"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -15787,7 +15369,7 @@
       <c r="K46" s="2"/>
     </row>
     <row r="47" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E47" s="60"/>
+      <c r="E47" s="58"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -15796,7 +15378,7 @@
       <c r="K47" s="2"/>
     </row>
     <row r="48" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E48" s="60"/>
+      <c r="E48" s="58"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -15805,7 +15387,7 @@
       <c r="K48" s="2"/>
     </row>
     <row r="49" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E49" s="60"/>
+      <c r="E49" s="58"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -15814,7 +15396,7 @@
       <c r="K49" s="2"/>
     </row>
     <row r="50" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E50" s="60"/>
+      <c r="E50" s="58"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -15823,7 +15405,7 @@
       <c r="K50" s="2"/>
     </row>
     <row r="51" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E51" s="60"/>
+      <c r="E51" s="58"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -15832,7 +15414,7 @@
       <c r="K51" s="2"/>
     </row>
     <row r="52" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E52" s="60"/>
+      <c r="E52" s="58"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -15841,7 +15423,7 @@
       <c r="K52" s="2"/>
     </row>
     <row r="53" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E53" s="60"/>
+      <c r="E53" s="58"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -15850,7 +15432,7 @@
       <c r="K53" s="2"/>
     </row>
     <row r="54" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E54" s="60"/>
+      <c r="E54" s="58"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -15859,7 +15441,7 @@
       <c r="K54" s="2"/>
     </row>
     <row r="55" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E55" s="60"/>
+      <c r="E55" s="58"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -15868,7 +15450,7 @@
       <c r="K55" s="2"/>
     </row>
     <row r="56" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E56" s="60"/>
+      <c r="E56" s="58"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -15877,7 +15459,7 @@
       <c r="K56" s="2"/>
     </row>
     <row r="57" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E57" s="60"/>
+      <c r="E57" s="58"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -15886,7 +15468,7 @@
       <c r="K57" s="2"/>
     </row>
     <row r="58" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E58" s="60"/>
+      <c r="E58" s="58"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -15895,7 +15477,7 @@
       <c r="K58" s="2"/>
     </row>
     <row r="59" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E59" s="60"/>
+      <c r="E59" s="58"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -15904,7 +15486,7 @@
       <c r="K59" s="2"/>
     </row>
     <row r="60" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E60" s="60"/>
+      <c r="E60" s="58"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -15913,7 +15495,7 @@
       <c r="K60" s="2"/>
     </row>
     <row r="61" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E61" s="60"/>
+      <c r="E61" s="58"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -15922,7 +15504,7 @@
       <c r="K61" s="2"/>
     </row>
     <row r="62" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E62" s="60"/>
+      <c r="E62" s="58"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -15931,7 +15513,7 @@
       <c r="K62" s="2"/>
     </row>
     <row r="63" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E63" s="60"/>
+      <c r="E63" s="58"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -15940,7 +15522,7 @@
       <c r="K63" s="2"/>
     </row>
     <row r="64" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E64" s="60"/>
+      <c r="E64" s="58"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -15949,7 +15531,7 @@
       <c r="K64" s="2"/>
     </row>
     <row r="65" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E65" s="60"/>
+      <c r="E65" s="58"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -15958,7 +15540,7 @@
       <c r="K65" s="2"/>
     </row>
     <row r="66" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E66" s="60"/>
+      <c r="E66" s="58"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -15967,7 +15549,7 @@
       <c r="K66" s="2"/>
     </row>
     <row r="67" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E67" s="60"/>
+      <c r="E67" s="58"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -15976,7 +15558,7 @@
       <c r="K67" s="2"/>
     </row>
     <row r="68" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E68" s="60"/>
+      <c r="E68" s="58"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -15985,7 +15567,7 @@
       <c r="K68" s="2"/>
     </row>
     <row r="69" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E69" s="60"/>
+      <c r="E69" s="58"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -15994,7 +15576,7 @@
       <c r="K69" s="2"/>
     </row>
     <row r="70" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E70" s="60"/>
+      <c r="E70" s="58"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -16003,7 +15585,7 @@
       <c r="K70" s="2"/>
     </row>
     <row r="71" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E71" s="60"/>
+      <c r="E71" s="58"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -16012,7 +15594,7 @@
       <c r="K71" s="2"/>
     </row>
     <row r="72" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E72" s="60"/>
+      <c r="E72" s="58"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -16021,7 +15603,7 @@
       <c r="K72" s="2"/>
     </row>
     <row r="73" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E73" s="60"/>
+      <c r="E73" s="58"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -16030,7 +15612,7 @@
       <c r="K73" s="2"/>
     </row>
     <row r="74" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E74" s="60"/>
+      <c r="E74" s="58"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -16039,7 +15621,7 @@
       <c r="K74" s="2"/>
     </row>
     <row r="75" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E75" s="60"/>
+      <c r="E75" s="58"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -16048,7 +15630,7 @@
       <c r="K75" s="2"/>
     </row>
     <row r="76" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E76" s="60"/>
+      <c r="E76" s="58"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -16057,7 +15639,7 @@
       <c r="K76" s="2"/>
     </row>
     <row r="77" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E77" s="60"/>
+      <c r="E77" s="58"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -16066,7 +15648,7 @@
       <c r="K77" s="2"/>
     </row>
     <row r="78" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E78" s="60"/>
+      <c r="E78" s="58"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -16075,7 +15657,7 @@
       <c r="K78" s="2"/>
     </row>
     <row r="79" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E79" s="60"/>
+      <c r="E79" s="58"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -16084,7 +15666,7 @@
       <c r="K79" s="2"/>
     </row>
     <row r="80" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E80" s="60"/>
+      <c r="E80" s="58"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -16093,7 +15675,7 @@
       <c r="K80" s="2"/>
     </row>
     <row r="81" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E81" s="60"/>
+      <c r="E81" s="58"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -16102,7 +15684,7 @@
       <c r="K81" s="2"/>
     </row>
     <row r="82" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E82" s="60"/>
+      <c r="E82" s="58"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -16111,7 +15693,7 @@
       <c r="K82" s="2"/>
     </row>
     <row r="83" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E83" s="60"/>
+      <c r="E83" s="58"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -16120,7 +15702,7 @@
       <c r="K83" s="2"/>
     </row>
     <row r="84" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E84" s="60"/>
+      <c r="E84" s="58"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -16129,7 +15711,7 @@
       <c r="K84" s="2"/>
     </row>
     <row r="85" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E85" s="60"/>
+      <c r="E85" s="58"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -16138,7 +15720,7 @@
       <c r="K85" s="2"/>
     </row>
     <row r="86" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E86" s="60"/>
+      <c r="E86" s="58"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -16147,7 +15729,7 @@
       <c r="K86" s="2"/>
     </row>
     <row r="87" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E87" s="60"/>
+      <c r="E87" s="58"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -16156,7 +15738,7 @@
       <c r="K87" s="2"/>
     </row>
     <row r="88" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E88" s="60"/>
+      <c r="E88" s="58"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -16165,7 +15747,7 @@
       <c r="K88" s="2"/>
     </row>
     <row r="89" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E89" s="60"/>
+      <c r="E89" s="58"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -16174,7 +15756,7 @@
       <c r="K89" s="2"/>
     </row>
     <row r="90" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E90" s="60"/>
+      <c r="E90" s="58"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -16183,7 +15765,7 @@
       <c r="K90" s="2"/>
     </row>
     <row r="91" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E91" s="60"/>
+      <c r="E91" s="58"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -16192,7 +15774,7 @@
       <c r="K91" s="2"/>
     </row>
     <row r="92" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E92" s="60"/>
+      <c r="E92" s="58"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -16201,7 +15783,7 @@
       <c r="K92" s="2"/>
     </row>
     <row r="93" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E93" s="60"/>
+      <c r="E93" s="58"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -16210,7 +15792,7 @@
       <c r="K93" s="2"/>
     </row>
     <row r="94" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E94" s="60"/>
+      <c r="E94" s="58"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -16219,7 +15801,7 @@
       <c r="K94" s="2"/>
     </row>
     <row r="95" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E95" s="60"/>
+      <c r="E95" s="58"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -16228,7 +15810,7 @@
       <c r="K95" s="2"/>
     </row>
     <row r="96" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E96" s="60"/>
+      <c r="E96" s="58"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -16237,7 +15819,7 @@
       <c r="K96" s="2"/>
     </row>
     <row r="97" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E97" s="60"/>
+      <c r="E97" s="58"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -16246,7 +15828,7 @@
       <c r="K97" s="2"/>
     </row>
     <row r="98" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E98" s="60"/>
+      <c r="E98" s="58"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -16255,7 +15837,7 @@
       <c r="K98" s="2"/>
     </row>
     <row r="99" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E99" s="60"/>
+      <c r="E99" s="58"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -16264,7 +15846,7 @@
       <c r="K99" s="2"/>
     </row>
     <row r="100" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E100" s="60"/>
+      <c r="E100" s="58"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -16273,7 +15855,7 @@
       <c r="K100" s="2"/>
     </row>
     <row r="101" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E101" s="60"/>
+      <c r="E101" s="58"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -16282,7 +15864,7 @@
       <c r="K101" s="2"/>
     </row>
     <row r="102" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E102" s="60"/>
+      <c r="E102" s="58"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -16291,7 +15873,7 @@
       <c r="K102" s="2"/>
     </row>
     <row r="103" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E103" s="60"/>
+      <c r="E103" s="58"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -16300,7 +15882,7 @@
       <c r="K103" s="2"/>
     </row>
     <row r="104" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E104" s="60"/>
+      <c r="E104" s="58"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -16309,7 +15891,7 @@
       <c r="K104" s="2"/>
     </row>
     <row r="105" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E105" s="60"/>
+      <c r="E105" s="58"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -16318,7 +15900,7 @@
       <c r="K105" s="2"/>
     </row>
     <row r="106" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E106" s="60"/>
+      <c r="E106" s="58"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -16327,7 +15909,7 @@
       <c r="K106" s="2"/>
     </row>
     <row r="107" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E107" s="60"/>
+      <c r="E107" s="58"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -16336,7 +15918,7 @@
       <c r="K107" s="2"/>
     </row>
     <row r="108" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E108" s="60"/>
+      <c r="E108" s="58"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -16345,7 +15927,7 @@
       <c r="K108" s="2"/>
     </row>
     <row r="109" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E109" s="60"/>
+      <c r="E109" s="58"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -16354,7 +15936,7 @@
       <c r="K109" s="2"/>
     </row>
     <row r="110" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E110" s="60"/>
+      <c r="E110" s="58"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -16363,7 +15945,7 @@
       <c r="K110" s="2"/>
     </row>
     <row r="111" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E111" s="60"/>
+      <c r="E111" s="58"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -16372,7 +15954,7 @@
       <c r="K111" s="2"/>
     </row>
     <row r="112" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E112" s="60"/>
+      <c r="E112" s="58"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -16381,7 +15963,7 @@
       <c r="K112" s="2"/>
     </row>
     <row r="113" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E113" s="60"/>
+      <c r="E113" s="58"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
@@ -16390,7 +15972,7 @@
       <c r="K113" s="2"/>
     </row>
     <row r="114" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E114" s="60"/>
+      <c r="E114" s="58"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -16399,7 +15981,7 @@
       <c r="K114" s="2"/>
     </row>
     <row r="115" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E115" s="60"/>
+      <c r="E115" s="58"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
@@ -16408,7 +15990,7 @@
       <c r="K115" s="2"/>
     </row>
     <row r="116" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E116" s="60"/>
+      <c r="E116" s="58"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -16417,7 +15999,7 @@
       <c r="K116" s="2"/>
     </row>
     <row r="117" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E117" s="60"/>
+      <c r="E117" s="58"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -16426,7 +16008,7 @@
       <c r="K117" s="2"/>
     </row>
     <row r="118" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E118" s="60"/>
+      <c r="E118" s="58"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
@@ -16435,7 +16017,7 @@
       <c r="K118" s="2"/>
     </row>
     <row r="119" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E119" s="60"/>
+      <c r="E119" s="58"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
@@ -16444,7 +16026,7 @@
       <c r="K119" s="2"/>
     </row>
     <row r="120" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E120" s="60"/>
+      <c r="E120" s="58"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
@@ -16453,7 +16035,7 @@
       <c r="K120" s="2"/>
     </row>
     <row r="121" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E121" s="60"/>
+      <c r="E121" s="58"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
@@ -16462,7 +16044,7 @@
       <c r="K121" s="2"/>
     </row>
     <row r="122" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E122" s="60"/>
+      <c r="E122" s="58"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
@@ -16471,7 +16053,7 @@
       <c r="K122" s="2"/>
     </row>
     <row r="123" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E123" s="60"/>
+      <c r="E123" s="58"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
@@ -16480,7 +16062,7 @@
       <c r="K123" s="2"/>
     </row>
     <row r="124" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E124" s="60"/>
+      <c r="E124" s="58"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
@@ -16489,7 +16071,7 @@
       <c r="K124" s="2"/>
     </row>
     <row r="125" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E125" s="60"/>
+      <c r="E125" s="58"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
@@ -16498,7 +16080,7 @@
       <c r="K125" s="2"/>
     </row>
     <row r="126" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E126" s="60"/>
+      <c r="E126" s="58"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
@@ -16507,7 +16089,7 @@
       <c r="K126" s="2"/>
     </row>
     <row r="127" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E127" s="60"/>
+      <c r="E127" s="58"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
@@ -16516,7 +16098,7 @@
       <c r="K127" s="2"/>
     </row>
     <row r="128" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E128" s="60"/>
+      <c r="E128" s="58"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
@@ -16525,7 +16107,7 @@
       <c r="K128" s="2"/>
     </row>
     <row r="129" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E129" s="60"/>
+      <c r="E129" s="58"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
@@ -16534,7 +16116,7 @@
       <c r="K129" s="2"/>
     </row>
     <row r="130" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E130" s="60"/>
+      <c r="E130" s="58"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
@@ -16543,7 +16125,7 @@
       <c r="K130" s="2"/>
     </row>
     <row r="131" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E131" s="60"/>
+      <c r="E131" s="58"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
@@ -16552,7 +16134,7 @@
       <c r="K131" s="2"/>
     </row>
     <row r="132" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E132" s="60"/>
+      <c r="E132" s="58"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
@@ -16561,7 +16143,7 @@
       <c r="K132" s="2"/>
     </row>
     <row r="133" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E133" s="60"/>
+      <c r="E133" s="58"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
@@ -16570,7 +16152,7 @@
       <c r="K133" s="2"/>
     </row>
     <row r="134" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E134" s="60"/>
+      <c r="E134" s="58"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
@@ -16579,7 +16161,7 @@
       <c r="K134" s="2"/>
     </row>
     <row r="135" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E135" s="60"/>
+      <c r="E135" s="58"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
@@ -16588,7 +16170,7 @@
       <c r="K135" s="2"/>
     </row>
     <row r="136" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E136" s="60"/>
+      <c r="E136" s="58"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
@@ -16597,7 +16179,7 @@
       <c r="K136" s="2"/>
     </row>
     <row r="137" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E137" s="60"/>
+      <c r="E137" s="58"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
@@ -16606,7 +16188,7 @@
       <c r="K137" s="2"/>
     </row>
     <row r="138" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E138" s="60"/>
+      <c r="E138" s="58"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
@@ -16615,7 +16197,7 @@
       <c r="K138" s="2"/>
     </row>
     <row r="139" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E139" s="60"/>
+      <c r="E139" s="58"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
@@ -16624,7 +16206,7 @@
       <c r="K139" s="2"/>
     </row>
     <row r="140" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E140" s="60"/>
+      <c r="E140" s="58"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
@@ -16633,7 +16215,7 @@
       <c r="K140" s="2"/>
     </row>
     <row r="141" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E141" s="60"/>
+      <c r="E141" s="58"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
@@ -16642,7 +16224,7 @@
       <c r="K141" s="2"/>
     </row>
     <row r="142" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E142" s="60"/>
+      <c r="E142" s="58"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
@@ -16651,7 +16233,7 @@
       <c r="K142" s="2"/>
     </row>
     <row r="143" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E143" s="60"/>
+      <c r="E143" s="58"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
@@ -16660,7 +16242,7 @@
       <c r="K143" s="2"/>
     </row>
     <row r="144" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E144" s="60"/>
+      <c r="E144" s="58"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
@@ -16669,7 +16251,7 @@
       <c r="K144" s="2"/>
     </row>
     <row r="145" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E145" s="60"/>
+      <c r="E145" s="58"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
@@ -16678,7 +16260,7 @@
       <c r="K145" s="2"/>
     </row>
     <row r="146" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E146" s="60"/>
+      <c r="E146" s="58"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
@@ -16687,7 +16269,7 @@
       <c r="K146" s="2"/>
     </row>
     <row r="147" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E147" s="60"/>
+      <c r="E147" s="58"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -16696,7 +16278,7 @@
       <c r="K147" s="2"/>
     </row>
     <row r="148" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E148" s="60"/>
+      <c r="E148" s="58"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -16705,7 +16287,7 @@
       <c r="K148" s="2"/>
     </row>
     <row r="149" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E149" s="60"/>
+      <c r="E149" s="58"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -16714,7 +16296,7 @@
       <c r="K149" s="2"/>
     </row>
     <row r="150" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E150" s="60"/>
+      <c r="E150" s="58"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -16723,7 +16305,7 @@
       <c r="K150" s="2"/>
     </row>
     <row r="151" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E151" s="60"/>
+      <c r="E151" s="58"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -16732,7 +16314,7 @@
       <c r="K151" s="2"/>
     </row>
     <row r="152" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E152" s="60"/>
+      <c r="E152" s="58"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -16741,7 +16323,7 @@
       <c r="K152" s="2"/>
     </row>
     <row r="153" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E153" s="60"/>
+      <c r="E153" s="58"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -16750,7 +16332,7 @@
       <c r="K153" s="2"/>
     </row>
     <row r="154" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E154" s="60"/>
+      <c r="E154" s="58"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -16759,7 +16341,7 @@
       <c r="K154" s="2"/>
     </row>
     <row r="155" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E155" s="60"/>
+      <c r="E155" s="58"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -16768,7 +16350,7 @@
       <c r="K155" s="2"/>
     </row>
     <row r="156" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E156" s="60"/>
+      <c r="E156" s="58"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -16777,7 +16359,7 @@
       <c r="K156" s="2"/>
     </row>
     <row r="157" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E157" s="60"/>
+      <c r="E157" s="58"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -16786,7 +16368,7 @@
       <c r="K157" s="2"/>
     </row>
     <row r="158" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E158" s="60"/>
+      <c r="E158" s="58"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -16795,7 +16377,7 @@
       <c r="K158" s="2"/>
     </row>
     <row r="159" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E159" s="60"/>
+      <c r="E159" s="58"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -16804,7 +16386,7 @@
       <c r="K159" s="2"/>
     </row>
     <row r="160" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E160" s="60"/>
+      <c r="E160" s="58"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -16813,7 +16395,7 @@
       <c r="K160" s="2"/>
     </row>
     <row r="161" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E161" s="60"/>
+      <c r="E161" s="58"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -16822,7 +16404,7 @@
       <c r="K161" s="2"/>
     </row>
     <row r="162" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E162" s="60"/>
+      <c r="E162" s="58"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -16831,7 +16413,7 @@
       <c r="K162" s="2"/>
     </row>
     <row r="163" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E163" s="60"/>
+      <c r="E163" s="58"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -16840,7 +16422,7 @@
       <c r="K163" s="2"/>
     </row>
     <row r="164" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E164" s="60"/>
+      <c r="E164" s="58"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -16849,7 +16431,7 @@
       <c r="K164" s="2"/>
     </row>
     <row r="165" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E165" s="60"/>
+      <c r="E165" s="58"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -16858,7 +16440,7 @@
       <c r="K165" s="2"/>
     </row>
     <row r="166" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E166" s="60"/>
+      <c r="E166" s="58"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -16867,7 +16449,7 @@
       <c r="K166" s="2"/>
     </row>
     <row r="167" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E167" s="60"/>
+      <c r="E167" s="58"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
@@ -16876,7 +16458,7 @@
       <c r="K167" s="2"/>
     </row>
     <row r="168" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E168" s="60"/>
+      <c r="E168" s="58"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
@@ -16885,7 +16467,7 @@
       <c r="K168" s="2"/>
     </row>
     <row r="169" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E169" s="60"/>
+      <c r="E169" s="58"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
@@ -16894,7 +16476,7 @@
       <c r="K169" s="2"/>
     </row>
     <row r="170" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E170" s="60"/>
+      <c r="E170" s="58"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
@@ -16903,7 +16485,7 @@
       <c r="K170" s="2"/>
     </row>
     <row r="171" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E171" s="60"/>
+      <c r="E171" s="58"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
@@ -16912,7 +16494,7 @@
       <c r="K171" s="2"/>
     </row>
     <row r="172" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E172" s="60"/>
+      <c r="E172" s="58"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
@@ -16921,7 +16503,7 @@
       <c r="K172" s="2"/>
     </row>
     <row r="173" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E173" s="60"/>
+      <c r="E173" s="58"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
@@ -16930,7 +16512,7 @@
       <c r="K173" s="2"/>
     </row>
     <row r="174" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E174" s="60"/>
+      <c r="E174" s="58"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
@@ -16939,7 +16521,7 @@
       <c r="K174" s="2"/>
     </row>
     <row r="175" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E175" s="60"/>
+      <c r="E175" s="58"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
@@ -16948,7 +16530,7 @@
       <c r="K175" s="2"/>
     </row>
     <row r="176" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E176" s="60"/>
+      <c r="E176" s="58"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
@@ -16957,7 +16539,7 @@
       <c r="K176" s="2"/>
     </row>
     <row r="177" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E177" s="60"/>
+      <c r="E177" s="58"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
@@ -16966,7 +16548,7 @@
       <c r="K177" s="2"/>
     </row>
     <row r="178" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E178" s="60"/>
+      <c r="E178" s="58"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
@@ -16975,7 +16557,7 @@
       <c r="K178" s="2"/>
     </row>
     <row r="179" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E179" s="60"/>
+      <c r="E179" s="58"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
@@ -16984,7 +16566,7 @@
       <c r="K179" s="2"/>
     </row>
     <row r="180" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E180" s="60"/>
+      <c r="E180" s="58"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
@@ -16993,7 +16575,7 @@
       <c r="K180" s="2"/>
     </row>
     <row r="181" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E181" s="60"/>
+      <c r="E181" s="58"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
@@ -17002,7 +16584,7 @@
       <c r="K181" s="2"/>
     </row>
     <row r="182" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E182" s="60"/>
+      <c r="E182" s="58"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
@@ -17011,7 +16593,7 @@
       <c r="K182" s="2"/>
     </row>
     <row r="183" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E183" s="60"/>
+      <c r="E183" s="58"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
@@ -17020,7 +16602,7 @@
       <c r="K183" s="2"/>
     </row>
     <row r="184" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E184" s="60"/>
+      <c r="E184" s="58"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
@@ -17029,7 +16611,7 @@
       <c r="K184" s="2"/>
     </row>
     <row r="185" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E185" s="60"/>
+      <c r="E185" s="58"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
@@ -17038,7 +16620,7 @@
       <c r="K185" s="2"/>
     </row>
     <row r="186" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E186" s="60"/>
+      <c r="E186" s="58"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
@@ -17047,7 +16629,7 @@
       <c r="K186" s="2"/>
     </row>
     <row r="187" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E187" s="60"/>
+      <c r="E187" s="58"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
@@ -17056,7 +16638,7 @@
       <c r="K187" s="2"/>
     </row>
     <row r="188" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E188" s="60"/>
+      <c r="E188" s="58"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
@@ -17065,7 +16647,7 @@
       <c r="K188" s="2"/>
     </row>
     <row r="189" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E189" s="60"/>
+      <c r="E189" s="58"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
@@ -17074,7 +16656,7 @@
       <c r="K189" s="2"/>
     </row>
     <row r="190" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E190" s="60"/>
+      <c r="E190" s="58"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
@@ -17083,7 +16665,7 @@
       <c r="K190" s="2"/>
     </row>
     <row r="191" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E191" s="60"/>
+      <c r="E191" s="58"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
@@ -17092,7 +16674,7 @@
       <c r="K191" s="2"/>
     </row>
     <row r="192" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E192" s="60"/>
+      <c r="E192" s="58"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
@@ -17101,7 +16683,7 @@
       <c r="K192" s="2"/>
     </row>
     <row r="193" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E193" s="60"/>
+      <c r="E193" s="58"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
@@ -17110,7 +16692,7 @@
       <c r="K193" s="2"/>
     </row>
     <row r="194" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E194" s="60"/>
+      <c r="E194" s="58"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
@@ -17119,7 +16701,7 @@
       <c r="K194" s="2"/>
     </row>
     <row r="195" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E195" s="60"/>
+      <c r="E195" s="58"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
@@ -17128,7 +16710,7 @@
       <c r="K195" s="2"/>
     </row>
     <row r="196" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E196" s="60"/>
+      <c r="E196" s="58"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
@@ -17137,7 +16719,7 @@
       <c r="K196" s="2"/>
     </row>
     <row r="197" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E197" s="60"/>
+      <c r="E197" s="58"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
@@ -17146,7 +16728,7 @@
       <c r="K197" s="2"/>
     </row>
     <row r="198" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E198" s="60"/>
+      <c r="E198" s="58"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
@@ -17155,7 +16737,7 @@
       <c r="K198" s="2"/>
     </row>
     <row r="199" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E199" s="60"/>
+      <c r="E199" s="58"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
@@ -17164,7 +16746,7 @@
       <c r="K199" s="2"/>
     </row>
     <row r="200" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E200" s="60"/>
+      <c r="E200" s="58"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
@@ -17173,7 +16755,7 @@
       <c r="K200" s="2"/>
     </row>
     <row r="201" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E201" s="60"/>
+      <c r="E201" s="58"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -17182,7 +16764,7 @@
       <c r="K201" s="2"/>
     </row>
     <row r="202" spans="5:11" x14ac:dyDescent="0.2">
-      <c r="E202" s="60"/>
+      <c r="E202" s="58"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
@@ -17191,7 +16773,7 @@
       <c r="K202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="surk/koutxQ0jRaBxnXIC56clVqAUQ53OoYW5d7jy0jalJvPky1M0N7SAsRDMK5oLPJ/WeRlv2QAtxZWSSSRFg==" saltValue="IiYMewxbKp25wB+aSXAGyQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KJe4ibr3BdYNrY5IlehB39tdNsNRfA1YqFBkS6i2uMK0LsLfke4xKhatXPaE4goTnWrdJrSj9l2LT2SZlv8ikQ==" saltValue="et/MYu9ZxsboYNnxsBogjw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
@@ -17236,20 +16818,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
-        <v>67</v>
+      <c r="A1" s="39" t="s">
+        <v>66</v>
       </c>
-      <c r="B1" s="31" t="s">
-        <v>48</v>
+      <c r="B1" s="30" t="s">
+        <v>47</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="32" t="s">
-        <v>50</v>
+      <c r="E1" s="31" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
@@ -18704,208 +18286,208 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A1" s="72" t="s">
-        <v>67</v>
+      <c r="A1" s="71" t="s">
+        <v>66</v>
       </c>
-      <c r="B1" s="72" t="s">
-        <v>162</v>
-      </c>
-      <c r="C1" s="72"/>
-      <c r="D1" s="73" t="s">
+      <c r="B1" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="72" t="s">
+      <c r="C1" s="71"/>
+      <c r="D1" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="O1" s="72"/>
-      <c r="P1" s="72"/>
-      <c r="Q1" s="72"/>
-      <c r="R1" s="72"/>
-      <c r="S1" s="72"/>
-      <c r="T1" s="72"/>
-      <c r="U1" s="72"/>
-      <c r="V1" s="72"/>
-      <c r="W1" s="72"/>
-      <c r="X1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="72"/>
+      <c r="N1" s="71" t="s">
+        <v>159</v>
+      </c>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="71"/>
+      <c r="T1" s="71"/>
+      <c r="U1" s="71"/>
+      <c r="V1" s="71"/>
+      <c r="W1" s="71"/>
+      <c r="X1" s="71"/>
       <c r="Y1" s="4"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A2" s="72"/>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="74" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="73" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="73" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="74" t="s">
-        <v>46</v>
-      </c>
-      <c r="J2" s="75"/>
-      <c r="K2" s="75"/>
-      <c r="L2" s="75"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
-      <c r="R2" s="72"/>
-      <c r="S2" s="72"/>
-      <c r="T2" s="72"/>
-      <c r="U2" s="72"/>
-      <c r="V2" s="72"/>
-      <c r="W2" s="72"/>
-      <c r="X2" s="72"/>
+      <c r="J2" s="74"/>
+      <c r="K2" s="74"/>
+      <c r="L2" s="74"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="71"/>
+      <c r="P2" s="71"/>
+      <c r="Q2" s="71"/>
+      <c r="R2" s="71"/>
+      <c r="S2" s="71"/>
+      <c r="T2" s="71"/>
+      <c r="U2" s="71"/>
+      <c r="V2" s="71"/>
+      <c r="W2" s="71"/>
+      <c r="X2" s="71"/>
       <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="77" t="s">
-        <v>159</v>
-      </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="77" t="s">
+      <c r="A3" s="71"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="G3" s="78"/>
-      <c r="H3" s="79" t="s">
-        <v>48</v>
+      <c r="E3" s="77"/>
+      <c r="F3" s="76" t="s">
+        <v>157</v>
       </c>
-      <c r="I3" s="77" t="s">
-        <v>159</v>
+      <c r="G3" s="77"/>
+      <c r="H3" s="78" t="s">
+        <v>47</v>
       </c>
-      <c r="J3" s="78"/>
-      <c r="K3" s="77" t="s">
+      <c r="I3" s="76" t="s">
         <v>158</v>
       </c>
-      <c r="L3" s="78"/>
-      <c r="M3" s="79" t="s">
-        <v>48</v>
-      </c>
-      <c r="N3" s="72" t="s">
+      <c r="J3" s="77"/>
+      <c r="K3" s="76" t="s">
         <v>157</v>
       </c>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72" t="s">
+      <c r="L3" s="77"/>
+      <c r="M3" s="78" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" s="71" t="s">
         <v>156</v>
       </c>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="73" t="s">
+      <c r="O3" s="71"/>
+      <c r="P3" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="73"/>
+      <c r="Q3" s="71"/>
+      <c r="R3" s="71"/>
+      <c r="S3" s="71"/>
+      <c r="T3" s="71"/>
+      <c r="U3" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
     </row>
     <row r="4" spans="1:25" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="72"/>
-      <c r="B4" s="31" t="s">
-        <v>88</v>
+      <c r="A4" s="71"/>
+      <c r="B4" s="30" t="s">
+        <v>87</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="35" t="s">
-        <v>93</v>
+      <c r="D4" s="34" t="s">
+        <v>92</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="80"/>
-      <c r="I4" s="35" t="s">
-        <v>93</v>
+      <c r="H4" s="79"/>
+      <c r="I4" s="34" t="s">
+        <v>92</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="80"/>
-      <c r="N4" s="31" t="s">
+      <c r="M4" s="79"/>
+      <c r="N4" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="O4" s="31" t="s">
+      <c r="O4" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="31" t="s">
+      <c r="P4" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="Q4" s="31" t="s">
+      <c r="Q4" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="R4" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="S4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="31" t="s">
+      <c r="T4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="V4" s="35" t="s">
+      <c r="U4" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="35" t="s">
+      <c r="V4" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="35" t="s">
+      <c r="W4" s="34" t="s">
         <v>95</v>
       </c>
+      <c r="X4" s="34" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
+      <c r="A5" s="36"/>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
@@ -24056,7 +23638,7 @@
       <c r="X203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eu9peeP+TfCw4pbAPu5JdYhbP7AJnAQ0jEzKcylJfcT+Z8UonMOCwfaM39MOouvrsBks4oHENTo7fjhvsCLXAg==" saltValue="9w+VVYxzVWv5Vzcvl1R04Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YwOt15oYQEWSJxTSpLizzMlUZjg5EMN4BNzkStTKuF3yI49Rbunrg3vRnyjPPeLEMyWKdeXnnwEWDshnPcMbkQ==" saltValue="MKEqt5rqz4HInOU5fG7RXg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="15">
     <mergeCell ref="A1:A4"/>
     <mergeCell ref="B1:C3"/>
@@ -24074,7 +23656,7 @@
     <mergeCell ref="P3:T3"/>
     <mergeCell ref="U3:X3"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4 U4 J4 I4 X4 W4 V4 D4" xr:uid="{91965C69-FE02-41D0-B18A-140404A18B82}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
@@ -24122,99 +23704,99 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
-      <c r="B1" s="93" t="s">
+      <c r="B1" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="96" t="s">
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="95" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="97"/>
-      <c r="I1" s="98"/>
-      <c r="J1" s="87" t="s">
-        <v>190</v>
+      <c r="H1" s="96"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="86" t="s">
+        <v>189</v>
       </c>
-      <c r="K1" s="90" t="s">
-        <v>100</v>
+      <c r="K1" s="89" t="s">
+        <v>99</v>
       </c>
-      <c r="L1" s="93" t="s">
-        <v>89</v>
+      <c r="L1" s="92" t="s">
+        <v>88</v>
       </c>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
-      <c r="P1" s="95"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="94"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="82"/>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="99" t="s">
-        <v>94</v>
+      <c r="C2" s="98" t="s">
+        <v>93</v>
       </c>
-      <c r="D2" s="100" t="s">
+      <c r="D2" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="101" t="s">
-        <v>93</v>
+      <c r="G2" s="100" t="s">
+        <v>92</v>
       </c>
-      <c r="H2" s="87" t="s">
+      <c r="H2" s="86" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="84" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
-      <c r="J2" s="88"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="86" t="s">
+      <c r="J2" s="87"/>
+      <c r="K2" s="90"/>
+      <c r="L2" s="80" t="s">
+        <v>162</v>
+      </c>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80" t="s">
         <v>163</v>
       </c>
-      <c r="M2" s="86"/>
-      <c r="N2" s="86" t="s">
-        <v>164</v>
-      </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="102" t="s">
+      <c r="O2" s="80"/>
+      <c r="P2" s="101" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="83"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="89"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="99"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="88"/>
       <c r="I3" s="85"/>
-      <c r="J3" s="89"/>
-      <c r="K3" s="92"/>
-      <c r="L3" s="38" t="s">
+      <c r="J3" s="88"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="42" t="s">
-        <v>101</v>
+      <c r="M3" s="41" t="s">
+        <v>100</v>
       </c>
-      <c r="N3" s="39" t="s">
+      <c r="N3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="42" t="s">
-        <v>101</v>
+      <c r="O3" s="41" t="s">
+        <v>100</v>
       </c>
-      <c r="P3" s="102"/>
+      <c r="P3" s="101"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -27816,8 +27398,9 @@
       <c r="P203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZMcGlpUYWH0nWXDK8FvCtX3HVIMQZdBe3U+XlxwQBGmIM8VezF6VdaJLm5Q9+1cm7ODph5ZTaPEJISiXAYOqRw==" saltValue="NYuWqTNvhgNChUDYwAx08Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="CZii86whYTLOLFnZ64t4rMbfDFB9/+CPuTgcoDrqusTbZeRxGmprLSdaMluk2ohqxVFRxRA3W5JQa0IRf+p2VA==" saltValue="ZTzfc8Seps9qGEdDYlS5Ig==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="H2:H3"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="I2:I3"/>
@@ -27834,7 +27417,6 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="P2:P3"/>
-    <mergeCell ref="H2:H3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M3 C2:C3 G2:H3 O4 K1 J1:J3" xr:uid="{DA10A34B-1BA4-48EB-B541-1349E1B06C98}">
@@ -27850,7 +27432,7 @@
     <hyperlink ref="J1" r:id="rId6" location="targetSpecies" display="SPECIES_1_CODE" xr:uid="{319F558C-0F36-4D91-9564-E88A253E4F33}"/>
     <hyperlink ref="G2:G3" r:id="rId7" location="countries" display="COUNTRY" xr:uid="{98362A2E-1CBD-43DD-8197-6A0D27DC3F68}"/>
     <hyperlink ref="H2:H3" r:id="rId8" location="Ports" display="PORT" xr:uid="{EE4F9719-6B03-476E-83A1-6471495A5B6C}"/>
-    <hyperlink ref="J1:J3" r:id="rId9" location="targetSpecies" display="LICESNED_TARGET_SPECIES" xr:uid="{541364A8-1D78-46B2-9FF8-3827395F93AC}"/>
+    <hyperlink ref="J1:J3" r:id="rId9" location="targetSpecies" display="LICENSED_TARGET_SPECIES" xr:uid="{541364A8-1D78-46B2-9FF8-3827395F93AC}"/>
     <hyperlink ref="K1:K3" r:id="rId10" location="gears" display="MAIN_FISHING_GEAR" xr:uid="{2D8FE2F6-4E9B-442D-832C-965139EBB615}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27880,72 +27462,72 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
-      <c r="B1" s="103" t="s">
+      <c r="B1" s="102" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102" t="s">
         <v>165</v>
       </c>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="82"/>
-      <c r="B2" s="74" t="s">
-        <v>159</v>
+      <c r="B2" s="73" t="s">
+        <v>158</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="79" t="s">
-        <v>48</v>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="78" t="s">
+        <v>47</v>
       </c>
-      <c r="G2" s="74" t="s">
-        <v>159</v>
+      <c r="G2" s="73" t="s">
+        <v>158</v>
       </c>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="79" t="s">
-        <v>48</v>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="78" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="83"/>
-      <c r="B3" s="35" t="s">
-        <v>93</v>
+      <c r="B3" s="34" t="s">
+        <v>92</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="80"/>
-      <c r="G3" s="35" t="s">
-        <v>93</v>
+      <c r="F3" s="79"/>
+      <c r="G3" s="34" t="s">
+        <v>92</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="J3" s="32" t="s">
+      <c r="J3" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="80"/>
+      <c r="K3" s="79"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -30548,7 +30130,7 @@
       <c r="K203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="SYyxpqsl2ngtwVABa+SgEQmTeOJ3tF7fWtcxRT2C4sn0Nm864G2TXFlBMJjChY9j6sgOnlma5mb0FLIEitc/jw==" saltValue="8pjWvbqqRPn6XVDZmFIoKg==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="YMs/q0+l4pR+qhzsczv2lJUD5KGGj/aGhLGQJuJZwXd3DJ3JowG0m0N5Ufn+bkhpkIixr/ICjrWfPq4PAuZaTQ==" saltValue="AOlxdoQ7t9oL4rms2j0mGw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="7">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:F1"/>
@@ -30618,237 +30200,237 @@
   <sheetData>
     <row r="1" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A1" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
+      <c r="N1" s="74"/>
+      <c r="O1" s="74"/>
+      <c r="P1" s="74"/>
+      <c r="Q1" s="74"/>
+      <c r="R1" s="74"/>
+      <c r="S1" s="74"/>
+      <c r="T1" s="75"/>
+      <c r="U1" s="73" t="s">
+        <v>123</v>
+      </c>
+      <c r="V1" s="74"/>
+      <c r="W1" s="74"/>
+      <c r="X1" s="74"/>
+      <c r="Y1" s="74"/>
+      <c r="Z1" s="74"/>
+      <c r="AA1" s="74"/>
+      <c r="AB1" s="74"/>
+      <c r="AC1" s="74"/>
+      <c r="AD1" s="74"/>
+      <c r="AE1" s="74"/>
+      <c r="AF1" s="74"/>
+      <c r="AG1" s="75"/>
+      <c r="AH1" s="73" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI1" s="74"/>
+      <c r="AJ1" s="74"/>
+      <c r="AK1" s="74"/>
+      <c r="AL1" s="74"/>
+      <c r="AM1" s="74"/>
+      <c r="AN1" s="74"/>
+      <c r="AO1" s="74"/>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A2" s="82"/>
+      <c r="B2" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="72" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="75"/>
-      <c r="Q1" s="75"/>
-      <c r="R1" s="75"/>
-      <c r="S1" s="75"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="74" t="s">
-        <v>124</v>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72" t="s">
+        <v>126</v>
       </c>
-      <c r="V1" s="75"/>
-      <c r="W1" s="75"/>
-      <c r="X1" s="75"/>
-      <c r="Y1" s="75"/>
-      <c r="Z1" s="75"/>
-      <c r="AA1" s="75"/>
-      <c r="AB1" s="75"/>
-      <c r="AC1" s="75"/>
-      <c r="AD1" s="75"/>
-      <c r="AE1" s="75"/>
-      <c r="AF1" s="75"/>
-      <c r="AG1" s="76"/>
-      <c r="AH1" s="74" t="s">
-        <v>167</v>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="78" t="s">
+        <v>90</v>
       </c>
-      <c r="AI1" s="75"/>
-      <c r="AJ1" s="75"/>
-      <c r="AK1" s="75"/>
-      <c r="AL1" s="75"/>
-      <c r="AM1" s="75"/>
-      <c r="AN1" s="75"/>
-      <c r="AO1" s="75"/>
-    </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A2" s="82"/>
-      <c r="B2" s="79" t="s">
-        <v>178</v>
+      <c r="L2" s="73" t="s">
+        <v>127</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="M2" s="74"/>
+      <c r="N2" s="74"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="75"/>
+      <c r="S2" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="75"/>
+      <c r="U2" s="72" t="s">
+        <v>112</v>
+      </c>
+      <c r="V2" s="72" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" s="72" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" s="72" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z2" s="72" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA2" s="72" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB2" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC2" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD2" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE2" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF2" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG2" s="72" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH2" s="95" t="s">
+        <v>119</v>
+      </c>
+      <c r="AI2" s="97"/>
+      <c r="AJ2" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="AK2" s="97"/>
+      <c r="AL2" s="95" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM2" s="97"/>
+      <c r="AN2" s="95" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO2" s="97"/>
+    </row>
+    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A3" s="83"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>179</v>
       </c>
-      <c r="D2" s="87" t="s">
+      <c r="H3" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="42" t="s">
+        <v>179</v>
+      </c>
+      <c r="K3" s="79"/>
+      <c r="L3" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="M3" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="N3" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="O3" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="P3" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q3" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="R3" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="S3" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="T3" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="73" t="s">
-        <v>126</v>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="72"/>
+      <c r="AB3" s="72"/>
+      <c r="AC3" s="72"/>
+      <c r="AD3" s="72"/>
+      <c r="AE3" s="72"/>
+      <c r="AF3" s="72"/>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="43" t="s">
+        <v>110</v>
       </c>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73" t="s">
-        <v>127</v>
+      <c r="AI3" s="35" t="s">
+        <v>111</v>
       </c>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="79" t="s">
-        <v>91</v>
-      </c>
-      <c r="L2" s="74" t="s">
-        <v>128</v>
-      </c>
-      <c r="M2" s="75"/>
-      <c r="N2" s="75"/>
-      <c r="O2" s="76"/>
-      <c r="P2" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q2" s="75"/>
-      <c r="R2" s="76"/>
-      <c r="S2" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="T2" s="76"/>
-      <c r="U2" s="73" t="s">
+      <c r="AJ3" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="V2" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="73" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" s="73" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y2" s="73" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z2" s="73" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA2" s="73" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB2" s="73" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC2" s="73" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD2" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE2" s="73" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF2" s="73" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG2" s="73" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH2" s="96" t="s">
-        <v>120</v>
-      </c>
-      <c r="AI2" s="98"/>
-      <c r="AJ2" s="96" t="s">
-        <v>121</v>
-      </c>
-      <c r="AK2" s="98"/>
-      <c r="AL2" s="96" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM2" s="98"/>
-      <c r="AN2" s="96" t="s">
-        <v>123</v>
-      </c>
-      <c r="AO2" s="98"/>
-    </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A3" s="83"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="K3" s="80"/>
-      <c r="L3" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="M3" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="N3" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="O3" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="P3" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q3" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="S3" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="T3" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="73"/>
-      <c r="Y3" s="73"/>
-      <c r="Z3" s="73"/>
-      <c r="AA3" s="73"/>
-      <c r="AB3" s="73"/>
-      <c r="AC3" s="73"/>
-      <c r="AD3" s="73"/>
-      <c r="AE3" s="73"/>
-      <c r="AF3" s="73"/>
-      <c r="AG3" s="73"/>
-      <c r="AH3" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI3" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="AJ3" s="36" t="s">
+      <c r="AK3" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="AK3" s="36" t="s">
+      <c r="AL3" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="AL3" s="36" t="s">
+      <c r="AM3" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="AM3" s="36" t="s">
+      <c r="AN3" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="AN3" s="36" t="s">
+      <c r="AO3" s="35" t="s">
         <v>118</v>
-      </c>
-      <c r="AO3" s="36" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -39452,8 +39034,22 @@
       <c r="AO203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="in9HWhrbfPeQLKOphe9HcQ3ZWSvu9v4Chn7tSlbMDS+5w+WrRSh6fFRY7HaRetWtqRaeTChN5KnyLnOrPZ3pZA==" saltValue="7WB/oWTeA55ZXeyLP0lXUw==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KSZOP9lMTEXsWzYKUYhsj/zU6ZOVE/mBxe81fCQl3ekCjn3NVG9TUS7cDnT1KjtzXG46MKurbwi0O4Xpa/Fc1w==" saltValue="W6PE468oYis0j3LEPkOY7Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="30">
+    <mergeCell ref="AD2:AD3"/>
+    <mergeCell ref="AE2:AE3"/>
+    <mergeCell ref="AF2:AF3"/>
+    <mergeCell ref="AG2:AG3"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="AB2:AB3"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="B1:T1"/>
     <mergeCell ref="AN2:AO2"/>
@@ -39470,20 +39066,6 @@
     <mergeCell ref="AC2:AC3"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:U3"/>
-    <mergeCell ref="V2:V3"/>
-    <mergeCell ref="K2:K3"/>
-    <mergeCell ref="AB2:AB3"/>
-    <mergeCell ref="AD2:AD3"/>
-    <mergeCell ref="AE2:AE3"/>
-    <mergeCell ref="AF2:AF3"/>
-    <mergeCell ref="AG2:AG3"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="X2:X3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="AA2:AA3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3 L3:R3 AH3:AO3" xr:uid="{259DA634-7C5F-4453-A9E2-D13FC35BABDC}">
@@ -39534,66 +39116,66 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="82" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="83" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1" s="83"/>
+      <c r="D1" s="92" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="93" t="s">
-        <v>171</v>
-      </c>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="95"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="94"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="82"/>
       <c r="B2" s="81" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="81" t="s">
+        <v>180</v>
+      </c>
+      <c r="D2" s="81" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="73" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2" s="75"/>
+      <c r="G2" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="81" t="s">
-        <v>181</v>
-      </c>
-      <c r="D2" s="81" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" s="74" t="s">
-        <v>169</v>
-      </c>
-      <c r="F2" s="76"/>
-      <c r="G2" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="76"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="83"/>
       <c r="B3" s="83"/>
       <c r="C3" s="83"/>
       <c r="D3" s="83"/>
-      <c r="E3" s="35" t="s">
-        <v>168</v>
+      <c r="E3" s="34" t="s">
+        <v>167</v>
       </c>
-      <c r="F3" s="44" t="s">
-        <v>49</v>
+      <c r="F3" s="42" t="s">
+        <v>48</v>
       </c>
-      <c r="G3" s="35" t="s">
-        <v>54</v>
+      <c r="G3" s="34" t="s">
+        <v>53</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="H3" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="I3" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="J3" s="35" t="s">
-        <v>182</v>
+      <c r="J3" s="34" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -41997,7 +41579,7 @@
       <c r="J203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="igaK2i73sbBRV3O0vaCukplXyRO3fF1UQv6Prt20o0q48tTKb04QpHP563M3z44G/ATLGVx2Lf+DGQs9QZqCDw==" saltValue="8AYecdzxIgfiD2HfUpu1aA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="b5Gow6C1ckEPntR4eHCn4ijN33GxYhCf8gsl6sjxux8CmLvIvRkLK30fXbxXG88aOQOE7/tWjGj6IBFRz55bNw==" saltValue="fR/2JmpRruEUMZfrFtwG7g==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="8">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:J1"/>
@@ -42053,126 +41635,126 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="81" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="116" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="118"/>
+      <c r="E1" s="117"/>
+      <c r="F1" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="D1" s="106"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="31" t="s">
+      <c r="G1" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="107" t="s">
+      <c r="H1" s="104"/>
+      <c r="I1" s="105"/>
+      <c r="J1" s="110" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="108"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="114" t="s">
-        <v>133</v>
+      <c r="K1" s="111"/>
+      <c r="L1" s="111"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="71" t="s">
+        <v>60</v>
       </c>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="72" t="s">
+      <c r="O1" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="107" t="s">
-        <v>62</v>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
+      <c r="T1" s="72" t="s">
+        <v>182</v>
       </c>
-      <c r="P1" s="108"/>
-      <c r="Q1" s="108"/>
-      <c r="R1" s="108"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="73" t="s">
-        <v>183</v>
-      </c>
-      <c r="U1" s="111" t="s">
-        <v>66</v>
+      <c r="U1" s="107" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="82"/>
       <c r="B2" s="82"/>
       <c r="C2" s="81" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="105"/>
+      <c r="D2" s="116" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="117"/>
       <c r="F2" s="81" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
-      <c r="G2" s="77"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="77"/>
-      <c r="P2" s="110"/>
-      <c r="Q2" s="110"/>
-      <c r="R2" s="110"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="73"/>
-      <c r="U2" s="112"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="115"/>
+      <c r="N2" s="71"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="77"/>
+      <c r="T2" s="72"/>
+      <c r="U2" s="108"/>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="83"/>
       <c r="B3" s="83"/>
       <c r="C3" s="83"/>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="32" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="83"/>
-      <c r="G3" s="35" t="s">
+      <c r="G3" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="H3" s="35" t="s">
+      <c r="I3" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="J3" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="K3" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="J3" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="K3" s="41" t="s">
+      <c r="L3" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="M3" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="M3" s="41" t="s">
+      <c r="N3" s="71"/>
+      <c r="O3" s="33" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="54" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q3" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="N3" s="72"/>
-      <c r="O3" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="P3" s="56" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q3" s="35" t="s">
+      <c r="R3" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="R3" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="S3" s="32" t="s">
+      <c r="S3" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="73"/>
-      <c r="U3" s="113"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="109"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
@@ -46775,21 +46357,21 @@
       <c r="U203" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="vb3l2GPyTmOeMpvedAjZ5so+j03iBDjWx3ozUq1oM5QjY9AJ+7qSyqXmIAxigMK0wo/0kW2bwbQpgi37D24U6w==" saltValue="804oboBvFb3X5NzoXiRygQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="5tobK3VP6Ek27LdVSnrk/uizpFbhY5HlgoT+7M1wrexD4NhFOxzhp6PhMAXqC8+/AKpBUPMbkUzuYUdhPzQJ/g==" saltValue="FSbt2M4r3fxCMpU0Yc2/mQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <dataConsolidate/>
   <mergeCells count="12">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="G1:I2"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="O1:S2"/>
     <mergeCell ref="U1:U3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="J1:M2"/>
     <mergeCell ref="N1:N3"/>
     <mergeCell ref="T1:T3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="G1:I2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" sqref="U1:U3 Q3:R3 G3:M3" xr:uid="{AF5AE5B6-046A-4AF7-91CF-4FE32EB3CEA6}">
@@ -46831,46 +46413,46 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
-      <c r="B1" s="90" t="s">
+      <c r="B1" s="89" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="119" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="120"/>
+      <c r="E1" s="89" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="120" t="s">
+      <c r="F1" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="G1" s="110" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="111"/>
+      <c r="I1" s="112"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="83"/>
+      <c r="B2" s="91"/>
+      <c r="C2" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="121"/>
-      <c r="E1" s="90" t="s">
-        <v>142</v>
+      <c r="E2" s="91"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="48" t="s">
+        <v>149</v>
       </c>
-      <c r="F1" s="81" t="s">
-        <v>143</v>
-      </c>
-      <c r="G1" s="114" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1" s="115"/>
-      <c r="I1" s="116"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="83"/>
-      <c r="B2" s="92"/>
-      <c r="C2" s="41" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="92"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="41" t="s">
-        <v>144</v>
+      <c r="I2" s="40" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -49074,7 +48656,7 @@
       <c r="I202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KVqh67nRVkOiMmy20oUJ5F9CkwITKM3GlBik3SNhHVLFuzdGT9kz+ag3iKOoWkoDPfpZfcG+8NA0B83vB7cN1A==" saltValue="OaVm8+DuECZ/kgvVodTBVA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Hhxqgxfgs6kOuKn5dSWeGLdWyf3RMORVLXnXsxGF0btctvD0+7tnXuf28CjDwObcnjwRuaeyJK2BnOgHoJevPw==" saltValue="s+VQdLK9xQvjpRo7OrK1VQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="6">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="G1:I1"/>
@@ -49125,64 +48707,64 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="81" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
-      <c r="B1" s="79" t="s">
-        <v>90</v>
+      <c r="B1" s="78" t="s">
+        <v>89</v>
       </c>
-      <c r="C1" s="79" t="s">
-        <v>189</v>
+      <c r="C1" s="78" t="s">
+        <v>188</v>
       </c>
-      <c r="D1" s="124" t="s">
+      <c r="D1" s="123" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="125" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="126"/>
+      <c r="G1" s="86" t="s">
         <v>141</v>
       </c>
-      <c r="E1" s="126" t="s">
+      <c r="H1" s="121" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="75"/>
+      <c r="K1" s="86" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="73" t="s">
+        <v>172</v>
+      </c>
+      <c r="M1" s="75"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="83"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="127"/>
-      <c r="G1" s="87" t="s">
-        <v>142</v>
+      <c r="G2" s="88"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="50" t="s">
+        <v>149</v>
       </c>
-      <c r="H1" s="122" t="s">
-        <v>143</v>
+      <c r="J2" s="49" t="s">
+        <v>35</v>
       </c>
-      <c r="I1" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="76"/>
-      <c r="K1" s="87" t="s">
+      <c r="K2" s="88"/>
+      <c r="L2" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="L1" s="74" t="s">
-        <v>173</v>
-      </c>
-      <c r="M1" s="76"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" s="83"/>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="89"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="52" t="s">
-        <v>150</v>
-      </c>
-      <c r="J2" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="89"/>
-      <c r="L2" s="35" t="s">
+      <c r="M2" s="34" t="s">
         <v>145</v>
-      </c>
-      <c r="M2" s="35" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
@@ -52186,7 +51768,7 @@
       <c r="M202" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="45fxR1Rk8LQTXI+zAwaEBF6hYocAbCTwMbeJXtMSGz5qPgTREN7mZKNUY6/jZD98i7tqhL7SKR+8KWlz+ZO9Nw==" saltValue="i9x8nHjsTcbyyI9efGpd3Q==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0gtkUWWzbM8LZWE8bFLbjmQTkLRP4DlL8sw3bYZiKXp1IZ9arai/d7squIGJWIxL890E9JQyCeXgtO5OptSwYw==" saltValue="D2M/bUXX7ad1W7ijlTX1AQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="10">
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="I1:J1"/>
